--- a/Luban/Excel/Skill.xlsx
+++ b/Luban/Excel/Skill.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45F3583D-E592-41B4-B698-F3BBEC15146B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ED7AA0B-4084-4D01-B23F-D3750847D26E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1973,9 +1973,6 @@
     <t>过阴</t>
   </si>
   <si>
-    <t>下一次行动使用招式所需的玄炁消耗变为等量的刚炁消耗</t>
-  </si>
-  <si>
     <t>若处于祖化身状态刚炁消耗变为玄炁消耗</t>
   </si>
   <si>
@@ -2015,9 +2012,6 @@
     <t>对目标造成160%技的伤害，扣除其15%全部属性并增加等量的属性，消耗其20刚炁20玄炁并增加等量的炁</t>
   </si>
   <si>
-    <t>清除其全部毒瘴状态并为全部角色施加1层毒瘴状态</t>
-  </si>
-  <si>
     <t>仅能对存在10层毒瘴状态的敌手使用</t>
   </si>
   <si>
@@ -2144,9 +2138,6 @@
     <t>阴流杀</t>
   </si>
   <si>
-    <t>造成145%技的伤害，下回合不会自然恢复炁</t>
-  </si>
-  <si>
     <t>对目标造成110%技的伤害，单方面攻击施加3层赤沸状态，若目标本回合还未行动过则额外施加2层赤沸状态</t>
   </si>
   <si>
@@ -2816,9 +2807,6 @@
     <t>存在化身类状态可使用</t>
   </si>
   <si>
-    <t>玄炁+当前30%（至少9），若处于化身类状态则改为玄炁+当前50%（至少15）</t>
-  </si>
-  <si>
     <t>↑→</t>
   </si>
   <si>
@@ -2831,9 +2819,6 @@
     <t>清除全部武增状态，若处于兽化身状态则不会清除武增状态</t>
   </si>
   <si>
-    <t>对目标造成135%力的伤害，行动快于目标则根据行动差的一半施加伤口状态，若处于禽化身状态则等量施加伤口状态</t>
-  </si>
-  <si>
     <t>对目标造成155%力的伤害，至少造成100%力的伤害时刚炁+50</t>
   </si>
   <si>
@@ -3555,9 +3540,6 @@
   </si>
   <si>
     <t>洗兵雨</t>
-  </si>
-  <si>
-    <t>清除全部角色的异常效果，将天气覆盖为雨天8个回合</t>
   </si>
   <si>
     <t>体未有损失时可使用</t>
@@ -3957,6 +3939,30 @@
   </si>
   <si>
     <t>招式的威力有概率增加50的百分比，概率随目标百分比损失的体增加</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>清除其全部毒瘴状态并为全部角色施加1层毒瘴状态</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄炁+当前30%（至少9），若处于化身类状态则改为玄炁+当前50%（至少15）</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>清除全部角色的异常效果，将天气覆盖为雨天8个回合</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>下一次行动使用招式所需的玄炁消耗变为等量的刚炁消耗</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>对目标造成135%力的伤害，行动快于目标则根据行动差的一半施加伤口状态，若处于禽化身状态则等量施加伤口状态</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成145%技的伤害，下回合不会自然恢复炁</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -5473,7 +5479,7 @@
         <v>112</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>1077</v>
+        <v>1071</v>
       </c>
       <c r="I17" s="14"/>
       <c r="J17" s="14"/>
@@ -6515,7 +6521,7 @@
         <v>1</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="H35" s="14"/>
       <c r="I35" s="14"/>
@@ -8283,7 +8289,7 @@
         <v>2</v>
       </c>
       <c r="G72" s="16" t="s">
-        <v>1084</v>
+        <v>1078</v>
       </c>
       <c r="H72" s="16" t="s">
         <v>288</v>
@@ -9031,7 +9037,7 @@
         <v>349</v>
       </c>
       <c r="J87" s="16" t="s">
-        <v>1079</v>
+        <v>1073</v>
       </c>
       <c r="Q87" s="14" t="s">
         <v>350</v>
@@ -9422,7 +9428,7 @@
         <v>2</v>
       </c>
       <c r="G95" s="16" t="s">
-        <v>1085</v>
+        <v>1079</v>
       </c>
       <c r="H95" s="22" t="s">
         <v>374</v>
@@ -9467,13 +9473,13 @@
         <v>2</v>
       </c>
       <c r="G96" s="16" t="s">
-        <v>1086</v>
+        <v>1080</v>
       </c>
       <c r="H96" s="16" t="s">
         <v>378</v>
       </c>
       <c r="N96" s="16" t="s">
-        <v>1088</v>
+        <v>1082</v>
       </c>
       <c r="R96" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R96" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q96,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q96))),1))</f>
@@ -9509,7 +9515,7 @@
         <v>2</v>
       </c>
       <c r="G97" s="16" t="s">
-        <v>1087</v>
+        <v>1081</v>
       </c>
       <c r="H97" s="22" t="s">
         <v>380</v>
@@ -10434,10 +10440,10 @@
       <c r="I116" s="14"/>
       <c r="J116" s="14"/>
       <c r="L116" s="16" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N116" s="16" t="s">
         <v>443</v>
-      </c>
-      <c r="N116" s="16" t="s">
-        <v>444</v>
       </c>
       <c r="O116" s="14">
         <v>1</v>
@@ -10462,7 +10468,7 @@
         <v>20507</v>
       </c>
       <c r="W116" s="14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Y116" s="14">
         <v>1</v>
@@ -10479,18 +10485,18 @@
         <v>12054</v>
       </c>
       <c r="B117" s="15" t="s">
+        <v>445</v>
+      </c>
+      <c r="C117" s="14">
+        <v>2</v>
+      </c>
+      <c r="H117" s="16" t="s">
         <v>446</v>
-      </c>
-      <c r="C117" s="14">
-        <v>2</v>
-      </c>
-      <c r="H117" s="16" t="s">
-        <v>447</v>
       </c>
       <c r="I117" s="14"/>
       <c r="J117" s="14"/>
       <c r="L117" s="16" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="O117" s="14">
         <v>1</v>
@@ -10515,7 +10521,7 @@
         <v>20507</v>
       </c>
       <c r="W117" s="14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Y117" s="14">
         <v>2</v>
@@ -10535,12 +10541,12 @@
         <v>2</v>
       </c>
       <c r="H118" s="16" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="I118" s="14"/>
       <c r="J118" s="14"/>
       <c r="L118" s="16" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="O118" s="14">
         <v>6</v>
@@ -10549,7 +10555,7 @@
         <v>999</v>
       </c>
       <c r="Q118" s="14" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="R118" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R118" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q118,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q118))),1))</f>
@@ -10565,7 +10571,7 @@
         <v>20507</v>
       </c>
       <c r="W118" s="14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Y118" s="14">
         <v>1</v>
@@ -10585,10 +10591,10 @@
         <v>2</v>
       </c>
       <c r="H119" s="16" t="s">
+        <v>451</v>
+      </c>
+      <c r="L119" s="16" t="s">
         <v>452</v>
-      </c>
-      <c r="L119" s="16" t="s">
-        <v>453</v>
       </c>
       <c r="N119" s="16" t="s">
         <v>201</v>
@@ -10600,7 +10606,7 @@
         <v>8</v>
       </c>
       <c r="Q119" s="14" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="R119" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R119" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q119,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q119))),1))</f>
@@ -10616,7 +10622,7 @@
         <v>20507</v>
       </c>
       <c r="W119" s="14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Y119" s="14">
         <v>1</v>
@@ -10633,21 +10639,21 @@
         <v>12057</v>
       </c>
       <c r="B120" s="15" t="s">
+        <v>454</v>
+      </c>
+      <c r="C120" s="14">
+        <v>2</v>
+      </c>
+      <c r="H120" s="14" t="s">
         <v>455</v>
-      </c>
-      <c r="C120" s="14">
-        <v>2</v>
-      </c>
-      <c r="H120" s="14" t="s">
-        <v>456</v>
       </c>
       <c r="I120" s="14"/>
       <c r="J120" s="14"/>
       <c r="L120" s="16" t="s">
-        <v>457</v>
+        <v>1092</v>
       </c>
       <c r="N120" s="16" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="P120" s="14">
         <v>999</v>
@@ -10680,13 +10686,13 @@
         <v>12058</v>
       </c>
       <c r="B121" s="15" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C121" s="14">
         <v>2</v>
       </c>
       <c r="G121" s="16" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="H121" s="16" t="s">
         <v>401</v>
@@ -10722,17 +10728,17 @@
         <v>12059</v>
       </c>
       <c r="B122" s="15" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C122" s="14">
         <v>2</v>
       </c>
       <c r="H122" s="16" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="I122" s="14"/>
       <c r="J122" s="14" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="P122" s="14">
         <v>999</v>
@@ -10765,21 +10771,21 @@
         <v>12060</v>
       </c>
       <c r="B123" s="15" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C123" s="14">
         <v>2</v>
       </c>
       <c r="H123" s="16" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="I123" s="14"/>
       <c r="J123" s="14"/>
       <c r="N123" s="16" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="Q123" s="14" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="R123" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R123" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q123,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q123))),1))</f>
@@ -10824,7 +10830,7 @@
         <v>349</v>
       </c>
       <c r="J124" s="16" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="Q124" s="14" t="s">
         <v>350</v>
@@ -10863,7 +10869,7 @@
         <v>2</v>
       </c>
       <c r="G125" s="16" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H125" s="16" t="s">
         <v>352</v>
@@ -10992,27 +10998,27 @@
         <v>12065</v>
       </c>
       <c r="B128" s="15" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C128" s="14">
         <v>2</v>
       </c>
       <c r="H128" s="16" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="I128" s="14"/>
       <c r="J128" s="14"/>
       <c r="L128" s="16" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="N128" s="16" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="O128" s="14">
         <v>3</v>
       </c>
       <c r="Q128" s="14" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="R128" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R128" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q128,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q128))),1))</f>
@@ -11031,7 +11037,7 @@
         <v>20501</v>
       </c>
       <c r="W128" s="14" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="Y128" s="14">
         <v>2</v>
@@ -11048,7 +11054,7 @@
         <v>12066</v>
       </c>
       <c r="B129" s="15" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C129" s="14">
         <v>2</v>
@@ -11061,13 +11067,13 @@
       </c>
       <c r="I129" s="14"/>
       <c r="J129" s="14" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="N129" s="16" t="s">
         <v>76</v>
       </c>
       <c r="Q129" s="14" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="R129" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R129" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q129,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q129))),1))</f>
@@ -11086,7 +11092,7 @@
         <v>20405</v>
       </c>
       <c r="W129" s="14" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="Y129" s="14">
         <v>1</v>
@@ -11103,27 +11109,27 @@
         <v>12067</v>
       </c>
       <c r="B130" s="15" t="s">
+        <v>478</v>
+      </c>
+      <c r="C130" s="14">
+        <v>2</v>
+      </c>
+      <c r="E130" s="16" t="s">
+        <v>479</v>
+      </c>
+      <c r="G130" s="16" t="s">
         <v>480</v>
       </c>
-      <c r="C130" s="14">
-        <v>2</v>
-      </c>
-      <c r="E130" s="16" t="s">
+      <c r="H130" s="16" t="s">
         <v>481</v>
-      </c>
-      <c r="G130" s="16" t="s">
-        <v>482</v>
-      </c>
-      <c r="H130" s="16" t="s">
-        <v>483</v>
       </c>
       <c r="I130" s="14"/>
       <c r="J130" s="14"/>
       <c r="L130" s="16" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="N130" s="16" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="R130" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R130" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q130,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q130))),1))</f>
@@ -11142,7 +11148,7 @@
         <v>20503</v>
       </c>
       <c r="W130" s="14" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y130" s="14">
         <v>1</v>
@@ -11159,16 +11165,16 @@
         <v>12068</v>
       </c>
       <c r="B131" s="15" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C131" s="14">
         <v>2</v>
       </c>
       <c r="G131" s="16" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
       <c r="H131" s="16" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="I131" s="14"/>
       <c r="J131" s="14"/>
@@ -11189,7 +11195,7 @@
         <v>20503</v>
       </c>
       <c r="W131" s="14" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y131" s="14">
         <v>2</v>
@@ -11206,20 +11212,20 @@
         <v>12069</v>
       </c>
       <c r="B132" s="15" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C132" s="14">
         <v>2</v>
       </c>
       <c r="E132" s="16" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="H132" s="16" t="s">
         <v>262</v>
       </c>
       <c r="I132" s="14"/>
       <c r="J132" s="14" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="Q132" s="14" t="s">
         <v>324</v>
@@ -11241,7 +11247,7 @@
         <v>20503</v>
       </c>
       <c r="W132" s="14" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y132" s="14">
         <v>2</v>
@@ -11258,7 +11264,7 @@
         <v>12070</v>
       </c>
       <c r="B133" s="20" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C133" s="14">
         <v>2</v>
@@ -11276,7 +11282,7 @@
         <v>0</v>
       </c>
       <c r="Q133" s="14" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="R133" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R133" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q133,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q133))),1))</f>
@@ -11306,19 +11312,19 @@
         <v>12071</v>
       </c>
       <c r="B134" s="15" t="s">
+        <v>492</v>
+      </c>
+      <c r="C134" s="14">
+        <v>2</v>
+      </c>
+      <c r="E134" s="16" t="s">
+        <v>493</v>
+      </c>
+      <c r="H134" s="16" t="s">
         <v>494</v>
       </c>
-      <c r="C134" s="14">
-        <v>2</v>
-      </c>
-      <c r="E134" s="16" t="s">
+      <c r="N134" s="16" t="s">
         <v>495</v>
-      </c>
-      <c r="H134" s="16" t="s">
-        <v>496</v>
-      </c>
-      <c r="N134" s="16" t="s">
-        <v>497</v>
       </c>
       <c r="R134" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R134" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q134,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q134))),1))</f>
@@ -11337,7 +11343,7 @@
         <v>20409</v>
       </c>
       <c r="W134" s="14" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="Y134" s="14">
         <v>1</v>
@@ -11354,13 +11360,13 @@
         <v>12072</v>
       </c>
       <c r="B135" s="15" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C135" s="14">
         <v>2</v>
       </c>
       <c r="H135" s="16" t="s">
-        <v>500</v>
+        <v>1097</v>
       </c>
       <c r="I135" s="14"/>
       <c r="J135" s="14"/>
@@ -11389,7 +11395,7 @@
         <v>2</v>
       </c>
       <c r="H136" s="14" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="I136" s="14"/>
       <c r="J136" s="14"/>
@@ -11415,20 +11421,20 @@
         <v>12074</v>
       </c>
       <c r="B137" s="15" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C137" s="14">
         <v>2</v>
       </c>
       <c r="H137" s="16" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="I137" s="14"/>
       <c r="J137" s="14" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="N137" s="16" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="R137" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R137" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q137,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q137))),1))</f>
@@ -11452,20 +11458,20 @@
         <v>12075</v>
       </c>
       <c r="B138" s="15" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="C138" s="14">
         <v>2</v>
       </c>
       <c r="H138" s="16" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="I138" s="14"/>
       <c r="J138" s="14" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="N138" s="16" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="R138" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R138" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q138,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q138))),1))</f>
@@ -11492,15 +11498,15 @@
         <v>2</v>
       </c>
       <c r="H139" s="16" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="I139" s="14"/>
       <c r="J139" s="14"/>
       <c r="L139" s="14" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="Q139" s="14" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="R139" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R139" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q139,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q139))),1))</f>
@@ -11539,10 +11545,10 @@
         <v>2</v>
       </c>
       <c r="E140" s="16" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="H140" s="16" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="I140" s="14"/>
       <c r="J140" s="14"/>
@@ -11550,7 +11556,7 @@
         <v>409</v>
       </c>
       <c r="N140" s="16" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="P140" s="14">
         <v>3</v>
@@ -11598,7 +11604,7 @@
         <v>405</v>
       </c>
       <c r="H141" s="14" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="I141" s="14"/>
       <c r="J141" s="14"/>
@@ -11642,15 +11648,15 @@
     </row>
     <row r="142" spans="1:27" ht="33" x14ac:dyDescent="0.15">
       <c r="H142" s="16" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="I142" s="14"/>
       <c r="J142" s="14"/>
       <c r="L142" s="16" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="N142" s="16" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="O142" s="14">
         <v>7</v>
@@ -11668,7 +11674,7 @@
         <v>20507</v>
       </c>
       <c r="W142" s="14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Y142" s="14">
         <v>7</v>
@@ -11690,18 +11696,18 @@
         <v>13001</v>
       </c>
       <c r="B144" s="20" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="C144" s="14">
         <v>3</v>
       </c>
       <c r="H144" s="14" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="I144" s="14"/>
       <c r="J144" s="14"/>
       <c r="L144" s="16" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="O144" s="14">
         <v>1</v>
@@ -11746,18 +11752,18 @@
         <v>13002</v>
       </c>
       <c r="B145" s="20" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C145" s="14">
         <v>3</v>
       </c>
       <c r="H145" s="14" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="I145" s="14"/>
       <c r="J145" s="14"/>
       <c r="L145" s="16" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="O145" s="14">
         <v>1</v>
@@ -11802,18 +11808,18 @@
         <v>13003</v>
       </c>
       <c r="B146" s="20" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C146" s="14">
         <v>3</v>
       </c>
       <c r="H146" s="14" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="I146" s="14"/>
       <c r="J146" s="14"/>
       <c r="L146" s="16" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="O146" s="14">
         <v>1</v>
@@ -11858,21 +11864,21 @@
         <v>13004</v>
       </c>
       <c r="B147" s="20" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C147" s="14">
         <v>3</v>
       </c>
       <c r="E147" s="16" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H147" s="14" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="I147" s="14"/>
       <c r="J147" s="14"/>
       <c r="L147" s="16" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="O147" s="14">
         <v>1</v>
@@ -11917,21 +11923,21 @@
         <v>13005</v>
       </c>
       <c r="B148" s="20" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="C148" s="14">
         <v>3</v>
       </c>
       <c r="E148" s="16" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="H148" s="14" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="I148" s="14"/>
       <c r="J148" s="14"/>
       <c r="L148" s="16" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="O148" s="14">
         <v>1</v>
@@ -11976,21 +11982,21 @@
         <v>13006</v>
       </c>
       <c r="B149" s="20" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="C149" s="14">
         <v>3</v>
       </c>
       <c r="E149" s="16" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="H149" s="14" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="I149" s="14"/>
       <c r="J149" s="14"/>
       <c r="L149" s="16" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="O149" s="14">
         <v>1</v>
@@ -12035,18 +12041,18 @@
         <v>13007</v>
       </c>
       <c r="B150" s="15" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="C150" s="14">
         <v>3</v>
       </c>
       <c r="E150" s="14" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="F150" s="14"/>
       <c r="G150" s="14"/>
       <c r="H150" s="14" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="I150" s="14"/>
       <c r="J150" s="14"/>
@@ -12096,19 +12102,19 @@
         <v>13008</v>
       </c>
       <c r="B151" s="20" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="C151" s="14">
         <v>3</v>
       </c>
       <c r="E151" s="16" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="G151" s="16" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="H151" s="14" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="I151" s="14"/>
       <c r="J151" s="14"/>
@@ -12122,7 +12128,7 @@
         <v>4</v>
       </c>
       <c r="Q151" s="14" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="R151" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R151" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q151,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q151))),1))</f>
@@ -12158,13 +12164,13 @@
         <v>13009</v>
       </c>
       <c r="B152" s="20" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C152" s="14">
         <v>3</v>
       </c>
       <c r="H152" s="14" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="I152" s="14"/>
       <c r="J152" s="14"/>
@@ -12178,7 +12184,7 @@
         <v>4</v>
       </c>
       <c r="Q152" s="14" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="R152" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R152" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q152,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q152))),1))</f>
@@ -12214,18 +12220,18 @@
         <v>13010</v>
       </c>
       <c r="B153" s="20" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="C153" s="14">
         <v>3</v>
       </c>
       <c r="H153" s="14" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="I153" s="14"/>
       <c r="J153" s="14"/>
       <c r="L153" s="16" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="O153" s="14">
         <v>1</v>
@@ -12234,7 +12240,7 @@
         <v>5</v>
       </c>
       <c r="Q153" s="14" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="R153" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R153" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q153,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q153))),1))</f>
@@ -12270,19 +12276,19 @@
         <v>13011</v>
       </c>
       <c r="B154" s="15" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="C154" s="14">
         <v>3</v>
       </c>
       <c r="E154" s="16" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
       <c r="G154" s="16" t="s">
         <v>169</v>
       </c>
       <c r="H154" s="14" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="I154" s="14"/>
       <c r="J154" s="14"/>
@@ -12293,7 +12299,7 @@
         <v>6</v>
       </c>
       <c r="Q154" s="14" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="R154" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R154" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q154,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q154))),1))</f>
@@ -12329,16 +12335,16 @@
         <v>13012</v>
       </c>
       <c r="B155" s="15" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="C155" s="14">
         <v>3</v>
       </c>
       <c r="H155" s="16" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="L155" s="16" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="O155" s="14">
         <v>1</v>
@@ -12380,18 +12386,18 @@
         <v>13013</v>
       </c>
       <c r="B156" s="20" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="C156" s="14">
         <v>3</v>
       </c>
       <c r="E156" s="14" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="F156" s="14"/>
       <c r="G156" s="14"/>
       <c r="H156" s="16" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="N156" s="16" t="s">
         <v>76</v>
@@ -12403,7 +12409,7 @@
         <v>6</v>
       </c>
       <c r="Q156" s="14" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="R156" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R156" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q156,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q156))),1))</f>
@@ -12439,18 +12445,18 @@
         <v>13014</v>
       </c>
       <c r="B157" s="20" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="C157" s="14">
         <v>3</v>
       </c>
       <c r="E157" s="14" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="F157" s="14"/>
       <c r="G157" s="14"/>
       <c r="H157" s="14" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="I157" s="14"/>
       <c r="J157" s="14"/>
@@ -12491,13 +12497,13 @@
         <v>13015</v>
       </c>
       <c r="B158" s="20" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="C158" s="14">
         <v>3</v>
       </c>
       <c r="H158" s="16" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="P158" s="14">
         <v>14</v>
@@ -12519,7 +12525,7 @@
         <v>20504</v>
       </c>
       <c r="W158" s="14" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="Y158" s="14">
         <v>1</v>
@@ -12536,7 +12542,7 @@
         <v>13016</v>
       </c>
       <c r="B159" s="20" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="C159" s="14">
         <v>3</v>
@@ -12554,7 +12560,7 @@
         <v>0</v>
       </c>
       <c r="Q159" s="14" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="R159" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R159" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q159,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q159))),1))</f>
@@ -12584,13 +12590,13 @@
         <v>13017</v>
       </c>
       <c r="B160" s="20" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C160" s="14">
         <v>3</v>
       </c>
       <c r="H160" s="14" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="I160" s="14"/>
       <c r="J160" s="14"/>
@@ -12625,13 +12631,13 @@
         <v>13018</v>
       </c>
       <c r="B161" s="20" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C161" s="14">
         <v>3</v>
       </c>
       <c r="H161" s="16" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="L161" s="16" t="s">
         <v>195</v>
@@ -12653,7 +12659,7 @@
         <v>20402</v>
       </c>
       <c r="W161" s="14" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="Y161" s="14">
         <v>1</v>
@@ -12670,13 +12676,13 @@
         <v>13019</v>
       </c>
       <c r="B162" s="15" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="C162" s="14">
         <v>3</v>
       </c>
       <c r="H162" s="16" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="O162" s="14">
         <v>5</v>
@@ -12692,7 +12698,7 @@
         <v>20402</v>
       </c>
       <c r="W162" s="14" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="Y162" s="14">
         <v>1</v>
@@ -12709,16 +12715,16 @@
         <v>13020</v>
       </c>
       <c r="B163" s="15" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="C163" s="14">
         <v>3</v>
       </c>
       <c r="H163" s="16" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="J163" s="16" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="R163" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R163" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q163,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q163))),1))</f>
@@ -12731,7 +12737,7 @@
         <v>20601</v>
       </c>
       <c r="W163" s="14" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="Y163" s="14">
         <v>1</v>
@@ -12748,19 +12754,19 @@
         <v>13021</v>
       </c>
       <c r="B164" s="20" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="C164" s="14">
         <v>3</v>
       </c>
       <c r="G164" s="16" t="s">
-        <v>1097</v>
+        <v>1091</v>
       </c>
       <c r="H164" s="16" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="N164" s="16" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="R164" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R164" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q164,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q164))),1))</f>
@@ -12793,16 +12799,16 @@
         <v>13022</v>
       </c>
       <c r="B165" s="15" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C165" s="14">
         <v>3</v>
       </c>
       <c r="H165" s="16" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="L165" s="16" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="Q165" s="14" t="s">
         <v>56</v>
@@ -12838,7 +12844,7 @@
         <v>13023</v>
       </c>
       <c r="B166" s="15" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C166" s="14">
         <v>3</v>
@@ -12865,18 +12871,18 @@
         <v>13024</v>
       </c>
       <c r="B167" s="20" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C167" s="14">
         <v>3</v>
       </c>
       <c r="H167" s="14" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="I167" s="14"/>
       <c r="J167" s="14"/>
       <c r="L167" s="16" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="O167" s="14">
         <v>1</v>
@@ -12912,20 +12918,20 @@
         <v>13025</v>
       </c>
       <c r="B168" s="15" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="C168" s="14">
         <v>3</v>
       </c>
       <c r="G168" s="14" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="H168" s="14" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="I168" s="14"/>
       <c r="L168" s="16" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="R168" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R168" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q168,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q168))),1))</f>
@@ -12941,7 +12947,7 @@
         <v>20506</v>
       </c>
       <c r="W168" s="14" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="Y168" s="14">
         <v>1</v>
@@ -12958,13 +12964,13 @@
         <v>13026</v>
       </c>
       <c r="B169" s="15" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="C169" s="14">
         <v>3</v>
       </c>
       <c r="E169" s="16" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="R169" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R169" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q169,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q169))),1))</f>
@@ -12977,7 +12983,7 @@
         <v>20506</v>
       </c>
       <c r="W169" s="14" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="Y169" s="14">
         <v>1</v>
@@ -12994,22 +13000,22 @@
         <v>13027</v>
       </c>
       <c r="B170" s="20" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="C170" s="14">
         <v>3</v>
       </c>
       <c r="H170" s="16" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="L170" s="16" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="N170" s="16" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="Q170" s="14" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="R170" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R170" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q170,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q170))),1))</f>
@@ -13042,19 +13048,19 @@
         <v>13028</v>
       </c>
       <c r="B171" s="15" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="C171" s="14">
         <v>3</v>
       </c>
       <c r="E171" s="16" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="H171" s="16" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="L171" s="16" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="Q171" s="14" t="s">
         <v>403</v>
@@ -13090,13 +13096,13 @@
         <v>13029</v>
       </c>
       <c r="B172" s="20" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="C172" s="14">
         <v>3</v>
       </c>
       <c r="H172" s="14" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="I172" s="14"/>
       <c r="J172" s="14"/>
@@ -13107,7 +13113,7 @@
         <v>3</v>
       </c>
       <c r="Q172" s="14" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="R172" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R172" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q172,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q172))),1))</f>
@@ -13140,16 +13146,16 @@
         <v>13030</v>
       </c>
       <c r="B173" s="20" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="C173" s="14">
         <v>3</v>
       </c>
       <c r="H173" s="16" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="L173" s="16" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="P173" s="14">
         <v>3</v>
@@ -13188,25 +13194,25 @@
         <v>13031</v>
       </c>
       <c r="B174" s="20" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="C174" s="14">
         <v>3</v>
       </c>
       <c r="E174" s="16" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="H174" s="16" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="L174" s="16" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="N174" s="16" t="s">
         <v>76</v>
       </c>
       <c r="Q174" s="14" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="R174" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R174" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q174,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q174))),1))</f>
@@ -13239,16 +13245,16 @@
         <v>13032</v>
       </c>
       <c r="B175" s="20" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="C175" s="14">
         <v>3</v>
       </c>
       <c r="E175" s="16" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="H175" s="14" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="I175" s="14"/>
       <c r="J175" s="14"/>
@@ -13289,16 +13295,16 @@
         <v>13033</v>
       </c>
       <c r="B176" s="20" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="C176" s="14">
         <v>3</v>
       </c>
       <c r="H176" s="16" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="L176" s="16" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="Q176" s="14" t="s">
         <v>366</v>
@@ -13337,10 +13343,10 @@
         <v>3</v>
       </c>
       <c r="H177" s="16" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="L177" s="16" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="Q177" s="14" t="s">
         <v>309</v>
@@ -13376,13 +13382,13 @@
         <v>3</v>
       </c>
       <c r="E178" s="16" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="H178" s="14" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="J178" s="16" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="R178" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R178" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q178,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q178))),1))</f>
@@ -13412,16 +13418,16 @@
         <v>13036</v>
       </c>
       <c r="B179" s="15" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="C179" s="14">
         <v>3</v>
       </c>
       <c r="H179" s="14" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="Q179" s="14" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="R179" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R179" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q179,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q179))),1))</f>
@@ -13457,10 +13463,10 @@
         <v>3</v>
       </c>
       <c r="E180" s="16" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="H180" s="14" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="R180" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R180" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q180,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q180))),1))</f>
@@ -13490,22 +13496,22 @@
         <v>13038</v>
       </c>
       <c r="B181" s="15" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C181" s="14">
         <v>3</v>
       </c>
       <c r="H181" s="14" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="J181" s="16" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="P181" s="14">
         <v>999</v>
       </c>
       <c r="Q181" s="14" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="R181" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R181" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q181,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q181))),1))</f>
@@ -13538,19 +13544,19 @@
         <v>13039</v>
       </c>
       <c r="B182" s="15" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="C182" s="14">
         <v>3</v>
       </c>
       <c r="G182" s="16" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="H182" s="14" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="N182" s="16" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="R182" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R182" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q182,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q182))),1))</f>
@@ -13583,22 +13589,22 @@
         <v>13040</v>
       </c>
       <c r="B183" s="15" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="C183" s="14">
         <v>3</v>
       </c>
       <c r="G183" s="16" t="s">
-        <v>1090</v>
+        <v>1084</v>
       </c>
       <c r="H183" s="14" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="L183" s="16" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="N183" s="16" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="R183" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R183" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q183,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q183))),1))</f>
@@ -13611,7 +13617,7 @@
         <v>20504</v>
       </c>
       <c r="W183" s="14" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="Y183" s="14">
         <v>1</v>
@@ -13628,25 +13634,25 @@
         <v>13041</v>
       </c>
       <c r="B184" s="15" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="C184" s="14">
         <v>3</v>
       </c>
       <c r="H184" s="14" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="L184" s="16" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="N184" s="16" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="P184" s="14">
         <v>7</v>
       </c>
       <c r="Q184" s="14" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="R184" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R184" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q184,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q184))),1))</f>
@@ -13679,22 +13685,22 @@
         <v>13042</v>
       </c>
       <c r="B185" s="15" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="C185" s="14">
         <v>3</v>
       </c>
       <c r="H185" s="14" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="N185" s="16" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="P185" s="14">
         <v>7</v>
       </c>
       <c r="Q185" s="14" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="R185" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R185" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q185,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q185))),1))</f>
@@ -13727,22 +13733,22 @@
         <v>13043</v>
       </c>
       <c r="B186" s="15" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C186" s="14">
         <v>3</v>
       </c>
       <c r="H186" s="14" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="J186" s="16" t="s">
-        <v>1091</v>
+        <v>1085</v>
       </c>
       <c r="P186" s="14">
         <v>999</v>
       </c>
       <c r="Q186" s="14" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="R186" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R186" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q186,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q186))),1))</f>
@@ -13775,22 +13781,22 @@
         <v>13044</v>
       </c>
       <c r="B187" s="15" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="C187" s="14">
         <v>3</v>
       </c>
       <c r="H187" s="14" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="J187" s="16" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="P187" s="14">
         <v>999</v>
       </c>
       <c r="Q187" s="14" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="R187" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R187" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q187,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q187))),1))</f>
@@ -13823,22 +13829,22 @@
         <v>13045</v>
       </c>
       <c r="B188" s="15" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="C188" s="14">
         <v>3</v>
       </c>
       <c r="H188" s="14" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="J188" s="16" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="P188" s="14">
         <v>999</v>
       </c>
       <c r="Q188" s="14" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="R188" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R188" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q188,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q188))),1))</f>
@@ -13871,22 +13877,22 @@
         <v>13046</v>
       </c>
       <c r="B189" s="20" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="C189" s="14">
         <v>3</v>
       </c>
       <c r="G189" s="16" t="s">
-        <v>1083</v>
+        <v>1077</v>
       </c>
       <c r="H189" s="14" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="L189" s="16" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="N189" s="16" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="O189" s="14">
         <v>2</v>
@@ -13922,19 +13928,19 @@
         <v>13047</v>
       </c>
       <c r="B190" s="15" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="C190" s="14">
         <v>3</v>
       </c>
       <c r="H190" s="14" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="J190" s="16" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="Q190" s="14" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="R190" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R190" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q190,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q190))),1))</f>
@@ -13967,25 +13973,25 @@
         <v>13048</v>
       </c>
       <c r="B191" s="15" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="C191" s="14">
         <v>3</v>
       </c>
       <c r="E191" s="16" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="H191" s="16" t="s">
-        <v>1092</v>
+        <v>1086</v>
       </c>
       <c r="L191" s="16" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="N191" s="16" t="s">
         <v>76</v>
       </c>
       <c r="Q191" s="14" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="R191" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R191" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q191,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q191))),1))</f>
@@ -14018,16 +14024,16 @@
         <v>13049</v>
       </c>
       <c r="B192" s="15" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C192" s="14">
         <v>3</v>
       </c>
       <c r="H192" s="16" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="L192" s="16" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="O192" s="14">
         <v>2</v>
@@ -14069,16 +14075,16 @@
         <v>13050</v>
       </c>
       <c r="B193" s="15" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="C193" s="14">
         <v>3</v>
       </c>
       <c r="H193" s="16" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="L193" s="16" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="O193" s="14">
         <v>2</v>
@@ -14120,16 +14126,16 @@
         <v>13051</v>
       </c>
       <c r="B194" s="15" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="C194" s="14">
         <v>3</v>
       </c>
       <c r="H194" s="16" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="L194" s="16" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="R194" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R194" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q194,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q194))),1))</f>
@@ -14159,19 +14165,19 @@
         <v>13052</v>
       </c>
       <c r="B195" s="15" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="C195" s="14">
         <v>3</v>
       </c>
       <c r="E195" s="16" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="H195" s="16" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="L195" s="24" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="Q195" s="1" t="s">
         <v>56</v>
@@ -14210,16 +14216,16 @@
         <v>13053</v>
       </c>
       <c r="B196" s="15" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="C196" s="14">
         <v>3</v>
       </c>
       <c r="H196" s="16" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="L196" s="16" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="Q196" s="14" t="s">
         <v>372</v>
@@ -14258,19 +14264,19 @@
         <v>13054</v>
       </c>
       <c r="B197" s="15" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="C197" s="14">
         <v>3</v>
       </c>
       <c r="H197" s="16" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="L197" s="16" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="Q197" s="14" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="R197" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R197" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q197,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q197))),1))</f>
@@ -14306,22 +14312,22 @@
         <v>13055</v>
       </c>
       <c r="B198" s="15" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="C198" s="14">
         <v>3</v>
       </c>
       <c r="E198" s="16" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="H198" s="16" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="L198" s="16" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="Q198" s="14" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="R198" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R198" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q198,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q198))),1))</f>
@@ -14357,19 +14363,19 @@
         <v>13056</v>
       </c>
       <c r="B199" s="15" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C199" s="14">
         <v>3</v>
       </c>
       <c r="G199" s="16" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="H199" s="16" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="Q199" s="14" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="R199" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R199" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q199,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q199))),1))</f>
@@ -14405,16 +14411,16 @@
         <v>13057</v>
       </c>
       <c r="B200" s="15" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="C200" s="14">
         <v>3</v>
       </c>
       <c r="E200" s="16" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="H200" s="16" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="R200" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R200" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q200,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q200))),1))</f>
@@ -14444,16 +14450,16 @@
         <v>13058</v>
       </c>
       <c r="B201" s="15" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="C201" s="14">
         <v>3</v>
       </c>
       <c r="H201" s="16" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="L201" s="16" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="O201" s="16">
         <v>800065</v>
@@ -14462,7 +14468,7 @@
         <v>12</v>
       </c>
       <c r="Q201" s="14" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="R201" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R201" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q201,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q201))),1))</f>
@@ -14498,19 +14504,19 @@
         <v>13059</v>
       </c>
       <c r="B202" s="15" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="C202" s="14">
         <v>3</v>
       </c>
       <c r="E202" s="16" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="H202" s="16" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="J202" s="16" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="N202" s="16" t="s">
         <v>76</v>
@@ -14555,19 +14561,19 @@
         <v>13060</v>
       </c>
       <c r="B203" s="15" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="C203" s="14">
         <v>3</v>
       </c>
       <c r="E203" s="16" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H203" s="16" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="L203" s="16" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="O203" s="16">
         <v>800067</v>
@@ -14606,22 +14612,22 @@
         <v>13061</v>
       </c>
       <c r="B204" s="15" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="C204" s="14">
         <v>3</v>
       </c>
       <c r="E204" s="16" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="H204" s="16" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="N204" s="16" t="s">
         <v>76</v>
       </c>
       <c r="Q204" s="14" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="R204" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R204" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q204,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q204))),1))</f>
@@ -14654,16 +14660,16 @@
         <v>13062</v>
       </c>
       <c r="B205" s="15" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="C205" s="14">
         <v>3</v>
       </c>
       <c r="H205" s="16" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="Q205" s="14" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="R205" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R205" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q205,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q205))),1))</f>
@@ -14696,19 +14702,19 @@
         <v>13063</v>
       </c>
       <c r="B206" s="15" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="C206" s="14">
         <v>3</v>
       </c>
       <c r="H206" s="16" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="P206" s="14">
         <v>9</v>
       </c>
       <c r="Q206" s="14" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="R206" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R206" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q206,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q206))),1))</f>
@@ -14741,7 +14747,7 @@
         <v>13064</v>
       </c>
       <c r="B207" s="15" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="C207" s="14">
         <v>3</v>
@@ -14750,10 +14756,10 @@
         <v>383</v>
       </c>
       <c r="H207" s="16" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="J207" s="16" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="N207" s="16" t="s">
         <v>191</v>
@@ -14792,25 +14798,25 @@
         <v>13065</v>
       </c>
       <c r="B208" s="15" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="C208" s="14">
         <v>3</v>
       </c>
       <c r="H208" s="16" t="s">
+        <v>692</v>
+      </c>
+      <c r="J208" s="16" t="s">
+        <v>693</v>
+      </c>
+      <c r="N208" s="16" t="s">
+        <v>694</v>
+      </c>
+      <c r="O208" s="14">
+        <v>1</v>
+      </c>
+      <c r="Q208" s="14" t="s">
         <v>695</v>
-      </c>
-      <c r="J208" s="16" t="s">
-        <v>696</v>
-      </c>
-      <c r="N208" s="16" t="s">
-        <v>697</v>
-      </c>
-      <c r="O208" s="14">
-        <v>1</v>
-      </c>
-      <c r="Q208" s="14" t="s">
-        <v>698</v>
       </c>
       <c r="R208" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R208" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q208,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q208))),1))</f>
@@ -14843,22 +14849,22 @@
         <v>13066</v>
       </c>
       <c r="B209" s="23" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="C209" s="14">
         <v>3</v>
       </c>
       <c r="G209" s="16" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="H209" s="16" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="J209" s="16" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="N209" s="16" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="O209" s="14">
         <v>1</v>
@@ -14897,7 +14903,7 @@
         <v>13067</v>
       </c>
       <c r="B210" s="15" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="C210" s="14">
         <v>3</v>
@@ -14906,18 +14912,18 @@
       <c r="F210" s="14"/>
       <c r="G210" s="14"/>
       <c r="H210" s="14" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="I210" s="14"/>
       <c r="J210" s="14"/>
       <c r="K210" s="14"/>
       <c r="L210" s="14" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="M210" s="14"/>
       <c r="N210" s="14"/>
       <c r="Q210" s="14" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="R210" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R210" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q210,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q210))),1))</f>
@@ -14950,17 +14956,17 @@
         <v>13068</v>
       </c>
       <c r="B211" s="15" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="C211" s="14">
         <v>3</v>
       </c>
       <c r="E211" s="14" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="F211" s="14"/>
       <c r="H211" s="14" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="I211" s="14"/>
       <c r="J211" s="14"/>
@@ -15002,7 +15008,7 @@
         <v>13069</v>
       </c>
       <c r="B212" s="15" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="C212" s="14">
         <v>3</v>
@@ -15011,18 +15017,18 @@
       <c r="F212" s="14"/>
       <c r="G212" s="14"/>
       <c r="H212" s="14" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="I212" s="14"/>
       <c r="J212" s="14" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="K212" s="14"/>
       <c r="L212" s="14"/>
       <c r="M212" s="14"/>
       <c r="N212" s="14"/>
       <c r="Q212" s="14" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="R212" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R212" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q212,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q212))),1))</f>
@@ -15055,7 +15061,7 @@
         <v>13070</v>
       </c>
       <c r="B213" s="15" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="C213" s="14">
         <v>3</v>
@@ -15064,15 +15070,15 @@
       <c r="F213" s="14"/>
       <c r="G213" s="14"/>
       <c r="H213" s="14" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="I213" s="14"/>
       <c r="J213" s="14" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="K213" s="14"/>
       <c r="L213" s="14" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="M213" s="14"/>
       <c r="N213" s="14"/>
@@ -15080,7 +15086,7 @@
         <v>2</v>
       </c>
       <c r="Q213" s="14" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="R213" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R213" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q213,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q213))),1))</f>
@@ -15113,16 +15119,16 @@
         <v>13071</v>
       </c>
       <c r="B214" s="15" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="C214" s="14">
         <v>3</v>
       </c>
       <c r="E214" s="16" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="G214" s="16" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="R214" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R214" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q214,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q214))),1))</f>
@@ -15135,7 +15141,7 @@
         <v>20402</v>
       </c>
       <c r="W214" s="14" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="Y214" s="14">
         <v>1</v>
@@ -15152,16 +15158,16 @@
         <v>13072</v>
       </c>
       <c r="B215" s="15" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="C215" s="14">
         <v>3</v>
       </c>
       <c r="E215" s="16" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="H215" s="16" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="O215" s="14">
         <v>7</v>
@@ -15200,16 +15206,16 @@
         <v>3</v>
       </c>
       <c r="G216" s="16" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="H216" s="16" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="L216" s="16" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="N216" s="16" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="O216" s="14">
         <v>1</v>
@@ -15234,7 +15240,7 @@
         <v>20507</v>
       </c>
       <c r="W216" s="14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Y216" s="14">
         <v>1</v>
@@ -15254,13 +15260,13 @@
         <v>3</v>
       </c>
       <c r="E217" s="16" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H217" s="16" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="L217" s="16" t="s">
-        <v>724</v>
+        <v>1093</v>
       </c>
       <c r="N217" s="16" t="s">
         <v>76</v>
@@ -15272,7 +15278,7 @@
         <v>6</v>
       </c>
       <c r="Q217" s="14" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="R217" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R217" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q217,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q217))),1))</f>
@@ -15288,7 +15294,7 @@
         <v>20507</v>
       </c>
       <c r="W217" s="14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Y217" s="14">
         <v>1</v>
@@ -15305,19 +15311,19 @@
         <v>13075</v>
       </c>
       <c r="B218" s="15" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="C218" s="14">
         <v>3</v>
       </c>
       <c r="G218" s="16" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="H218" s="16" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="L218" s="16" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="O218" s="14">
         <v>1</v>
@@ -15342,7 +15348,7 @@
         <v>20507</v>
       </c>
       <c r="W218" s="14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Y218" s="14">
         <v>1</v>
@@ -15362,10 +15368,10 @@
         <v>3</v>
       </c>
       <c r="H219" s="16" t="s">
-        <v>729</v>
+        <v>1096</v>
       </c>
       <c r="L219" s="16" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="O219" s="14">
         <v>1</v>
@@ -15390,7 +15396,7 @@
         <v>20507</v>
       </c>
       <c r="W219" s="14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Y219" s="14">
         <v>1</v>
@@ -15410,7 +15416,7 @@
         <v>3</v>
       </c>
       <c r="H220" s="16" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="O220" s="14">
         <v>4</v>
@@ -15419,7 +15425,7 @@
         <v>999</v>
       </c>
       <c r="Q220" s="14" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="R220" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R220" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q220,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q220))),1))</f>
@@ -15435,7 +15441,7 @@
         <v>20507</v>
       </c>
       <c r="W220" s="14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Y220" s="14">
         <v>1</v>
@@ -15455,7 +15461,7 @@
         <v>3</v>
       </c>
       <c r="H221" s="16" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="O221" s="14">
         <v>5</v>
@@ -15464,7 +15470,7 @@
         <v>999</v>
       </c>
       <c r="Q221" s="14" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="R221" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R221" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q221,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q221))),1))</f>
@@ -15480,7 +15486,7 @@
         <v>20507</v>
       </c>
       <c r="W221" s="14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Y221" s="14">
         <v>1</v>
@@ -15500,16 +15506,16 @@
         <v>3</v>
       </c>
       <c r="E222" s="16" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="G222" s="16" t="s">
         <v>169</v>
       </c>
       <c r="H222" s="16" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="L222" s="16" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="O222" s="14">
         <v>4</v>
@@ -15534,7 +15540,7 @@
         <v>20507</v>
       </c>
       <c r="W222" s="14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Y222" s="14">
         <v>1</v>
@@ -15554,13 +15560,13 @@
         <v>3</v>
       </c>
       <c r="H223" s="16" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="J223" s="16" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="N223" s="16" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="O223" s="14">
         <v>7</v>
@@ -15585,7 +15591,7 @@
         <v>20507</v>
       </c>
       <c r="W223" s="14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Y223" s="14">
         <v>1</v>
@@ -15602,13 +15608,13 @@
         <v>13081</v>
       </c>
       <c r="B224" s="15" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="C224" s="14">
         <v>3</v>
       </c>
       <c r="H224" s="16" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="Q224" s="14" t="s">
         <v>366</v>
@@ -15647,10 +15653,10 @@
         <v>3</v>
       </c>
       <c r="H225" s="16" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="N225" s="16" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="O225" s="14">
         <v>5</v>
@@ -15659,7 +15665,7 @@
         <v>6</v>
       </c>
       <c r="Q225" s="14" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="R225" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R225" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q225,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q225))),1))</f>
@@ -15675,7 +15681,7 @@
         <v>20507</v>
       </c>
       <c r="W225" s="14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Y225" s="14">
         <v>1</v>
@@ -15692,16 +15698,16 @@
         <v>13083</v>
       </c>
       <c r="B226" s="15" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="C226" s="14">
         <v>3</v>
       </c>
       <c r="H226" s="16" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="J226" s="16" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="P226" s="14">
         <v>999</v>
@@ -15734,13 +15740,13 @@
         <v>13084</v>
       </c>
       <c r="B227" s="15" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="C227" s="14">
         <v>3</v>
       </c>
       <c r="H227" s="16" t="s">
-        <v>1094</v>
+        <v>1088</v>
       </c>
       <c r="P227" s="14">
         <v>999</v>
@@ -15773,7 +15779,7 @@
         <v>13085</v>
       </c>
       <c r="B228" s="15" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="C228" s="14">
         <v>3</v>
@@ -15782,10 +15788,10 @@
         <v>169</v>
       </c>
       <c r="H228" s="16" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="J228" s="16" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="P228" s="14">
         <v>999</v>
@@ -15818,18 +15824,18 @@
         <v>13086</v>
       </c>
       <c r="B229" s="15" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="C229" s="14">
         <v>3</v>
       </c>
       <c r="H229" s="14" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="I229" s="14"/>
       <c r="J229" s="14"/>
       <c r="L229" s="16" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="P229" s="14">
         <v>999</v>
@@ -15862,13 +15868,13 @@
         <v>13087</v>
       </c>
       <c r="B230" s="15" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="C230" s="14">
         <v>3</v>
       </c>
       <c r="H230" s="16" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="P230" s="14">
         <v>999</v>
@@ -15901,13 +15907,13 @@
         <v>13088</v>
       </c>
       <c r="B231" s="15" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="C231" s="14">
         <v>3</v>
       </c>
       <c r="H231" s="16" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="L231" s="16" t="s">
         <v>360</v>
@@ -15943,13 +15949,13 @@
         <v>13089</v>
       </c>
       <c r="B232" s="15" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="C232" s="14">
         <v>3</v>
       </c>
       <c r="H232" s="16" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="P232" s="14">
         <v>999</v>
@@ -15982,16 +15988,16 @@
         <v>13090</v>
       </c>
       <c r="B233" s="15" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="C233" s="14">
         <v>3</v>
       </c>
       <c r="H233" s="16" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="J233" s="16" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="P233" s="14">
         <v>999</v>
@@ -16024,16 +16030,16 @@
         <v>13091</v>
       </c>
       <c r="B234" s="15" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="C234" s="14">
         <v>3</v>
       </c>
       <c r="E234" s="16" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="H234" s="16" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="N234" s="16" t="s">
         <v>76</v>
@@ -16072,21 +16078,21 @@
         <v>13092</v>
       </c>
       <c r="B235" s="15" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="C235" s="14">
         <v>3</v>
       </c>
       <c r="E235" s="16" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="H235" s="16" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="I235" s="14"/>
       <c r="J235" s="14"/>
       <c r="L235" s="16" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="R235" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R235" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q235,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q235))),1))</f>
@@ -16113,16 +16119,16 @@
         <v>13093</v>
       </c>
       <c r="B236" s="15" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="C236" s="14">
         <v>3</v>
       </c>
       <c r="H236" s="16" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="N236" s="16" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="R236" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R236" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q236,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q236))),1))</f>
@@ -16135,7 +16141,7 @@
         <v>20508</v>
       </c>
       <c r="W236" s="14" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="Y236" s="14">
         <v>1</v>
@@ -16152,13 +16158,13 @@
         <v>13094</v>
       </c>
       <c r="B237" s="15" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="C237" s="14">
         <v>3</v>
       </c>
       <c r="H237" s="16" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="R237" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R237" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q237,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q237))),1))</f>
@@ -16182,22 +16188,22 @@
         <v>13095</v>
       </c>
       <c r="B238" s="15" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C238" s="14">
         <v>3</v>
       </c>
       <c r="H238" s="14" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="J238" s="16" t="s">
-        <v>1095</v>
+        <v>1089</v>
       </c>
       <c r="P238" s="14">
         <v>999</v>
       </c>
       <c r="Q238" s="14" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="R238" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R238" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q238,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q238))),1))</f>
@@ -16227,22 +16233,22 @@
         <v>13096</v>
       </c>
       <c r="B239" s="15" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C239" s="14">
         <v>3</v>
       </c>
       <c r="H239" s="14" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="J239" s="16" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="P239" s="14">
         <v>999</v>
       </c>
       <c r="Q239" s="14" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="R239" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R239" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q239,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q239))),1))</f>
@@ -16272,22 +16278,22 @@
         <v>13097</v>
       </c>
       <c r="B240" s="15" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="C240" s="14">
         <v>3</v>
       </c>
       <c r="H240" s="14" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="J240" s="16" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="P240" s="14">
         <v>999</v>
       </c>
       <c r="Q240" s="14" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="R240" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R240" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q240,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q240))),1))</f>
@@ -16317,22 +16323,22 @@
         <v>13098</v>
       </c>
       <c r="B241" s="15" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="C241" s="14">
         <v>3</v>
       </c>
       <c r="H241" s="14" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="J241" s="16" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="P241" s="14">
         <v>999</v>
       </c>
       <c r="Q241" s="14" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="R241" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R241" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q241,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q241))),1))</f>
@@ -16362,16 +16368,16 @@
         <v>13099</v>
       </c>
       <c r="B242" s="15" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="C242" s="14">
         <v>3</v>
       </c>
       <c r="H242" s="16" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="J242" s="16" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="P242" s="14">
         <v>999</v>
@@ -16404,13 +16410,13 @@
         <v>13100</v>
       </c>
       <c r="B243" s="15" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="C243" s="14">
         <v>3</v>
       </c>
       <c r="H243" s="16" t="s">
-        <v>1096</v>
+        <v>1090</v>
       </c>
       <c r="P243" s="14">
         <v>999</v>
@@ -16443,18 +16449,18 @@
         <v>13101</v>
       </c>
       <c r="B244" s="15" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="C244" s="14">
         <v>3</v>
       </c>
       <c r="H244" s="14" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="I244" s="14"/>
       <c r="J244" s="14"/>
       <c r="L244" s="16" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="P244" s="14">
         <v>999</v>
@@ -16487,13 +16493,13 @@
         <v>13102</v>
       </c>
       <c r="B245" s="15" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="C245" s="14">
         <v>3</v>
       </c>
       <c r="H245" s="16" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="P245" s="14">
         <v>999</v>
@@ -16526,13 +16532,13 @@
         <v>13103</v>
       </c>
       <c r="B246" s="15" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="C246" s="14">
         <v>3</v>
       </c>
       <c r="H246" s="16" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="L246" s="16" t="s">
         <v>360</v>
@@ -16568,16 +16574,16 @@
         <v>13104</v>
       </c>
       <c r="B247" s="15" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="C247" s="14">
         <v>3</v>
       </c>
       <c r="H247" s="16" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="J247" s="16" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="P247" s="14">
         <v>999</v>
@@ -16610,13 +16616,13 @@
         <v>13105</v>
       </c>
       <c r="B248" s="15" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="C248" s="14">
         <v>3</v>
       </c>
       <c r="H248" s="16" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="P248" s="14">
         <v>999</v>
@@ -16649,18 +16655,18 @@
         <v>13106</v>
       </c>
       <c r="B249" s="15" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="C249" s="14">
         <v>3</v>
       </c>
       <c r="H249" s="14" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="I249" s="14"/>
       <c r="J249" s="14"/>
       <c r="L249" s="16" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="P249" s="14">
         <v>999</v>
@@ -16693,13 +16699,13 @@
         <v>13107</v>
       </c>
       <c r="B250" s="15" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="C250" s="14">
         <v>3</v>
       </c>
       <c r="H250" s="16" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="P250" s="14">
         <v>999</v>
@@ -16732,13 +16738,13 @@
         <v>13108</v>
       </c>
       <c r="B251" s="15" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="C251" s="14">
         <v>3</v>
       </c>
       <c r="H251" s="16" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="L251" s="16" t="s">
         <v>360</v>
@@ -16774,7 +16780,7 @@
         <v>13109</v>
       </c>
       <c r="B252" s="15" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="C252" s="14">
         <v>3</v>
@@ -16790,7 +16796,7 @@
         <v>20407</v>
       </c>
       <c r="W252" s="14" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="Y252" s="14">
         <v>1</v>
@@ -16810,7 +16816,7 @@
         <v>3</v>
       </c>
       <c r="H253" s="16" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="R253" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R253" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q253,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q253))),1))</f>
@@ -16823,7 +16829,7 @@
         <v>20508</v>
       </c>
       <c r="W253" s="14" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="Y253" s="14">
         <v>1</v>
@@ -16843,7 +16849,7 @@
         <v>3</v>
       </c>
       <c r="H254" s="16" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="R254" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R254" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q254,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q254))),1))</f>
@@ -16856,7 +16862,7 @@
         <v>20508</v>
       </c>
       <c r="W254" s="14" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="Y254" s="14">
         <v>1</v>
@@ -16876,7 +16882,7 @@
         <v>3</v>
       </c>
       <c r="H255" s="16" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="R255" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R255" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q255,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q255))),1))</f>
@@ -16909,7 +16915,7 @@
         <v>3</v>
       </c>
       <c r="H256" s="16" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="R256" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R256" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q256,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q256))),1))</f>
@@ -16942,22 +16948,22 @@
         <v>3</v>
       </c>
       <c r="G257" s="16" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="H257" s="16" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="J257" s="16" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="L257" s="16" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="P257" s="14">
         <v>5</v>
       </c>
       <c r="Q257" s="14" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="R257" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R257" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q257,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q257))),1))</f>
@@ -16976,7 +16982,7 @@
         <v>20602</v>
       </c>
       <c r="W257" s="14" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="Y257" s="14">
         <v>1</v>
@@ -16993,16 +16999,16 @@
         <v>13115</v>
       </c>
       <c r="B258" s="15" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="C258" s="14">
         <v>3</v>
       </c>
       <c r="H258" s="16" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="L258" s="16" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="P258" s="14">
         <v>999</v>
@@ -17044,13 +17050,13 @@
         <v>3</v>
       </c>
       <c r="H259" s="16" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="J259" s="16" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="L259" s="16" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="Q259" s="14" t="s">
         <v>434</v>
@@ -17088,16 +17094,16 @@
         <v>3</v>
       </c>
       <c r="E260" s="16" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="H260" s="16" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="J260" s="16" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="L260" s="16" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="N260" s="16" t="s">
         <v>76</v>
@@ -17135,10 +17141,10 @@
         <v>3</v>
       </c>
       <c r="H261" s="16" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="L261" s="16" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="S261" s="14">
         <v>1</v>
@@ -17170,13 +17176,13 @@
         <v>14001</v>
       </c>
       <c r="B264" s="15" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="C264" s="14">
         <v>4</v>
       </c>
       <c r="H264" s="16" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="O264" s="14">
         <v>3</v>
@@ -17185,7 +17191,7 @@
         <v>3</v>
       </c>
       <c r="Q264" s="14" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="R264" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R264" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q264,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q264))),1))</f>
@@ -17221,16 +17227,16 @@
         <v>14002</v>
       </c>
       <c r="B265" s="15" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="C265" s="14">
         <v>4</v>
       </c>
       <c r="E265" s="16" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="H265" s="16" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="O265" s="14">
         <v>6</v>
@@ -17239,7 +17245,7 @@
         <v>3</v>
       </c>
       <c r="Q265" s="14" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="R265" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R265" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q265,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q265))),1))</f>
@@ -17275,7 +17281,7 @@
         <v>14003</v>
       </c>
       <c r="B266" s="15" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="C266" s="14">
         <v>4</v>
@@ -17287,10 +17293,10 @@
         <v>249</v>
       </c>
       <c r="H266" s="16" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="L266" s="16" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="O266" s="14">
         <v>3</v>
@@ -17299,7 +17305,7 @@
         <v>4</v>
       </c>
       <c r="Q266" s="14" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="R266" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R266" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q266,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q266))),1))</f>
@@ -17335,7 +17341,7 @@
         <v>14004</v>
       </c>
       <c r="B267" s="15" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="C267" s="14">
         <v>4</v>
@@ -17344,7 +17350,7 @@
         <v>270</v>
       </c>
       <c r="H267" s="16" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="N267" s="16" t="s">
         <v>76</v>
@@ -17383,7 +17389,7 @@
         <v>14005</v>
       </c>
       <c r="B268" s="15" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="C268" s="14">
         <v>4</v>
@@ -17392,13 +17398,13 @@
         <v>270</v>
       </c>
       <c r="H268" s="16" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="N268" s="16" t="s">
         <v>76</v>
       </c>
       <c r="Q268" s="14" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="R268" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R268" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q268,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q268))),1))</f>
@@ -17431,16 +17437,16 @@
         <v>14006</v>
       </c>
       <c r="B269" s="15" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="C269" s="14">
         <v>4</v>
       </c>
       <c r="H269" s="16" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="L269" s="16" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="O269" s="14">
         <v>3</v>
@@ -17476,7 +17482,7 @@
         <v>14007</v>
       </c>
       <c r="B270" s="20" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="C270" s="14">
         <v>4</v>
@@ -17485,10 +17491,10 @@
         <v>85</v>
       </c>
       <c r="H270" s="16" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
       <c r="L270" s="16" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="O270" s="14">
         <v>1</v>
@@ -17497,7 +17503,7 @@
         <v>4</v>
       </c>
       <c r="Q270" s="14" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="R270" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R270" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q270,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q270))),1))</f>
@@ -17530,7 +17536,7 @@
         <v>14008</v>
       </c>
       <c r="B271" s="20" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="C271" s="14">
         <v>4</v>
@@ -17539,10 +17545,10 @@
         <v>85</v>
       </c>
       <c r="H271" s="16" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="L271" s="16" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="O271" s="14">
         <v>1</v>
@@ -17584,16 +17590,16 @@
         <v>14009</v>
       </c>
       <c r="B272" s="15" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="C272" s="14">
         <v>4</v>
       </c>
       <c r="E272" s="16" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="H272" s="16" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="N272" s="16" t="s">
         <v>201</v>
@@ -17618,7 +17624,7 @@
         <v>20406</v>
       </c>
       <c r="W272" s="14" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="Y272" s="14">
         <v>2</v>
@@ -17635,13 +17641,13 @@
         <v>14010</v>
       </c>
       <c r="B273" s="15" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="C273" s="14">
         <v>4</v>
       </c>
       <c r="H273" s="16" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="R273" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R273" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q273,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q273))),1))</f>
@@ -17668,16 +17674,16 @@
         <v>14011</v>
       </c>
       <c r="B274" s="15" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="C274" s="14">
         <v>4</v>
       </c>
       <c r="E274" s="16" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="H274" s="16" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="R274" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R274" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q274,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q274))),1))</f>
@@ -17704,7 +17710,7 @@
         <v>14012</v>
       </c>
       <c r="B275" s="15" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="C275" s="14">
         <v>4</v>
@@ -17728,19 +17734,19 @@
         <v>14013</v>
       </c>
       <c r="B276" s="15" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="C276" s="14">
         <v>4</v>
       </c>
       <c r="E276" s="16" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="H276" s="16" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="Q276" s="14" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="R276" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R276" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q276,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q276))),1))</f>
@@ -17770,19 +17776,19 @@
         <v>14014</v>
       </c>
       <c r="B277" s="20" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="C277" s="14">
         <v>4</v>
       </c>
       <c r="E277" s="16" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="H277" s="16" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="Q277" s="14" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="R277" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R277" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q277,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q277))),1))</f>
@@ -17812,19 +17818,19 @@
         <v>14015</v>
       </c>
       <c r="B278" s="15" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="C278" s="14">
         <v>4</v>
       </c>
       <c r="E278" s="16" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="H278" s="16" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="Q278" s="14" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="R278" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R278" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q278,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q278))),1))</f>
@@ -17857,7 +17863,7 @@
         <v>14016</v>
       </c>
       <c r="B279" s="15" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
       <c r="C279" s="14">
         <v>4</v>
@@ -17869,7 +17875,7 @@
         <v>249</v>
       </c>
       <c r="H279" s="16" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="O279" s="14">
         <v>3</v>
@@ -17885,7 +17891,7 @@
         <v>20602</v>
       </c>
       <c r="W279" s="14" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="Y279" s="14">
         <v>2</v>
@@ -17902,19 +17908,19 @@
         <v>14017</v>
       </c>
       <c r="B280" s="15" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="C280" s="14">
         <v>4</v>
       </c>
       <c r="E280" s="16" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="H280" s="16" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="L280" s="16" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="O280" s="14">
         <v>7</v>
@@ -17933,7 +17939,7 @@
         <v>20602</v>
       </c>
       <c r="W280" s="14" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="Y280" s="14">
         <v>2</v>
@@ -17950,7 +17956,7 @@
         <v>14018</v>
       </c>
       <c r="B281" s="15" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="C281" s="14">
         <v>4</v>
@@ -17998,16 +18004,16 @@
         <v>14019</v>
       </c>
       <c r="B282" s="15" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="C282" s="14">
         <v>4</v>
       </c>
       <c r="E282" s="16" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="H282" s="16" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="R282" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R282" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q282,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q282))),1))</f>
@@ -18037,19 +18043,19 @@
         <v>14020</v>
       </c>
       <c r="B283" s="20" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="C283" s="14">
         <v>4</v>
       </c>
       <c r="E283" s="16" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="H283" s="16" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="Q283" s="14" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="R283" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R283" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q283,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q283))),1))</f>
@@ -18079,25 +18085,25 @@
         <v>14021</v>
       </c>
       <c r="B284" s="15" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="C284" s="14">
         <v>4</v>
       </c>
       <c r="G284" s="16" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="H284" s="16" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="L284" s="16" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="P284" s="14">
         <v>999</v>
       </c>
       <c r="Q284" s="14" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="R284" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R284" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q284,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q284))),1))</f>
@@ -18127,25 +18133,25 @@
         <v>14022</v>
       </c>
       <c r="B285" s="15" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="C285" s="14">
         <v>4</v>
       </c>
       <c r="G285" s="16" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="H285" s="16" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="L285" s="16" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="P285" s="14">
         <v>999</v>
       </c>
       <c r="Q285" s="14" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="R285" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R285" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q285,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q285))),1))</f>
@@ -18175,22 +18181,22 @@
         <v>14023</v>
       </c>
       <c r="B286" s="15" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="C286" s="14">
         <v>4</v>
       </c>
       <c r="H286" s="16" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="J286" s="16" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="P286" s="14">
         <v>999</v>
       </c>
       <c r="Q286" s="14" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="R286" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R286" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q286,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q286))),1))</f>
@@ -18220,22 +18226,22 @@
         <v>14024</v>
       </c>
       <c r="B287" s="15" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="C287" s="14">
         <v>4</v>
       </c>
       <c r="H287" s="16" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="J287" s="16" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="P287" s="14">
         <v>999</v>
       </c>
       <c r="Q287" s="14" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="R287" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R287" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q287,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q287))),1))</f>
@@ -18265,22 +18271,22 @@
         <v>14025</v>
       </c>
       <c r="B288" s="15" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="C288" s="14">
         <v>4</v>
       </c>
       <c r="G288" s="16" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="H288" s="16" t="s">
         <v>55</v>
       </c>
       <c r="J288" s="16" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="Q288" s="14" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="R288" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R288" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q288,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q288))),1))</f>
@@ -18310,22 +18316,22 @@
         <v>14026</v>
       </c>
       <c r="B289" s="15" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="C289" s="14">
         <v>4</v>
       </c>
       <c r="G289" s="16" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="H289" s="16" t="s">
         <v>55</v>
       </c>
       <c r="J289" s="16" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="Q289" s="14" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="R289" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R289" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q289,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q289))),1))</f>
@@ -18355,16 +18361,16 @@
         <v>14027</v>
       </c>
       <c r="B290" s="15" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="C290" s="14">
         <v>4</v>
       </c>
       <c r="H290" s="16" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="N290" s="16" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="O290" s="14">
         <v>3</v>
@@ -18400,22 +18406,22 @@
         <v>14028</v>
       </c>
       <c r="B291" s="15" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="C291" s="14">
         <v>4</v>
       </c>
       <c r="E291" s="16" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="G291" s="16" t="s">
         <v>169</v>
       </c>
       <c r="H291" s="16" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="N291" s="16" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="R291" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R291" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q291,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q291))),1))</f>
@@ -18442,7 +18448,7 @@
         <v>14029</v>
       </c>
       <c r="B292" s="15" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="C292" s="14">
         <v>4</v>
@@ -18475,19 +18481,19 @@
         <v>14030</v>
       </c>
       <c r="B293" s="15" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="C293" s="14">
         <v>4</v>
       </c>
       <c r="E293" s="16" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="H293" s="16" t="s">
         <v>398</v>
       </c>
       <c r="J293" s="16" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="L293" s="16" t="s">
         <v>195</v>
@@ -18520,16 +18526,16 @@
         <v>14031</v>
       </c>
       <c r="B294" s="15" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="C294" s="14">
         <v>4</v>
       </c>
       <c r="H294" s="16" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="N294" s="16" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="P294" s="14">
         <v>1</v>
@@ -18568,7 +18574,7 @@
         <v>14032</v>
       </c>
       <c r="B295" s="15" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="C295" s="14">
         <v>4</v>
@@ -18580,16 +18586,16 @@
         <v>249</v>
       </c>
       <c r="H295" s="16" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="L295" s="16" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="P295" s="14">
         <v>5</v>
       </c>
       <c r="Q295" s="14" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="R295" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R295" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q295,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q295))),1))</f>
@@ -18602,7 +18608,7 @@
         <v>20402</v>
       </c>
       <c r="W295" s="14" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="Y295" s="14">
         <v>2</v>
@@ -18619,13 +18625,13 @@
         <v>14033</v>
       </c>
       <c r="B296" s="15" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="C296" s="14">
         <v>4</v>
       </c>
       <c r="H296" s="16" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
       <c r="P296" s="14">
         <v>12</v>
@@ -18638,7 +18644,7 @@
         <v>20407</v>
       </c>
       <c r="W296" s="14" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="Y296" s="14">
         <v>2</v>
@@ -18655,13 +18661,13 @@
         <v>14034</v>
       </c>
       <c r="B297" s="15" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="C297" s="14">
         <v>4</v>
       </c>
       <c r="H297" s="16" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="P297" s="14">
         <v>7</v>
@@ -18677,7 +18683,7 @@
         <v>20603</v>
       </c>
       <c r="W297" s="14" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="Y297" s="14">
         <v>2</v>
@@ -18694,16 +18700,16 @@
         <v>14035</v>
       </c>
       <c r="B298" s="15" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="C298" s="14">
         <v>4</v>
       </c>
       <c r="E298" s="16" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="H298" s="16" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="P298" s="14">
         <v>2</v>
@@ -18716,7 +18722,7 @@
         <v>20603</v>
       </c>
       <c r="W298" s="14" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="Y298" s="14">
         <v>2</v>
@@ -18733,19 +18739,19 @@
         <v>14036</v>
       </c>
       <c r="B299" s="15" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="C299" s="14">
         <v>4</v>
       </c>
       <c r="E299" s="16" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="H299" s="16" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="J299" s="16" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="P299" s="14">
         <v>999</v>
@@ -18778,19 +18784,19 @@
         <v>14037</v>
       </c>
       <c r="B300" s="15" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="C300" s="14">
         <v>4</v>
       </c>
       <c r="E300" s="16" t="s">
+        <v>899</v>
+      </c>
+      <c r="H300" s="16" t="s">
+        <v>903</v>
+      </c>
+      <c r="J300" s="16" t="s">
         <v>904</v>
-      </c>
-      <c r="H300" s="16" t="s">
-        <v>908</v>
-      </c>
-      <c r="J300" s="16" t="s">
-        <v>909</v>
       </c>
       <c r="P300" s="14">
         <v>999</v>
@@ -18823,16 +18829,16 @@
         <v>14038</v>
       </c>
       <c r="B301" s="15" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="C301" s="14">
         <v>4</v>
       </c>
       <c r="H301" s="16" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
       <c r="J301" s="16" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="P301" s="14">
         <v>10</v>
@@ -18862,7 +18868,7 @@
         <v>14039</v>
       </c>
       <c r="B302" s="23" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="C302" s="14">
         <v>4</v>
@@ -18877,7 +18883,7 @@
         <v>409</v>
       </c>
       <c r="N302" s="16" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="P302" s="14">
         <v>6</v>
@@ -18910,7 +18916,7 @@
         <v>14040</v>
       </c>
       <c r="B303" s="15" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="C303" s="14">
         <v>4</v>
@@ -18919,7 +18925,7 @@
         <v>182</v>
       </c>
       <c r="H303" s="16" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="P303" s="14">
         <v>5</v>
@@ -18955,16 +18961,16 @@
         <v>14041</v>
       </c>
       <c r="B304" s="15" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="C304" s="14">
         <v>4</v>
       </c>
       <c r="E304" s="16" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="H304" s="16" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="P304" s="14">
         <v>7</v>
@@ -18983,7 +18989,7 @@
         <v>20402</v>
       </c>
       <c r="W304" s="14" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="Y304" s="14">
         <v>2</v>
@@ -19000,16 +19006,16 @@
         <v>14042</v>
       </c>
       <c r="B305" s="15" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
       <c r="C305" s="14">
         <v>4</v>
       </c>
       <c r="H305" s="16" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="L305" s="16" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="Q305" s="14" t="s">
         <v>366</v>
@@ -19045,10 +19051,10 @@
         <v>4</v>
       </c>
       <c r="H306" s="16" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="J306" s="16" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="Q306" s="14" t="s">
         <v>142</v>
@@ -19081,16 +19087,16 @@
         <v>14044</v>
       </c>
       <c r="B307" s="15" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="C307" s="14">
         <v>4</v>
       </c>
       <c r="H307" s="16" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="J307" s="16" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="R307" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R307" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q307,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q307))),1))</f>
@@ -19117,7 +19123,7 @@
         <v>14045</v>
       </c>
       <c r="B308" s="15" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
       <c r="C308" s="14">
         <v>4</v>
@@ -19132,13 +19138,13 @@
         <v>14046</v>
       </c>
       <c r="B309" s="15" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="C309" s="14">
         <v>4</v>
       </c>
       <c r="H309" s="16" t="s">
-        <v>930</v>
+        <v>925</v>
       </c>
       <c r="O309" s="14">
         <v>6</v>
@@ -19154,7 +19160,7 @@
         <v>20402</v>
       </c>
       <c r="W309" s="14" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="Y309" s="14">
         <v>2</v>
@@ -19171,16 +19177,16 @@
         <v>14047</v>
       </c>
       <c r="B310" s="15" t="s">
-        <v>931</v>
+        <v>926</v>
       </c>
       <c r="C310" s="14">
         <v>4</v>
       </c>
       <c r="E310" s="16" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="H310" s="16" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
       <c r="O310" s="14">
         <v>1</v>
@@ -19202,7 +19208,7 @@
         <v>20407</v>
       </c>
       <c r="W310" s="14" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="Y310" s="14">
         <v>2</v>
@@ -19243,10 +19249,10 @@
         <v>4</v>
       </c>
       <c r="E312" s="16" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="H312" s="16" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="O312" s="14">
         <v>6</v>
@@ -19282,16 +19288,16 @@
         <v>4</v>
       </c>
       <c r="E313" s="16" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="H313" s="16" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="O313" s="14">
         <v>6</v>
       </c>
       <c r="Q313" s="14" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="R313" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R313" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q313,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q313))),1))</f>
@@ -19321,10 +19327,10 @@
         <v>4</v>
       </c>
       <c r="E314" s="16" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="H314" s="16" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="O314" s="14">
         <v>6</v>
@@ -19357,19 +19363,19 @@
         <v>14052</v>
       </c>
       <c r="B315" s="15" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="C315" s="14">
         <v>4</v>
       </c>
       <c r="E315" s="16" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="H315" s="16" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
       <c r="N315" s="16" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="O315" s="14">
         <v>4</v>
@@ -19394,7 +19400,7 @@
         <v>20507</v>
       </c>
       <c r="W315" s="14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Y315" s="14">
         <v>2</v>
@@ -19411,19 +19417,19 @@
         <v>14053</v>
       </c>
       <c r="B316" s="15" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="C316" s="14">
         <v>4</v>
       </c>
       <c r="E316" s="16" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="H316" s="16" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="N316" s="16" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="O316" s="14">
         <v>5</v>
@@ -19448,7 +19454,7 @@
         <v>20507</v>
       </c>
       <c r="W316" s="14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Y316" s="14">
         <v>2</v>
@@ -19465,19 +19471,19 @@
         <v>14054</v>
       </c>
       <c r="B317" s="15" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="C317" s="14">
         <v>4</v>
       </c>
       <c r="E317" s="16" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
       <c r="H317" s="16" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="N317" s="16" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="O317" s="14">
         <v>6</v>
@@ -19502,7 +19508,7 @@
         <v>20507</v>
       </c>
       <c r="W317" s="14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Y317" s="14">
         <v>2</v>
@@ -19522,10 +19528,10 @@
         <v>4</v>
       </c>
       <c r="H318" s="16" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="L318" s="16" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
       <c r="O318" s="14">
         <v>6</v>
@@ -19534,7 +19540,7 @@
         <v>99</v>
       </c>
       <c r="Q318" s="14" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="R318" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R318" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q318,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q318))),1))</f>
@@ -19550,7 +19556,7 @@
         <v>20507</v>
       </c>
       <c r="W318" s="14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Y318" s="14">
         <v>2</v>
@@ -19567,13 +19573,13 @@
         <v>14056</v>
       </c>
       <c r="B319" s="15" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="C319" s="14">
         <v>4</v>
       </c>
       <c r="H319" s="16" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="O319" s="14">
         <v>1</v>
@@ -19582,7 +19588,7 @@
         <v>8</v>
       </c>
       <c r="Q319" s="14" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="R319" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R319" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q319,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q319))),1))</f>
@@ -19598,7 +19604,7 @@
         <v>20507</v>
       </c>
       <c r="W319" s="14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Y319" s="14">
         <v>2</v>
@@ -19615,16 +19621,16 @@
         <v>14057</v>
       </c>
       <c r="B320" s="15" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="C320" s="14">
         <v>4</v>
       </c>
       <c r="E320" s="16" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="H320" s="16" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="O320" s="14">
         <v>6</v>
@@ -19633,7 +19639,7 @@
         <v>8</v>
       </c>
       <c r="Q320" s="14" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="R320" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R320" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q320,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q320))),1))</f>
@@ -19649,7 +19655,7 @@
         <v>20507</v>
       </c>
       <c r="W320" s="14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Y320" s="14">
         <v>2</v>
@@ -19666,16 +19672,16 @@
         <v>14058</v>
       </c>
       <c r="B321" s="15" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="C321" s="14">
         <v>4</v>
       </c>
       <c r="H321" s="16" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="N321" s="16" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="O321" s="14">
         <v>5</v>
@@ -19684,7 +19690,7 @@
         <v>999</v>
       </c>
       <c r="Q321" s="14" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="R321" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R321" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q321,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q321))),1))</f>
@@ -19700,7 +19706,7 @@
         <v>20507</v>
       </c>
       <c r="W321" s="14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Y321" s="14">
         <v>2</v>
@@ -19717,16 +19723,16 @@
         <v>14059</v>
       </c>
       <c r="B322" s="15" t="s">
-        <v>958</v>
+        <v>953</v>
       </c>
       <c r="C322" s="14">
         <v>4</v>
       </c>
       <c r="H322" s="16" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="L322" s="16" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="R322" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R322" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q322,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q322))),1))</f>
@@ -19736,7 +19742,7 @@
         <v>20406</v>
       </c>
       <c r="W322" s="14" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="Y322" s="14">
         <v>2</v>
@@ -19756,7 +19762,7 @@
         <v>4</v>
       </c>
       <c r="H323" s="16" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="R323" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R323" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q323,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q323))),1))</f>
@@ -19786,7 +19792,7 @@
         <v>4</v>
       </c>
       <c r="H324" s="16" t="s">
-        <v>962</v>
+        <v>957</v>
       </c>
       <c r="R324" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R324" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q324,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q324))),1))</f>
@@ -19799,7 +19805,7 @@
         <v>20405</v>
       </c>
       <c r="W324" s="14" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="Y324" s="14">
         <v>2</v>
@@ -19816,13 +19822,13 @@
         <v>14062</v>
       </c>
       <c r="B325" s="15" t="s">
-        <v>963</v>
+        <v>958</v>
       </c>
       <c r="C325" s="14">
         <v>4</v>
       </c>
       <c r="H325" s="16" t="s">
-        <v>964</v>
+        <v>959</v>
       </c>
       <c r="L325" s="16" t="s">
         <v>195</v>
@@ -19855,16 +19861,16 @@
         <v>14063</v>
       </c>
       <c r="B326" s="15" t="s">
-        <v>965</v>
+        <v>960</v>
       </c>
       <c r="C326" s="14">
         <v>4</v>
       </c>
       <c r="H326" s="16" t="s">
-        <v>966</v>
+        <v>961</v>
       </c>
       <c r="J326" s="16" t="s">
-        <v>967</v>
+        <v>962</v>
       </c>
       <c r="R326" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R326" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q326,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q326))),1))</f>
@@ -19891,7 +19897,7 @@
         <v>14064</v>
       </c>
       <c r="B327" s="15" t="s">
-        <v>968</v>
+        <v>963</v>
       </c>
       <c r="C327" s="14">
         <v>4</v>
@@ -19900,7 +19906,7 @@
         <v>94</v>
       </c>
       <c r="H327" s="16" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="N327" s="16" t="s">
         <v>214</v>
@@ -19933,16 +19939,16 @@
         <v>14065</v>
       </c>
       <c r="B328" s="15" t="s">
-        <v>970</v>
+        <v>965</v>
       </c>
       <c r="C328" s="14">
         <v>4</v>
       </c>
       <c r="H328" s="16" t="s">
-        <v>971</v>
+        <v>1094</v>
       </c>
       <c r="N328" s="16" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="O328" s="16"/>
       <c r="R328" s="14" t="e" cm="1">
@@ -19953,7 +19959,7 @@
         <v>20409</v>
       </c>
       <c r="W328" s="14" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="Y328" s="14">
         <v>2</v>
@@ -19970,25 +19976,25 @@
         <v>14066</v>
       </c>
       <c r="B329" s="15" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="C329" s="14">
         <v>4</v>
       </c>
       <c r="G329" s="16" t="s">
-        <v>1076</v>
+        <v>1070</v>
       </c>
       <c r="H329" s="16" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="L329" s="16" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="P329" s="14">
         <v>999</v>
       </c>
       <c r="Q329" s="14" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="R329" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R329" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q329,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q329))),1))</f>
@@ -20018,25 +20024,25 @@
         <v>14067</v>
       </c>
       <c r="B330" s="15" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="C330" s="14">
         <v>4</v>
       </c>
       <c r="G330" s="16" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="H330" s="16" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="L330" s="16" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="P330" s="14">
         <v>999</v>
       </c>
       <c r="Q330" s="14" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="R330" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R330" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q330,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q330))),1))</f>
@@ -20066,22 +20072,22 @@
         <v>14068</v>
       </c>
       <c r="B331" s="15" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="C331" s="14">
         <v>4</v>
       </c>
       <c r="H331" s="16" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="J331" s="16" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="P331" s="14">
         <v>999</v>
       </c>
       <c r="Q331" s="14" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="R331" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R331" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q331,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q331))),1))</f>
@@ -20102,22 +20108,22 @@
         <v>14069</v>
       </c>
       <c r="B332" s="15" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="C332" s="14">
         <v>4</v>
       </c>
       <c r="H332" s="16" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="J332" s="16" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="P332" s="14">
         <v>999</v>
       </c>
       <c r="Q332" s="14" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="R332" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R332" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q332,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q332))),1))</f>
@@ -20138,13 +20144,13 @@
         <v>14070</v>
       </c>
       <c r="B333" s="15" t="s">
-        <v>963</v>
+        <v>958</v>
       </c>
       <c r="C333" s="14">
         <v>4</v>
       </c>
       <c r="H333" s="16" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="L333" s="16" t="s">
         <v>195</v>
@@ -20177,13 +20183,13 @@
         <v>14071</v>
       </c>
       <c r="B334" s="15" t="s">
-        <v>963</v>
+        <v>958</v>
       </c>
       <c r="C334" s="14">
         <v>4</v>
       </c>
       <c r="H334" s="16" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="L334" s="16" t="s">
         <v>195</v>
@@ -20216,16 +20222,16 @@
         <v>14072</v>
       </c>
       <c r="B335" s="15" t="s">
-        <v>979</v>
+        <v>973</v>
       </c>
       <c r="C335" s="14">
         <v>4</v>
       </c>
       <c r="H335" s="16" t="s">
-        <v>980</v>
+        <v>974</v>
       </c>
       <c r="L335" s="16" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="R335" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R335" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q335,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q335))),1))</f>
@@ -20235,7 +20241,7 @@
         <v>20503</v>
       </c>
       <c r="W335" s="14" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y335" s="14">
         <v>2</v>
@@ -20252,16 +20258,16 @@
         <v>14073</v>
       </c>
       <c r="B336" s="15" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="C336" s="14">
         <v>4</v>
       </c>
       <c r="H336" s="16" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="Q336" s="14" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="R336" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R336" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q336,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q336))),1))</f>
@@ -20271,7 +20277,7 @@
         <v>20406</v>
       </c>
       <c r="W336" s="14" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="Y336" s="14">
         <v>2</v>
@@ -20291,13 +20297,13 @@
         <v>4</v>
       </c>
       <c r="G337" s="16" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="H337" s="16" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="Q337" s="14" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="R337" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R337" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q337,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q337))),1))</f>
@@ -20307,7 +20313,7 @@
         <v>20503</v>
       </c>
       <c r="W337" s="14" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y337" s="14">
         <v>2</v>
@@ -20324,13 +20330,13 @@
         <v>14075</v>
       </c>
       <c r="B338" s="15" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
       <c r="C338" s="14">
         <v>4</v>
       </c>
       <c r="H338" s="16" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
       <c r="R338" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R338" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q338,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q338))),1))</f>
@@ -20351,19 +20357,19 @@
         <v>14076</v>
       </c>
       <c r="B339" s="23" t="s">
-        <v>989</v>
+        <v>983</v>
       </c>
       <c r="C339" s="14">
         <v>4</v>
       </c>
       <c r="E339" s="16" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="H339" s="16" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
       <c r="J339" s="16" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="R339" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R339" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q339,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q339))),1))</f>
@@ -20393,7 +20399,7 @@
         <v>4</v>
       </c>
       <c r="H340" s="16" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="R340" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R340" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q340,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q340))),1))</f>
@@ -20417,7 +20423,7 @@
         <v>4</v>
       </c>
       <c r="H341" s="16" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="L341" s="16" t="s">
         <v>99</v>
@@ -20441,16 +20447,16 @@
         <v>14079</v>
       </c>
       <c r="B342" s="15" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
       <c r="C342" s="14">
         <v>4</v>
       </c>
       <c r="H342" s="16" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
       <c r="L342" s="16" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="R342" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R342" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q342,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q342))),1))</f>
@@ -20477,7 +20483,7 @@
         <v>4</v>
       </c>
       <c r="H343" s="16" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="R343" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R343" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q343,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q343))),1))</f>
@@ -20487,7 +20493,7 @@
         <v>20705</v>
       </c>
       <c r="W343" s="14" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="Y343" s="14">
         <v>1</v>
@@ -20507,10 +20513,10 @@
         <v>4</v>
       </c>
       <c r="H344" s="16" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="N344" s="16" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="R344" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R344" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q344,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q344))),1))</f>
@@ -20520,7 +20526,7 @@
         <v>20705</v>
       </c>
       <c r="W344" s="14" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="Y344" s="14">
         <v>1</v>
@@ -20540,10 +20546,10 @@
         <v>4</v>
       </c>
       <c r="H345" s="16" t="s">
-        <v>1001</v>
+        <v>995</v>
       </c>
       <c r="N345" s="16" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="R345" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R345" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q345,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q345))),1))</f>
@@ -20553,7 +20559,7 @@
         <v>20705</v>
       </c>
       <c r="W345" s="14" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="Y345" s="14">
         <v>1</v>
@@ -20573,16 +20579,16 @@
         <v>4</v>
       </c>
       <c r="E346" s="16" t="s">
-        <v>1003</v>
+        <v>997</v>
       </c>
       <c r="G346" s="16" t="s">
         <v>249</v>
       </c>
       <c r="H346" s="16" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="L346" s="16" t="s">
-        <v>1005</v>
+        <v>999</v>
       </c>
       <c r="Q346" s="14" t="s">
         <v>333</v>
@@ -20609,13 +20615,13 @@
         <v>14084</v>
       </c>
       <c r="B347" s="15" t="s">
-        <v>1006</v>
+        <v>1000</v>
       </c>
       <c r="C347" s="14">
         <v>4</v>
       </c>
       <c r="E347" s="16" t="s">
-        <v>1007</v>
+        <v>1001</v>
       </c>
       <c r="R347" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R347" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q347,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q347))),1))</f>
@@ -20630,19 +20636,19 @@
         <v>14085</v>
       </c>
       <c r="B348" s="15" t="s">
-        <v>1008</v>
+        <v>1002</v>
       </c>
       <c r="C348" s="14">
         <v>4</v>
       </c>
       <c r="E348" s="16" t="s">
-        <v>1009</v>
+        <v>1003</v>
       </c>
       <c r="H348" s="16" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="L348" s="16" t="s">
-        <v>1011</v>
+        <v>1005</v>
       </c>
       <c r="Q348" s="14" t="s">
         <v>92</v>
@@ -20672,19 +20678,19 @@
         <v>14086</v>
       </c>
       <c r="B349" s="15" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="C349" s="14">
         <v>4</v>
       </c>
       <c r="E349" s="16" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="H349" s="16" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="L349" s="16" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="Q349" s="14" t="s">
         <v>92</v>
@@ -20717,19 +20723,19 @@
         <v>4</v>
       </c>
       <c r="E350" s="16" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="G350" s="16" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="H350" s="16" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="L350" s="16" t="s">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="N350" s="16" t="s">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="O350" s="14">
         <v>3</v>
@@ -20738,7 +20744,7 @@
         <v>12</v>
       </c>
       <c r="Q350" s="14" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="R350" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R350" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q350,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q350))),1))</f>
@@ -20768,7 +20774,7 @@
         <v>14088</v>
       </c>
       <c r="H351" s="16" t="s">
-        <v>1019</v>
+        <v>1013</v>
       </c>
       <c r="T351" s="14" t="s">
         <v>51</v>
@@ -20811,15 +20817,15 @@
         <v>76</v>
       </c>
       <c r="C1" t="s">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="E1" t="s">
-        <v>1021</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>1022</v>
+        <v>1016</v>
       </c>
       <c r="C2" t="s">
         <v>294</v>
@@ -20829,28 +20835,28 @@
         <v>8</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>1023</v>
+        <v>1017</v>
       </c>
       <c r="F2">
         <f>COUNTIF(Skill!V:V,20702)</f>
         <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>1024</v>
+        <v>1018</v>
       </c>
       <c r="H2">
         <f>COUNTIF(Skill!V:V,20402)</f>
         <v>6</v>
       </c>
       <c r="I2" t="s">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="J2">
         <f>COUNTIF(Skill!V:V,20307)</f>
         <v>4</v>
       </c>
       <c r="K2" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="L2">
         <f>COUNTIF(Skill!V:V,20705)</f>
@@ -20861,24 +20867,24 @@
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
-        <v>1026</v>
+        <v>1020</v>
       </c>
       <c r="C3" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="D3">
         <f>COUNTIF(Skill!V:V,20601)</f>
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="F3">
         <f>COUNTIF(Skill!V:V,20602)</f>
         <v>3</v>
       </c>
       <c r="G3" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="H3">
         <f>COUNTIF(Skill!V:V,20603)</f>
@@ -20896,10 +20902,10 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>1027</v>
+        <v>1021</v>
       </c>
       <c r="C4" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D4">
         <f>COUNTIF(Skill!V:V,20501)</f>
@@ -20913,14 +20919,14 @@
         <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H4">
         <f>COUNTIF(Skill!V:V,20503)</f>
         <v>5</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="J4">
         <f>COUNTIF(Skill!V:V,20504)</f>
@@ -20934,21 +20940,21 @@
         <v>6</v>
       </c>
       <c r="M4" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="N4">
         <f>COUNTIF(Skill!V:V,20506)</f>
         <v>2</v>
       </c>
       <c r="O4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="P4">
         <f>COUNTIF(Skill!V:V,20507)</f>
         <v>21</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="R4">
         <f>COUNTIF(Skill!V:V,20508)</f>
@@ -20958,7 +20964,7 @@
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="C5" t="s">
         <v>228</v>
@@ -20984,35 +20990,35 @@
         <v>6</v>
       </c>
       <c r="K5" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L5">
         <f>COUNTIF(Skill!V:V,20405)</f>
         <v>2</v>
       </c>
       <c r="M5" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="N5">
         <f>COUNTIF(Skill!V:V,20406)</f>
         <v>3</v>
       </c>
       <c r="O5" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="P5">
         <f>COUNTIF(Skill!V:V,20407)</f>
         <v>3</v>
       </c>
       <c r="Q5" t="s">
-        <v>1031</v>
+        <v>1025</v>
       </c>
       <c r="R5">
         <f>COUNTIF(Skill!V:V,20408)</f>
         <v>0</v>
       </c>
       <c r="S5" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="T5">
         <f>COUNTIF(Skill!V:V,20409)</f>
@@ -21021,7 +21027,7 @@
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="C6" t="s">
         <v>57</v>
@@ -21059,7 +21065,7 @@
         <v>7</v>
       </c>
       <c r="M6" t="s">
-        <v>1033</v>
+        <v>1027</v>
       </c>
       <c r="N6">
         <f>COUNTIF(Skill!V:V,20306)</f>
@@ -21072,7 +21078,7 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
-        <v>1034</v>
+        <v>1028</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>61</v>
@@ -21089,7 +21095,7 @@
         <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>1035</v>
+        <v>1029</v>
       </c>
       <c r="H7">
         <f>COUNTIF(Skill!V:V,20203)</f>
@@ -21103,7 +21109,7 @@
         <v>5</v>
       </c>
       <c r="K7" t="s">
-        <v>1036</v>
+        <v>1030</v>
       </c>
       <c r="L7">
         <f>COUNTIF(Skill!V:V,20205)</f>
@@ -21114,7 +21120,7 @@
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>1037</v>
+        <v>1031</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>71</v>
@@ -21137,10 +21143,10 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.15">
       <c r="G13" t="s">
-        <v>1038</v>
+        <v>1032</v>
       </c>
       <c r="H13" s="25" t="s">
-        <v>1039</v>
+        <v>1033</v>
       </c>
       <c r="I13" s="25"/>
       <c r="J13" s="25" t="s">
@@ -21148,19 +21154,19 @@
       </c>
       <c r="K13" s="25"/>
       <c r="L13" s="25" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
       <c r="M13" s="25"/>
       <c r="Q13" t="s">
-        <v>1041</v>
+        <v>1035</v>
       </c>
       <c r="R13" t="s">
-        <v>1042</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.15">
       <c r="G14" t="s">
-        <v>1026</v>
+        <v>1020</v>
       </c>
       <c r="H14" s="25">
         <v>125</v>
@@ -21175,7 +21181,7 @@
       </c>
       <c r="M14" s="25"/>
       <c r="Q14" t="s">
-        <v>1043</v>
+        <v>1037</v>
       </c>
       <c r="R14" t="s">
         <v>231</v>
@@ -21183,7 +21189,7 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.15">
       <c r="G15" t="s">
-        <v>1027</v>
+        <v>1021</v>
       </c>
       <c r="H15" s="25">
         <v>120</v>
@@ -21198,15 +21204,15 @@
       </c>
       <c r="M15" s="25"/>
       <c r="Q15" t="s">
-        <v>1044</v>
+        <v>1038</v>
       </c>
       <c r="R15" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.15">
       <c r="G16" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="H16" s="25">
         <v>115</v>
@@ -21221,15 +21227,15 @@
       </c>
       <c r="M16" s="25"/>
       <c r="Q16" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
       <c r="R16" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="17" spans="7:15" x14ac:dyDescent="0.15">
       <c r="G17" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="H17" s="25">
         <v>110</v>
@@ -21246,7 +21252,7 @@
     </row>
     <row r="18" spans="7:15" x14ac:dyDescent="0.15">
       <c r="G18" t="s">
-        <v>1034</v>
+        <v>1028</v>
       </c>
       <c r="H18" s="25">
         <v>105</v>
@@ -21263,7 +21269,7 @@
     </row>
     <row r="19" spans="7:15" x14ac:dyDescent="0.15">
       <c r="G19" t="s">
-        <v>1037</v>
+        <v>1031</v>
       </c>
       <c r="H19" s="25">
         <v>100</v>
@@ -21284,18 +21290,18 @@
     </row>
     <row r="21" spans="7:15" x14ac:dyDescent="0.15">
       <c r="G21" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="H21" s="25" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
       <c r="I21" s="25"/>
       <c r="J21" s="25" t="s">
-        <v>1048</v>
+        <v>1042</v>
       </c>
       <c r="K21" s="25"/>
       <c r="L21" s="25" t="s">
-        <v>1049</v>
+        <v>1043</v>
       </c>
       <c r="M21" s="26"/>
       <c r="O21" s="10"/>
@@ -21357,31 +21363,31 @@
   <sheetData>
     <row r="3" spans="1:16" x14ac:dyDescent="0.15">
       <c r="B3" t="s">
-        <v>1050</v>
+        <v>1044</v>
       </c>
       <c r="C3" t="s">
-        <v>1051</v>
+        <v>1045</v>
       </c>
       <c r="D3" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
       <c r="H3" t="s">
-        <v>1034</v>
+        <v>1028</v>
       </c>
       <c r="I3" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="J3" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="K3" t="s">
-        <v>1027</v>
+        <v>1021</v>
       </c>
       <c r="L3" t="s">
-        <v>1026</v>
+        <v>1020</v>
       </c>
       <c r="M3" t="s">
-        <v>1022</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.15">
@@ -21389,13 +21395,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1053</v>
+        <v>1047</v>
       </c>
       <c r="C4" t="s">
-        <v>1054</v>
+        <v>1048</v>
       </c>
       <c r="D4" t="s">
-        <v>1055</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.15">
@@ -21403,13 +21409,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="C5" t="s">
         <v>377</v>
       </c>
       <c r="D5" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.15">
@@ -21417,13 +21423,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>1058</v>
+        <v>1052</v>
       </c>
       <c r="C6" t="s">
         <v>377</v>
       </c>
       <c r="D6" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.15">
@@ -21431,13 +21437,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>1060</v>
+        <v>1054</v>
       </c>
       <c r="C7" t="s">
-        <v>1054</v>
+        <v>1048</v>
       </c>
       <c r="D7" t="s">
-        <v>1061</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.15">
@@ -21445,13 +21451,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>1062</v>
+        <v>1056</v>
       </c>
       <c r="C8" t="s">
-        <v>1054</v>
+        <v>1048</v>
       </c>
       <c r="D8" t="s">
-        <v>1063</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.15">
@@ -21459,13 +21465,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>1064</v>
+        <v>1058</v>
       </c>
       <c r="C9" t="s">
-        <v>1054</v>
+        <v>1048</v>
       </c>
       <c r="D9" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.15">
@@ -21473,13 +21479,13 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>1066</v>
+        <v>1060</v>
       </c>
       <c r="C10" t="s">
-        <v>1054</v>
+        <v>1048</v>
       </c>
       <c r="D10" t="s">
-        <v>1067</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.15">
@@ -21500,7 +21506,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.15">
       <c r="F16" t="s">
-        <v>1068</v>
+        <v>1062</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
@@ -21512,7 +21518,7 @@
     <row r="17" spans="5:16" x14ac:dyDescent="0.15">
       <c r="E17" s="6"/>
       <c r="F17" t="s">
-        <v>1069</v>
+        <v>1063</v>
       </c>
       <c r="G17" s="6"/>
       <c r="J17" s="6"/>
@@ -21523,7 +21529,7 @@
     <row r="18" spans="5:16" x14ac:dyDescent="0.15">
       <c r="E18" s="6"/>
       <c r="F18" t="s">
-        <v>1070</v>
+        <v>1064</v>
       </c>
       <c r="G18" s="6"/>
       <c r="J18" s="6"/>
@@ -21677,7 +21683,7 @@
         <v>14</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>1071</v>
+        <v>1065</v>
       </c>
       <c r="Y1" s="3" t="s">
         <v>16</v>
@@ -21702,25 +21708,25 @@
         <v>22</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>1074</v>
+        <v>1068</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>29</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>1075</v>
+        <v>1069</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>31</v>
@@ -21824,7 +21830,7 @@
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B27" s="1" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="C27" s="1" cm="1">
         <f t="array" ref="C27">SUMPRODUCT(LEN(P:P)-LEN(SUBSTITUTE(P:P,"↑","")))</f>
@@ -21851,7 +21857,7 @@
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B30" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C30" s="1" cm="1">
         <f t="array" ref="C30">SUMPRODUCT(LEN(P:P)-LEN(SUBSTITUTE(P:P,"→","")))</f>

--- a/Luban/Excel/Skill.xlsx
+++ b/Luban/Excel/Skill.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ED7AA0B-4084-4D01-B23F-D3750847D26E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F48283B2-2119-4355-81B5-B0A33F87737E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21317,30 +21317,30 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:M16"/>
     <mergeCell ref="H13:I13"/>
     <mergeCell ref="J13:K13"/>
     <mergeCell ref="L13:M13"/>
     <mergeCell ref="H14:I14"/>
     <mergeCell ref="J14:K14"/>
     <mergeCell ref="L14:M14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:M21"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Luban/Excel/Skill.xlsx
+++ b/Luban/Excel/Skill.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F48283B2-2119-4355-81B5-B0A33F87737E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{287D16B4-187A-45D5-A469-2FE1D317DC9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Skill" sheetId="1" r:id="rId1"/>
@@ -642,7 +642,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2046" uniqueCount="1098">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2046" uniqueCount="1100">
   <si>
     <t>id</t>
   </si>
@@ -1277,9 +1277,6 @@
     <t>800078|800079|800090</t>
   </si>
   <si>
-    <t>炁脉涌动</t>
-  </si>
-  <si>
     <t>本次行动不会被破招且持续到下次行动，下次行动决定后获得1次行动次数</t>
   </si>
   <si>
@@ -1973,9 +1970,6 @@
     <t>过阴</t>
   </si>
   <si>
-    <t>若处于祖化身状态刚炁消耗变为玄炁消耗</t>
-  </si>
-  <si>
     <t>萨么通幽</t>
   </si>
   <si>
@@ -3168,9 +3162,6 @@
   </si>
   <si>
     <t>烟云待</t>
-  </si>
-  <si>
-    <t>获得1层傍剑（标记目标）</t>
   </si>
   <si>
     <t>溯流</t>
@@ -3963,6 +3954,26 @@
   </si>
   <si>
     <t>造成145%技的伤害，下回合不会自然恢复炁</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>炁脉涌动</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>持有猊煞状态可使用</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得1层傍剑（标记目标）</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>至少持有5层毒瘴状态才可使用</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>若处于祖化身状态刚炁消耗变为玄炁消耗</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -5479,7 +5490,7 @@
         <v>112</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="I17" s="14"/>
       <c r="J17" s="14"/>
@@ -6521,7 +6532,7 @@
         <v>1</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="H35" s="14"/>
       <c r="I35" s="14"/>
@@ -6870,20 +6881,20 @@
         <v>11039</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>211</v>
+        <v>1095</v>
       </c>
       <c r="C42" s="14">
         <v>1</v>
       </c>
       <c r="F42" s="14"/>
       <c r="G42" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="H42" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="H42" s="14" t="s">
+      <c r="N42" s="16" t="s">
         <v>213</v>
-      </c>
-      <c r="N42" s="16" t="s">
-        <v>214</v>
       </c>
       <c r="O42" s="14" t="s">
         <v>210</v>
@@ -6925,7 +6936,7 @@
         <v>1</v>
       </c>
       <c r="H43" s="16" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O43" s="14" t="s">
         <v>202</v>
@@ -6970,12 +6981,12 @@
         <v>130</v>
       </c>
       <c r="H44" s="14" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I44" s="14"/>
       <c r="J44" s="14"/>
       <c r="L44" s="16" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O44" s="14" t="s">
         <v>133</v>
@@ -7023,12 +7034,12 @@
         <v>130</v>
       </c>
       <c r="H45" s="14" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I45" s="14"/>
       <c r="J45" s="14"/>
       <c r="L45" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O45" s="14" t="s">
         <v>133</v>
@@ -7081,7 +7092,7 @@
       <c r="I46" s="14"/>
       <c r="J46" s="14"/>
       <c r="L46" s="16" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O46" s="14" t="s">
         <v>133</v>
@@ -7134,7 +7145,7 @@
       <c r="I47" s="14"/>
       <c r="J47" s="14"/>
       <c r="L47" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O47" s="14" t="s">
         <v>133</v>
@@ -7179,7 +7190,7 @@
         <v>1</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H48" s="14" t="s">
         <v>199</v>
@@ -7232,7 +7243,7 @@
         <v>1</v>
       </c>
       <c r="H49" s="16" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O49" s="14" t="s">
         <v>202</v>
@@ -7278,7 +7289,7 @@
       </c>
       <c r="I50" s="14"/>
       <c r="J50" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O50" s="14" t="s">
         <v>202</v>
@@ -7317,7 +7328,7 @@
         <v>1</v>
       </c>
       <c r="H51" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I51" s="14"/>
       <c r="J51" s="14"/>
@@ -7343,7 +7354,7 @@
         <v>1</v>
       </c>
       <c r="H52" s="14" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I52" s="14"/>
       <c r="J52" s="14"/>
@@ -7366,16 +7377,16 @@
         <v>11050</v>
       </c>
       <c r="B53" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="C53" s="14">
+        <v>1</v>
+      </c>
+      <c r="E53" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="C53" s="14">
-        <v>1</v>
-      </c>
-      <c r="E53" s="16" t="s">
+      <c r="G53" s="16" t="s">
         <v>225</v>
-      </c>
-      <c r="G53" s="16" t="s">
-        <v>226</v>
       </c>
       <c r="H53" s="14"/>
       <c r="I53" s="14"/>
@@ -7386,7 +7397,7 @@
         <v>54</v>
       </c>
       <c r="Q53" s="14" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="R53" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R53" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q53,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q53))),1))</f>
@@ -7405,7 +7416,7 @@
         <v>20401</v>
       </c>
       <c r="W53" s="14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Y53" s="14">
         <v>2</v>
@@ -7422,13 +7433,13 @@
         <v>11051</v>
       </c>
       <c r="B54" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="C54" s="14">
+        <v>1</v>
+      </c>
+      <c r="G54" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="C54" s="14">
-        <v>1</v>
-      </c>
-      <c r="G54" s="16" t="s">
-        <v>230</v>
       </c>
       <c r="L54" s="16" t="s">
         <v>49</v>
@@ -7440,7 +7451,7 @@
         <v>1</v>
       </c>
       <c r="Q54" s="14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="R54" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R54" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q54,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q54))),1))</f>
@@ -7453,7 +7464,7 @@
         <v>20204</v>
       </c>
       <c r="W54" s="14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Y54" s="14">
         <v>2</v>
@@ -7470,18 +7481,18 @@
         <v>11052</v>
       </c>
       <c r="B55" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="H55" s="16" t="s">
         <v>233</v>
-      </c>
-      <c r="H55" s="16" t="s">
-        <v>234</v>
       </c>
       <c r="I55" s="14"/>
       <c r="J55" s="14"/>
       <c r="L55" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q55" s="14" t="s">
         <v>235</v>
-      </c>
-      <c r="Q55" s="14" t="s">
-        <v>236</v>
       </c>
       <c r="R55" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R55" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q55,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q55))),1))</f>
@@ -7494,7 +7505,7 @@
         <v>20204</v>
       </c>
       <c r="W55" s="14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Y55" s="14">
         <v>1</v>
@@ -7511,7 +7522,7 @@
         <v>11053</v>
       </c>
       <c r="B56" s="14" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C56" s="14">
         <v>1</v>
@@ -7520,17 +7531,17 @@
       <c r="F56" s="14"/>
       <c r="G56" s="14"/>
       <c r="H56" s="14" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I56" s="14"/>
       <c r="J56" s="14"/>
       <c r="K56" s="14"/>
       <c r="L56" s="14" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M56" s="14"/>
       <c r="N56" s="14" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q56" s="14" t="s">
         <v>50</v>
@@ -7572,7 +7583,7 @@
         <v>1</v>
       </c>
       <c r="H57" s="14" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I57" s="14"/>
       <c r="J57" s="14"/>
@@ -7610,12 +7621,12 @@
         <v>1</v>
       </c>
       <c r="G58" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H58" s="14"/>
       <c r="I58" s="14"/>
       <c r="J58" s="14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q58" s="14" t="s">
         <v>60</v>
@@ -7651,17 +7662,17 @@
         <v>1</v>
       </c>
       <c r="G59" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="H59" s="14" t="s">
         <v>243</v>
-      </c>
-      <c r="H59" s="14" t="s">
-        <v>244</v>
       </c>
       <c r="I59" s="14"/>
       <c r="J59" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="L59" s="14" t="s">
         <v>244</v>
-      </c>
-      <c r="L59" s="14" t="s">
-        <v>245</v>
       </c>
       <c r="P59" s="14">
         <v>3</v>
@@ -7686,7 +7697,7 @@
         <v>20604</v>
       </c>
       <c r="W59" s="14" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Y59" s="14">
         <v>2</v>
@@ -7703,7 +7714,7 @@
         <v>11057</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C60" s="14">
         <v>1</v>
@@ -7712,7 +7723,7 @@
       <c r="I60" s="14"/>
       <c r="J60" s="14"/>
       <c r="N60" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P60" s="14">
         <v>999</v>
@@ -7741,15 +7752,15 @@
         <v>1</v>
       </c>
       <c r="G61" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="H61" s="14" t="s">
         <v>249</v>
-      </c>
-      <c r="H61" s="14" t="s">
-        <v>250</v>
       </c>
       <c r="I61" s="14"/>
       <c r="J61" s="14"/>
       <c r="L61" s="16" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O61" s="14">
         <v>7</v>
@@ -7767,7 +7778,7 @@
         <v>20604</v>
       </c>
       <c r="W61" s="14" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Y61" s="14">
         <v>2</v>
@@ -7784,7 +7795,7 @@
         <v>1</v>
       </c>
       <c r="G62" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H62" s="14"/>
       <c r="I62" s="14"/>
@@ -7822,27 +7833,27 @@
         <v>12001</v>
       </c>
       <c r="B64" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="C64" s="14">
+        <v>2</v>
+      </c>
+      <c r="H64" s="14" t="s">
         <v>253</v>
-      </c>
-      <c r="C64" s="14">
-        <v>2</v>
-      </c>
-      <c r="H64" s="14" t="s">
-        <v>254</v>
       </c>
       <c r="I64" s="14"/>
       <c r="J64" s="14"/>
       <c r="L64" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="O64" s="14">
+        <v>1</v>
+      </c>
+      <c r="P64" s="14">
+        <v>2</v>
+      </c>
+      <c r="Q64" s="14" t="s">
         <v>255</v>
-      </c>
-      <c r="O64" s="14">
-        <v>1</v>
-      </c>
-      <c r="P64" s="14">
-        <v>2</v>
-      </c>
-      <c r="Q64" s="14" t="s">
-        <v>256</v>
       </c>
       <c r="R64" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R64" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q64,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q64))),1))</f>
@@ -7878,18 +7889,18 @@
         <v>12002</v>
       </c>
       <c r="B65" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="C65" s="14">
+        <v>2</v>
+      </c>
+      <c r="H65" s="14" t="s">
         <v>257</v>
-      </c>
-      <c r="C65" s="14">
-        <v>2</v>
-      </c>
-      <c r="H65" s="14" t="s">
-        <v>258</v>
       </c>
       <c r="I65" s="14"/>
       <c r="J65" s="14"/>
       <c r="L65" s="16" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O65" s="14">
         <v>1</v>
@@ -7898,7 +7909,7 @@
         <v>4</v>
       </c>
       <c r="Q65" s="14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="R65" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R65" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q65,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q65))),1))</f>
@@ -7934,18 +7945,18 @@
         <v>12003</v>
       </c>
       <c r="B66" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="C66" s="14">
+        <v>2</v>
+      </c>
+      <c r="H66" s="14" t="s">
         <v>261</v>
-      </c>
-      <c r="C66" s="14">
-        <v>2</v>
-      </c>
-      <c r="H66" s="14" t="s">
-        <v>262</v>
       </c>
       <c r="I66" s="14"/>
       <c r="J66" s="14"/>
       <c r="L66" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O66" s="14">
         <v>1</v>
@@ -7954,7 +7965,7 @@
         <v>6</v>
       </c>
       <c r="Q66" s="14" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="R66" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R66" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q66,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q66))),1))</f>
@@ -7990,21 +8001,21 @@
         <v>12004</v>
       </c>
       <c r="B67" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="C67" s="14">
+        <v>2</v>
+      </c>
+      <c r="E67" s="16" t="s">
         <v>265</v>
       </c>
-      <c r="C67" s="14">
-        <v>2</v>
-      </c>
-      <c r="E67" s="16" t="s">
-        <v>266</v>
-      </c>
       <c r="H67" s="14" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I67" s="14"/>
       <c r="J67" s="14"/>
       <c r="L67" s="16" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O67" s="14">
         <v>1</v>
@@ -8013,7 +8024,7 @@
         <v>6</v>
       </c>
       <c r="Q67" s="14" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="R67" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R67" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q67,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q67))),1))</f>
@@ -8049,21 +8060,21 @@
         <v>12005</v>
       </c>
       <c r="B68" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="C68" s="14">
+        <v>2</v>
+      </c>
+      <c r="E68" s="16" t="s">
         <v>269</v>
       </c>
-      <c r="C68" s="14">
-        <v>2</v>
-      </c>
-      <c r="E68" s="16" t="s">
+      <c r="H68" s="14" t="s">
         <v>270</v>
-      </c>
-      <c r="H68" s="14" t="s">
-        <v>271</v>
       </c>
       <c r="I68" s="14"/>
       <c r="J68" s="14"/>
       <c r="L68" s="16" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O68" s="14">
         <v>1</v>
@@ -8072,7 +8083,7 @@
         <v>5</v>
       </c>
       <c r="Q68" s="14" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="R68" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R68" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q68,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q68))),1))</f>
@@ -8108,21 +8119,21 @@
         <v>12006</v>
       </c>
       <c r="B69" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="C69" s="14">
+        <v>2</v>
+      </c>
+      <c r="E69" s="16" t="s">
         <v>274</v>
       </c>
-      <c r="C69" s="14">
-        <v>2</v>
-      </c>
-      <c r="E69" s="16" t="s">
+      <c r="H69" s="14" t="s">
         <v>275</v>
-      </c>
-      <c r="H69" s="14" t="s">
-        <v>276</v>
       </c>
       <c r="I69" s="14"/>
       <c r="J69" s="14"/>
       <c r="L69" s="16" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O69" s="14">
         <v>1</v>
@@ -8131,7 +8142,7 @@
         <v>4</v>
       </c>
       <c r="Q69" s="14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="R69" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R69" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q69,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q69))),1))</f>
@@ -8167,18 +8178,18 @@
         <v>12007</v>
       </c>
       <c r="B70" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="C70" s="14">
+        <v>2</v>
+      </c>
+      <c r="H70" s="14" t="s">
         <v>279</v>
-      </c>
-      <c r="C70" s="14">
-        <v>2</v>
-      </c>
-      <c r="H70" s="14" t="s">
-        <v>280</v>
       </c>
       <c r="I70" s="14"/>
       <c r="J70" s="14"/>
       <c r="L70" s="16" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O70" s="14">
         <v>3</v>
@@ -8187,7 +8198,7 @@
         <v>8</v>
       </c>
       <c r="Q70" s="14" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="R70" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R70" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q70,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q70))),1))</f>
@@ -8223,22 +8234,22 @@
         <v>12008</v>
       </c>
       <c r="B71" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="C71" s="14">
+        <v>2</v>
+      </c>
+      <c r="E71" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="C71" s="14">
-        <v>2</v>
-      </c>
-      <c r="E71" s="16" t="s">
+      <c r="H71" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="J71" s="16" t="s">
         <v>283</v>
       </c>
-      <c r="H71" s="16" t="s">
-        <v>276</v>
-      </c>
-      <c r="J71" s="16" t="s">
+      <c r="L71" s="16" t="s">
         <v>284</v>
-      </c>
-      <c r="L71" s="16" t="s">
-        <v>285</v>
       </c>
       <c r="O71" s="14">
         <v>6</v>
@@ -8247,7 +8258,7 @@
         <v>10</v>
       </c>
       <c r="Q71" s="14" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="R71" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R71" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q71,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q71))),1))</f>
@@ -8283,19 +8294,19 @@
         <v>12009</v>
       </c>
       <c r="B72" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="C72" s="14">
+        <v>2</v>
+      </c>
+      <c r="G72" s="16" t="s">
+        <v>1075</v>
+      </c>
+      <c r="H72" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="C72" s="14">
-        <v>2</v>
-      </c>
-      <c r="G72" s="16" t="s">
-        <v>1078</v>
-      </c>
-      <c r="H72" s="16" t="s">
+      <c r="L72" s="16" t="s">
         <v>288</v>
-      </c>
-      <c r="L72" s="16" t="s">
-        <v>289</v>
       </c>
       <c r="O72" s="14">
         <v>1</v>
@@ -8304,7 +8315,7 @@
         <v>7</v>
       </c>
       <c r="Q72" s="14" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="R72" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R72" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q72,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q72))),1))</f>
@@ -8323,7 +8334,7 @@
         <v>20401</v>
       </c>
       <c r="W72" s="14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Y72" s="14">
         <v>1</v>
@@ -8340,16 +8351,16 @@
         <v>12010</v>
       </c>
       <c r="B73" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="C73" s="14">
+        <v>2</v>
+      </c>
+      <c r="G73" s="16" t="s">
         <v>291</v>
       </c>
-      <c r="C73" s="14">
-        <v>2</v>
-      </c>
-      <c r="G73" s="16" t="s">
+      <c r="Q73" s="14" t="s">
         <v>292</v>
-      </c>
-      <c r="Q73" s="14" t="s">
-        <v>293</v>
       </c>
       <c r="R73" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R73" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q73,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q73))),1))</f>
@@ -8368,7 +8379,7 @@
         <v>20701</v>
       </c>
       <c r="W73" s="14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Y73" s="14">
         <v>2</v>
@@ -8385,16 +8396,16 @@
         <v>12011</v>
       </c>
       <c r="B74" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="C74" s="14">
+        <v>2</v>
+      </c>
+      <c r="H74" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="J74" s="16" t="s">
         <v>295</v>
-      </c>
-      <c r="C74" s="14">
-        <v>2</v>
-      </c>
-      <c r="H74" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="J74" s="16" t="s">
-        <v>296</v>
       </c>
       <c r="R74" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R74" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q74,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q74))),1))</f>
@@ -8407,7 +8418,7 @@
         <v>20502</v>
       </c>
       <c r="W74" s="14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Y74" s="14">
         <v>1</v>
@@ -8424,16 +8435,16 @@
         <v>12012</v>
       </c>
       <c r="B75" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="C75" s="14">
+        <v>2</v>
+      </c>
+      <c r="H75" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="J75" s="16" t="s">
         <v>298</v>
-      </c>
-      <c r="C75" s="14">
-        <v>2</v>
-      </c>
-      <c r="H75" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="J75" s="16" t="s">
-        <v>299</v>
       </c>
       <c r="R75" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R75" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q75,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q75))),1))</f>
@@ -8446,7 +8457,7 @@
         <v>20502</v>
       </c>
       <c r="W75" s="14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Y75" s="14">
         <v>1</v>
@@ -8463,25 +8474,25 @@
         <v>12013</v>
       </c>
       <c r="B76" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="C76" s="14">
+        <v>2</v>
+      </c>
+      <c r="G76" s="16" t="s">
         <v>300</v>
       </c>
-      <c r="C76" s="14">
-        <v>2</v>
-      </c>
-      <c r="G76" s="16" t="s">
+      <c r="H76" s="16" t="s">
         <v>301</v>
       </c>
-      <c r="H76" s="16" t="s">
+      <c r="L76" s="16" t="s">
         <v>302</v>
-      </c>
-      <c r="L76" s="16" t="s">
-        <v>303</v>
       </c>
       <c r="P76" s="14">
         <v>4</v>
       </c>
       <c r="Q76" s="14" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="R76" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R76" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q76,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q76))),1))</f>
@@ -8500,7 +8511,7 @@
         <v>20502</v>
       </c>
       <c r="W76" s="14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Y76" s="14">
         <v>2</v>
@@ -8517,25 +8528,25 @@
         <v>12014</v>
       </c>
       <c r="B77" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="C77" s="14">
+        <v>2</v>
+      </c>
+      <c r="G77" s="16" t="s">
         <v>305</v>
       </c>
-      <c r="C77" s="14">
-        <v>2</v>
-      </c>
-      <c r="G77" s="16" t="s">
+      <c r="H77" s="16" t="s">
         <v>306</v>
       </c>
-      <c r="H77" s="16" t="s">
+      <c r="L77" s="16" t="s">
         <v>307</v>
-      </c>
-      <c r="L77" s="16" t="s">
-        <v>308</v>
       </c>
       <c r="P77" s="14">
         <v>4</v>
       </c>
       <c r="Q77" s="14" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="R77" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R77" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q77,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q77))),1))</f>
@@ -8554,7 +8565,7 @@
         <v>20502</v>
       </c>
       <c r="W77" s="14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Y77" s="14">
         <v>2</v>
@@ -8571,25 +8582,25 @@
         <v>12015</v>
       </c>
       <c r="B78" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="C78" s="14">
+        <v>2</v>
+      </c>
+      <c r="G78" s="16" t="s">
         <v>310</v>
       </c>
-      <c r="C78" s="14">
-        <v>2</v>
-      </c>
-      <c r="G78" s="16" t="s">
+      <c r="H78" s="16" t="s">
         <v>311</v>
       </c>
-      <c r="H78" s="16" t="s">
+      <c r="L78" s="16" t="s">
         <v>312</v>
-      </c>
-      <c r="L78" s="16" t="s">
-        <v>313</v>
       </c>
       <c r="P78" s="14">
         <v>4</v>
       </c>
       <c r="Q78" s="14" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="R78" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R78" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q78,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q78))),1))</f>
@@ -8608,7 +8619,7 @@
         <v>20502</v>
       </c>
       <c r="W78" s="14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Y78" s="14">
         <v>2</v>
@@ -8625,25 +8636,25 @@
         <v>12016</v>
       </c>
       <c r="B79" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="C79" s="14">
+        <v>2</v>
+      </c>
+      <c r="G79" s="16" t="s">
         <v>315</v>
       </c>
-      <c r="C79" s="14">
-        <v>2</v>
-      </c>
-      <c r="G79" s="16" t="s">
+      <c r="H79" s="16" t="s">
         <v>316</v>
       </c>
-      <c r="H79" s="16" t="s">
+      <c r="L79" s="16" t="s">
         <v>317</v>
-      </c>
-      <c r="L79" s="16" t="s">
-        <v>318</v>
       </c>
       <c r="P79" s="14">
         <v>4</v>
       </c>
       <c r="Q79" s="14" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="R79" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R79" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q79,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q79))),1))</f>
@@ -8662,7 +8673,7 @@
         <v>20502</v>
       </c>
       <c r="W79" s="14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Y79" s="14">
         <v>2</v>
@@ -8679,27 +8690,27 @@
         <v>12017</v>
       </c>
       <c r="B80" s="20" t="s">
+        <v>319</v>
+      </c>
+      <c r="C80" s="14">
+        <v>2</v>
+      </c>
+      <c r="G80" s="16" t="s">
         <v>320</v>
       </c>
-      <c r="C80" s="14">
-        <v>2</v>
-      </c>
-      <c r="G80" s="16" t="s">
+      <c r="H80" s="22" t="s">
         <v>321</v>
-      </c>
-      <c r="H80" s="22" t="s">
-        <v>322</v>
       </c>
       <c r="I80" s="22"/>
       <c r="J80" s="22"/>
       <c r="L80" s="16" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="P80" s="14">
         <v>4</v>
       </c>
       <c r="Q80" s="14" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="R80" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R80" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q80,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q80))),1))</f>
@@ -8718,7 +8729,7 @@
         <v>20502</v>
       </c>
       <c r="W80" s="14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Y80" s="14">
         <v>2</v>
@@ -8735,19 +8746,19 @@
         <v>12018</v>
       </c>
       <c r="B81" s="20" t="s">
+        <v>324</v>
+      </c>
+      <c r="C81" s="14">
+        <v>2</v>
+      </c>
+      <c r="G81" s="16" t="s">
         <v>325</v>
       </c>
-      <c r="C81" s="14">
-        <v>2</v>
-      </c>
-      <c r="G81" s="16" t="s">
+      <c r="H81" s="16" t="s">
         <v>326</v>
       </c>
-      <c r="H81" s="16" t="s">
+      <c r="L81" s="16" t="s">
         <v>327</v>
-      </c>
-      <c r="L81" s="16" t="s">
-        <v>328</v>
       </c>
       <c r="P81" s="14">
         <v>4</v>
@@ -8772,7 +8783,7 @@
         <v>20502</v>
       </c>
       <c r="W81" s="14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Y81" s="14">
         <v>2</v>
@@ -8789,25 +8800,25 @@
         <v>12019</v>
       </c>
       <c r="B82" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="C82" s="14">
+        <v>2</v>
+      </c>
+      <c r="G82" s="16" t="s">
         <v>329</v>
       </c>
-      <c r="C82" s="14">
-        <v>2</v>
-      </c>
-      <c r="G82" s="16" t="s">
+      <c r="H82" s="16" t="s">
         <v>330</v>
       </c>
-      <c r="H82" s="16" t="s">
+      <c r="L82" s="16" t="s">
         <v>331</v>
-      </c>
-      <c r="L82" s="16" t="s">
-        <v>332</v>
       </c>
       <c r="P82" s="14">
         <v>4</v>
       </c>
       <c r="Q82" s="14" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="R82" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R82" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q82,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q82))),1))</f>
@@ -8826,7 +8837,7 @@
         <v>20502</v>
       </c>
       <c r="W82" s="14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Y82" s="14">
         <v>2</v>
@@ -8843,25 +8854,25 @@
         <v>12020</v>
       </c>
       <c r="B83" s="20" t="s">
+        <v>333</v>
+      </c>
+      <c r="C83" s="14">
+        <v>2</v>
+      </c>
+      <c r="G83" s="16" t="s">
         <v>334</v>
       </c>
-      <c r="C83" s="14">
-        <v>2</v>
-      </c>
-      <c r="G83" s="16" t="s">
+      <c r="H83" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="H83" s="16" t="s">
+      <c r="L83" s="16" t="s">
         <v>336</v>
-      </c>
-      <c r="L83" s="16" t="s">
-        <v>337</v>
       </c>
       <c r="P83" s="14">
         <v>4</v>
       </c>
       <c r="Q83" s="14" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="R83" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R83" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q83,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q83))),1))</f>
@@ -8880,7 +8891,7 @@
         <v>20502</v>
       </c>
       <c r="W83" s="14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Y83" s="14">
         <v>2</v>
@@ -8897,22 +8908,22 @@
         <v>12021</v>
       </c>
       <c r="B84" s="20" t="s">
+        <v>338</v>
+      </c>
+      <c r="C84" s="14">
+        <v>2</v>
+      </c>
+      <c r="G84" s="16" t="s">
         <v>339</v>
       </c>
-      <c r="C84" s="14">
-        <v>2</v>
-      </c>
-      <c r="G84" s="16" t="s">
+      <c r="H84" s="16" t="s">
         <v>340</v>
-      </c>
-      <c r="H84" s="16" t="s">
-        <v>341</v>
       </c>
       <c r="P84" s="14">
         <v>7</v>
       </c>
       <c r="Q84" s="14" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="R84" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R84" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q84,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q84))),1))</f>
@@ -8948,13 +8959,13 @@
         <v>12022</v>
       </c>
       <c r="B85" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="C85" s="14">
+        <v>2</v>
+      </c>
+      <c r="H85" s="14" t="s">
         <v>343</v>
-      </c>
-      <c r="C85" s="14">
-        <v>2</v>
-      </c>
-      <c r="H85" s="14" t="s">
-        <v>344</v>
       </c>
       <c r="R85" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R85" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q85,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q85))),1))</f>
@@ -8967,7 +8978,7 @@
         <v>20701</v>
       </c>
       <c r="W85" s="14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Y85" s="14">
         <v>1</v>
@@ -8984,13 +8995,13 @@
         <v>12023</v>
       </c>
       <c r="B86" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="C86" s="14">
+        <v>2</v>
+      </c>
+      <c r="H86" s="16" t="s">
         <v>345</v>
-      </c>
-      <c r="C86" s="14">
-        <v>2</v>
-      </c>
-      <c r="H86" s="16" t="s">
-        <v>346</v>
       </c>
       <c r="P86" s="14">
         <v>999</v>
@@ -9011,7 +9022,7 @@
         <v>20505</v>
       </c>
       <c r="W86" s="14" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Y86" s="14">
         <v>1</v>
@@ -9028,19 +9039,19 @@
         <v>12024</v>
       </c>
       <c r="B87" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="C87" s="14">
+        <v>2</v>
+      </c>
+      <c r="H87" s="16" t="s">
         <v>348</v>
       </c>
-      <c r="C87" s="14">
-        <v>2</v>
-      </c>
-      <c r="H87" s="16" t="s">
+      <c r="J87" s="16" t="s">
+        <v>1070</v>
+      </c>
+      <c r="Q87" s="14" t="s">
         <v>349</v>
-      </c>
-      <c r="J87" s="16" t="s">
-        <v>1073</v>
-      </c>
-      <c r="Q87" s="14" t="s">
-        <v>350</v>
       </c>
       <c r="R87" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R87" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q87,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q87))),1))</f>
@@ -9076,20 +9087,20 @@
         <v>12025</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C88" s="14">
         <v>2</v>
       </c>
       <c r="G88" s="16" t="s">
+        <v>350</v>
+      </c>
+      <c r="H88" s="16" t="s">
         <v>351</v>
-      </c>
-      <c r="H88" s="16" t="s">
-        <v>352</v>
       </c>
       <c r="I88" s="14"/>
       <c r="Q88" s="14" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="R88" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R88" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q88,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q88))),1))</f>
@@ -9125,23 +9136,23 @@
         <v>12026</v>
       </c>
       <c r="B89" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="C89" s="14">
+        <v>2</v>
+      </c>
+      <c r="H89" s="16" t="s">
         <v>353</v>
-      </c>
-      <c r="C89" s="14">
-        <v>2</v>
-      </c>
-      <c r="H89" s="16" t="s">
-        <v>354</v>
       </c>
       <c r="I89" s="14"/>
       <c r="J89" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="L89" s="16" t="s">
         <v>355</v>
       </c>
-      <c r="L89" s="16" t="s">
+      <c r="Q89" s="14" t="s">
         <v>356</v>
-      </c>
-      <c r="Q89" s="14" t="s">
-        <v>357</v>
       </c>
       <c r="R89" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R89" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q89,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q89))),1))</f>
@@ -9165,7 +9176,7 @@
         <v>12027</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C90" s="14">
         <v>2</v>
@@ -9174,15 +9185,15 @@
         <v>144</v>
       </c>
       <c r="H90" s="16" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="I90" s="14"/>
       <c r="J90" s="14"/>
       <c r="L90" s="16" t="s">
+        <v>359</v>
+      </c>
+      <c r="Q90" s="14" t="s">
         <v>360</v>
-      </c>
-      <c r="Q90" s="14" t="s">
-        <v>361</v>
       </c>
       <c r="R90" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R90" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q90,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q90))),1))</f>
@@ -9218,23 +9229,23 @@
         <v>12028</v>
       </c>
       <c r="B91" s="15" t="s">
+        <v>361</v>
+      </c>
+      <c r="C91" s="14">
+        <v>2</v>
+      </c>
+      <c r="E91" s="16" t="s">
         <v>362</v>
       </c>
-      <c r="C91" s="14">
-        <v>2</v>
-      </c>
-      <c r="E91" s="16" t="s">
+      <c r="H91" s="16" t="s">
         <v>363</v>
-      </c>
-      <c r="H91" s="16" t="s">
-        <v>364</v>
       </c>
       <c r="I91" s="14"/>
       <c r="J91" s="16" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q91" s="14" t="s">
         <v>365</v>
-      </c>
-      <c r="Q91" s="14" t="s">
-        <v>366</v>
       </c>
       <c r="R91" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R91" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q91,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q91))),1))</f>
@@ -9270,7 +9281,7 @@
         <v>12029</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C92" s="14">
         <v>2</v>
@@ -9279,15 +9290,15 @@
         <v>144</v>
       </c>
       <c r="H92" s="16" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="I92" s="14"/>
       <c r="J92" s="14"/>
       <c r="L92" s="16" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Q92" s="14" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="R92" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R92" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q92,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q92))),1))</f>
@@ -9323,23 +9334,23 @@
         <v>12030</v>
       </c>
       <c r="B93" s="15" t="s">
+        <v>361</v>
+      </c>
+      <c r="C93" s="14">
+        <v>2</v>
+      </c>
+      <c r="E93" s="16" t="s">
         <v>362</v>
       </c>
-      <c r="C93" s="14">
-        <v>2</v>
-      </c>
-      <c r="E93" s="16" t="s">
-        <v>363</v>
-      </c>
       <c r="H93" s="16" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I93" s="14"/>
       <c r="J93" s="16" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Q93" s="14" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="R93" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R93" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q93,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q93))),1))</f>
@@ -9375,18 +9386,18 @@
         <v>12031</v>
       </c>
       <c r="B94" s="15" t="s">
+        <v>369</v>
+      </c>
+      <c r="C94" s="14">
+        <v>2</v>
+      </c>
+      <c r="H94" s="14" t="s">
         <v>370</v>
-      </c>
-      <c r="C94" s="14">
-        <v>2</v>
-      </c>
-      <c r="H94" s="14" t="s">
-        <v>371</v>
       </c>
       <c r="I94" s="14"/>
       <c r="J94" s="14"/>
       <c r="Q94" s="14" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="R94" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R94" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q94,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q94))),1))</f>
@@ -9422,22 +9433,22 @@
         <v>12032</v>
       </c>
       <c r="B95" s="15" t="s">
+        <v>372</v>
+      </c>
+      <c r="C95" s="14">
+        <v>2</v>
+      </c>
+      <c r="G95" s="16" t="s">
+        <v>1076</v>
+      </c>
+      <c r="H95" s="22" t="s">
         <v>373</v>
       </c>
-      <c r="C95" s="14">
-        <v>2</v>
-      </c>
-      <c r="G95" s="16" t="s">
-        <v>1079</v>
-      </c>
-      <c r="H95" s="22" t="s">
+      <c r="J95" s="16" t="s">
         <v>374</v>
       </c>
-      <c r="J95" s="16" t="s">
+      <c r="N95" s="16" t="s">
         <v>375</v>
-      </c>
-      <c r="N95" s="16" t="s">
-        <v>376</v>
       </c>
       <c r="R95" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R95" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q95,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q95))),1))</f>
@@ -9467,19 +9478,19 @@
         <v>12033</v>
       </c>
       <c r="B96" s="15" t="s">
+        <v>376</v>
+      </c>
+      <c r="C96" s="14">
+        <v>2</v>
+      </c>
+      <c r="G96" s="16" t="s">
+        <v>1077</v>
+      </c>
+      <c r="H96" s="16" t="s">
         <v>377</v>
       </c>
-      <c r="C96" s="14">
-        <v>2</v>
-      </c>
-      <c r="G96" s="16" t="s">
-        <v>1080</v>
-      </c>
-      <c r="H96" s="16" t="s">
-        <v>378</v>
-      </c>
       <c r="N96" s="16" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="R96" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R96" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q96,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q96))),1))</f>
@@ -9509,16 +9520,16 @@
         <v>12034</v>
       </c>
       <c r="B97" s="15" t="s">
+        <v>378</v>
+      </c>
+      <c r="C97" s="14">
+        <v>2</v>
+      </c>
+      <c r="G97" s="16" t="s">
+        <v>1078</v>
+      </c>
+      <c r="H97" s="22" t="s">
         <v>379</v>
-      </c>
-      <c r="C97" s="14">
-        <v>2</v>
-      </c>
-      <c r="G97" s="16" t="s">
-        <v>1081</v>
-      </c>
-      <c r="H97" s="22" t="s">
-        <v>380</v>
       </c>
       <c r="R97" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R97" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q97,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q97))),1))</f>
@@ -9548,16 +9559,16 @@
         <v>12035</v>
       </c>
       <c r="B98" s="15" t="s">
+        <v>380</v>
+      </c>
+      <c r="C98" s="14">
+        <v>2</v>
+      </c>
+      <c r="H98" s="16" t="s">
         <v>381</v>
       </c>
-      <c r="C98" s="14">
-        <v>2</v>
-      </c>
-      <c r="H98" s="16" t="s">
+      <c r="L98" s="16" t="s">
         <v>382</v>
-      </c>
-      <c r="L98" s="16" t="s">
-        <v>383</v>
       </c>
       <c r="R98" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R98" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q98,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q98))),1))</f>
@@ -9576,7 +9587,7 @@
         <v>20302</v>
       </c>
       <c r="W98" s="14" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Y98" s="14">
         <v>2</v>
@@ -9593,7 +9604,7 @@
         <v>12036</v>
       </c>
       <c r="B99" s="15" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C99" s="14">
         <v>2</v>
@@ -9602,10 +9613,10 @@
         <v>85</v>
       </c>
       <c r="H99" s="16" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="L99" s="16" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="R99" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R99" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q99,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q99))),1))</f>
@@ -9641,13 +9652,13 @@
         <v>12037</v>
       </c>
       <c r="B100" s="15" t="s">
+        <v>386</v>
+      </c>
+      <c r="C100" s="14">
+        <v>2</v>
+      </c>
+      <c r="H100" s="16" t="s">
         <v>387</v>
-      </c>
-      <c r="C100" s="14">
-        <v>2</v>
-      </c>
-      <c r="H100" s="16" t="s">
-        <v>388</v>
       </c>
       <c r="R100" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R100" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q100,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q100))),1))</f>
@@ -9666,7 +9677,7 @@
         <v>20304</v>
       </c>
       <c r="W100" s="14" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="Y100" s="14">
         <v>1</v>
@@ -9683,22 +9694,22 @@
         <v>12038</v>
       </c>
       <c r="B101" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="C101" s="14">
+        <v>2</v>
+      </c>
+      <c r="E101" s="16" t="s">
         <v>390</v>
       </c>
-      <c r="C101" s="14">
-        <v>2</v>
-      </c>
-      <c r="E101" s="16" t="s">
+      <c r="G101" s="16" t="s">
         <v>391</v>
       </c>
-      <c r="G101" s="16" t="s">
+      <c r="H101" s="16" t="s">
         <v>392</v>
       </c>
-      <c r="H101" s="16" t="s">
+      <c r="J101" s="16" t="s">
         <v>393</v>
-      </c>
-      <c r="J101" s="16" t="s">
-        <v>394</v>
       </c>
       <c r="N101" s="16" t="s">
         <v>76</v>
@@ -9737,22 +9748,22 @@
         <v>12039</v>
       </c>
       <c r="B102" s="15" t="s">
+        <v>394</v>
+      </c>
+      <c r="C102" s="14">
+        <v>2</v>
+      </c>
+      <c r="E102" s="16" t="s">
         <v>395</v>
       </c>
-      <c r="C102" s="14">
-        <v>2</v>
-      </c>
-      <c r="E102" s="16" t="s">
+      <c r="H102" s="16" t="s">
         <v>396</v>
       </c>
-      <c r="H102" s="16" t="s">
+      <c r="L102" s="16" t="s">
         <v>397</v>
       </c>
-      <c r="L102" s="16" t="s">
+      <c r="Q102" s="14" t="s">
         <v>398</v>
-      </c>
-      <c r="Q102" s="14" t="s">
-        <v>399</v>
       </c>
       <c r="R102" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R102" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q102,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q102))),1))</f>
@@ -9788,19 +9799,19 @@
         <v>12040</v>
       </c>
       <c r="B103" s="15" t="s">
+        <v>399</v>
+      </c>
+      <c r="C103" s="14">
+        <v>2</v>
+      </c>
+      <c r="H103" s="16" t="s">
         <v>400</v>
       </c>
-      <c r="C103" s="14">
-        <v>2</v>
-      </c>
-      <c r="H103" s="16" t="s">
+      <c r="L103" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="L103" s="16" t="s">
+      <c r="Q103" s="14" t="s">
         <v>402</v>
-      </c>
-      <c r="Q103" s="14" t="s">
-        <v>403</v>
       </c>
       <c r="R103" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R103" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q103,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q103))),1))</f>
@@ -9836,19 +9847,19 @@
         <v>12041</v>
       </c>
       <c r="B104" s="15" t="s">
+        <v>403</v>
+      </c>
+      <c r="C104" s="14">
+        <v>2</v>
+      </c>
+      <c r="E104" s="16" t="s">
         <v>404</v>
       </c>
-      <c r="C104" s="14">
-        <v>2</v>
-      </c>
-      <c r="E104" s="16" t="s">
+      <c r="H104" s="16" t="s">
         <v>405</v>
       </c>
-      <c r="H104" s="16" t="s">
-        <v>406</v>
-      </c>
       <c r="L104" s="16" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="R104" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R104" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q104,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q104))),1))</f>
@@ -9884,16 +9895,16 @@
         <v>12042</v>
       </c>
       <c r="B105" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="C105" s="14">
+        <v>2</v>
+      </c>
+      <c r="H105" s="16" t="s">
         <v>407</v>
       </c>
-      <c r="C105" s="14">
-        <v>2</v>
-      </c>
-      <c r="H105" s="16" t="s">
+      <c r="L105" s="16" t="s">
         <v>408</v>
-      </c>
-      <c r="L105" s="16" t="s">
-        <v>409</v>
       </c>
       <c r="R105" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R105" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q105,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q105))),1))</f>
@@ -9929,22 +9940,22 @@
         <v>12043</v>
       </c>
       <c r="B106" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="C106" s="14">
+        <v>2</v>
+      </c>
+      <c r="E106" s="16" t="s">
         <v>410</v>
       </c>
-      <c r="C106" s="14">
-        <v>2</v>
-      </c>
-      <c r="E106" s="16" t="s">
+      <c r="H106" s="16" t="s">
         <v>411</v>
       </c>
-      <c r="H106" s="16" t="s">
+      <c r="J106" s="16" t="s">
         <v>412</v>
       </c>
-      <c r="J106" s="16" t="s">
-        <v>413</v>
-      </c>
       <c r="L106" s="16" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="R106" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R106" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q106,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q106))),1))</f>
@@ -9980,16 +9991,16 @@
         <v>12044</v>
       </c>
       <c r="B107" s="15" t="s">
+        <v>413</v>
+      </c>
+      <c r="C107" s="14">
+        <v>2</v>
+      </c>
+      <c r="H107" s="16" t="s">
         <v>414</v>
       </c>
-      <c r="C107" s="14">
-        <v>2</v>
-      </c>
-      <c r="H107" s="16" t="s">
+      <c r="Q107" s="14" t="s">
         <v>415</v>
-      </c>
-      <c r="Q107" s="14" t="s">
-        <v>416</v>
       </c>
       <c r="R107" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R107" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q107,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q107))),1))</f>
@@ -10025,22 +10036,22 @@
         <v>12045</v>
       </c>
       <c r="B108" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="C108" s="14">
+        <v>2</v>
+      </c>
+      <c r="H108" s="16" t="s">
+        <v>270</v>
+      </c>
+      <c r="J108" s="16" t="s">
         <v>417</v>
-      </c>
-      <c r="C108" s="14">
-        <v>2</v>
-      </c>
-      <c r="H108" s="16" t="s">
-        <v>271</v>
-      </c>
-      <c r="J108" s="16" t="s">
-        <v>418</v>
       </c>
       <c r="L108" s="16" t="s">
         <v>178</v>
       </c>
       <c r="Q108" s="14" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="R108" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R108" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q108,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q108))),1))</f>
@@ -10076,25 +10087,25 @@
         <v>12046</v>
       </c>
       <c r="B109" s="15" t="s">
+        <v>419</v>
+      </c>
+      <c r="C109" s="14">
+        <v>2</v>
+      </c>
+      <c r="E109" s="16" t="s">
         <v>420</v>
       </c>
-      <c r="C109" s="14">
-        <v>2</v>
-      </c>
-      <c r="E109" s="16" t="s">
+      <c r="H109" s="16" t="s">
         <v>421</v>
       </c>
-      <c r="H109" s="16" t="s">
+      <c r="J109" s="16" t="s">
         <v>422</v>
-      </c>
-      <c r="J109" s="16" t="s">
-        <v>423</v>
       </c>
       <c r="N109" s="16" t="s">
         <v>76</v>
       </c>
       <c r="Q109" s="14" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="R109" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R109" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q109,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q109))),1))</f>
@@ -10130,16 +10141,16 @@
         <v>12047</v>
       </c>
       <c r="B110" s="15" t="s">
+        <v>424</v>
+      </c>
+      <c r="C110" s="14">
+        <v>2</v>
+      </c>
+      <c r="H110" s="16" t="s">
         <v>425</v>
       </c>
-      <c r="C110" s="14">
-        <v>2</v>
-      </c>
-      <c r="H110" s="16" t="s">
-        <v>426</v>
-      </c>
       <c r="Q110" s="14" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="R110" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R110" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q110,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q110))),1))</f>
@@ -10178,16 +10189,16 @@
         <v>2</v>
       </c>
       <c r="E111" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="H111" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="L111" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q111" s="14" t="s">
         <v>427</v>
-      </c>
-      <c r="H111" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="L111" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="Q111" s="14" t="s">
-        <v>428</v>
       </c>
       <c r="R111" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R111" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q111,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q111))),1))</f>
@@ -10223,19 +10234,19 @@
         <v>12049</v>
       </c>
       <c r="B112" s="15" t="s">
+        <v>428</v>
+      </c>
+      <c r="C112" s="14">
+        <v>2</v>
+      </c>
+      <c r="H112" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="J112" s="16" t="s">
         <v>429</v>
       </c>
-      <c r="C112" s="14">
-        <v>2</v>
-      </c>
-      <c r="H112" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="J112" s="16" t="s">
-        <v>430</v>
-      </c>
       <c r="Q112" s="14" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="R112" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R112" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q112,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q112))),1))</f>
@@ -10271,22 +10282,22 @@
         <v>12050</v>
       </c>
       <c r="B113" s="15" t="s">
+        <v>430</v>
+      </c>
+      <c r="C113" s="14">
+        <v>2</v>
+      </c>
+      <c r="E113" s="16" t="s">
         <v>431</v>
       </c>
-      <c r="C113" s="14">
-        <v>2</v>
-      </c>
-      <c r="E113" s="16" t="s">
+      <c r="H113" s="16" t="s">
         <v>432</v>
-      </c>
-      <c r="H113" s="16" t="s">
-        <v>433</v>
       </c>
       <c r="N113" s="16" t="s">
         <v>76</v>
       </c>
       <c r="Q113" s="14" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="R113" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R113" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q113,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q113))),1))</f>
@@ -10322,16 +10333,16 @@
         <v>12051</v>
       </c>
       <c r="B114" s="15" t="s">
+        <v>434</v>
+      </c>
+      <c r="C114" s="14">
+        <v>2</v>
+      </c>
+      <c r="E114" s="16" t="s">
         <v>435</v>
       </c>
-      <c r="C114" s="14">
-        <v>2</v>
-      </c>
-      <c r="E114" s="16" t="s">
+      <c r="H114" s="16" t="s">
         <v>436</v>
-      </c>
-      <c r="H114" s="16" t="s">
-        <v>437</v>
       </c>
       <c r="I114" s="14"/>
       <c r="J114" s="14"/>
@@ -10339,7 +10350,7 @@
         <v>76</v>
       </c>
       <c r="Q114" s="14" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="R114" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R114" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q114,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q114))),1))</f>
@@ -10375,13 +10386,13 @@
         <v>12052</v>
       </c>
       <c r="B115" s="15" t="s">
+        <v>437</v>
+      </c>
+      <c r="C115" s="14">
+        <v>2</v>
+      </c>
+      <c r="H115" s="16" t="s">
         <v>438</v>
-      </c>
-      <c r="C115" s="14">
-        <v>2</v>
-      </c>
-      <c r="H115" s="16" t="s">
-        <v>439</v>
       </c>
       <c r="N115" s="16" t="s">
         <v>201</v>
@@ -10393,7 +10404,7 @@
         <v>4</v>
       </c>
       <c r="Q115" s="14" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="R115" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R115" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q115,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q115))),1))</f>
@@ -10412,7 +10423,7 @@
         <v>20307</v>
       </c>
       <c r="W115" s="14" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Y115" s="14">
         <v>2</v>
@@ -10429,21 +10440,21 @@
         <v>12053</v>
       </c>
       <c r="B116" s="15" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C116" s="14">
         <v>2</v>
       </c>
       <c r="H116" s="16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I116" s="14"/>
       <c r="J116" s="14"/>
       <c r="L116" s="16" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="N116" s="16" t="s">
-        <v>443</v>
+        <v>1099</v>
       </c>
       <c r="O116" s="14">
         <v>1</v>
@@ -10468,7 +10479,7 @@
         <v>20507</v>
       </c>
       <c r="W116" s="14" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="Y116" s="14">
         <v>1</v>
@@ -10485,18 +10496,18 @@
         <v>12054</v>
       </c>
       <c r="B117" s="15" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C117" s="14">
         <v>2</v>
       </c>
       <c r="H117" s="16" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="I117" s="14"/>
       <c r="J117" s="14"/>
       <c r="L117" s="16" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="O117" s="14">
         <v>1</v>
@@ -10505,7 +10516,7 @@
         <v>1</v>
       </c>
       <c r="Q117" s="14" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="R117" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R117" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q117,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q117))),1))</f>
@@ -10521,7 +10532,7 @@
         <v>20507</v>
       </c>
       <c r="W117" s="14" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="Y117" s="14">
         <v>2</v>
@@ -10541,12 +10552,12 @@
         <v>2</v>
       </c>
       <c r="H118" s="16" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="I118" s="14"/>
       <c r="J118" s="14"/>
       <c r="L118" s="16" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="O118" s="14">
         <v>6</v>
@@ -10555,7 +10566,7 @@
         <v>999</v>
       </c>
       <c r="Q118" s="14" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="R118" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R118" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q118,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q118))),1))</f>
@@ -10571,7 +10582,7 @@
         <v>20507</v>
       </c>
       <c r="W118" s="14" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="Y118" s="14">
         <v>1</v>
@@ -10591,10 +10602,10 @@
         <v>2</v>
       </c>
       <c r="H119" s="16" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="L119" s="16" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="N119" s="16" t="s">
         <v>201</v>
@@ -10606,7 +10617,7 @@
         <v>8</v>
       </c>
       <c r="Q119" s="14" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="R119" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R119" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q119,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q119))),1))</f>
@@ -10622,7 +10633,7 @@
         <v>20507</v>
       </c>
       <c r="W119" s="14" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="Y119" s="14">
         <v>1</v>
@@ -10639,21 +10650,21 @@
         <v>12057</v>
       </c>
       <c r="B120" s="15" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C120" s="14">
         <v>2</v>
       </c>
       <c r="H120" s="14" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="I120" s="14"/>
       <c r="J120" s="14"/>
       <c r="L120" s="16" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="N120" s="16" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="P120" s="14">
         <v>999</v>
@@ -10686,16 +10697,16 @@
         <v>12058</v>
       </c>
       <c r="B121" s="15" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C121" s="14">
         <v>2</v>
       </c>
       <c r="G121" s="16" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="H121" s="16" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="P121" s="14">
         <v>999</v>
@@ -10728,17 +10739,17 @@
         <v>12059</v>
       </c>
       <c r="B122" s="15" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C122" s="14">
         <v>2</v>
       </c>
       <c r="H122" s="16" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="I122" s="14"/>
       <c r="J122" s="14" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="P122" s="14">
         <v>999</v>
@@ -10771,21 +10782,21 @@
         <v>12060</v>
       </c>
       <c r="B123" s="15" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C123" s="14">
         <v>2</v>
       </c>
       <c r="H123" s="16" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="I123" s="14"/>
       <c r="J123" s="14"/>
       <c r="N123" s="16" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="Q123" s="14" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="R123" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R123" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q123,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q123))),1))</f>
@@ -10821,19 +10832,19 @@
         <v>12061</v>
       </c>
       <c r="B124" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="C124" s="14">
+        <v>2</v>
+      </c>
+      <c r="H124" s="16" t="s">
         <v>348</v>
       </c>
-      <c r="C124" s="14">
-        <v>2</v>
-      </c>
-      <c r="H124" s="16" t="s">
+      <c r="J124" s="16" t="s">
+        <v>464</v>
+      </c>
+      <c r="Q124" s="14" t="s">
         <v>349</v>
-      </c>
-      <c r="J124" s="16" t="s">
-        <v>466</v>
-      </c>
-      <c r="Q124" s="14" t="s">
-        <v>350</v>
       </c>
       <c r="R124" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R124" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q124,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q124))),1))</f>
@@ -10863,20 +10874,20 @@
         <v>12062</v>
       </c>
       <c r="B125" s="15" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C125" s="14">
         <v>2</v>
       </c>
       <c r="G125" s="16" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="H125" s="16" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="I125" s="14"/>
       <c r="Q125" s="14" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="R125" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R125" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q125,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q125))),1))</f>
@@ -10906,23 +10917,23 @@
         <v>12063</v>
       </c>
       <c r="B126" s="15" t="s">
+        <v>361</v>
+      </c>
+      <c r="C126" s="14">
+        <v>2</v>
+      </c>
+      <c r="G126" s="16" t="s">
         <v>362</v>
       </c>
-      <c r="C126" s="14">
-        <v>2</v>
-      </c>
-      <c r="G126" s="16" t="s">
+      <c r="H126" s="16" t="s">
         <v>363</v>
-      </c>
-      <c r="H126" s="16" t="s">
-        <v>364</v>
       </c>
       <c r="I126" s="14"/>
       <c r="J126" s="16" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q126" s="14" t="s">
         <v>365</v>
-      </c>
-      <c r="Q126" s="14" t="s">
-        <v>366</v>
       </c>
       <c r="R126" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R126" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q126,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q126))),1))</f>
@@ -10952,23 +10963,23 @@
         <v>12064</v>
       </c>
       <c r="B127" s="15" t="s">
+        <v>361</v>
+      </c>
+      <c r="C127" s="14">
+        <v>2</v>
+      </c>
+      <c r="G127" s="16" t="s">
         <v>362</v>
       </c>
-      <c r="C127" s="14">
-        <v>2</v>
-      </c>
-      <c r="G127" s="16" t="s">
-        <v>363</v>
-      </c>
       <c r="H127" s="16" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I127" s="14"/>
       <c r="J127" s="16" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Q127" s="14" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="R127" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R127" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q127,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q127))),1))</f>
@@ -10998,27 +11009,27 @@
         <v>12065</v>
       </c>
       <c r="B128" s="15" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C128" s="14">
         <v>2</v>
       </c>
       <c r="H128" s="16" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="I128" s="14"/>
       <c r="J128" s="14"/>
       <c r="L128" s="16" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="N128" s="16" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="O128" s="14">
         <v>3</v>
       </c>
       <c r="Q128" s="14" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="R128" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R128" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q128,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q128))),1))</f>
@@ -11037,7 +11048,7 @@
         <v>20501</v>
       </c>
       <c r="W128" s="14" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="Y128" s="14">
         <v>2</v>
@@ -11054,26 +11065,26 @@
         <v>12066</v>
       </c>
       <c r="B129" s="15" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C129" s="14">
         <v>2</v>
       </c>
       <c r="E129" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H129" s="16" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I129" s="14"/>
       <c r="J129" s="14" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="N129" s="16" t="s">
         <v>76</v>
       </c>
       <c r="Q129" s="14" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="R129" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R129" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q129,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q129))),1))</f>
@@ -11092,7 +11103,7 @@
         <v>20405</v>
       </c>
       <c r="W129" s="14" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="Y129" s="14">
         <v>1</v>
@@ -11109,27 +11120,27 @@
         <v>12067</v>
       </c>
       <c r="B130" s="15" t="s">
+        <v>476</v>
+      </c>
+      <c r="C130" s="14">
+        <v>2</v>
+      </c>
+      <c r="E130" s="16" t="s">
+        <v>477</v>
+      </c>
+      <c r="G130" s="16" t="s">
         <v>478</v>
       </c>
-      <c r="C130" s="14">
-        <v>2</v>
-      </c>
-      <c r="E130" s="16" t="s">
+      <c r="H130" s="16" t="s">
         <v>479</v>
-      </c>
-      <c r="G130" s="16" t="s">
-        <v>480</v>
-      </c>
-      <c r="H130" s="16" t="s">
-        <v>481</v>
       </c>
       <c r="I130" s="14"/>
       <c r="J130" s="14"/>
       <c r="L130" s="16" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="N130" s="16" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="R130" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R130" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q130,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q130))),1))</f>
@@ -11148,7 +11159,7 @@
         <v>20503</v>
       </c>
       <c r="W130" s="14" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="Y130" s="14">
         <v>1</v>
@@ -11165,16 +11176,16 @@
         <v>12068</v>
       </c>
       <c r="B131" s="15" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C131" s="14">
         <v>2</v>
       </c>
       <c r="G131" s="16" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="H131" s="16" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="I131" s="14"/>
       <c r="J131" s="14"/>
@@ -11195,7 +11206,7 @@
         <v>20503</v>
       </c>
       <c r="W131" s="14" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="Y131" s="14">
         <v>2</v>
@@ -11212,23 +11223,23 @@
         <v>12069</v>
       </c>
       <c r="B132" s="15" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C132" s="14">
         <v>2</v>
       </c>
       <c r="E132" s="16" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="H132" s="16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I132" s="14"/>
       <c r="J132" s="14" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="Q132" s="14" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="R132" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R132" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q132,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q132))),1))</f>
@@ -11247,7 +11258,7 @@
         <v>20503</v>
       </c>
       <c r="W132" s="14" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="Y132" s="14">
         <v>2</v>
@@ -11264,7 +11275,7 @@
         <v>12070</v>
       </c>
       <c r="B133" s="20" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C133" s="14">
         <v>2</v>
@@ -11282,7 +11293,7 @@
         <v>0</v>
       </c>
       <c r="Q133" s="14" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="R133" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R133" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q133,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q133))),1))</f>
@@ -11312,19 +11323,19 @@
         <v>12071</v>
       </c>
       <c r="B134" s="15" t="s">
+        <v>490</v>
+      </c>
+      <c r="C134" s="14">
+        <v>2</v>
+      </c>
+      <c r="E134" s="16" t="s">
+        <v>491</v>
+      </c>
+      <c r="H134" s="16" t="s">
         <v>492</v>
       </c>
-      <c r="C134" s="14">
-        <v>2</v>
-      </c>
-      <c r="E134" s="16" t="s">
+      <c r="N134" s="16" t="s">
         <v>493</v>
-      </c>
-      <c r="H134" s="16" t="s">
-        <v>494</v>
-      </c>
-      <c r="N134" s="16" t="s">
-        <v>495</v>
       </c>
       <c r="R134" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R134" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q134,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q134))),1))</f>
@@ -11343,7 +11354,7 @@
         <v>20409</v>
       </c>
       <c r="W134" s="14" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="Y134" s="14">
         <v>1</v>
@@ -11360,13 +11371,13 @@
         <v>12072</v>
       </c>
       <c r="B135" s="15" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C135" s="14">
         <v>2</v>
       </c>
       <c r="H135" s="16" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="I135" s="14"/>
       <c r="J135" s="14"/>
@@ -11395,7 +11406,7 @@
         <v>2</v>
       </c>
       <c r="H136" s="14" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="I136" s="14"/>
       <c r="J136" s="14"/>
@@ -11421,20 +11432,20 @@
         <v>12074</v>
       </c>
       <c r="B137" s="15" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C137" s="14">
         <v>2</v>
       </c>
       <c r="H137" s="16" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="I137" s="14"/>
       <c r="J137" s="14" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="N137" s="16" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="R137" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R137" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q137,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q137))),1))</f>
@@ -11458,20 +11469,20 @@
         <v>12075</v>
       </c>
       <c r="B138" s="15" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C138" s="14">
         <v>2</v>
       </c>
       <c r="H138" s="16" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="I138" s="14"/>
       <c r="J138" s="14" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="N138" s="16" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="R138" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R138" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q138,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q138))),1))</f>
@@ -11498,15 +11509,15 @@
         <v>2</v>
       </c>
       <c r="H139" s="16" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="I139" s="14"/>
       <c r="J139" s="14"/>
       <c r="L139" s="14" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="Q139" s="14" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="R139" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R139" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q139,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q139))),1))</f>
@@ -11545,24 +11556,24 @@
         <v>2</v>
       </c>
       <c r="E140" s="16" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="H140" s="16" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="I140" s="14"/>
       <c r="J140" s="14"/>
       <c r="L140" s="16" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="N140" s="16" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="P140" s="14">
         <v>3</v>
       </c>
       <c r="Q140" s="14" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="R140" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R140" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q140,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q140))),1))</f>
@@ -11581,7 +11592,7 @@
         <v>20401</v>
       </c>
       <c r="W140" s="14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Y140" s="14">
         <v>2</v>
@@ -11601,10 +11612,10 @@
         <v>2</v>
       </c>
       <c r="E141" s="16" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H141" s="14" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="I141" s="14"/>
       <c r="J141" s="14"/>
@@ -11615,7 +11626,7 @@
         <v>1</v>
       </c>
       <c r="Q141" s="14" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="R141" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R141" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q141,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q141))),1))</f>
@@ -11634,7 +11645,7 @@
         <v>20401</v>
       </c>
       <c r="W141" s="14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Y141" s="14">
         <v>2</v>
@@ -11648,15 +11659,15 @@
     </row>
     <row r="142" spans="1:27" ht="33" x14ac:dyDescent="0.15">
       <c r="H142" s="16" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="I142" s="14"/>
       <c r="J142" s="14"/>
       <c r="L142" s="16" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="N142" s="16" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="O142" s="14">
         <v>7</v>
@@ -11674,7 +11685,7 @@
         <v>20507</v>
       </c>
       <c r="W142" s="14" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="Y142" s="14">
         <v>7</v>
@@ -11696,18 +11707,18 @@
         <v>13001</v>
       </c>
       <c r="B144" s="20" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C144" s="14">
         <v>3</v>
       </c>
       <c r="H144" s="14" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="I144" s="14"/>
       <c r="J144" s="14"/>
       <c r="L144" s="16" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="O144" s="14">
         <v>1</v>
@@ -11716,7 +11727,7 @@
         <v>2</v>
       </c>
       <c r="Q144" s="14" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="R144" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R144" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q144,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q144))),1))</f>
@@ -11752,18 +11763,18 @@
         <v>13002</v>
       </c>
       <c r="B145" s="20" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C145" s="14">
         <v>3</v>
       </c>
       <c r="H145" s="14" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="I145" s="14"/>
       <c r="J145" s="14"/>
       <c r="L145" s="16" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="O145" s="14">
         <v>1</v>
@@ -11772,7 +11783,7 @@
         <v>4</v>
       </c>
       <c r="Q145" s="14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="R145" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R145" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q145,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q145))),1))</f>
@@ -11808,18 +11819,18 @@
         <v>13003</v>
       </c>
       <c r="B146" s="20" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C146" s="14">
         <v>3</v>
       </c>
       <c r="H146" s="14" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="I146" s="14"/>
       <c r="J146" s="14"/>
       <c r="L146" s="16" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="O146" s="14">
         <v>1</v>
@@ -11828,7 +11839,7 @@
         <v>6</v>
       </c>
       <c r="Q146" s="14" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="R146" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R146" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q146,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q146))),1))</f>
@@ -11864,21 +11875,21 @@
         <v>13004</v>
       </c>
       <c r="B147" s="20" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C147" s="14">
         <v>3</v>
       </c>
       <c r="E147" s="16" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H147" s="14" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="I147" s="14"/>
       <c r="J147" s="14"/>
       <c r="L147" s="16" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="O147" s="14">
         <v>1</v>
@@ -11887,7 +11898,7 @@
         <v>6</v>
       </c>
       <c r="Q147" s="14" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="R147" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R147" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q147,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q147))),1))</f>
@@ -11923,21 +11934,21 @@
         <v>13005</v>
       </c>
       <c r="B148" s="20" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C148" s="14">
         <v>3</v>
       </c>
       <c r="E148" s="16" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="H148" s="14" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="I148" s="14"/>
       <c r="J148" s="14"/>
       <c r="L148" s="16" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="O148" s="14">
         <v>1</v>
@@ -11946,7 +11957,7 @@
         <v>5</v>
       </c>
       <c r="Q148" s="14" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="R148" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R148" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q148,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q148))),1))</f>
@@ -11982,21 +11993,21 @@
         <v>13006</v>
       </c>
       <c r="B149" s="20" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C149" s="14">
         <v>3</v>
       </c>
       <c r="E149" s="16" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="H149" s="14" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="I149" s="14"/>
       <c r="J149" s="14"/>
       <c r="L149" s="16" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="O149" s="14">
         <v>1</v>
@@ -12005,7 +12016,7 @@
         <v>4</v>
       </c>
       <c r="Q149" s="14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="R149" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R149" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q149,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q149))),1))</f>
@@ -12041,23 +12052,23 @@
         <v>13007</v>
       </c>
       <c r="B150" s="15" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C150" s="14">
         <v>3</v>
       </c>
       <c r="E150" s="14" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F150" s="14"/>
       <c r="G150" s="14"/>
       <c r="H150" s="14" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="I150" s="14"/>
       <c r="J150" s="14"/>
       <c r="L150" s="16" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="O150" s="14">
         <v>5</v>
@@ -12066,7 +12077,7 @@
         <v>4</v>
       </c>
       <c r="Q150" s="14" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="R150" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R150" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q150,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q150))),1))</f>
@@ -12102,19 +12113,19 @@
         <v>13008</v>
       </c>
       <c r="B151" s="20" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C151" s="14">
         <v>3</v>
       </c>
       <c r="E151" s="16" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="G151" s="16" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="H151" s="14" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="I151" s="14"/>
       <c r="J151" s="14"/>
@@ -12128,7 +12139,7 @@
         <v>4</v>
       </c>
       <c r="Q151" s="14" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="R151" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R151" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q151,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q151))),1))</f>
@@ -12164,18 +12175,18 @@
         <v>13009</v>
       </c>
       <c r="B152" s="20" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C152" s="14">
         <v>3</v>
       </c>
       <c r="H152" s="14" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="I152" s="14"/>
       <c r="J152" s="14"/>
       <c r="L152" s="16" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="O152" s="14">
         <v>1</v>
@@ -12184,7 +12195,7 @@
         <v>4</v>
       </c>
       <c r="Q152" s="14" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="R152" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R152" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q152,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q152))),1))</f>
@@ -12220,18 +12231,18 @@
         <v>13010</v>
       </c>
       <c r="B153" s="20" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C153" s="14">
         <v>3</v>
       </c>
       <c r="H153" s="14" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="I153" s="14"/>
       <c r="J153" s="14"/>
       <c r="L153" s="16" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="O153" s="14">
         <v>1</v>
@@ -12240,7 +12251,7 @@
         <v>5</v>
       </c>
       <c r="Q153" s="14" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="R153" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R153" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q153,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q153))),1))</f>
@@ -12276,19 +12287,19 @@
         <v>13011</v>
       </c>
       <c r="B154" s="15" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C154" s="14">
         <v>3</v>
       </c>
       <c r="E154" s="16" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="G154" s="16" t="s">
         <v>169</v>
       </c>
       <c r="H154" s="14" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="I154" s="14"/>
       <c r="J154" s="14"/>
@@ -12299,7 +12310,7 @@
         <v>6</v>
       </c>
       <c r="Q154" s="14" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="R154" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R154" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q154,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q154))),1))</f>
@@ -12318,7 +12329,7 @@
         <v>20401</v>
       </c>
       <c r="W154" s="14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Y154" s="14">
         <v>1</v>
@@ -12335,16 +12346,16 @@
         <v>13012</v>
       </c>
       <c r="B155" s="15" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C155" s="14">
         <v>3</v>
       </c>
       <c r="H155" s="16" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="L155" s="16" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="O155" s="14">
         <v>1</v>
@@ -12386,18 +12397,18 @@
         <v>13013</v>
       </c>
       <c r="B156" s="20" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C156" s="14">
         <v>3</v>
       </c>
       <c r="E156" s="14" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="F156" s="14"/>
       <c r="G156" s="14"/>
       <c r="H156" s="16" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="N156" s="16" t="s">
         <v>76</v>
@@ -12409,7 +12420,7 @@
         <v>6</v>
       </c>
       <c r="Q156" s="14" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="R156" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R156" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q156,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q156))),1))</f>
@@ -12445,18 +12456,18 @@
         <v>13014</v>
       </c>
       <c r="B157" s="20" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C157" s="14">
         <v>3</v>
       </c>
       <c r="E157" s="14" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="F157" s="14"/>
       <c r="G157" s="14"/>
       <c r="H157" s="14" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="I157" s="14"/>
       <c r="J157" s="14"/>
@@ -12497,13 +12508,13 @@
         <v>13015</v>
       </c>
       <c r="B158" s="20" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C158" s="14">
         <v>3</v>
       </c>
       <c r="H158" s="16" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="P158" s="14">
         <v>14</v>
@@ -12525,7 +12536,7 @@
         <v>20504</v>
       </c>
       <c r="W158" s="14" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="Y158" s="14">
         <v>1</v>
@@ -12542,7 +12553,7 @@
         <v>13016</v>
       </c>
       <c r="B159" s="20" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C159" s="14">
         <v>3</v>
@@ -12560,7 +12571,7 @@
         <v>0</v>
       </c>
       <c r="Q159" s="14" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="R159" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R159" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q159,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q159))),1))</f>
@@ -12590,13 +12601,13 @@
         <v>13017</v>
       </c>
       <c r="B160" s="20" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C160" s="14">
         <v>3</v>
       </c>
       <c r="H160" s="14" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="I160" s="14"/>
       <c r="J160" s="14"/>
@@ -12614,7 +12625,7 @@
         <v>20401</v>
       </c>
       <c r="W160" s="14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Y160" s="14">
         <v>1</v>
@@ -12631,13 +12642,13 @@
         <v>13018</v>
       </c>
       <c r="B161" s="20" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C161" s="14">
         <v>3</v>
       </c>
       <c r="H161" s="16" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="L161" s="16" t="s">
         <v>195</v>
@@ -12659,7 +12670,7 @@
         <v>20402</v>
       </c>
       <c r="W161" s="14" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="Y161" s="14">
         <v>1</v>
@@ -12676,13 +12687,13 @@
         <v>13019</v>
       </c>
       <c r="B162" s="15" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C162" s="14">
         <v>3</v>
       </c>
       <c r="H162" s="16" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="O162" s="14">
         <v>5</v>
@@ -12698,7 +12709,7 @@
         <v>20402</v>
       </c>
       <c r="W162" s="14" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="Y162" s="14">
         <v>1</v>
@@ -12715,16 +12726,16 @@
         <v>13020</v>
       </c>
       <c r="B163" s="15" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C163" s="14">
         <v>3</v>
       </c>
       <c r="H163" s="16" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="J163" s="16" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="R163" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R163" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q163,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q163))),1))</f>
@@ -12737,7 +12748,7 @@
         <v>20601</v>
       </c>
       <c r="W163" s="14" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="Y163" s="14">
         <v>1</v>
@@ -12754,19 +12765,19 @@
         <v>13021</v>
       </c>
       <c r="B164" s="20" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C164" s="14">
         <v>3</v>
       </c>
       <c r="G164" s="16" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="H164" s="16" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="N164" s="16" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="R164" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R164" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q164,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q164))),1))</f>
@@ -12799,16 +12810,16 @@
         <v>13022</v>
       </c>
       <c r="B165" s="15" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C165" s="14">
         <v>3</v>
       </c>
       <c r="H165" s="16" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="L165" s="16" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="Q165" s="14" t="s">
         <v>56</v>
@@ -12844,7 +12855,7 @@
         <v>13023</v>
       </c>
       <c r="B166" s="15" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C166" s="14">
         <v>3</v>
@@ -12871,18 +12882,18 @@
         <v>13024</v>
       </c>
       <c r="B167" s="20" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C167" s="14">
         <v>3</v>
       </c>
       <c r="H167" s="14" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="I167" s="14"/>
       <c r="J167" s="14"/>
       <c r="L167" s="16" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="O167" s="14">
         <v>1</v>
@@ -12918,20 +12929,20 @@
         <v>13025</v>
       </c>
       <c r="B168" s="15" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C168" s="14">
         <v>3</v>
       </c>
       <c r="G168" s="14" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="H168" s="14" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="I168" s="14"/>
       <c r="L168" s="16" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="R168" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R168" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q168,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q168))),1))</f>
@@ -12947,7 +12958,7 @@
         <v>20506</v>
       </c>
       <c r="W168" s="14" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="Y168" s="14">
         <v>1</v>
@@ -12964,13 +12975,13 @@
         <v>13026</v>
       </c>
       <c r="B169" s="15" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C169" s="14">
         <v>3</v>
       </c>
       <c r="E169" s="16" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="R169" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R169" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q169,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q169))),1))</f>
@@ -12983,7 +12994,7 @@
         <v>20506</v>
       </c>
       <c r="W169" s="14" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="Y169" s="14">
         <v>1</v>
@@ -13000,22 +13011,22 @@
         <v>13027</v>
       </c>
       <c r="B170" s="20" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C170" s="14">
         <v>3</v>
       </c>
       <c r="H170" s="16" t="s">
+        <v>584</v>
+      </c>
+      <c r="L170" s="16" t="s">
+        <v>450</v>
+      </c>
+      <c r="N170" s="16" t="s">
+        <v>585</v>
+      </c>
+      <c r="Q170" s="14" t="s">
         <v>586</v>
-      </c>
-      <c r="L170" s="16" t="s">
-        <v>452</v>
-      </c>
-      <c r="N170" s="16" t="s">
-        <v>587</v>
-      </c>
-      <c r="Q170" s="14" t="s">
-        <v>588</v>
       </c>
       <c r="R170" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R170" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q170,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q170))),1))</f>
@@ -13048,22 +13059,22 @@
         <v>13028</v>
       </c>
       <c r="B171" s="15" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C171" s="14">
         <v>3</v>
       </c>
       <c r="E171" s="16" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="H171" s="16" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="L171" s="16" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="Q171" s="14" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="R171" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R171" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q171,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q171))),1))</f>
@@ -13096,24 +13107,24 @@
         <v>13029</v>
       </c>
       <c r="B172" s="20" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C172" s="14">
         <v>3</v>
       </c>
       <c r="H172" s="14" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="I172" s="14"/>
       <c r="J172" s="14"/>
       <c r="L172" s="16" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="P172" s="14">
         <v>3</v>
       </c>
       <c r="Q172" s="14" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="R172" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R172" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q172,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q172))),1))</f>
@@ -13146,22 +13157,22 @@
         <v>13030</v>
       </c>
       <c r="B173" s="20" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C173" s="14">
         <v>3</v>
       </c>
       <c r="H173" s="16" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="L173" s="16" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="P173" s="14">
         <v>3</v>
       </c>
       <c r="Q173" s="14" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="R173" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R173" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q173,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q173))),1))</f>
@@ -13194,25 +13205,25 @@
         <v>13031</v>
       </c>
       <c r="B174" s="20" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C174" s="14">
         <v>3</v>
       </c>
       <c r="E174" s="16" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="H174" s="16" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="L174" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="N174" s="16" t="s">
         <v>76</v>
       </c>
       <c r="Q174" s="14" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="R174" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R174" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q174,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q174))),1))</f>
@@ -13245,16 +13256,16 @@
         <v>13032</v>
       </c>
       <c r="B175" s="20" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C175" s="14">
         <v>3</v>
       </c>
       <c r="E175" s="16" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="H175" s="14" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="I175" s="14"/>
       <c r="J175" s="14"/>
@@ -13295,19 +13306,19 @@
         <v>13033</v>
       </c>
       <c r="B176" s="20" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C176" s="14">
         <v>3</v>
       </c>
       <c r="H176" s="16" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="L176" s="16" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="Q176" s="14" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="R176" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R176" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q176,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q176))),1))</f>
@@ -13343,13 +13354,13 @@
         <v>3</v>
       </c>
       <c r="H177" s="16" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="L177" s="16" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="Q177" s="14" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="R177" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R177" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q177,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q177))),1))</f>
@@ -13362,7 +13373,7 @@
         <v>20401</v>
       </c>
       <c r="W177" s="14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Y177" s="14">
         <v>1</v>
@@ -13382,13 +13393,13 @@
         <v>3</v>
       </c>
       <c r="E178" s="16" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="H178" s="14" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="J178" s="16" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="R178" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R178" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q178,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q178))),1))</f>
@@ -13401,7 +13412,7 @@
         <v>20505</v>
       </c>
       <c r="W178" s="14" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Y178" s="14">
         <v>1</v>
@@ -13418,16 +13429,16 @@
         <v>13036</v>
       </c>
       <c r="B179" s="15" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C179" s="14">
         <v>3</v>
       </c>
       <c r="H179" s="14" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="Q179" s="14" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="R179" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R179" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q179,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q179))),1))</f>
@@ -13443,7 +13454,7 @@
         <v>20701</v>
       </c>
       <c r="W179" s="14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Y179" s="14">
         <v>1</v>
@@ -13463,10 +13474,10 @@
         <v>3</v>
       </c>
       <c r="E180" s="16" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="H180" s="14" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="R180" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R180" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q180,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q180))),1))</f>
@@ -13479,7 +13490,7 @@
         <v>20505</v>
       </c>
       <c r="W180" s="14" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Y180" s="14">
         <v>1</v>
@@ -13496,22 +13507,22 @@
         <v>13038</v>
       </c>
       <c r="B181" s="15" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C181" s="14">
         <v>3</v>
       </c>
       <c r="H181" s="14" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="J181" s="16" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="P181" s="14">
         <v>999</v>
       </c>
       <c r="Q181" s="14" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="R181" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R181" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q181,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q181))),1))</f>
@@ -13544,19 +13555,19 @@
         <v>13039</v>
       </c>
       <c r="B182" s="15" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C182" s="14">
         <v>3</v>
       </c>
       <c r="G182" s="16" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="H182" s="14" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="N182" s="16" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="R182" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R182" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q182,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q182))),1))</f>
@@ -13589,22 +13600,22 @@
         <v>13040</v>
       </c>
       <c r="B183" s="15" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C183" s="14">
         <v>3</v>
       </c>
       <c r="G183" s="16" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="H183" s="14" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="L183" s="16" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="N183" s="16" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="R183" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R183" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q183,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q183))),1))</f>
@@ -13617,7 +13628,7 @@
         <v>20504</v>
       </c>
       <c r="W183" s="14" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="Y183" s="14">
         <v>1</v>
@@ -13634,25 +13645,25 @@
         <v>13041</v>
       </c>
       <c r="B184" s="15" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C184" s="14">
         <v>3</v>
       </c>
       <c r="H184" s="14" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="L184" s="16" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="N184" s="16" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="P184" s="14">
         <v>7</v>
       </c>
       <c r="Q184" s="14" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="R184" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R184" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q184,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q184))),1))</f>
@@ -13685,22 +13696,22 @@
         <v>13042</v>
       </c>
       <c r="B185" s="15" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C185" s="14">
         <v>3</v>
       </c>
       <c r="H185" s="14" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="N185" s="16" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="P185" s="14">
         <v>7</v>
       </c>
       <c r="Q185" s="14" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="R185" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R185" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q185,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q185))),1))</f>
@@ -13733,22 +13744,22 @@
         <v>13043</v>
       </c>
       <c r="B186" s="15" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C186" s="14">
         <v>3</v>
       </c>
       <c r="H186" s="14" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="J186" s="16" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="P186" s="14">
         <v>999</v>
       </c>
       <c r="Q186" s="14" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="R186" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R186" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q186,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q186))),1))</f>
@@ -13781,22 +13792,22 @@
         <v>13044</v>
       </c>
       <c r="B187" s="15" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C187" s="14">
         <v>3</v>
       </c>
       <c r="H187" s="14" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="J187" s="16" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="P187" s="14">
         <v>999</v>
       </c>
       <c r="Q187" s="14" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="R187" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R187" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q187,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q187))),1))</f>
@@ -13829,22 +13840,22 @@
         <v>13045</v>
       </c>
       <c r="B188" s="15" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C188" s="14">
         <v>3</v>
       </c>
       <c r="H188" s="14" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="J188" s="16" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="P188" s="14">
         <v>999</v>
       </c>
       <c r="Q188" s="14" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="R188" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R188" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q188,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q188))),1))</f>
@@ -13877,22 +13888,22 @@
         <v>13046</v>
       </c>
       <c r="B189" s="20" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C189" s="14">
         <v>3</v>
       </c>
       <c r="G189" s="16" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="H189" s="14" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="L189" s="16" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="N189" s="16" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="O189" s="14">
         <v>2</v>
@@ -13911,7 +13922,7 @@
         <v>20701</v>
       </c>
       <c r="W189" s="14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Y189" s="14">
         <v>1</v>
@@ -13928,19 +13939,19 @@
         <v>13047</v>
       </c>
       <c r="B190" s="15" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C190" s="14">
         <v>3</v>
       </c>
       <c r="H190" s="14" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="J190" s="16" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="Q190" s="14" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="R190" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R190" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q190,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q190))),1))</f>
@@ -13973,25 +13984,25 @@
         <v>13048</v>
       </c>
       <c r="B191" s="15" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C191" s="14">
         <v>3</v>
       </c>
       <c r="E191" s="16" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="H191" s="16" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="L191" s="16" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="N191" s="16" t="s">
         <v>76</v>
       </c>
       <c r="Q191" s="14" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="R191" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R191" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q191,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q191))),1))</f>
@@ -14024,16 +14035,16 @@
         <v>13049</v>
       </c>
       <c r="B192" s="15" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C192" s="14">
         <v>3</v>
       </c>
       <c r="H192" s="16" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="L192" s="16" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="O192" s="14">
         <v>2</v>
@@ -14042,7 +14053,7 @@
         <v>12</v>
       </c>
       <c r="Q192" s="14" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="R192" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R192" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q192,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q192))),1))</f>
@@ -14075,16 +14086,16 @@
         <v>13050</v>
       </c>
       <c r="B193" s="15" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C193" s="14">
         <v>3</v>
       </c>
       <c r="H193" s="16" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L193" s="16" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="O193" s="14">
         <v>2</v>
@@ -14093,7 +14104,7 @@
         <v>6</v>
       </c>
       <c r="Q193" s="14" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="R193" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R193" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q193,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q193))),1))</f>
@@ -14109,7 +14120,7 @@
         <v>20401</v>
       </c>
       <c r="W193" s="14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Y193" s="14">
         <v>1</v>
@@ -14126,16 +14137,16 @@
         <v>13051</v>
       </c>
       <c r="B194" s="15" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C194" s="14">
         <v>3</v>
       </c>
       <c r="H194" s="16" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="L194" s="16" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="R194" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R194" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q194,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q194))),1))</f>
@@ -14148,7 +14159,7 @@
         <v>20401</v>
       </c>
       <c r="W194" s="14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Y194" s="14">
         <v>1</v>
@@ -14165,19 +14176,19 @@
         <v>13052</v>
       </c>
       <c r="B195" s="15" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C195" s="14">
         <v>3</v>
       </c>
       <c r="E195" s="16" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="H195" s="16" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="L195" s="24" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="Q195" s="1" t="s">
         <v>56</v>
@@ -14216,19 +14227,19 @@
         <v>13053</v>
       </c>
       <c r="B196" s="15" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C196" s="14">
         <v>3</v>
       </c>
       <c r="H196" s="16" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="L196" s="16" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="Q196" s="14" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="R196" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R196" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q196,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q196))),1))</f>
@@ -14264,19 +14275,19 @@
         <v>13054</v>
       </c>
       <c r="B197" s="15" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C197" s="14">
         <v>3</v>
       </c>
       <c r="H197" s="16" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="L197" s="16" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="Q197" s="14" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="R197" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R197" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q197,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q197))),1))</f>
@@ -14312,22 +14323,22 @@
         <v>13055</v>
       </c>
       <c r="B198" s="15" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C198" s="14">
         <v>3</v>
       </c>
       <c r="E198" s="16" t="s">
+        <v>658</v>
+      </c>
+      <c r="H198" s="16" t="s">
+        <v>659</v>
+      </c>
+      <c r="L198" s="16" t="s">
         <v>660</v>
       </c>
-      <c r="H198" s="16" t="s">
-        <v>661</v>
-      </c>
-      <c r="L198" s="16" t="s">
-        <v>662</v>
-      </c>
       <c r="Q198" s="14" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="R198" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R198" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q198,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q198))),1))</f>
@@ -14363,19 +14374,19 @@
         <v>13056</v>
       </c>
       <c r="B199" s="15" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C199" s="14">
         <v>3</v>
       </c>
       <c r="G199" s="16" t="s">
+        <v>662</v>
+      </c>
+      <c r="H199" s="16" t="s">
+        <v>663</v>
+      </c>
+      <c r="Q199" s="14" t="s">
         <v>664</v>
-      </c>
-      <c r="H199" s="16" t="s">
-        <v>665</v>
-      </c>
-      <c r="Q199" s="14" t="s">
-        <v>666</v>
       </c>
       <c r="R199" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R199" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q199,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q199))),1))</f>
@@ -14411,16 +14422,16 @@
         <v>13057</v>
       </c>
       <c r="B200" s="15" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C200" s="14">
         <v>3</v>
       </c>
       <c r="E200" s="16" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="H200" s="16" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="R200" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R200" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q200,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q200))),1))</f>
@@ -14450,16 +14461,16 @@
         <v>13058</v>
       </c>
       <c r="B201" s="15" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C201" s="14">
         <v>3</v>
       </c>
       <c r="H201" s="16" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="L201" s="16" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="O201" s="16">
         <v>800065</v>
@@ -14468,7 +14479,7 @@
         <v>12</v>
       </c>
       <c r="Q201" s="14" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="R201" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R201" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q201,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q201))),1))</f>
@@ -14487,7 +14498,7 @@
         <v>20204</v>
       </c>
       <c r="W201" s="14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Y201" s="14">
         <v>1</v>
@@ -14504,19 +14515,19 @@
         <v>13059</v>
       </c>
       <c r="B202" s="15" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C202" s="14">
         <v>3</v>
       </c>
       <c r="E202" s="16" t="s">
+        <v>672</v>
+      </c>
+      <c r="H202" s="16" t="s">
+        <v>673</v>
+      </c>
+      <c r="J202" s="16" t="s">
         <v>674</v>
-      </c>
-      <c r="H202" s="16" t="s">
-        <v>675</v>
-      </c>
-      <c r="J202" s="16" t="s">
-        <v>676</v>
       </c>
       <c r="N202" s="16" t="s">
         <v>76</v>
@@ -14525,7 +14536,7 @@
         <v>800066</v>
       </c>
       <c r="Q202" s="14" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="R202" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R202" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q202,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q202))),1))</f>
@@ -14544,7 +14555,7 @@
         <v>20204</v>
       </c>
       <c r="W202" s="14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Y202" s="14">
         <v>1</v>
@@ -14561,19 +14572,19 @@
         <v>13060</v>
       </c>
       <c r="B203" s="15" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C203" s="14">
         <v>3</v>
       </c>
       <c r="E203" s="16" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="H203" s="16" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="L203" s="16" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="O203" s="16">
         <v>800067</v>
@@ -14595,7 +14606,7 @@
         <v>20204</v>
       </c>
       <c r="W203" s="14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Y203" s="14">
         <v>1</v>
@@ -14612,22 +14623,22 @@
         <v>13061</v>
       </c>
       <c r="B204" s="15" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C204" s="14">
         <v>3</v>
       </c>
       <c r="E204" s="16" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H204" s="16" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="N204" s="16" t="s">
         <v>76</v>
       </c>
       <c r="Q204" s="14" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="R204" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R204" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q204,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q204))),1))</f>
@@ -14660,16 +14671,16 @@
         <v>13062</v>
       </c>
       <c r="B205" s="15" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C205" s="14">
         <v>3</v>
       </c>
       <c r="H205" s="16" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="Q205" s="14" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="R205" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R205" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q205,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q205))),1))</f>
@@ -14702,19 +14713,19 @@
         <v>13063</v>
       </c>
       <c r="B206" s="15" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C206" s="14">
         <v>3</v>
       </c>
       <c r="H206" s="16" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="P206" s="14">
         <v>9</v>
       </c>
       <c r="Q206" s="14" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="R206" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R206" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q206,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q206))),1))</f>
@@ -14747,22 +14758,22 @@
         <v>13064</v>
       </c>
       <c r="B207" s="15" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C207" s="14">
         <v>3</v>
       </c>
       <c r="E207" s="16" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H207" s="16" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="J207" s="16" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="N207" s="16" t="s">
-        <v>191</v>
+        <v>1096</v>
       </c>
       <c r="Q207" s="14" t="s">
         <v>175</v>
@@ -14798,25 +14809,25 @@
         <v>13065</v>
       </c>
       <c r="B208" s="15" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C208" s="14">
         <v>3</v>
       </c>
       <c r="H208" s="16" t="s">
+        <v>690</v>
+      </c>
+      <c r="J208" s="16" t="s">
+        <v>691</v>
+      </c>
+      <c r="N208" s="16" t="s">
         <v>692</v>
       </c>
-      <c r="J208" s="16" t="s">
+      <c r="O208" s="14">
+        <v>1</v>
+      </c>
+      <c r="Q208" s="14" t="s">
         <v>693</v>
-      </c>
-      <c r="N208" s="16" t="s">
-        <v>694</v>
-      </c>
-      <c r="O208" s="14">
-        <v>1</v>
-      </c>
-      <c r="Q208" s="14" t="s">
-        <v>695</v>
       </c>
       <c r="R208" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R208" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q208,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q208))),1))</f>
@@ -14832,7 +14843,7 @@
         <v>20701</v>
       </c>
       <c r="W208" s="14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Y208" s="14">
         <v>1</v>
@@ -14849,28 +14860,28 @@
         <v>13066</v>
       </c>
       <c r="B209" s="23" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C209" s="14">
         <v>3</v>
       </c>
       <c r="G209" s="16" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="H209" s="16" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="J209" s="16" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="N209" s="16" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="O209" s="14">
         <v>1</v>
       </c>
       <c r="Q209" s="14" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="R209" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R209" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q209,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q209))),1))</f>
@@ -14886,7 +14897,7 @@
         <v>20701</v>
       </c>
       <c r="W209" s="14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Y209" s="14">
         <v>1</v>
@@ -14903,7 +14914,7 @@
         <v>13067</v>
       </c>
       <c r="B210" s="15" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C210" s="14">
         <v>3</v>
@@ -14912,18 +14923,18 @@
       <c r="F210" s="14"/>
       <c r="G210" s="14"/>
       <c r="H210" s="14" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="I210" s="14"/>
       <c r="J210" s="14"/>
       <c r="K210" s="14"/>
       <c r="L210" s="14" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="M210" s="14"/>
       <c r="N210" s="14"/>
       <c r="Q210" s="14" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="R210" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R210" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q210,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q210))),1))</f>
@@ -14956,17 +14967,17 @@
         <v>13068</v>
       </c>
       <c r="B211" s="15" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C211" s="14">
         <v>3</v>
       </c>
       <c r="E211" s="14" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="F211" s="14"/>
       <c r="H211" s="14" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="I211" s="14"/>
       <c r="J211" s="14"/>
@@ -14975,7 +14986,7 @@
       <c r="M211" s="14"/>
       <c r="N211" s="14"/>
       <c r="Q211" s="14" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="R211" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R211" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q211,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q211))),1))</f>
@@ -15008,7 +15019,7 @@
         <v>13069</v>
       </c>
       <c r="B212" s="15" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C212" s="14">
         <v>3</v>
@@ -15017,18 +15028,18 @@
       <c r="F212" s="14"/>
       <c r="G212" s="14"/>
       <c r="H212" s="14" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="I212" s="14"/>
       <c r="J212" s="14" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="K212" s="14"/>
       <c r="L212" s="14"/>
       <c r="M212" s="14"/>
       <c r="N212" s="14"/>
       <c r="Q212" s="14" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="R212" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R212" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q212,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q212))),1))</f>
@@ -15061,7 +15072,7 @@
         <v>13070</v>
       </c>
       <c r="B213" s="15" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C213" s="14">
         <v>3</v>
@@ -15070,15 +15081,15 @@
       <c r="F213" s="14"/>
       <c r="G213" s="14"/>
       <c r="H213" s="14" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="I213" s="14"/>
       <c r="J213" s="14" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="K213" s="14"/>
       <c r="L213" s="14" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="M213" s="14"/>
       <c r="N213" s="14"/>
@@ -15086,7 +15097,7 @@
         <v>2</v>
       </c>
       <c r="Q213" s="14" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="R213" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R213" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q213,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q213))),1))</f>
@@ -15119,16 +15130,16 @@
         <v>13071</v>
       </c>
       <c r="B214" s="15" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C214" s="14">
         <v>3</v>
       </c>
       <c r="E214" s="16" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="G214" s="16" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="R214" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R214" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q214,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q214))),1))</f>
@@ -15141,7 +15152,7 @@
         <v>20402</v>
       </c>
       <c r="W214" s="14" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="Y214" s="14">
         <v>1</v>
@@ -15158,16 +15169,16 @@
         <v>13072</v>
       </c>
       <c r="B215" s="15" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="C215" s="14">
         <v>3</v>
       </c>
       <c r="E215" s="16" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="H215" s="16" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="O215" s="14">
         <v>7</v>
@@ -15186,7 +15197,7 @@
         <v>20701</v>
       </c>
       <c r="W215" s="14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Y215" s="14">
         <v>1</v>
@@ -15206,16 +15217,16 @@
         <v>3</v>
       </c>
       <c r="G216" s="16" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="H216" s="16" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="L216" s="16" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N216" s="16" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="O216" s="14">
         <v>1</v>
@@ -15224,7 +15235,7 @@
         <v>6</v>
       </c>
       <c r="Q216" s="14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="R216" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R216" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q216,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q216))),1))</f>
@@ -15240,7 +15251,7 @@
         <v>20507</v>
       </c>
       <c r="W216" s="14" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="Y216" s="14">
         <v>1</v>
@@ -15260,13 +15271,13 @@
         <v>3</v>
       </c>
       <c r="E217" s="16" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H217" s="16" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L217" s="16" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="N217" s="16" t="s">
         <v>76</v>
@@ -15278,7 +15289,7 @@
         <v>6</v>
       </c>
       <c r="Q217" s="14" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="R217" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R217" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q217,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q217))),1))</f>
@@ -15294,7 +15305,7 @@
         <v>20507</v>
       </c>
       <c r="W217" s="14" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="Y217" s="14">
         <v>1</v>
@@ -15311,19 +15322,19 @@
         <v>13075</v>
       </c>
       <c r="B218" s="15" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C218" s="14">
         <v>3</v>
       </c>
       <c r="G218" s="16" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="H218" s="16" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="L218" s="16" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="O218" s="14">
         <v>1</v>
@@ -15332,7 +15343,7 @@
         <v>3</v>
       </c>
       <c r="Q218" s="14" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="R218" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R218" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q218,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q218))),1))</f>
@@ -15348,7 +15359,7 @@
         <v>20507</v>
       </c>
       <c r="W218" s="14" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="Y218" s="14">
         <v>1</v>
@@ -15368,10 +15379,10 @@
         <v>3</v>
       </c>
       <c r="H219" s="16" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="L219" s="16" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="O219" s="14">
         <v>1</v>
@@ -15380,7 +15391,7 @@
         <v>5</v>
       </c>
       <c r="Q219" s="14" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="R219" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R219" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q219,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q219))),1))</f>
@@ -15396,7 +15407,7 @@
         <v>20507</v>
       </c>
       <c r="W219" s="14" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="Y219" s="14">
         <v>1</v>
@@ -15416,7 +15427,7 @@
         <v>3</v>
       </c>
       <c r="H220" s="16" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="O220" s="14">
         <v>4</v>
@@ -15425,7 +15436,7 @@
         <v>999</v>
       </c>
       <c r="Q220" s="14" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="R220" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R220" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q220,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q220))),1))</f>
@@ -15441,7 +15452,7 @@
         <v>20507</v>
       </c>
       <c r="W220" s="14" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="Y220" s="14">
         <v>1</v>
@@ -15461,7 +15472,7 @@
         <v>3</v>
       </c>
       <c r="H221" s="16" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="O221" s="14">
         <v>5</v>
@@ -15470,7 +15481,7 @@
         <v>999</v>
       </c>
       <c r="Q221" s="14" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="R221" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R221" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q221,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q221))),1))</f>
@@ -15486,7 +15497,7 @@
         <v>20507</v>
       </c>
       <c r="W221" s="14" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="Y221" s="14">
         <v>1</v>
@@ -15506,16 +15517,16 @@
         <v>3</v>
       </c>
       <c r="E222" s="16" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="G222" s="16" t="s">
         <v>169</v>
       </c>
       <c r="H222" s="16" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="L222" s="16" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="O222" s="14">
         <v>4</v>
@@ -15540,7 +15551,7 @@
         <v>20507</v>
       </c>
       <c r="W222" s="14" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="Y222" s="14">
         <v>1</v>
@@ -15560,13 +15571,13 @@
         <v>3</v>
       </c>
       <c r="H223" s="16" t="s">
+        <v>730</v>
+      </c>
+      <c r="J223" s="16" t="s">
+        <v>731</v>
+      </c>
+      <c r="N223" s="16" t="s">
         <v>732</v>
-      </c>
-      <c r="J223" s="16" t="s">
-        <v>733</v>
-      </c>
-      <c r="N223" s="16" t="s">
-        <v>734</v>
       </c>
       <c r="O223" s="14">
         <v>7</v>
@@ -15591,7 +15602,7 @@
         <v>20507</v>
       </c>
       <c r="W223" s="14" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="Y223" s="14">
         <v>1</v>
@@ -15608,16 +15619,16 @@
         <v>13081</v>
       </c>
       <c r="B224" s="15" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C224" s="14">
         <v>3</v>
       </c>
       <c r="H224" s="16" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="Q224" s="14" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="R224" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R224" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q224,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q224))),1))</f>
@@ -15653,10 +15664,10 @@
         <v>3</v>
       </c>
       <c r="H225" s="16" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="N225" s="16" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O225" s="14">
         <v>5</v>
@@ -15665,7 +15676,7 @@
         <v>6</v>
       </c>
       <c r="Q225" s="14" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="R225" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R225" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q225,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q225))),1))</f>
@@ -15681,7 +15692,7 @@
         <v>20507</v>
       </c>
       <c r="W225" s="14" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="Y225" s="14">
         <v>1</v>
@@ -15698,16 +15709,16 @@
         <v>13083</v>
       </c>
       <c r="B226" s="15" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="C226" s="14">
         <v>3</v>
       </c>
       <c r="H226" s="16" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="J226" s="16" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="P226" s="14">
         <v>999</v>
@@ -15740,13 +15751,13 @@
         <v>13084</v>
       </c>
       <c r="B227" s="15" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C227" s="14">
         <v>3</v>
       </c>
       <c r="H227" s="16" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="P227" s="14">
         <v>999</v>
@@ -15779,7 +15790,7 @@
         <v>13085</v>
       </c>
       <c r="B228" s="15" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="C228" s="14">
         <v>3</v>
@@ -15788,10 +15799,10 @@
         <v>169</v>
       </c>
       <c r="H228" s="16" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="J228" s="16" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="P228" s="14">
         <v>999</v>
@@ -15824,18 +15835,18 @@
         <v>13086</v>
       </c>
       <c r="B229" s="15" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C229" s="14">
         <v>3</v>
       </c>
       <c r="H229" s="14" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="I229" s="14"/>
       <c r="J229" s="14"/>
       <c r="L229" s="16" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="P229" s="14">
         <v>999</v>
@@ -15868,13 +15879,13 @@
         <v>13087</v>
       </c>
       <c r="B230" s="15" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="C230" s="14">
         <v>3</v>
       </c>
       <c r="H230" s="16" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="P230" s="14">
         <v>999</v>
@@ -15907,16 +15918,16 @@
         <v>13088</v>
       </c>
       <c r="B231" s="15" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C231" s="14">
         <v>3</v>
       </c>
       <c r="H231" s="16" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="L231" s="16" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="P231" s="14">
         <v>999</v>
@@ -15949,13 +15960,13 @@
         <v>13089</v>
       </c>
       <c r="B232" s="15" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C232" s="14">
         <v>3</v>
       </c>
       <c r="H232" s="16" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="P232" s="14">
         <v>999</v>
@@ -15988,16 +15999,16 @@
         <v>13090</v>
       </c>
       <c r="B233" s="15" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="C233" s="14">
         <v>3</v>
       </c>
       <c r="H233" s="16" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="J233" s="16" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="P233" s="14">
         <v>999</v>
@@ -16030,22 +16041,22 @@
         <v>13091</v>
       </c>
       <c r="B234" s="15" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="C234" s="14">
         <v>3</v>
       </c>
       <c r="E234" s="16" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="H234" s="16" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="N234" s="16" t="s">
         <v>76</v>
       </c>
       <c r="Q234" s="14" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="R234" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R234" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q234,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q234))),1))</f>
@@ -16078,21 +16089,21 @@
         <v>13092</v>
       </c>
       <c r="B235" s="15" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C235" s="14">
         <v>3</v>
       </c>
       <c r="E235" s="16" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="H235" s="16" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="I235" s="14"/>
       <c r="J235" s="14"/>
       <c r="L235" s="16" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="R235" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R235" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q235,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q235))),1))</f>
@@ -16119,16 +16130,16 @@
         <v>13093</v>
       </c>
       <c r="B236" s="15" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="C236" s="14">
         <v>3</v>
       </c>
       <c r="H236" s="16" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="N236" s="16" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="R236" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R236" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q236,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q236))),1))</f>
@@ -16141,7 +16152,7 @@
         <v>20508</v>
       </c>
       <c r="W236" s="14" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="Y236" s="14">
         <v>1</v>
@@ -16158,13 +16169,13 @@
         <v>13094</v>
       </c>
       <c r="B237" s="15" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="C237" s="14">
         <v>3</v>
       </c>
       <c r="H237" s="16" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="R237" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R237" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q237,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q237))),1))</f>
@@ -16188,22 +16199,22 @@
         <v>13095</v>
       </c>
       <c r="B238" s="15" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C238" s="14">
         <v>3</v>
       </c>
       <c r="H238" s="14" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="J238" s="16" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="P238" s="14">
         <v>999</v>
       </c>
       <c r="Q238" s="14" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="R238" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R238" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q238,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q238))),1))</f>
@@ -16233,22 +16244,22 @@
         <v>13096</v>
       </c>
       <c r="B239" s="15" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C239" s="14">
         <v>3</v>
       </c>
       <c r="H239" s="14" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="J239" s="16" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="P239" s="14">
         <v>999</v>
       </c>
       <c r="Q239" s="14" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="R239" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R239" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q239,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q239))),1))</f>
@@ -16278,22 +16289,22 @@
         <v>13097</v>
       </c>
       <c r="B240" s="15" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C240" s="14">
         <v>3</v>
       </c>
       <c r="H240" s="14" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="J240" s="16" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="P240" s="14">
         <v>999</v>
       </c>
       <c r="Q240" s="14" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="R240" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R240" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q240,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q240))),1))</f>
@@ -16323,22 +16334,22 @@
         <v>13098</v>
       </c>
       <c r="B241" s="15" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C241" s="14">
         <v>3</v>
       </c>
       <c r="H241" s="14" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="J241" s="16" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="P241" s="14">
         <v>999</v>
       </c>
       <c r="Q241" s="14" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="R241" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R241" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q241,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q241))),1))</f>
@@ -16368,16 +16379,16 @@
         <v>13099</v>
       </c>
       <c r="B242" s="15" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="C242" s="14">
         <v>3</v>
       </c>
       <c r="H242" s="16" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="J242" s="16" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="P242" s="14">
         <v>999</v>
@@ -16410,13 +16421,13 @@
         <v>13100</v>
       </c>
       <c r="B243" s="15" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C243" s="14">
         <v>3</v>
       </c>
       <c r="H243" s="16" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="P243" s="14">
         <v>999</v>
@@ -16449,18 +16460,18 @@
         <v>13101</v>
       </c>
       <c r="B244" s="15" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C244" s="14">
         <v>3</v>
       </c>
       <c r="H244" s="14" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="I244" s="14"/>
       <c r="J244" s="14"/>
       <c r="L244" s="16" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="P244" s="14">
         <v>999</v>
@@ -16493,13 +16504,13 @@
         <v>13102</v>
       </c>
       <c r="B245" s="15" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="C245" s="14">
         <v>3</v>
       </c>
       <c r="H245" s="16" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="P245" s="14">
         <v>999</v>
@@ -16532,16 +16543,16 @@
         <v>13103</v>
       </c>
       <c r="B246" s="15" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C246" s="14">
         <v>3</v>
       </c>
       <c r="H246" s="16" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="L246" s="16" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="P246" s="14">
         <v>999</v>
@@ -16574,16 +16585,16 @@
         <v>13104</v>
       </c>
       <c r="B247" s="15" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="C247" s="14">
         <v>3</v>
       </c>
       <c r="H247" s="16" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="J247" s="16" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="P247" s="14">
         <v>999</v>
@@ -16616,13 +16627,13 @@
         <v>13105</v>
       </c>
       <c r="B248" s="15" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C248" s="14">
         <v>3</v>
       </c>
       <c r="H248" s="16" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="P248" s="14">
         <v>999</v>
@@ -16655,18 +16666,18 @@
         <v>13106</v>
       </c>
       <c r="B249" s="15" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C249" s="14">
         <v>3</v>
       </c>
       <c r="H249" s="14" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="I249" s="14"/>
       <c r="J249" s="14"/>
       <c r="L249" s="16" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="P249" s="14">
         <v>999</v>
@@ -16699,13 +16710,13 @@
         <v>13107</v>
       </c>
       <c r="B250" s="15" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="C250" s="14">
         <v>3</v>
       </c>
       <c r="H250" s="16" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="P250" s="14">
         <v>999</v>
@@ -16738,16 +16749,16 @@
         <v>13108</v>
       </c>
       <c r="B251" s="15" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C251" s="14">
         <v>3</v>
       </c>
       <c r="H251" s="16" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="L251" s="16" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="P251" s="14">
         <v>999</v>
@@ -16780,7 +16791,7 @@
         <v>13109</v>
       </c>
       <c r="B252" s="15" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C252" s="14">
         <v>3</v>
@@ -16796,7 +16807,7 @@
         <v>20407</v>
       </c>
       <c r="W252" s="14" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="Y252" s="14">
         <v>1</v>
@@ -16816,7 +16827,7 @@
         <v>3</v>
       </c>
       <c r="H253" s="16" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="R253" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R253" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q253,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q253))),1))</f>
@@ -16829,7 +16840,7 @@
         <v>20508</v>
       </c>
       <c r="W253" s="14" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="Y253" s="14">
         <v>1</v>
@@ -16849,7 +16860,7 @@
         <v>3</v>
       </c>
       <c r="H254" s="16" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="R254" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R254" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q254,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q254))),1))</f>
@@ -16862,7 +16873,7 @@
         <v>20508</v>
       </c>
       <c r="W254" s="14" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="Y254" s="14">
         <v>1</v>
@@ -16882,7 +16893,7 @@
         <v>3</v>
       </c>
       <c r="H255" s="16" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="R255" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R255" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q255,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q255))),1))</f>
@@ -16915,7 +16926,7 @@
         <v>3</v>
       </c>
       <c r="H256" s="16" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="R256" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R256" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q256,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q256))),1))</f>
@@ -16948,22 +16959,22 @@
         <v>3</v>
       </c>
       <c r="G257" s="16" t="s">
+        <v>784</v>
+      </c>
+      <c r="H257" s="16" t="s">
+        <v>785</v>
+      </c>
+      <c r="J257" s="16" t="s">
         <v>786</v>
       </c>
-      <c r="H257" s="16" t="s">
+      <c r="L257" s="16" t="s">
         <v>787</v>
-      </c>
-      <c r="J257" s="16" t="s">
-        <v>788</v>
-      </c>
-      <c r="L257" s="16" t="s">
-        <v>789</v>
       </c>
       <c r="P257" s="14">
         <v>5</v>
       </c>
       <c r="Q257" s="14" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="R257" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R257" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q257,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q257))),1))</f>
@@ -16982,7 +16993,7 @@
         <v>20602</v>
       </c>
       <c r="W257" s="14" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="Y257" s="14">
         <v>1</v>
@@ -16999,16 +17010,16 @@
         <v>13115</v>
       </c>
       <c r="B258" s="15" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C258" s="14">
         <v>3</v>
       </c>
       <c r="H258" s="16" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="L258" s="16" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="P258" s="14">
         <v>999</v>
@@ -17030,7 +17041,7 @@
         <v>20604</v>
       </c>
       <c r="W258" s="14" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Y258" s="14">
         <v>1</v>
@@ -17050,16 +17061,16 @@
         <v>3</v>
       </c>
       <c r="H259" s="16" t="s">
+        <v>793</v>
+      </c>
+      <c r="J259" s="16" t="s">
+        <v>794</v>
+      </c>
+      <c r="L259" s="16" t="s">
         <v>795</v>
       </c>
-      <c r="J259" s="16" t="s">
-        <v>796</v>
-      </c>
-      <c r="L259" s="16" t="s">
-        <v>797</v>
-      </c>
       <c r="Q259" s="14" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="S259" s="14">
         <v>1</v>
@@ -17074,7 +17085,7 @@
         <v>20604</v>
       </c>
       <c r="W259" s="14" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Y259" s="14">
         <v>1</v>
@@ -17094,16 +17105,16 @@
         <v>3</v>
       </c>
       <c r="E260" s="16" t="s">
+        <v>796</v>
+      </c>
+      <c r="H260" s="16" t="s">
+        <v>673</v>
+      </c>
+      <c r="J260" s="16" t="s">
+        <v>797</v>
+      </c>
+      <c r="L260" s="16" t="s">
         <v>798</v>
-      </c>
-      <c r="H260" s="16" t="s">
-        <v>675</v>
-      </c>
-      <c r="J260" s="16" t="s">
-        <v>799</v>
-      </c>
-      <c r="L260" s="16" t="s">
-        <v>800</v>
       </c>
       <c r="N260" s="16" t="s">
         <v>76</v>
@@ -17121,7 +17132,7 @@
         <v>20604</v>
       </c>
       <c r="W260" s="14" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Y260" s="14">
         <v>1</v>
@@ -17141,10 +17152,10 @@
         <v>3</v>
       </c>
       <c r="H261" s="16" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="L261" s="16" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="S261" s="14">
         <v>1</v>
@@ -17159,7 +17170,7 @@
         <v>20604</v>
       </c>
       <c r="W261" s="14" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Y261" s="14">
         <v>1</v>
@@ -17176,13 +17187,13 @@
         <v>14001</v>
       </c>
       <c r="B264" s="15" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C264" s="14">
         <v>4</v>
       </c>
       <c r="H264" s="16" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="O264" s="14">
         <v>3</v>
@@ -17191,7 +17202,7 @@
         <v>3</v>
       </c>
       <c r="Q264" s="14" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="R264" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R264" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q264,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q264))),1))</f>
@@ -17210,7 +17221,7 @@
         <v>20304</v>
       </c>
       <c r="W264" s="14" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="Y264" s="14">
         <v>2</v>
@@ -17227,16 +17238,16 @@
         <v>14002</v>
       </c>
       <c r="B265" s="15" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="C265" s="14">
         <v>4</v>
       </c>
       <c r="E265" s="16" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="H265" s="16" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="O265" s="14">
         <v>6</v>
@@ -17245,7 +17256,7 @@
         <v>3</v>
       </c>
       <c r="Q265" s="14" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="R265" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R265" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q265,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q265))),1))</f>
@@ -17264,7 +17275,7 @@
         <v>20304</v>
       </c>
       <c r="W265" s="14" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="Y265" s="14">
         <v>2</v>
@@ -17281,7 +17292,7 @@
         <v>14003</v>
       </c>
       <c r="B266" s="15" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C266" s="14">
         <v>4</v>
@@ -17290,13 +17301,13 @@
         <v>144</v>
       </c>
       <c r="G266" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H266" s="16" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="L266" s="16" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="O266" s="14">
         <v>3</v>
@@ -17305,7 +17316,7 @@
         <v>4</v>
       </c>
       <c r="Q266" s="14" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="R266" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R266" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q266,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q266))),1))</f>
@@ -17324,7 +17335,7 @@
         <v>20302</v>
       </c>
       <c r="W266" s="14" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Y266" s="14">
         <v>2</v>
@@ -17341,22 +17352,22 @@
         <v>14004</v>
       </c>
       <c r="B267" s="15" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="C267" s="14">
         <v>4</v>
       </c>
       <c r="E267" s="16" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H267" s="16" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="N267" s="16" t="s">
         <v>76</v>
       </c>
       <c r="Q267" s="14" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="R267" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R267" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q267,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q267))),1))</f>
@@ -17372,7 +17383,7 @@
         <v>20302</v>
       </c>
       <c r="W267" s="14" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Y267" s="14">
         <v>2</v>
@@ -17389,22 +17400,22 @@
         <v>14005</v>
       </c>
       <c r="B268" s="15" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C268" s="14">
         <v>4</v>
       </c>
       <c r="E268" s="16" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H268" s="16" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="N268" s="16" t="s">
         <v>76</v>
       </c>
       <c r="Q268" s="14" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="R268" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R268" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q268,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q268))),1))</f>
@@ -17420,7 +17431,7 @@
         <v>20302</v>
       </c>
       <c r="W268" s="14" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Y268" s="14">
         <v>2</v>
@@ -17437,16 +17448,16 @@
         <v>14006</v>
       </c>
       <c r="B269" s="15" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="C269" s="14">
         <v>4</v>
       </c>
       <c r="H269" s="16" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L269" s="16" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="O269" s="14">
         <v>3</v>
@@ -17465,7 +17476,7 @@
         <v>20302</v>
       </c>
       <c r="W269" s="14" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Y269" s="14">
         <v>2</v>
@@ -17482,7 +17493,7 @@
         <v>14007</v>
       </c>
       <c r="B270" s="20" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="C270" s="14">
         <v>4</v>
@@ -17491,10 +17502,10 @@
         <v>85</v>
       </c>
       <c r="H270" s="16" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="L270" s="16" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="O270" s="14">
         <v>1</v>
@@ -17503,7 +17514,7 @@
         <v>4</v>
       </c>
       <c r="Q270" s="14" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="R270" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R270" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q270,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q270))),1))</f>
@@ -17519,7 +17530,7 @@
         <v>20502</v>
       </c>
       <c r="W270" s="14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Y270" s="14">
         <v>2</v>
@@ -17536,7 +17547,7 @@
         <v>14008</v>
       </c>
       <c r="B271" s="20" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C271" s="14">
         <v>4</v>
@@ -17545,10 +17556,10 @@
         <v>85</v>
       </c>
       <c r="H271" s="16" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="L271" s="16" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="O271" s="14">
         <v>1</v>
@@ -17557,7 +17568,7 @@
         <v>4</v>
       </c>
       <c r="Q271" s="14" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="R271" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R271" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q271,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q271))),1))</f>
@@ -17573,7 +17584,7 @@
         <v>20502</v>
       </c>
       <c r="W271" s="14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Y271" s="14">
         <v>2</v>
@@ -17590,16 +17601,16 @@
         <v>14009</v>
       </c>
       <c r="B272" s="15" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C272" s="14">
         <v>4</v>
       </c>
       <c r="E272" s="16" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="H272" s="16" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="N272" s="16" t="s">
         <v>201</v>
@@ -17608,7 +17619,7 @@
         <v>2</v>
       </c>
       <c r="Q272" s="14" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="R272" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R272" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q272,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q272))),1))</f>
@@ -17624,7 +17635,7 @@
         <v>20406</v>
       </c>
       <c r="W272" s="14" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="Y272" s="14">
         <v>2</v>
@@ -17641,13 +17652,13 @@
         <v>14010</v>
       </c>
       <c r="B273" s="15" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C273" s="14">
         <v>4</v>
       </c>
       <c r="H273" s="16" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="R273" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R273" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q273,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q273))),1))</f>
@@ -17657,7 +17668,7 @@
         <v>20302</v>
       </c>
       <c r="W273" s="14" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Y273" s="14">
         <v>2</v>
@@ -17674,16 +17685,16 @@
         <v>14011</v>
       </c>
       <c r="B274" s="15" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C274" s="14">
         <v>4</v>
       </c>
       <c r="E274" s="16" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="H274" s="16" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="R274" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R274" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q274,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q274))),1))</f>
@@ -17693,7 +17704,7 @@
         <v>20302</v>
       </c>
       <c r="W274" s="14" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Y274" s="14">
         <v>2</v>
@@ -17710,7 +17721,7 @@
         <v>14012</v>
       </c>
       <c r="B275" s="15" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C275" s="14">
         <v>4</v>
@@ -17723,7 +17734,7 @@
         <v>20505</v>
       </c>
       <c r="W275" s="14" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AA275" s="14">
         <v>1</v>
@@ -17734,19 +17745,19 @@
         <v>14013</v>
       </c>
       <c r="B276" s="15" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C276" s="14">
         <v>4</v>
       </c>
       <c r="E276" s="16" t="s">
+        <v>836</v>
+      </c>
+      <c r="H276" s="16" t="s">
+        <v>837</v>
+      </c>
+      <c r="Q276" s="14" t="s">
         <v>838</v>
-      </c>
-      <c r="H276" s="16" t="s">
-        <v>839</v>
-      </c>
-      <c r="Q276" s="14" t="s">
-        <v>840</v>
       </c>
       <c r="R276" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R276" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q276,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q276))),1))</f>
@@ -17759,7 +17770,7 @@
         <v>20505</v>
       </c>
       <c r="W276" s="14" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Y276" s="14">
         <v>2</v>
@@ -17776,19 +17787,19 @@
         <v>14014</v>
       </c>
       <c r="B277" s="20" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="C277" s="14">
         <v>4</v>
       </c>
       <c r="E277" s="16" t="s">
-        <v>842</v>
+        <v>1097</v>
       </c>
       <c r="H277" s="16" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="Q277" s="14" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="R277" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R277" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q277,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q277))),1))</f>
@@ -17801,7 +17812,7 @@
         <v>20505</v>
       </c>
       <c r="W277" s="14" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Y277" s="14">
         <v>2</v>
@@ -17818,19 +17829,19 @@
         <v>14015</v>
       </c>
       <c r="B278" s="15" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="C278" s="14">
         <v>4</v>
       </c>
       <c r="E278" s="16" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="H278" s="16" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="Q278" s="14" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="R278" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R278" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q278,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q278))),1))</f>
@@ -17846,7 +17857,7 @@
         <v>20304</v>
       </c>
       <c r="W278" s="14" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="Y278" s="14">
         <v>2</v>
@@ -17863,7 +17874,7 @@
         <v>14016</v>
       </c>
       <c r="B279" s="15" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="C279" s="14">
         <v>4</v>
@@ -17872,10 +17883,10 @@
         <v>195</v>
       </c>
       <c r="G279" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H279" s="16" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="O279" s="14">
         <v>3</v>
@@ -17891,7 +17902,7 @@
         <v>20602</v>
       </c>
       <c r="W279" s="14" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="Y279" s="14">
         <v>2</v>
@@ -17908,25 +17919,25 @@
         <v>14017</v>
       </c>
       <c r="B280" s="15" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="C280" s="14">
         <v>4</v>
       </c>
       <c r="E280" s="16" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="H280" s="16" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="L280" s="16" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="O280" s="14">
         <v>7</v>
       </c>
       <c r="Q280" s="14" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="R280" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R280" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q280,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q280))),1))</f>
@@ -17939,7 +17950,7 @@
         <v>20602</v>
       </c>
       <c r="W280" s="14" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="Y280" s="14">
         <v>2</v>
@@ -17956,7 +17967,7 @@
         <v>14018</v>
       </c>
       <c r="B281" s="15" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="C281" s="14">
         <v>4</v>
@@ -17974,7 +17985,7 @@
         <v>0</v>
       </c>
       <c r="Q281" s="14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="R281" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R281" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q281,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q281))),1))</f>
@@ -18004,16 +18015,16 @@
         <v>14019</v>
       </c>
       <c r="B282" s="15" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="C282" s="14">
         <v>4</v>
       </c>
       <c r="E282" s="16" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="H282" s="16" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="R282" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R282" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q282,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q282))),1))</f>
@@ -18043,19 +18054,19 @@
         <v>14020</v>
       </c>
       <c r="B283" s="20" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C283" s="14">
         <v>4</v>
       </c>
       <c r="E283" s="16" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="H283" s="16" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="Q283" s="14" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="R283" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R283" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q283,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q283))),1))</f>
@@ -18085,25 +18096,25 @@
         <v>14021</v>
       </c>
       <c r="B284" s="15" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="C284" s="14">
         <v>4</v>
       </c>
       <c r="G284" s="16" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="H284" s="16" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="L284" s="16" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="P284" s="14">
         <v>999</v>
       </c>
       <c r="Q284" s="14" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="R284" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R284" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q284,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q284))),1))</f>
@@ -18133,25 +18144,25 @@
         <v>14022</v>
       </c>
       <c r="B285" s="15" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="C285" s="14">
         <v>4</v>
       </c>
       <c r="G285" s="16" t="s">
+        <v>858</v>
+      </c>
+      <c r="H285" s="16" t="s">
         <v>861</v>
       </c>
-      <c r="H285" s="16" t="s">
-        <v>864</v>
-      </c>
       <c r="L285" s="16" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="P285" s="14">
         <v>999</v>
       </c>
       <c r="Q285" s="14" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="R285" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R285" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q285,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q285))),1))</f>
@@ -18181,22 +18192,22 @@
         <v>14023</v>
       </c>
       <c r="B286" s="15" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="C286" s="14">
         <v>4</v>
       </c>
       <c r="H286" s="16" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="J286" s="16" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="P286" s="14">
         <v>999</v>
       </c>
       <c r="Q286" s="14" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="R286" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R286" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q286,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q286))),1))</f>
@@ -18226,22 +18237,22 @@
         <v>14024</v>
       </c>
       <c r="B287" s="15" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="C287" s="14">
         <v>4</v>
       </c>
       <c r="H287" s="16" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="J287" s="16" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="P287" s="14">
         <v>999</v>
       </c>
       <c r="Q287" s="14" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="R287" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R287" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q287,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q287))),1))</f>
@@ -18271,22 +18282,22 @@
         <v>14025</v>
       </c>
       <c r="B288" s="15" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="C288" s="14">
         <v>4</v>
       </c>
       <c r="G288" s="16" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="H288" s="16" t="s">
         <v>55</v>
       </c>
       <c r="J288" s="16" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="Q288" s="14" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="R288" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R288" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q288,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q288))),1))</f>
@@ -18316,22 +18327,22 @@
         <v>14026</v>
       </c>
       <c r="B289" s="15" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="C289" s="14">
         <v>4</v>
       </c>
       <c r="G289" s="16" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="H289" s="16" t="s">
         <v>55</v>
       </c>
       <c r="J289" s="16" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="Q289" s="14" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="R289" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R289" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q289,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q289))),1))</f>
@@ -18361,16 +18372,16 @@
         <v>14027</v>
       </c>
       <c r="B290" s="15" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="C290" s="14">
         <v>4</v>
       </c>
       <c r="H290" s="16" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="N290" s="16" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="O290" s="14">
         <v>3</v>
@@ -18389,7 +18400,7 @@
         <v>20502</v>
       </c>
       <c r="W290" s="14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Y290" s="14">
         <v>2</v>
@@ -18406,22 +18417,22 @@
         <v>14028</v>
       </c>
       <c r="B291" s="15" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="C291" s="14">
         <v>4</v>
       </c>
       <c r="E291" s="16" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="G291" s="16" t="s">
         <v>169</v>
       </c>
       <c r="H291" s="16" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="N291" s="16" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="R291" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R291" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q291,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q291))),1))</f>
@@ -18431,7 +18442,7 @@
         <v>20502</v>
       </c>
       <c r="W291" s="14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Y291" s="14">
         <v>2</v>
@@ -18448,7 +18459,7 @@
         <v>14029</v>
       </c>
       <c r="B292" s="15" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="C292" s="14">
         <v>4</v>
@@ -18481,19 +18492,19 @@
         <v>14030</v>
       </c>
       <c r="B293" s="15" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="C293" s="14">
         <v>4</v>
       </c>
       <c r="E293" s="16" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="H293" s="16" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="J293" s="16" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="L293" s="16" t="s">
         <v>195</v>
@@ -18526,16 +18537,16 @@
         <v>14031</v>
       </c>
       <c r="B294" s="15" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="C294" s="14">
         <v>4</v>
       </c>
       <c r="H294" s="16" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="N294" s="16" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="P294" s="14">
         <v>1</v>
@@ -18574,7 +18585,7 @@
         <v>14032</v>
       </c>
       <c r="B295" s="15" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="C295" s="14">
         <v>4</v>
@@ -18583,19 +18594,19 @@
         <v>195</v>
       </c>
       <c r="G295" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H295" s="16" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="L295" s="16" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="P295" s="14">
         <v>5</v>
       </c>
       <c r="Q295" s="14" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="R295" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R295" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q295,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q295))),1))</f>
@@ -18608,7 +18619,7 @@
         <v>20402</v>
       </c>
       <c r="W295" s="14" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="Y295" s="14">
         <v>2</v>
@@ -18625,13 +18636,13 @@
         <v>14033</v>
       </c>
       <c r="B296" s="15" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="C296" s="14">
         <v>4</v>
       </c>
       <c r="H296" s="16" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="P296" s="14">
         <v>12</v>
@@ -18644,7 +18655,7 @@
         <v>20407</v>
       </c>
       <c r="W296" s="14" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="Y296" s="14">
         <v>2</v>
@@ -18661,13 +18672,13 @@
         <v>14034</v>
       </c>
       <c r="B297" s="15" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="C297" s="14">
         <v>4</v>
       </c>
       <c r="H297" s="16" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="P297" s="14">
         <v>7</v>
@@ -18683,7 +18694,7 @@
         <v>20603</v>
       </c>
       <c r="W297" s="14" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="Y297" s="14">
         <v>2</v>
@@ -18700,16 +18711,16 @@
         <v>14035</v>
       </c>
       <c r="B298" s="15" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="C298" s="14">
         <v>4</v>
       </c>
       <c r="E298" s="16" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="H298" s="16" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="P298" s="14">
         <v>2</v>
@@ -18722,7 +18733,7 @@
         <v>20603</v>
       </c>
       <c r="W298" s="14" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="Y298" s="14">
         <v>2</v>
@@ -18739,19 +18750,19 @@
         <v>14036</v>
       </c>
       <c r="B299" s="15" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="C299" s="14">
         <v>4</v>
       </c>
       <c r="E299" s="16" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="H299" s="16" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="J299" s="16" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="P299" s="14">
         <v>999</v>
@@ -18784,19 +18795,19 @@
         <v>14037</v>
       </c>
       <c r="B300" s="15" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="C300" s="14">
         <v>4</v>
       </c>
       <c r="E300" s="16" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="H300" s="16" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="J300" s="16" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="P300" s="14">
         <v>999</v>
@@ -18829,16 +18840,16 @@
         <v>14038</v>
       </c>
       <c r="B301" s="15" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="C301" s="14">
         <v>4</v>
       </c>
       <c r="H301" s="16" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="J301" s="16" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="P301" s="14">
         <v>10</v>
@@ -18851,7 +18862,7 @@
         <v>20302</v>
       </c>
       <c r="W301" s="14" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Y301" s="14">
         <v>2</v>
@@ -18868,7 +18879,7 @@
         <v>14039</v>
       </c>
       <c r="B302" s="23" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="C302" s="14">
         <v>4</v>
@@ -18877,13 +18888,13 @@
         <v>177</v>
       </c>
       <c r="H302" s="16" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="L302" s="16" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="N302" s="16" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="P302" s="14">
         <v>6</v>
@@ -18899,7 +18910,7 @@
         <v>20701</v>
       </c>
       <c r="W302" s="14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Y302" s="14">
         <v>2</v>
@@ -18916,7 +18927,7 @@
         <v>14040</v>
       </c>
       <c r="B303" s="15" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="C303" s="14">
         <v>4</v>
@@ -18925,7 +18936,7 @@
         <v>182</v>
       </c>
       <c r="H303" s="16" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="P303" s="14">
         <v>5</v>
@@ -18961,22 +18972,22 @@
         <v>14041</v>
       </c>
       <c r="B304" s="15" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="C304" s="14">
         <v>4</v>
       </c>
       <c r="E304" s="16" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="H304" s="16" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="P304" s="14">
         <v>7</v>
       </c>
       <c r="Q304" s="14" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="R304" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R304" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q304,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q304))),1))</f>
@@ -18989,7 +19000,7 @@
         <v>20402</v>
       </c>
       <c r="W304" s="14" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="Y304" s="14">
         <v>2</v>
@@ -19006,19 +19017,19 @@
         <v>14042</v>
       </c>
       <c r="B305" s="15" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="C305" s="14">
         <v>4</v>
       </c>
       <c r="H305" s="16" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="L305" s="16" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="Q305" s="14" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="R305" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R305" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q305,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q305))),1))</f>
@@ -19051,10 +19062,10 @@
         <v>4</v>
       </c>
       <c r="H306" s="16" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="J306" s="16" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="Q306" s="14" t="s">
         <v>142</v>
@@ -19087,16 +19098,16 @@
         <v>14044</v>
       </c>
       <c r="B307" s="15" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="C307" s="14">
         <v>4</v>
       </c>
       <c r="H307" s="16" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="J307" s="16" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="R307" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R307" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q307,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q307))),1))</f>
@@ -19123,7 +19134,7 @@
         <v>14045</v>
       </c>
       <c r="B308" s="15" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="C308" s="14">
         <v>4</v>
@@ -19138,13 +19149,13 @@
         <v>14046</v>
       </c>
       <c r="B309" s="15" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="C309" s="14">
         <v>4</v>
       </c>
       <c r="H309" s="16" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="O309" s="14">
         <v>6</v>
@@ -19160,7 +19171,7 @@
         <v>20402</v>
       </c>
       <c r="W309" s="14" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="Y309" s="14">
         <v>2</v>
@@ -19177,16 +19188,16 @@
         <v>14047</v>
       </c>
       <c r="B310" s="15" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="C310" s="14">
         <v>4</v>
       </c>
       <c r="E310" s="16" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="H310" s="16" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="O310" s="14">
         <v>1</v>
@@ -19195,7 +19206,7 @@
         <v>5</v>
       </c>
       <c r="Q310" s="14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="R310" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R310" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q310,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q310))),1))</f>
@@ -19208,7 +19219,7 @@
         <v>20407</v>
       </c>
       <c r="W310" s="14" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="Y310" s="14">
         <v>2</v>
@@ -19249,10 +19260,10 @@
         <v>4</v>
       </c>
       <c r="E312" s="16" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="H312" s="16" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="O312" s="14">
         <v>6</v>
@@ -19268,7 +19279,7 @@
         <v>20307</v>
       </c>
       <c r="W312" s="14" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Y312" s="14">
         <v>2</v>
@@ -19288,16 +19299,16 @@
         <v>4</v>
       </c>
       <c r="E313" s="16" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="H313" s="16" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="O313" s="14">
         <v>6</v>
       </c>
       <c r="Q313" s="14" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="R313" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R313" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q313,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q313))),1))</f>
@@ -19307,7 +19318,7 @@
         <v>20307</v>
       </c>
       <c r="W313" s="14" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Y313" s="14">
         <v>2</v>
@@ -19327,10 +19338,10 @@
         <v>4</v>
       </c>
       <c r="E314" s="16" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="H314" s="16" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="O314" s="14">
         <v>6</v>
@@ -19346,7 +19357,7 @@
         <v>20307</v>
       </c>
       <c r="W314" s="14" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Y314" s="14">
         <v>2</v>
@@ -19363,19 +19374,19 @@
         <v>14052</v>
       </c>
       <c r="B315" s="15" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="C315" s="14">
         <v>4</v>
       </c>
       <c r="E315" s="16" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="H315" s="16" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="N315" s="16" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="O315" s="14">
         <v>4</v>
@@ -19384,7 +19395,7 @@
         <v>1</v>
       </c>
       <c r="Q315" s="14" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="R315" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R315" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q315,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q315))),1))</f>
@@ -19400,7 +19411,7 @@
         <v>20507</v>
       </c>
       <c r="W315" s="14" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="Y315" s="14">
         <v>2</v>
@@ -19417,19 +19428,19 @@
         <v>14053</v>
       </c>
       <c r="B316" s="15" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="C316" s="14">
         <v>4</v>
       </c>
       <c r="E316" s="16" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="H316" s="16" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="N316" s="16" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="O316" s="14">
         <v>5</v>
@@ -19438,7 +19449,7 @@
         <v>1</v>
       </c>
       <c r="Q316" s="14" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="R316" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R316" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q316,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q316))),1))</f>
@@ -19454,7 +19465,7 @@
         <v>20507</v>
       </c>
       <c r="W316" s="14" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="Y316" s="14">
         <v>2</v>
@@ -19471,19 +19482,19 @@
         <v>14054</v>
       </c>
       <c r="B317" s="15" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="C317" s="14">
         <v>4</v>
       </c>
       <c r="E317" s="16" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="H317" s="16" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="N317" s="16" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="O317" s="14">
         <v>6</v>
@@ -19492,7 +19503,7 @@
         <v>1</v>
       </c>
       <c r="Q317" s="14" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="R317" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R317" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q317,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q317))),1))</f>
@@ -19508,7 +19519,7 @@
         <v>20507</v>
       </c>
       <c r="W317" s="14" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="Y317" s="14">
         <v>2</v>
@@ -19528,10 +19539,10 @@
         <v>4</v>
       </c>
       <c r="H318" s="16" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="L318" s="16" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="O318" s="14">
         <v>6</v>
@@ -19540,7 +19551,7 @@
         <v>99</v>
       </c>
       <c r="Q318" s="14" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="R318" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R318" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q318,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q318))),1))</f>
@@ -19556,7 +19567,7 @@
         <v>20507</v>
       </c>
       <c r="W318" s="14" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="Y318" s="14">
         <v>2</v>
@@ -19573,13 +19584,13 @@
         <v>14056</v>
       </c>
       <c r="B319" s="15" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="C319" s="14">
         <v>4</v>
       </c>
       <c r="H319" s="16" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="O319" s="14">
         <v>1</v>
@@ -19588,7 +19599,7 @@
         <v>8</v>
       </c>
       <c r="Q319" s="14" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="R319" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R319" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q319,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q319))),1))</f>
@@ -19604,7 +19615,7 @@
         <v>20507</v>
       </c>
       <c r="W319" s="14" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="Y319" s="14">
         <v>2</v>
@@ -19621,16 +19632,16 @@
         <v>14057</v>
       </c>
       <c r="B320" s="15" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="C320" s="14">
         <v>4</v>
       </c>
       <c r="E320" s="16" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="H320" s="16" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="O320" s="14">
         <v>6</v>
@@ -19639,7 +19650,7 @@
         <v>8</v>
       </c>
       <c r="Q320" s="14" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="R320" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R320" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q320,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q320))),1))</f>
@@ -19655,7 +19666,7 @@
         <v>20507</v>
       </c>
       <c r="W320" s="14" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="Y320" s="14">
         <v>2</v>
@@ -19672,16 +19683,16 @@
         <v>14058</v>
       </c>
       <c r="B321" s="15" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="C321" s="14">
         <v>4</v>
       </c>
       <c r="H321" s="16" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="N321" s="16" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="O321" s="14">
         <v>5</v>
@@ -19690,7 +19701,7 @@
         <v>999</v>
       </c>
       <c r="Q321" s="14" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="R321" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R321" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q321,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q321))),1))</f>
@@ -19706,7 +19717,7 @@
         <v>20507</v>
       </c>
       <c r="W321" s="14" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="Y321" s="14">
         <v>2</v>
@@ -19723,16 +19734,16 @@
         <v>14059</v>
       </c>
       <c r="B322" s="15" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="C322" s="14">
         <v>4</v>
       </c>
       <c r="H322" s="16" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="L322" s="16" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="R322" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R322" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q322,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q322))),1))</f>
@@ -19742,7 +19753,7 @@
         <v>20406</v>
       </c>
       <c r="W322" s="14" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="Y322" s="14">
         <v>2</v>
@@ -19762,7 +19773,7 @@
         <v>4</v>
       </c>
       <c r="H323" s="16" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="R323" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R323" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q323,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q323))),1))</f>
@@ -19792,7 +19803,7 @@
         <v>4</v>
       </c>
       <c r="H324" s="16" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="R324" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R324" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q324,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q324))),1))</f>
@@ -19805,7 +19816,7 @@
         <v>20405</v>
       </c>
       <c r="W324" s="14" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="Y324" s="14">
         <v>2</v>
@@ -19822,13 +19833,13 @@
         <v>14062</v>
       </c>
       <c r="B325" s="15" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="C325" s="14">
         <v>4</v>
       </c>
       <c r="H325" s="16" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="L325" s="16" t="s">
         <v>195</v>
@@ -19861,16 +19872,16 @@
         <v>14063</v>
       </c>
       <c r="B326" s="15" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="C326" s="14">
         <v>4</v>
       </c>
       <c r="H326" s="16" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="J326" s="16" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="R326" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R326" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q326,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q326))),1))</f>
@@ -19897,7 +19908,7 @@
         <v>14064</v>
       </c>
       <c r="B327" s="15" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="C327" s="14">
         <v>4</v>
@@ -19906,10 +19917,10 @@
         <v>94</v>
       </c>
       <c r="H327" s="16" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="N327" s="16" t="s">
-        <v>214</v>
+        <v>1098</v>
       </c>
       <c r="P327" s="14">
         <v>999</v>
@@ -19939,16 +19950,16 @@
         <v>14065</v>
       </c>
       <c r="B328" s="15" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="C328" s="14">
         <v>4</v>
       </c>
       <c r="H328" s="16" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="N328" s="16" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="O328" s="16"/>
       <c r="R328" s="14" t="e" cm="1">
@@ -19959,7 +19970,7 @@
         <v>20409</v>
       </c>
       <c r="W328" s="14" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="Y328" s="14">
         <v>2</v>
@@ -19976,25 +19987,25 @@
         <v>14066</v>
       </c>
       <c r="B329" s="15" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="C329" s="14">
         <v>4</v>
       </c>
       <c r="G329" s="16" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="H329" s="16" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="L329" s="16" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="P329" s="14">
         <v>999</v>
       </c>
       <c r="Q329" s="14" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="R329" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R329" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q329,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q329))),1))</f>
@@ -20024,25 +20035,25 @@
         <v>14067</v>
       </c>
       <c r="B330" s="15" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="C330" s="14">
         <v>4</v>
       </c>
       <c r="G330" s="16" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="H330" s="16" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="L330" s="16" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="P330" s="14">
         <v>999</v>
       </c>
       <c r="Q330" s="14" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="R330" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R330" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q330,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q330))),1))</f>
@@ -20072,22 +20083,22 @@
         <v>14068</v>
       </c>
       <c r="B331" s="15" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="C331" s="14">
         <v>4</v>
       </c>
       <c r="H331" s="16" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="J331" s="16" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="P331" s="14">
         <v>999</v>
       </c>
       <c r="Q331" s="14" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="R331" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R331" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q331,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q331))),1))</f>
@@ -20108,22 +20119,22 @@
         <v>14069</v>
       </c>
       <c r="B332" s="15" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="C332" s="14">
         <v>4</v>
       </c>
       <c r="H332" s="16" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="J332" s="16" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="P332" s="14">
         <v>999</v>
       </c>
       <c r="Q332" s="14" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="R332" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R332" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q332,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q332))),1))</f>
@@ -20144,13 +20155,13 @@
         <v>14070</v>
       </c>
       <c r="B333" s="15" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="C333" s="14">
         <v>4</v>
       </c>
       <c r="H333" s="16" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="L333" s="16" t="s">
         <v>195</v>
@@ -20183,13 +20194,13 @@
         <v>14071</v>
       </c>
       <c r="B334" s="15" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="C334" s="14">
         <v>4</v>
       </c>
       <c r="H334" s="16" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="L334" s="16" t="s">
         <v>195</v>
@@ -20222,16 +20233,16 @@
         <v>14072</v>
       </c>
       <c r="B335" s="15" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="C335" s="14">
         <v>4</v>
       </c>
       <c r="H335" s="16" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="L335" s="16" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="R335" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R335" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q335,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q335))),1))</f>
@@ -20241,7 +20252,7 @@
         <v>20503</v>
       </c>
       <c r="W335" s="14" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="Y335" s="14">
         <v>2</v>
@@ -20258,16 +20269,16 @@
         <v>14073</v>
       </c>
       <c r="B336" s="15" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="C336" s="14">
         <v>4</v>
       </c>
       <c r="H336" s="16" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="Q336" s="14" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="R336" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R336" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q336,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q336))),1))</f>
@@ -20277,7 +20288,7 @@
         <v>20406</v>
       </c>
       <c r="W336" s="14" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="Y336" s="14">
         <v>2</v>
@@ -20297,13 +20308,13 @@
         <v>4</v>
       </c>
       <c r="G337" s="16" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="H337" s="16" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="Q337" s="14" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="R337" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R337" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q337,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q337))),1))</f>
@@ -20313,7 +20324,7 @@
         <v>20503</v>
       </c>
       <c r="W337" s="14" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="Y337" s="14">
         <v>2</v>
@@ -20330,13 +20341,13 @@
         <v>14075</v>
       </c>
       <c r="B338" s="15" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="C338" s="14">
         <v>4</v>
       </c>
       <c r="H338" s="16" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="R338" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R338" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q338,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q338))),1))</f>
@@ -20357,19 +20368,19 @@
         <v>14076</v>
       </c>
       <c r="B339" s="23" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="C339" s="14">
         <v>4</v>
       </c>
       <c r="E339" s="16" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="H339" s="16" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="J339" s="16" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="R339" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R339" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q339,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q339))),1))</f>
@@ -20399,7 +20410,7 @@
         <v>4</v>
       </c>
       <c r="H340" s="16" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="R340" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R340" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q340,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q340))),1))</f>
@@ -20423,7 +20434,7 @@
         <v>4</v>
       </c>
       <c r="H341" s="16" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="L341" s="16" t="s">
         <v>99</v>
@@ -20447,16 +20458,16 @@
         <v>14079</v>
       </c>
       <c r="B342" s="15" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="C342" s="14">
         <v>4</v>
       </c>
       <c r="H342" s="16" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="L342" s="16" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="R342" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R342" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q342,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q342))),1))</f>
@@ -20483,7 +20494,7 @@
         <v>4</v>
       </c>
       <c r="H343" s="16" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="R343" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R343" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q343,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q343))),1))</f>
@@ -20493,7 +20504,7 @@
         <v>20705</v>
       </c>
       <c r="W343" s="14" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="Y343" s="14">
         <v>1</v>
@@ -20513,10 +20524,10 @@
         <v>4</v>
       </c>
       <c r="H344" s="16" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="N344" s="16" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="R344" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R344" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q344,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q344))),1))</f>
@@ -20526,7 +20537,7 @@
         <v>20705</v>
       </c>
       <c r="W344" s="14" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="Y344" s="14">
         <v>1</v>
@@ -20546,10 +20557,10 @@
         <v>4</v>
       </c>
       <c r="H345" s="16" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="N345" s="16" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="R345" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R345" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q345,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q345))),1))</f>
@@ -20559,7 +20570,7 @@
         <v>20705</v>
       </c>
       <c r="W345" s="14" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="Y345" s="14">
         <v>1</v>
@@ -20579,19 +20590,19 @@
         <v>4</v>
       </c>
       <c r="E346" s="16" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="G346" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H346" s="16" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="L346" s="16" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="Q346" s="14" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="R346" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R346" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q346,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q346))),1))</f>
@@ -20615,13 +20626,13 @@
         <v>14084</v>
       </c>
       <c r="B347" s="15" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="C347" s="14">
         <v>4</v>
       </c>
       <c r="E347" s="16" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="R347" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R347" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q347,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q347))),1))</f>
@@ -20636,19 +20647,19 @@
         <v>14085</v>
       </c>
       <c r="B348" s="15" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="C348" s="14">
         <v>4</v>
       </c>
       <c r="E348" s="16" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="H348" s="16" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="L348" s="16" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="Q348" s="14" t="s">
         <v>92</v>
@@ -20661,7 +20672,7 @@
         <v>20604</v>
       </c>
       <c r="W348" s="14" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Y348" s="14">
         <v>2</v>
@@ -20678,19 +20689,19 @@
         <v>14086</v>
       </c>
       <c r="B349" s="15" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="C349" s="14">
         <v>4</v>
       </c>
       <c r="E349" s="16" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="H349" s="16" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="L349" s="16" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="Q349" s="14" t="s">
         <v>92</v>
@@ -20703,7 +20714,7 @@
         <v>20604</v>
       </c>
       <c r="W349" s="14" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Y349" s="14">
         <v>2</v>
@@ -20723,19 +20734,19 @@
         <v>4</v>
       </c>
       <c r="E350" s="16" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="G350" s="16" t="s">
+        <v>1006</v>
+      </c>
+      <c r="H350" s="16" t="s">
+        <v>1007</v>
+      </c>
+      <c r="L350" s="16" t="s">
+        <v>1008</v>
+      </c>
+      <c r="N350" s="16" t="s">
         <v>1009</v>
-      </c>
-      <c r="H350" s="16" t="s">
-        <v>1010</v>
-      </c>
-      <c r="L350" s="16" t="s">
-        <v>1011</v>
-      </c>
-      <c r="N350" s="16" t="s">
-        <v>1012</v>
       </c>
       <c r="O350" s="14">
         <v>3</v>
@@ -20744,7 +20755,7 @@
         <v>12</v>
       </c>
       <c r="Q350" s="14" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="R350" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R350" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q350,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q350))),1))</f>
@@ -20774,7 +20785,7 @@
         <v>14088</v>
       </c>
       <c r="H351" s="16" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="T351" s="14" t="s">
         <v>51</v>
@@ -20817,46 +20828,46 @@
         <v>76</v>
       </c>
       <c r="C1" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="E1" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="C2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D2">
         <f>COUNTIF(Skill!V:V,20701)</f>
         <v>8</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="F2">
         <f>COUNTIF(Skill!V:V,20702)</f>
         <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="H2">
         <f>COUNTIF(Skill!V:V,20402)</f>
         <v>6</v>
       </c>
       <c r="I2" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="J2">
         <f>COUNTIF(Skill!V:V,20307)</f>
         <v>4</v>
       </c>
       <c r="K2" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="L2">
         <f>COUNTIF(Skill!V:V,20705)</f>
@@ -20867,31 +20878,31 @@
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="C3" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="D3">
         <f>COUNTIF(Skill!V:V,20601)</f>
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="F3">
         <f>COUNTIF(Skill!V:V,20602)</f>
         <v>3</v>
       </c>
       <c r="G3" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="H3">
         <f>COUNTIF(Skill!V:V,20603)</f>
         <v>2</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J3">
         <f>COUNTIF(Skill!V:V,20604)</f>
@@ -20902,59 +20913,59 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="C4" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D4">
         <f>COUNTIF(Skill!V:V,20501)</f>
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F4">
         <f>COUNTIF(Skill!V:V,20502)</f>
         <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="H4">
         <f>COUNTIF(Skill!V:V,20503)</f>
         <v>5</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="J4">
         <f>COUNTIF(Skill!V:V,20504)</f>
         <v>2</v>
       </c>
       <c r="K4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="L4">
         <f>COUNTIF(Skill!V:V,20505)</f>
         <v>6</v>
       </c>
       <c r="M4" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="N4">
         <f>COUNTIF(Skill!V:V,20506)</f>
         <v>2</v>
       </c>
       <c r="O4" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="P4">
         <f>COUNTIF(Skill!V:V,20507)</f>
         <v>21</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="R4">
         <f>COUNTIF(Skill!V:V,20508)</f>
@@ -20964,10 +20975,10 @@
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="C5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D5">
         <f>COUNTIF(Skill!V:V,20401)</f>
@@ -20990,35 +21001,35 @@
         <v>6</v>
       </c>
       <c r="K5" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L5">
         <f>COUNTIF(Skill!V:V,20405)</f>
         <v>2</v>
       </c>
       <c r="M5" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="N5">
         <f>COUNTIF(Skill!V:V,20406)</f>
         <v>3</v>
       </c>
       <c r="O5" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="P5">
         <f>COUNTIF(Skill!V:V,20407)</f>
         <v>3</v>
       </c>
       <c r="Q5" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="R5">
         <f>COUNTIF(Skill!V:V,20408)</f>
         <v>0</v>
       </c>
       <c r="S5" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="T5">
         <f>COUNTIF(Skill!V:V,20409)</f>
@@ -21027,7 +21038,7 @@
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="C6" t="s">
         <v>57</v>
@@ -21037,7 +21048,7 @@
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F6">
         <f>COUNTIF(Skill!V:V,20302)</f>
@@ -21051,7 +21062,7 @@
         <v>8</v>
       </c>
       <c r="I6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="J6">
         <f>COUNTIF(Skill!V:V,20304)</f>
@@ -21065,7 +21076,7 @@
         <v>7</v>
       </c>
       <c r="M6" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="N6">
         <f>COUNTIF(Skill!V:V,20306)</f>
@@ -21078,7 +21089,7 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>61</v>
@@ -21095,21 +21106,21 @@
         <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="H7">
         <f>COUNTIF(Skill!V:V,20203)</f>
         <v>8</v>
       </c>
       <c r="I7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J7">
         <f>COUNTIF(Skill!V:V,20204)</f>
         <v>5</v>
       </c>
       <c r="K7" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="L7">
         <f>COUNTIF(Skill!V:V,20205)</f>
@@ -21120,7 +21131,7 @@
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>71</v>
@@ -21143,30 +21154,30 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.15">
       <c r="G13" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="H13" s="25" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="I13" s="25"/>
       <c r="J13" s="25" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="K13" s="25"/>
       <c r="L13" s="25" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="M13" s="25"/>
       <c r="Q13" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="R13" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.15">
       <c r="G14" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="H14" s="25">
         <v>125</v>
@@ -21181,15 +21192,15 @@
       </c>
       <c r="M14" s="25"/>
       <c r="Q14" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="R14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.15">
       <c r="G15" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="H15" s="25">
         <v>120</v>
@@ -21204,15 +21215,15 @@
       </c>
       <c r="M15" s="25"/>
       <c r="Q15" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="R15" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.15">
       <c r="G16" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="H16" s="25">
         <v>115</v>
@@ -21227,15 +21238,15 @@
       </c>
       <c r="M16" s="25"/>
       <c r="Q16" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="R16" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="17" spans="7:15" x14ac:dyDescent="0.15">
       <c r="G17" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="H17" s="25">
         <v>110</v>
@@ -21252,7 +21263,7 @@
     </row>
     <row r="18" spans="7:15" x14ac:dyDescent="0.15">
       <c r="G18" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="H18" s="25">
         <v>105</v>
@@ -21269,7 +21280,7 @@
     </row>
     <row r="19" spans="7:15" x14ac:dyDescent="0.15">
       <c r="G19" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="H19" s="25">
         <v>100</v>
@@ -21290,18 +21301,18 @@
     </row>
     <row r="21" spans="7:15" x14ac:dyDescent="0.15">
       <c r="G21" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="H21" s="25" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="I21" s="25"/>
       <c r="J21" s="25" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="K21" s="25"/>
       <c r="L21" s="25" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="M21" s="26"/>
       <c r="O21" s="10"/>
@@ -21317,30 +21328,30 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:M18"/>
     <mergeCell ref="H19:I19"/>
     <mergeCell ref="J19:K19"/>
     <mergeCell ref="L19:M19"/>
     <mergeCell ref="H21:I21"/>
     <mergeCell ref="J21:K21"/>
     <mergeCell ref="L21:M21"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L14:M14"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21363,31 +21374,31 @@
   <sheetData>
     <row r="3" spans="1:16" x14ac:dyDescent="0.15">
       <c r="B3" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="C3" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="D3" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="H3" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="I3" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="J3" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="K3" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="L3" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="M3" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.15">
@@ -21395,13 +21406,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="C4" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="D4" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.15">
@@ -21409,13 +21420,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="C5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D5" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.15">
@@ -21423,13 +21434,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="C6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D6" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.15">
@@ -21437,13 +21448,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="C7" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="D7" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.15">
@@ -21451,13 +21462,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="C8" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="D8" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.15">
@@ -21465,13 +21476,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="C9" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="D9" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.15">
@@ -21479,13 +21490,13 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="C10" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="D10" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.15">
@@ -21506,7 +21517,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.15">
       <c r="F16" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
@@ -21518,7 +21529,7 @@
     <row r="17" spans="5:16" x14ac:dyDescent="0.15">
       <c r="E17" s="6"/>
       <c r="F17" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="G17" s="6"/>
       <c r="J17" s="6"/>
@@ -21529,7 +21540,7 @@
     <row r="18" spans="5:16" x14ac:dyDescent="0.15">
       <c r="E18" s="6"/>
       <c r="F18" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="G18" s="6"/>
       <c r="J18" s="6"/>
@@ -21683,7 +21694,7 @@
         <v>14</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="Y1" s="3" t="s">
         <v>16</v>
@@ -21708,25 +21719,25 @@
         <v>22</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>29</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>31</v>
@@ -21830,7 +21841,7 @@
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B27" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C27" s="1" cm="1">
         <f t="array" ref="C27">SUMPRODUCT(LEN(P:P)-LEN(SUBSTITUTE(P:P,"↑","")))</f>
@@ -21839,7 +21850,7 @@
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B28" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C28" s="1" cm="1">
         <f t="array" ref="C28">SUMPRODUCT(LEN(P:P)-LEN(SUBSTITUTE(P:P,"↓","")))</f>
@@ -21857,7 +21868,7 @@
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B30" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C30" s="1" cm="1">
         <f t="array" ref="C30">SUMPRODUCT(LEN(P:P)-LEN(SUBSTITUTE(P:P,"→","")))</f>

--- a/Luban/Excel/Skill.xlsx
+++ b/Luban/Excel/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{287D16B4-187A-45D5-A469-2FE1D317DC9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D09194B0-BD74-4EE8-80DA-F2C927A52463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="3525" yWindow="6810" windowWidth="35565" windowHeight="9315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Skill" sheetId="1" r:id="rId1"/>
@@ -642,7 +642,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2046" uniqueCount="1100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2046" uniqueCount="1101">
   <si>
     <t>id</t>
   </si>
@@ -3974,6 +3974,10 @@
   </si>
   <si>
     <t>若处于祖化身状态刚炁消耗变为玄炁消耗</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动期间破与防翻倍，本次行动不会被破招且持续到下个回合开始</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -6012,7 +6016,7 @@
         <v>1</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>149</v>
+        <v>1100</v>
       </c>
       <c r="H26" s="14"/>
       <c r="I26" s="14"/>
@@ -21328,30 +21332,30 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:M16"/>
     <mergeCell ref="H13:I13"/>
     <mergeCell ref="J13:K13"/>
     <mergeCell ref="L13:M13"/>
     <mergeCell ref="H14:I14"/>
     <mergeCell ref="J14:K14"/>
     <mergeCell ref="L14:M14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:M21"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Luban/Excel/Skill.xlsx
+++ b/Luban/Excel/Skill.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF687A8-63CF-4BF4-92A7-66F019111127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03FC4958-5772-4AEB-A756-6E5ADD0C8244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -642,7 +642,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2047" uniqueCount="1116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2047" uniqueCount="1126">
   <si>
     <t>id</t>
   </si>
@@ -1523,9 +1523,6 @@
     <t>迭浪倾川</t>
   </si>
   <si>
-    <t>若持有键超过3个则随机消耗3个键在下一息重复该行动</t>
-  </si>
-  <si>
     <t>←→←</t>
   </si>
   <si>
@@ -1556,9 +1553,6 @@
     <t>←→</t>
   </si>
   <si>
-    <t>在下一息重复该行动，至多3次</t>
-  </si>
-  <si>
     <t>对目标造成135%技的伤害，窃取目标2个增益状态</t>
   </si>
   <si>
@@ -1568,9 +1562,6 @@
     <t>抹残香</t>
   </si>
   <si>
-    <t>对目标造成105%技的伤害，若处于第一息则施加1层僵硬状态和2层破绽状态</t>
-  </si>
-  <si>
     <t>→←</t>
   </si>
   <si>
@@ -1580,18 +1571,12 @@
     <t>对目标造成100%技的伤害，</t>
   </si>
   <si>
-    <t>威力增加0~50的百分比</t>
-  </si>
-  <si>
     <t>至少持有3个不同的键时可使用</t>
   </si>
   <si>
     <t>中</t>
   </si>
   <si>
-    <t>对目标造成50%技的伤害，威力增加0~140的百分比</t>
-  </si>
-  <si>
     <t>大</t>
   </si>
   <si>
@@ -1601,9 +1586,6 @@
     <t>小雷令</t>
   </si>
   <si>
-    <t>对目标造成105%技的伤害，施加3层技衰状态</t>
-  </si>
-  <si>
     <t>玄炁+15</t>
   </si>
   <si>
@@ -1613,42 +1595,18 @@
     <t>燕子回梭</t>
   </si>
   <si>
-    <t>对目标造成95%技的伤害，施加1层缓速状态</t>
-  </si>
-  <si>
     <t>截斗运</t>
   </si>
   <si>
-    <t>对目标造成125%技的伤害，施加2层失持状态</t>
-  </si>
-  <si>
     <t>炁卜</t>
   </si>
   <si>
     <t>苍涛破岳</t>
   </si>
   <si>
-    <t>招式的玄炁消耗转为当前100%</t>
-  </si>
-  <si>
-    <t>本次行动招式威力受到的增幅加倍</t>
-  </si>
-  <si>
-    <t>对目标造成130%技的伤害，追加50%技的伤害</t>
-  </si>
-  <si>
-    <t>（若产生过交锋，未成功且本回合未被其他友方使用过招式则在本回合下次行动时可使用隐藏招式：沉嵩镇渊）</t>
-  </si>
-  <si>
     <t>撕裂魂魄</t>
   </si>
   <si>
-    <t>招式的玄炁消耗转为当前40%，行动加快1息</t>
-  </si>
-  <si>
-    <t>对目标造成160%技的伤害，施加5层玄屏状态，若目标为鬼怪则造成的伤害加倍且消耗其全部刚炁</t>
-  </si>
-  <si>
     <t>随机获得2个键</t>
   </si>
   <si>
@@ -1661,9 +1619,6 @@
     <t>对目标造成130%技的伤害</t>
   </si>
   <si>
-    <t>刚炁+20，本回合下次术杀式威力增加15的百分比</t>
-  </si>
-  <si>
     <t>↓←←→</t>
   </si>
   <si>
@@ -1671,9 +1626,6 @@
   </si>
   <si>
     <t>招式的玄炁消耗转为当前60%，至多60</t>
-  </si>
-  <si>
-    <t>对目标造成135%技的伤害，施加3层寒沁状态</t>
   </si>
   <si>
     <t>野火</t>
@@ -4100,6 +4052,110 @@
   </si>
   <si>
     <t>施加3层术衰状态</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>若持有键超过3个则随机消耗3个键在下一息重复该行动</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>对全部敌手造成100%技的伤害，减少其1个键</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>在下一息重复该行动，至多重复2次</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>随机获得3个键</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>对目标造成125%技的伤害，窃取目标1个增益状态</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>若键的数量大于敌手则威力增加10的百分比，且时窃取目标1个增益状态的效果改为交锋时触发</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>在下一息重复该行动，至多3次</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>对目标造成135%技的伤害，窃取目标2个增益状态</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>对目标造成105%技的伤害，若处于第一息则施加1层僵硬状态和2层破绽状态</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>对目标造成50%技的伤害，威力增加0~140的百分比</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>对目标造成105%技的伤害，施加3层技衰状态</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄炁+15</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动加快1息</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>对目标造成95%技的伤害，施加1层缓速状态</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>对目标造成125%技的伤害，施加2层失持状态</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>招式的玄炁消耗转为当前100%</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>本次行动招式威力受到的增幅加倍</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>威力增加0~50的百分比</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>对目标造成130%技的伤害，追加50%技的伤害</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>（若产生过交锋，未成功且本回合未被其他友方使用过招式则在本回合下次行动时可使用隐藏招式：沉嵩镇渊）</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>招式的玄炁消耗转为当前40%，行动加快1息</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>对目标造成160%技的伤害，施加5层玄屏状态，若目标为鬼怪则造成的伤害加倍且消耗其全部刚炁</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>随机获得2个键</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁+20，本回合下次术杀式威力增加15的百分比</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>招式的玄炁消耗转为当前60%，至多60</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>对目标造成135%技的伤害，施加3层寒沁状态</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -4879,16 +4935,16 @@
         <v>1</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>1069</v>
+        <v>1053</v>
       </c>
       <c r="G4" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J4" s="16" t="s">
-        <v>1043</v>
+        <v>1027</v>
       </c>
       <c r="L4" s="16" t="s">
-        <v>1063</v>
+        <v>1047</v>
       </c>
       <c r="O4" s="14">
         <v>1</v>
@@ -4939,13 +4995,13 @@
         <v>1</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>1061</v>
+        <v>1045</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>1068</v>
+        <v>1052</v>
       </c>
       <c r="L5" s="16" t="s">
-        <v>1063</v>
+        <v>1047</v>
       </c>
       <c r="O5" s="14">
         <v>1</v>
@@ -4999,7 +5055,7 @@
         <v>46</v>
       </c>
       <c r="J6" s="16" t="s">
-        <v>1070</v>
+        <v>1054</v>
       </c>
       <c r="O6" s="14">
         <v>1</v>
@@ -5050,7 +5106,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>1072</v>
+        <v>1056</v>
       </c>
       <c r="J7" s="16" t="s">
         <v>60</v>
@@ -5553,13 +5609,13 @@
         <v>11013</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>1040</v>
+        <v>1024</v>
       </c>
       <c r="C16" s="14">
         <v>1</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>1039</v>
+        <v>1023</v>
       </c>
       <c r="H16" s="16" t="s">
         <v>104</v>
@@ -5616,7 +5672,7 @@
         <v>107</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>1006</v>
+        <v>990</v>
       </c>
       <c r="I17" s="14"/>
       <c r="J17" s="14"/>
@@ -5849,12 +5905,12 @@
         <v>125</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>1049</v>
+        <v>1033</v>
       </c>
       <c r="I21" s="14"/>
       <c r="J21" s="14"/>
       <c r="L21" s="16" t="s">
-        <v>1050</v>
+        <v>1034</v>
       </c>
       <c r="O21" s="14" t="s">
         <v>126</v>
@@ -5908,12 +5964,12 @@
         <v>125</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>1052</v>
+        <v>1036</v>
       </c>
       <c r="I22" s="14"/>
       <c r="J22" s="14"/>
       <c r="L22" s="16" t="s">
-        <v>1051</v>
+        <v>1035</v>
       </c>
       <c r="O22" s="14" t="s">
         <v>126</v>
@@ -5967,7 +6023,7 @@
         <v>130</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>1056</v>
+        <v>1040</v>
       </c>
       <c r="I23" s="14"/>
       <c r="J23" s="14"/>
@@ -5975,7 +6031,7 @@
         <v>131</v>
       </c>
       <c r="N23" s="16" t="s">
-        <v>1071</v>
+        <v>1055</v>
       </c>
       <c r="O23" s="14" t="s">
         <v>126</v>
@@ -6026,10 +6082,10 @@
         <v>1</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>1073</v>
+        <v>1057</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>1074</v>
+        <v>1058</v>
       </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
@@ -6082,15 +6138,15 @@
         <v>1</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>1075</v>
+        <v>1059</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>1056</v>
+        <v>1040</v>
       </c>
       <c r="I25" s="14"/>
       <c r="J25" s="14"/>
       <c r="L25" s="16" t="s">
-        <v>1076</v>
+        <v>1060</v>
       </c>
       <c r="O25" s="14" t="s">
         <v>126</v>
@@ -6141,15 +6197,15 @@
         <v>1</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>1038</v>
+        <v>1022</v>
       </c>
       <c r="H26" s="14"/>
       <c r="I26" s="14"/>
       <c r="J26" s="14" t="s">
-        <v>1077</v>
+        <v>1061</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>1063</v>
+        <v>1047</v>
       </c>
       <c r="O26" s="14">
         <v>1</v>
@@ -6200,15 +6256,15 @@
         <v>1</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>1078</v>
+        <v>1062</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>1079</v>
+        <v>1063</v>
       </c>
       <c r="I27" s="14"/>
       <c r="J27" s="14"/>
       <c r="L27" s="16" t="s">
-        <v>1080</v>
+        <v>1064</v>
       </c>
       <c r="O27" s="14">
         <v>2</v>
@@ -6259,15 +6315,15 @@
         <v>1</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>1041</v>
+        <v>1025</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>1081</v>
+        <v>1065</v>
       </c>
       <c r="I28" s="14"/>
       <c r="J28" s="14"/>
       <c r="L28" s="16" t="s">
-        <v>1082</v>
+        <v>1066</v>
       </c>
       <c r="O28" s="14">
         <v>2</v>
@@ -6318,10 +6374,10 @@
         <v>1</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>1068</v>
+        <v>1052</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>1083</v>
+        <v>1067</v>
       </c>
       <c r="I29" s="14"/>
       <c r="J29" s="14"/>
@@ -6379,7 +6435,7 @@
       <c r="H30" s="14"/>
       <c r="I30" s="14"/>
       <c r="J30" s="14" t="s">
-        <v>1084</v>
+        <v>1068</v>
       </c>
       <c r="O30" s="14">
         <v>1</v>
@@ -6438,7 +6494,7 @@
       <c r="I31" s="14"/>
       <c r="J31" s="14"/>
       <c r="N31" s="16" t="s">
-        <v>1085</v>
+        <v>1069</v>
       </c>
       <c r="O31" s="14">
         <v>1</v>
@@ -6489,12 +6545,12 @@
         <v>1</v>
       </c>
       <c r="H32" s="14" t="s">
-        <v>1086</v>
+        <v>1070</v>
       </c>
       <c r="I32" s="14"/>
       <c r="J32" s="14"/>
       <c r="L32" s="16" t="s">
-        <v>1087</v>
+        <v>1071</v>
       </c>
       <c r="O32" s="14">
         <v>5</v>
@@ -6539,22 +6595,22 @@
         <v>11030</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>1042</v>
+        <v>1026</v>
       </c>
       <c r="C33" s="14">
         <v>1</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>1088</v>
+        <v>1072</v>
       </c>
       <c r="H33" s="14"/>
       <c r="I33" s="14"/>
       <c r="J33" s="14"/>
       <c r="L33" s="16" t="s">
-        <v>1089</v>
+        <v>1073</v>
       </c>
       <c r="N33" s="16" t="s">
-        <v>1090</v>
+        <v>1074</v>
       </c>
       <c r="O33" s="14">
         <v>1</v>
@@ -6605,10 +6661,10 @@
         <v>1</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>1091</v>
+        <v>1075</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>1092</v>
+        <v>1076</v>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="14"/>
@@ -6661,13 +6717,13 @@
         <v>1</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>1009</v>
+        <v>993</v>
       </c>
       <c r="H35" s="14"/>
       <c r="I35" s="14"/>
       <c r="J35" s="14"/>
       <c r="L35" s="16" t="s">
-        <v>1063</v>
+        <v>1047</v>
       </c>
       <c r="O35" s="14" t="s">
         <v>160</v>
@@ -6718,14 +6774,14 @@
         <v>1</v>
       </c>
       <c r="H36" s="16" t="s">
-        <v>1093</v>
+        <v>1077</v>
       </c>
       <c r="I36" s="14"/>
       <c r="L36" s="16" t="s">
-        <v>1094</v>
+        <v>1078</v>
       </c>
       <c r="N36" s="16" t="s">
-        <v>1034</v>
+        <v>1018</v>
       </c>
       <c r="O36" s="14">
         <v>1</v>
@@ -6776,10 +6832,10 @@
         <v>1</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>1095</v>
+        <v>1079</v>
       </c>
       <c r="H37" s="16" t="s">
-        <v>1096</v>
+        <v>1080</v>
       </c>
       <c r="I37" s="14"/>
       <c r="J37" s="14"/>
@@ -6826,7 +6882,7 @@
         <v>1</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>1097</v>
+        <v>1081</v>
       </c>
       <c r="H38" s="14" t="s">
         <v>168</v>
@@ -6879,7 +6935,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="16" t="s">
-        <v>1057</v>
+        <v>1041</v>
       </c>
       <c r="O39" s="14" t="s">
         <v>171</v>
@@ -6921,11 +6977,11 @@
         <v>1</v>
       </c>
       <c r="H40" s="14" t="s">
-        <v>1053</v>
+        <v>1037</v>
       </c>
       <c r="I40" s="14"/>
       <c r="J40" s="16" t="s">
-        <v>1098</v>
+        <v>1082</v>
       </c>
       <c r="O40" s="14" t="s">
         <v>171</v>
@@ -6970,11 +7026,11 @@
         <v>137</v>
       </c>
       <c r="H41" s="14" t="s">
-        <v>1044</v>
+        <v>1028</v>
       </c>
       <c r="I41" s="14"/>
       <c r="J41" s="16" t="s">
-        <v>1043</v>
+        <v>1027</v>
       </c>
       <c r="O41" s="14" t="s">
         <v>175</v>
@@ -7010,17 +7066,17 @@
         <v>11039</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>1033</v>
+        <v>1017</v>
       </c>
       <c r="C42" s="14">
         <v>1</v>
       </c>
       <c r="F42" s="14"/>
       <c r="G42" s="16" t="s">
-        <v>1046</v>
+        <v>1030</v>
       </c>
       <c r="H42" s="14" t="s">
-        <v>1045</v>
+        <v>1029</v>
       </c>
       <c r="N42" s="16" t="s">
         <v>176</v>
@@ -7065,7 +7121,7 @@
         <v>1</v>
       </c>
       <c r="H43" s="16" t="s">
-        <v>1058</v>
+        <v>1042</v>
       </c>
       <c r="O43" s="14" t="s">
         <v>171</v>
@@ -7110,12 +7166,12 @@
         <v>125</v>
       </c>
       <c r="H44" s="14" t="s">
-        <v>1047</v>
+        <v>1031</v>
       </c>
       <c r="I44" s="14"/>
       <c r="J44" s="14"/>
       <c r="L44" s="16" t="s">
-        <v>1048</v>
+        <v>1032</v>
       </c>
       <c r="O44" s="14" t="s">
         <v>126</v>
@@ -7163,12 +7219,12 @@
         <v>125</v>
       </c>
       <c r="H45" s="14" t="s">
-        <v>1054</v>
+        <v>1038</v>
       </c>
       <c r="I45" s="14"/>
       <c r="J45" s="14"/>
       <c r="L45" s="16" t="s">
-        <v>1055</v>
+        <v>1039</v>
       </c>
       <c r="O45" s="14" t="s">
         <v>126</v>
@@ -7213,15 +7269,15 @@
         <v>1</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>1075</v>
+        <v>1059</v>
       </c>
       <c r="H46" s="14" t="s">
-        <v>1056</v>
+        <v>1040</v>
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14"/>
       <c r="L46" s="16" t="s">
-        <v>1048</v>
+        <v>1032</v>
       </c>
       <c r="O46" s="14" t="s">
         <v>126</v>
@@ -7266,15 +7322,15 @@
         <v>1</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>1075</v>
+        <v>1059</v>
       </c>
       <c r="H47" s="14" t="s">
-        <v>1056</v>
+        <v>1040</v>
       </c>
       <c r="I47" s="14"/>
       <c r="J47" s="14"/>
       <c r="L47" s="16" t="s">
-        <v>1055</v>
+        <v>1039</v>
       </c>
       <c r="O47" s="14" t="s">
         <v>126</v>
@@ -7372,7 +7428,7 @@
         <v>1</v>
       </c>
       <c r="H49" s="16" t="s">
-        <v>1058</v>
+        <v>1042</v>
       </c>
       <c r="O49" s="14" t="s">
         <v>171</v>
@@ -7414,11 +7470,11 @@
         <v>1</v>
       </c>
       <c r="H50" s="14" t="s">
-        <v>1053</v>
+        <v>1037</v>
       </c>
       <c r="I50" s="14"/>
       <c r="J50" s="16" t="s">
-        <v>1099</v>
+        <v>1083</v>
       </c>
       <c r="O50" s="14" t="s">
         <v>171</v>
@@ -7457,7 +7513,7 @@
         <v>1</v>
       </c>
       <c r="H51" s="16" t="s">
-        <v>1059</v>
+        <v>1043</v>
       </c>
       <c r="I51" s="14"/>
       <c r="J51" s="14"/>
@@ -7483,7 +7539,7 @@
         <v>1</v>
       </c>
       <c r="H52" s="14" t="s">
-        <v>1060</v>
+        <v>1044</v>
       </c>
       <c r="I52" s="14"/>
       <c r="J52" s="14"/>
@@ -7512,18 +7568,18 @@
         <v>1</v>
       </c>
       <c r="E53" s="16" t="s">
-        <v>1062</v>
+        <v>1046</v>
       </c>
       <c r="G53" s="16" t="s">
-        <v>1100</v>
+        <v>1084</v>
       </c>
       <c r="H53" s="14"/>
       <c r="I53" s="14"/>
       <c r="J53" s="16" t="s">
-        <v>1043</v>
+        <v>1027</v>
       </c>
       <c r="L53" s="16" t="s">
-        <v>1061</v>
+        <v>1045</v>
       </c>
       <c r="Q53" s="14" t="s">
         <v>179</v>
@@ -7571,7 +7627,7 @@
         <v>182</v>
       </c>
       <c r="L54" s="16" t="s">
-        <v>1063</v>
+        <v>1047</v>
       </c>
       <c r="O54" s="14">
         <v>1</v>
@@ -7613,12 +7669,12 @@
         <v>185</v>
       </c>
       <c r="H55" s="16" t="s">
-        <v>1065</v>
+        <v>1049</v>
       </c>
       <c r="I55" s="14"/>
       <c r="J55" s="14"/>
       <c r="L55" s="16" t="s">
-        <v>1064</v>
+        <v>1048</v>
       </c>
       <c r="Q55" s="14" t="s">
         <v>186</v>
@@ -7660,13 +7716,13 @@
       <c r="F56" s="14"/>
       <c r="G56" s="14"/>
       <c r="H56" s="14" t="s">
-        <v>1066</v>
+        <v>1050</v>
       </c>
       <c r="I56" s="14"/>
       <c r="J56" s="14"/>
       <c r="K56" s="14"/>
       <c r="L56" s="14" t="s">
-        <v>1067</v>
+        <v>1051</v>
       </c>
       <c r="M56" s="14"/>
       <c r="N56" s="14" t="s">
@@ -7973,7 +8029,7 @@
       <c r="I64" s="14"/>
       <c r="J64" s="14"/>
       <c r="L64" s="16" t="s">
-        <v>1101</v>
+        <v>1085</v>
       </c>
       <c r="O64" s="14">
         <v>1</v>
@@ -8136,7 +8192,7 @@
         <v>2</v>
       </c>
       <c r="E67" s="16" t="s">
-        <v>1102</v>
+        <v>1086</v>
       </c>
       <c r="H67" s="14" t="s">
         <v>202</v>
@@ -8144,7 +8200,7 @@
       <c r="I67" s="14"/>
       <c r="J67" s="14"/>
       <c r="L67" s="16" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
       <c r="O67" s="14">
         <v>1</v>
@@ -8313,12 +8369,12 @@
         <v>2</v>
       </c>
       <c r="H70" s="14" t="s">
-        <v>1104</v>
+        <v>1088</v>
       </c>
       <c r="I70" s="14"/>
       <c r="J70" s="14"/>
       <c r="L70" s="16" t="s">
-        <v>1101</v>
+        <v>1085</v>
       </c>
       <c r="O70" s="14">
         <v>3</v>
@@ -8369,16 +8425,16 @@
         <v>2</v>
       </c>
       <c r="E71" s="16" t="s">
-        <v>1107</v>
+        <v>1091</v>
       </c>
       <c r="H71" s="16" t="s">
         <v>223</v>
       </c>
       <c r="J71" s="16" t="s">
-        <v>1106</v>
+        <v>1090</v>
       </c>
       <c r="L71" s="16" t="s">
-        <v>1105</v>
+        <v>1089</v>
       </c>
       <c r="O71" s="14">
         <v>6</v>
@@ -8429,13 +8485,13 @@
         <v>2</v>
       </c>
       <c r="G72" s="16" t="s">
-        <v>1013</v>
+        <v>997</v>
       </c>
       <c r="H72" s="16" t="s">
         <v>231</v>
       </c>
       <c r="L72" s="16" t="s">
-        <v>1108</v>
+        <v>1092</v>
       </c>
       <c r="O72" s="14">
         <v>1</v>
@@ -9043,10 +9099,10 @@
         <v>2</v>
       </c>
       <c r="G84" s="16" t="s">
-        <v>1109</v>
+        <v>1093</v>
       </c>
       <c r="H84" s="16" t="s">
-        <v>1110</v>
+        <v>1094</v>
       </c>
       <c r="P84" s="14">
         <v>7</v>
@@ -9174,10 +9230,10 @@
         <v>2</v>
       </c>
       <c r="H87" s="16" t="s">
-        <v>1111</v>
+        <v>1095</v>
       </c>
       <c r="J87" s="16" t="s">
-        <v>1008</v>
+        <v>992</v>
       </c>
       <c r="Q87" s="14" t="s">
         <v>290</v>
@@ -9222,10 +9278,10 @@
         <v>2</v>
       </c>
       <c r="G88" s="16" t="s">
-        <v>1113</v>
+        <v>1097</v>
       </c>
       <c r="H88" s="16" t="s">
-        <v>1112</v>
+        <v>1096</v>
       </c>
       <c r="I88" s="14"/>
       <c r="Q88" s="14" t="s">
@@ -9271,17 +9327,17 @@
         <v>2</v>
       </c>
       <c r="H89" s="16" t="s">
-        <v>1114</v>
+        <v>1098</v>
       </c>
       <c r="I89" s="14"/>
       <c r="J89" s="14" t="s">
-        <v>1115</v>
+        <v>1099</v>
       </c>
       <c r="L89" s="16" t="s">
+        <v>1100</v>
+      </c>
+      <c r="Q89" s="14" t="s">
         <v>293</v>
-      </c>
-      <c r="Q89" s="14" t="s">
-        <v>294</v>
       </c>
       <c r="R89" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R89" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q89,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q89))),1))</f>
@@ -9305,24 +9361,24 @@
         <v>12027</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C90" s="14">
         <v>2</v>
       </c>
       <c r="E90" s="16" t="s">
-        <v>1073</v>
+        <v>1057</v>
       </c>
       <c r="H90" s="16" t="s">
-        <v>296</v>
+        <v>1101</v>
       </c>
       <c r="I90" s="14"/>
       <c r="J90" s="14"/>
       <c r="L90" s="16" t="s">
+        <v>1102</v>
+      </c>
+      <c r="Q90" s="14" t="s">
         <v>297</v>
-      </c>
-      <c r="Q90" s="14" t="s">
-        <v>298</v>
       </c>
       <c r="R90" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R90" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q90,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q90))),1))</f>
@@ -9358,23 +9414,23 @@
         <v>12028</v>
       </c>
       <c r="B91" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C91" s="14">
         <v>2</v>
       </c>
       <c r="E91" s="16" t="s">
-        <v>300</v>
+        <v>1103</v>
       </c>
       <c r="H91" s="16" t="s">
-        <v>301</v>
+        <v>1104</v>
       </c>
       <c r="I91" s="14"/>
       <c r="J91" s="16" t="s">
+        <v>1105</v>
+      </c>
+      <c r="Q91" s="14" t="s">
         <v>302</v>
-      </c>
-      <c r="Q91" s="14" t="s">
-        <v>303</v>
       </c>
       <c r="R91" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R91" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q91,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q91))),1))</f>
@@ -9410,7 +9466,7 @@
         <v>12029</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C92" s="14">
         <v>2</v>
@@ -9419,15 +9475,15 @@
         <v>134</v>
       </c>
       <c r="H92" s="16" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I92" s="14"/>
       <c r="J92" s="14"/>
       <c r="L92" s="16" t="s">
-        <v>304</v>
+        <v>1106</v>
       </c>
       <c r="Q92" s="14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="R92" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R92" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q92,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q92))),1))</f>
@@ -9463,23 +9519,23 @@
         <v>12030</v>
       </c>
       <c r="B93" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C93" s="14">
         <v>2</v>
       </c>
       <c r="E93" s="16" t="s">
-        <v>300</v>
+        <v>1103</v>
       </c>
       <c r="H93" s="16" t="s">
-        <v>305</v>
+        <v>1107</v>
       </c>
       <c r="I93" s="14"/>
       <c r="J93" s="16" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="Q93" s="14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="R93" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R93" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q93,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q93))),1))</f>
@@ -9515,18 +9571,18 @@
         <v>12031</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C94" s="14">
         <v>2</v>
       </c>
       <c r="H94" s="14" t="s">
-        <v>308</v>
+        <v>1108</v>
       </c>
       <c r="I94" s="14"/>
       <c r="J94" s="14"/>
       <c r="Q94" s="14" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="R94" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R94" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q94,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q94))),1))</f>
@@ -9562,22 +9618,22 @@
         <v>12032</v>
       </c>
       <c r="B95" s="15" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C95" s="14">
         <v>2</v>
       </c>
       <c r="G95" s="16" t="s">
-        <v>1014</v>
+        <v>998</v>
       </c>
       <c r="H95" s="22" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="J95" s="16" t="s">
-        <v>312</v>
+        <v>1117</v>
       </c>
       <c r="N95" s="16" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="R95" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R95" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q95,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q95))),1))</f>
@@ -9607,19 +9663,19 @@
         <v>12033</v>
       </c>
       <c r="B96" s="15" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C96" s="14">
         <v>2</v>
       </c>
       <c r="G96" s="16" t="s">
-        <v>1015</v>
+        <v>999</v>
       </c>
       <c r="H96" s="16" t="s">
-        <v>315</v>
+        <v>1109</v>
       </c>
       <c r="N96" s="16" t="s">
-        <v>1017</v>
+        <v>1001</v>
       </c>
       <c r="R96" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R96" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q96,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q96))),1))</f>
@@ -9649,16 +9705,16 @@
         <v>12034</v>
       </c>
       <c r="B97" s="15" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C97" s="14">
         <v>2</v>
       </c>
       <c r="G97" s="16" t="s">
-        <v>1016</v>
+        <v>1000</v>
       </c>
       <c r="H97" s="22" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="R97" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R97" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q97,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q97))),1))</f>
@@ -9688,16 +9744,16 @@
         <v>12035</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C98" s="14">
         <v>2</v>
       </c>
       <c r="H98" s="16" t="s">
-        <v>319</v>
+        <v>1110</v>
       </c>
       <c r="L98" s="16" t="s">
-        <v>320</v>
+        <v>1111</v>
       </c>
       <c r="R98" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R98" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q98,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q98))),1))</f>
@@ -9716,7 +9772,7 @@
         <v>20302</v>
       </c>
       <c r="W98" s="14" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="Y98" s="14">
         <v>2</v>
@@ -9733,19 +9789,19 @@
         <v>12036</v>
       </c>
       <c r="B99" s="15" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C99" s="14">
         <v>2</v>
       </c>
       <c r="E99" s="16" t="s">
-        <v>81</v>
+        <v>1112</v>
       </c>
       <c r="H99" s="16" t="s">
-        <v>323</v>
+        <v>1113</v>
       </c>
       <c r="L99" s="16" t="s">
-        <v>203</v>
+        <v>1085</v>
       </c>
       <c r="R99" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R99" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q99,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q99))),1))</f>
@@ -9781,13 +9837,13 @@
         <v>12037</v>
       </c>
       <c r="B100" s="15" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="C100" s="14">
         <v>2</v>
       </c>
       <c r="H100" s="16" t="s">
-        <v>325</v>
+        <v>1114</v>
       </c>
       <c r="R100" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R100" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q100,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q100))),1))</f>
@@ -9806,7 +9862,7 @@
         <v>20304</v>
       </c>
       <c r="W100" s="14" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="Y100" s="14">
         <v>1</v>
@@ -9823,22 +9879,22 @@
         <v>12038</v>
       </c>
       <c r="B101" s="15" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="C101" s="14">
         <v>2</v>
       </c>
       <c r="E101" s="16" t="s">
-        <v>328</v>
+        <v>1115</v>
       </c>
       <c r="G101" s="16" t="s">
-        <v>329</v>
+        <v>1116</v>
       </c>
       <c r="H101" s="16" t="s">
-        <v>330</v>
+        <v>1118</v>
       </c>
       <c r="J101" s="16" t="s">
-        <v>331</v>
+        <v>1119</v>
       </c>
       <c r="N101" s="16" t="s">
         <v>72</v>
@@ -9877,22 +9933,22 @@
         <v>12039</v>
       </c>
       <c r="B102" s="15" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="C102" s="14">
         <v>2</v>
       </c>
       <c r="E102" s="16" t="s">
-        <v>333</v>
+        <v>1120</v>
       </c>
       <c r="H102" s="16" t="s">
-        <v>334</v>
+        <v>1121</v>
       </c>
       <c r="L102" s="16" t="s">
-        <v>335</v>
+        <v>1122</v>
       </c>
       <c r="Q102" s="14" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="R102" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R102" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q102,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q102))),1))</f>
@@ -9928,19 +9984,19 @@
         <v>12040</v>
       </c>
       <c r="B103" s="15" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="C103" s="14">
         <v>2</v>
       </c>
       <c r="H103" s="16" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="L103" s="16" t="s">
-        <v>339</v>
+        <v>1123</v>
       </c>
       <c r="Q103" s="14" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="R103" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R103" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q103,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q103))),1))</f>
@@ -9976,19 +10032,19 @@
         <v>12041</v>
       </c>
       <c r="B104" s="15" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="C104" s="14">
         <v>2</v>
       </c>
       <c r="E104" s="16" t="s">
-        <v>342</v>
+        <v>1124</v>
       </c>
       <c r="H104" s="16" t="s">
-        <v>343</v>
+        <v>1125</v>
       </c>
       <c r="L104" s="16" t="s">
-        <v>214</v>
+        <v>1087</v>
       </c>
       <c r="R104" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R104" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q104,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q104))),1))</f>
@@ -10024,16 +10080,16 @@
         <v>12042</v>
       </c>
       <c r="B105" s="15" t="s">
-        <v>344</v>
+        <v>328</v>
       </c>
       <c r="C105" s="14">
         <v>2</v>
       </c>
       <c r="H105" s="16" t="s">
-        <v>345</v>
+        <v>329</v>
       </c>
       <c r="L105" s="16" t="s">
-        <v>346</v>
+        <v>330</v>
       </c>
       <c r="R105" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R105" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q105,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q105))),1))</f>
@@ -10069,19 +10125,19 @@
         <v>12043</v>
       </c>
       <c r="B106" s="15" t="s">
-        <v>347</v>
+        <v>331</v>
       </c>
       <c r="C106" s="14">
         <v>2</v>
       </c>
       <c r="E106" s="16" t="s">
-        <v>348</v>
+        <v>332</v>
       </c>
       <c r="H106" s="16" t="s">
-        <v>349</v>
+        <v>333</v>
       </c>
       <c r="J106" s="16" t="s">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="L106" s="16" t="s">
         <v>214</v>
@@ -10120,16 +10176,16 @@
         <v>12044</v>
       </c>
       <c r="B107" s="15" t="s">
-        <v>351</v>
+        <v>335</v>
       </c>
       <c r="C107" s="14">
         <v>2</v>
       </c>
       <c r="H107" s="16" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="Q107" s="14" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="R107" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R107" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q107,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q107))),1))</f>
@@ -10165,7 +10221,7 @@
         <v>12045</v>
       </c>
       <c r="B108" s="15" t="s">
-        <v>354</v>
+        <v>338</v>
       </c>
       <c r="C108" s="14">
         <v>2</v>
@@ -10174,13 +10230,13 @@
         <v>218</v>
       </c>
       <c r="J108" s="16" t="s">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="L108" s="16" t="s">
         <v>154</v>
       </c>
       <c r="Q108" s="14" t="s">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="R108" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R108" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q108,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q108))),1))</f>
@@ -10216,25 +10272,25 @@
         <v>12046</v>
       </c>
       <c r="B109" s="15" t="s">
-        <v>357</v>
+        <v>341</v>
       </c>
       <c r="C109" s="14">
         <v>2</v>
       </c>
       <c r="E109" s="16" t="s">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="H109" s="16" t="s">
-        <v>359</v>
+        <v>343</v>
       </c>
       <c r="J109" s="16" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="N109" s="16" t="s">
         <v>72</v>
       </c>
       <c r="Q109" s="14" t="s">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="R109" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R109" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q109,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q109))),1))</f>
@@ -10270,13 +10326,13 @@
         <v>12047</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="C110" s="14">
         <v>2</v>
       </c>
       <c r="H110" s="16" t="s">
-        <v>363</v>
+        <v>347</v>
       </c>
       <c r="Q110" s="14" t="s">
         <v>246</v>
@@ -10318,7 +10374,7 @@
         <v>2</v>
       </c>
       <c r="E111" s="16" t="s">
-        <v>364</v>
+        <v>348</v>
       </c>
       <c r="H111" s="16" t="s">
         <v>206</v>
@@ -10327,7 +10383,7 @@
         <v>203</v>
       </c>
       <c r="Q111" s="14" t="s">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="R111" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R111" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q111,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q111))),1))</f>
@@ -10363,7 +10419,7 @@
         <v>12049</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="C112" s="14">
         <v>2</v>
@@ -10372,10 +10428,10 @@
         <v>210</v>
       </c>
       <c r="J112" s="16" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="Q112" s="14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="R112" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R112" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q112,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q112))),1))</f>
@@ -10411,22 +10467,22 @@
         <v>12050</v>
       </c>
       <c r="B113" s="15" t="s">
-        <v>368</v>
+        <v>352</v>
       </c>
       <c r="C113" s="14">
         <v>2</v>
       </c>
       <c r="E113" s="16" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="H113" s="16" t="s">
-        <v>370</v>
+        <v>354</v>
       </c>
       <c r="N113" s="16" t="s">
         <v>72</v>
       </c>
       <c r="Q113" s="14" t="s">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="R113" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R113" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q113,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q113))),1))</f>
@@ -10462,16 +10518,16 @@
         <v>12051</v>
       </c>
       <c r="B114" s="15" t="s">
-        <v>372</v>
+        <v>356</v>
       </c>
       <c r="C114" s="14">
         <v>2</v>
       </c>
       <c r="E114" s="16" t="s">
-        <v>373</v>
+        <v>357</v>
       </c>
       <c r="H114" s="16" t="s">
-        <v>374</v>
+        <v>358</v>
       </c>
       <c r="I114" s="14"/>
       <c r="J114" s="14"/>
@@ -10515,13 +10571,13 @@
         <v>12052</v>
       </c>
       <c r="B115" s="15" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="C115" s="14">
         <v>2</v>
       </c>
       <c r="H115" s="16" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="N115" s="16" t="s">
         <v>170</v>
@@ -10533,7 +10589,7 @@
         <v>4</v>
       </c>
       <c r="Q115" s="14" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="R115" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R115" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q115,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q115))),1))</f>
@@ -10552,7 +10608,7 @@
         <v>20307</v>
       </c>
       <c r="W115" s="14" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="Y115" s="14">
         <v>2</v>
@@ -10569,7 +10625,7 @@
         <v>12053</v>
       </c>
       <c r="B116" s="15" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
       <c r="C116" s="14">
         <v>2</v>
@@ -10580,10 +10636,10 @@
       <c r="I116" s="14"/>
       <c r="J116" s="14"/>
       <c r="L116" s="16" t="s">
-        <v>1030</v>
+        <v>1014</v>
       </c>
       <c r="N116" s="16" t="s">
-        <v>1037</v>
+        <v>1021</v>
       </c>
       <c r="O116" s="14">
         <v>1</v>
@@ -10608,7 +10664,7 @@
         <v>20507</v>
       </c>
       <c r="W116" s="14" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="Y116" s="14">
         <v>1</v>
@@ -10625,18 +10681,18 @@
         <v>12054</v>
       </c>
       <c r="B117" s="15" t="s">
-        <v>381</v>
+        <v>365</v>
       </c>
       <c r="C117" s="14">
         <v>2</v>
       </c>
       <c r="H117" s="16" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="I117" s="14"/>
       <c r="J117" s="14"/>
       <c r="L117" s="16" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="O117" s="14">
         <v>1</v>
@@ -10661,7 +10717,7 @@
         <v>20507</v>
       </c>
       <c r="W117" s="14" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="Y117" s="14">
         <v>2</v>
@@ -10681,12 +10737,12 @@
         <v>2</v>
       </c>
       <c r="H118" s="16" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
       <c r="I118" s="14"/>
       <c r="J118" s="14"/>
       <c r="L118" s="16" t="s">
-        <v>385</v>
+        <v>369</v>
       </c>
       <c r="O118" s="14">
         <v>6</v>
@@ -10695,7 +10751,7 @@
         <v>999</v>
       </c>
       <c r="Q118" s="14" t="s">
-        <v>386</v>
+        <v>370</v>
       </c>
       <c r="R118" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R118" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q118,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q118))),1))</f>
@@ -10711,7 +10767,7 @@
         <v>20507</v>
       </c>
       <c r="W118" s="14" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="Y118" s="14">
         <v>1</v>
@@ -10731,10 +10787,10 @@
         <v>2</v>
       </c>
       <c r="H119" s="16" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="L119" s="16" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="N119" s="16" t="s">
         <v>170</v>
@@ -10746,7 +10802,7 @@
         <v>8</v>
       </c>
       <c r="Q119" s="14" t="s">
-        <v>389</v>
+        <v>373</v>
       </c>
       <c r="R119" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R119" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q119,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q119))),1))</f>
@@ -10762,7 +10818,7 @@
         <v>20507</v>
       </c>
       <c r="W119" s="14" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="Y119" s="14">
         <v>1</v>
@@ -10779,21 +10835,21 @@
         <v>12057</v>
       </c>
       <c r="B120" s="15" t="s">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="C120" s="14">
         <v>2</v>
       </c>
       <c r="H120" s="14" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="I120" s="14"/>
       <c r="J120" s="14"/>
       <c r="L120" s="16" t="s">
-        <v>1027</v>
+        <v>1011</v>
       </c>
       <c r="N120" s="16" t="s">
-        <v>392</v>
+        <v>376</v>
       </c>
       <c r="P120" s="14">
         <v>999</v>
@@ -10826,16 +10882,16 @@
         <v>12058</v>
       </c>
       <c r="B121" s="15" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="C121" s="14">
         <v>2</v>
       </c>
       <c r="G121" s="16" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="H121" s="16" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="P121" s="14">
         <v>999</v>
@@ -10868,17 +10924,17 @@
         <v>12059</v>
       </c>
       <c r="B122" s="15" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="C122" s="14">
         <v>2</v>
       </c>
       <c r="H122" s="16" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="I122" s="14"/>
       <c r="J122" s="14" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="P122" s="14">
         <v>999</v>
@@ -10911,21 +10967,21 @@
         <v>12060</v>
       </c>
       <c r="B123" s="15" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="C123" s="14">
         <v>2</v>
       </c>
       <c r="H123" s="16" t="s">
-        <v>399</v>
+        <v>383</v>
       </c>
       <c r="I123" s="14"/>
       <c r="J123" s="14"/>
       <c r="N123" s="16" t="s">
-        <v>400</v>
+        <v>384</v>
       </c>
       <c r="Q123" s="14" t="s">
-        <v>401</v>
+        <v>385</v>
       </c>
       <c r="R123" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R123" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q123,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q123))),1))</f>
@@ -10970,7 +11026,7 @@
         <v>289</v>
       </c>
       <c r="J124" s="16" t="s">
-        <v>402</v>
+        <v>386</v>
       </c>
       <c r="Q124" s="14" t="s">
         <v>290</v>
@@ -11009,7 +11065,7 @@
         <v>2</v>
       </c>
       <c r="G125" s="16" t="s">
-        <v>403</v>
+        <v>387</v>
       </c>
       <c r="H125" s="16" t="s">
         <v>291</v>
@@ -11046,23 +11102,23 @@
         <v>12063</v>
       </c>
       <c r="B126" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="C126" s="14">
+        <v>2</v>
+      </c>
+      <c r="G126" s="16" t="s">
         <v>299</v>
       </c>
-      <c r="C126" s="14">
-        <v>2</v>
-      </c>
-      <c r="G126" s="16" t="s">
+      <c r="H126" s="16" t="s">
         <v>300</v>
-      </c>
-      <c r="H126" s="16" t="s">
-        <v>301</v>
       </c>
       <c r="I126" s="14"/>
       <c r="J126" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q126" s="14" t="s">
         <v>302</v>
-      </c>
-      <c r="Q126" s="14" t="s">
-        <v>303</v>
       </c>
       <c r="R126" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R126" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q126,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q126))),1))</f>
@@ -11092,23 +11148,23 @@
         <v>12064</v>
       </c>
       <c r="B127" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="C127" s="14">
+        <v>2</v>
+      </c>
+      <c r="G127" s="16" t="s">
         <v>299</v>
       </c>
-      <c r="C127" s="14">
-        <v>2</v>
-      </c>
-      <c r="G127" s="16" t="s">
-        <v>300</v>
-      </c>
       <c r="H127" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="I127" s="14"/>
       <c r="J127" s="16" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="Q127" s="14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="R127" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R127" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q127,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q127))),1))</f>
@@ -11138,27 +11194,27 @@
         <v>12065</v>
       </c>
       <c r="B128" s="15" t="s">
-        <v>404</v>
+        <v>388</v>
       </c>
       <c r="C128" s="14">
         <v>2</v>
       </c>
       <c r="H128" s="16" t="s">
-        <v>405</v>
+        <v>389</v>
       </c>
       <c r="I128" s="14"/>
       <c r="J128" s="14"/>
       <c r="L128" s="16" t="s">
-        <v>406</v>
+        <v>390</v>
       </c>
       <c r="N128" s="16" t="s">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="O128" s="14">
         <v>3</v>
       </c>
       <c r="Q128" s="14" t="s">
-        <v>408</v>
+        <v>392</v>
       </c>
       <c r="R128" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R128" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q128,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q128))),1))</f>
@@ -11177,7 +11233,7 @@
         <v>20501</v>
       </c>
       <c r="W128" s="14" t="s">
-        <v>409</v>
+        <v>393</v>
       </c>
       <c r="Y128" s="14">
         <v>2</v>
@@ -11194,7 +11250,7 @@
         <v>12066</v>
       </c>
       <c r="B129" s="15" t="s">
-        <v>410</v>
+        <v>394</v>
       </c>
       <c r="C129" s="14">
         <v>2</v>
@@ -11203,17 +11259,17 @@
         <v>222</v>
       </c>
       <c r="H129" s="16" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="I129" s="14"/>
       <c r="J129" s="14" t="s">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="N129" s="16" t="s">
         <v>72</v>
       </c>
       <c r="Q129" s="14" t="s">
-        <v>412</v>
+        <v>396</v>
       </c>
       <c r="R129" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R129" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q129,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q129))),1))</f>
@@ -11232,7 +11288,7 @@
         <v>20405</v>
       </c>
       <c r="W129" s="14" t="s">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="Y129" s="14">
         <v>1</v>
@@ -11249,27 +11305,27 @@
         <v>12067</v>
       </c>
       <c r="B130" s="15" t="s">
-        <v>414</v>
+        <v>398</v>
       </c>
       <c r="C130" s="14">
         <v>2</v>
       </c>
       <c r="E130" s="16" t="s">
-        <v>415</v>
+        <v>399</v>
       </c>
       <c r="G130" s="16" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
       <c r="H130" s="16" t="s">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="I130" s="14"/>
       <c r="J130" s="14"/>
       <c r="L130" s="16" t="s">
-        <v>418</v>
+        <v>402</v>
       </c>
       <c r="N130" s="16" t="s">
-        <v>419</v>
+        <v>403</v>
       </c>
       <c r="R130" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R130" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q130,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q130))),1))</f>
@@ -11288,7 +11344,7 @@
         <v>20503</v>
       </c>
       <c r="W130" s="14" t="s">
-        <v>420</v>
+        <v>404</v>
       </c>
       <c r="Y130" s="14">
         <v>1</v>
@@ -11305,16 +11361,16 @@
         <v>12068</v>
       </c>
       <c r="B131" s="15" t="s">
-        <v>421</v>
+        <v>405</v>
       </c>
       <c r="C131" s="14">
         <v>2</v>
       </c>
       <c r="G131" s="16" t="s">
-        <v>1010</v>
+        <v>994</v>
       </c>
       <c r="H131" s="16" t="s">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="I131" s="14"/>
       <c r="J131" s="14"/>
@@ -11335,7 +11391,7 @@
         <v>20503</v>
       </c>
       <c r="W131" s="14" t="s">
-        <v>420</v>
+        <v>404</v>
       </c>
       <c r="Y131" s="14">
         <v>2</v>
@@ -11352,20 +11408,20 @@
         <v>12069</v>
       </c>
       <c r="B132" s="15" t="s">
-        <v>423</v>
+        <v>407</v>
       </c>
       <c r="C132" s="14">
         <v>2</v>
       </c>
       <c r="E132" s="16" t="s">
-        <v>424</v>
+        <v>408</v>
       </c>
       <c r="H132" s="16" t="s">
         <v>210</v>
       </c>
       <c r="I132" s="14"/>
       <c r="J132" s="14" t="s">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="Q132" s="14" t="s">
         <v>266</v>
@@ -11387,7 +11443,7 @@
         <v>20503</v>
       </c>
       <c r="W132" s="14" t="s">
-        <v>420</v>
+        <v>404</v>
       </c>
       <c r="Y132" s="14">
         <v>2</v>
@@ -11404,13 +11460,13 @@
         <v>12070</v>
       </c>
       <c r="B133" s="20" t="s">
-        <v>426</v>
+        <v>410</v>
       </c>
       <c r="C133" s="14">
         <v>2</v>
       </c>
       <c r="E133" s="16" t="s">
-        <v>1039</v>
+        <v>1023</v>
       </c>
       <c r="H133" s="16" t="s">
         <v>104</v>
@@ -11422,7 +11478,7 @@
         <v>0</v>
       </c>
       <c r="Q133" s="14" t="s">
-        <v>427</v>
+        <v>411</v>
       </c>
       <c r="R133" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R133" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q133,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q133))),1))</f>
@@ -11452,19 +11508,19 @@
         <v>12071</v>
       </c>
       <c r="B134" s="15" t="s">
-        <v>428</v>
+        <v>412</v>
       </c>
       <c r="C134" s="14">
         <v>2</v>
       </c>
       <c r="E134" s="16" t="s">
-        <v>429</v>
+        <v>413</v>
       </c>
       <c r="H134" s="16" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="N134" s="16" t="s">
-        <v>431</v>
+        <v>415</v>
       </c>
       <c r="R134" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R134" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q134,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q134))),1))</f>
@@ -11483,7 +11539,7 @@
         <v>20409</v>
       </c>
       <c r="W134" s="14" t="s">
-        <v>432</v>
+        <v>416</v>
       </c>
       <c r="Y134" s="14">
         <v>1</v>
@@ -11500,13 +11556,13 @@
         <v>12072</v>
       </c>
       <c r="B135" s="15" t="s">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="C135" s="14">
         <v>2</v>
       </c>
       <c r="H135" s="16" t="s">
-        <v>1032</v>
+        <v>1016</v>
       </c>
       <c r="I135" s="14"/>
       <c r="J135" s="14"/>
@@ -11535,7 +11591,7 @@
         <v>2</v>
       </c>
       <c r="H136" s="14" t="s">
-        <v>434</v>
+        <v>418</v>
       </c>
       <c r="I136" s="14"/>
       <c r="J136" s="14"/>
@@ -11561,20 +11617,20 @@
         <v>12074</v>
       </c>
       <c r="B137" s="15" t="s">
-        <v>435</v>
+        <v>419</v>
       </c>
       <c r="C137" s="14">
         <v>2</v>
       </c>
       <c r="H137" s="16" t="s">
-        <v>436</v>
+        <v>420</v>
       </c>
       <c r="I137" s="14"/>
       <c r="J137" s="14" t="s">
-        <v>437</v>
+        <v>421</v>
       </c>
       <c r="N137" s="16" t="s">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="R137" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R137" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q137,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q137))),1))</f>
@@ -11598,20 +11654,20 @@
         <v>12075</v>
       </c>
       <c r="B138" s="15" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
       <c r="C138" s="14">
         <v>2</v>
       </c>
       <c r="H138" s="16" t="s">
-        <v>436</v>
+        <v>420</v>
       </c>
       <c r="I138" s="14"/>
       <c r="J138" s="14" t="s">
-        <v>440</v>
+        <v>424</v>
       </c>
       <c r="N138" s="16" t="s">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="R138" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R138" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q138,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q138))),1))</f>
@@ -11638,15 +11694,15 @@
         <v>2</v>
       </c>
       <c r="H139" s="16" t="s">
-        <v>441</v>
+        <v>425</v>
       </c>
       <c r="I139" s="14"/>
       <c r="J139" s="14"/>
       <c r="L139" s="14" t="s">
-        <v>442</v>
+        <v>426</v>
       </c>
       <c r="Q139" s="14" t="s">
-        <v>443</v>
+        <v>427</v>
       </c>
       <c r="R139" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R139" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q139,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q139))),1))</f>
@@ -11685,18 +11741,18 @@
         <v>2</v>
       </c>
       <c r="E140" s="16" t="s">
-        <v>444</v>
+        <v>428</v>
       </c>
       <c r="H140" s="16" t="s">
-        <v>445</v>
+        <v>429</v>
       </c>
       <c r="I140" s="14"/>
       <c r="J140" s="14"/>
       <c r="L140" s="16" t="s">
-        <v>346</v>
+        <v>330</v>
       </c>
       <c r="N140" s="16" t="s">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="P140" s="14">
         <v>3</v>
@@ -11741,10 +11797,10 @@
         <v>2</v>
       </c>
       <c r="E141" s="16" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="H141" s="14" t="s">
-        <v>447</v>
+        <v>431</v>
       </c>
       <c r="I141" s="14"/>
       <c r="J141" s="14"/>
@@ -11755,7 +11811,7 @@
         <v>1</v>
       </c>
       <c r="Q141" s="14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="R141" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R141" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q141,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q141))),1))</f>
@@ -11788,15 +11844,15 @@
     </row>
     <row r="142" spans="1:27" ht="33" x14ac:dyDescent="0.15">
       <c r="H142" s="16" t="s">
-        <v>448</v>
+        <v>432</v>
       </c>
       <c r="I142" s="14"/>
       <c r="J142" s="14"/>
       <c r="L142" s="16" t="s">
-        <v>449</v>
+        <v>433</v>
       </c>
       <c r="N142" s="16" t="s">
-        <v>450</v>
+        <v>434</v>
       </c>
       <c r="O142" s="14">
         <v>7</v>
@@ -11814,7 +11870,7 @@
         <v>20507</v>
       </c>
       <c r="W142" s="14" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="Y142" s="14">
         <v>7</v>
@@ -11836,18 +11892,18 @@
         <v>13001</v>
       </c>
       <c r="B144" s="20" t="s">
-        <v>451</v>
+        <v>435</v>
       </c>
       <c r="C144" s="14">
         <v>3</v>
       </c>
       <c r="H144" s="14" t="s">
-        <v>452</v>
+        <v>436</v>
       </c>
       <c r="I144" s="14"/>
       <c r="J144" s="14"/>
       <c r="L144" s="16" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="O144" s="14">
         <v>1</v>
@@ -11892,18 +11948,18 @@
         <v>13002</v>
       </c>
       <c r="B145" s="20" t="s">
-        <v>453</v>
+        <v>437</v>
       </c>
       <c r="C145" s="14">
         <v>3</v>
       </c>
       <c r="H145" s="14" t="s">
-        <v>454</v>
+        <v>438</v>
       </c>
       <c r="I145" s="14"/>
       <c r="J145" s="14"/>
       <c r="L145" s="16" t="s">
-        <v>455</v>
+        <v>439</v>
       </c>
       <c r="O145" s="14">
         <v>1</v>
@@ -11948,18 +12004,18 @@
         <v>13003</v>
       </c>
       <c r="B146" s="20" t="s">
-        <v>456</v>
+        <v>440</v>
       </c>
       <c r="C146" s="14">
         <v>3</v>
       </c>
       <c r="H146" s="14" t="s">
-        <v>457</v>
+        <v>441</v>
       </c>
       <c r="I146" s="14"/>
       <c r="J146" s="14"/>
       <c r="L146" s="16" t="s">
-        <v>458</v>
+        <v>442</v>
       </c>
       <c r="O146" s="14">
         <v>1</v>
@@ -12004,21 +12060,21 @@
         <v>13004</v>
       </c>
       <c r="B147" s="20" t="s">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="C147" s="14">
         <v>3</v>
       </c>
       <c r="E147" s="16" t="s">
-        <v>460</v>
+        <v>444</v>
       </c>
       <c r="H147" s="14" t="s">
-        <v>452</v>
+        <v>436</v>
       </c>
       <c r="I147" s="14"/>
       <c r="J147" s="14"/>
       <c r="L147" s="16" t="s">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="O147" s="14">
         <v>1</v>
@@ -12063,21 +12119,21 @@
         <v>13005</v>
       </c>
       <c r="B148" s="20" t="s">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="C148" s="14">
         <v>3</v>
       </c>
       <c r="E148" s="16" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="H148" s="14" t="s">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="I148" s="14"/>
       <c r="J148" s="14"/>
       <c r="L148" s="16" t="s">
-        <v>465</v>
+        <v>449</v>
       </c>
       <c r="O148" s="14">
         <v>1</v>
@@ -12122,21 +12178,21 @@
         <v>13006</v>
       </c>
       <c r="B149" s="20" t="s">
-        <v>466</v>
+        <v>450</v>
       </c>
       <c r="C149" s="14">
         <v>3</v>
       </c>
       <c r="E149" s="16" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="H149" s="14" t="s">
-        <v>468</v>
+        <v>452</v>
       </c>
       <c r="I149" s="14"/>
       <c r="J149" s="14"/>
       <c r="L149" s="16" t="s">
-        <v>469</v>
+        <v>453</v>
       </c>
       <c r="O149" s="14">
         <v>1</v>
@@ -12181,23 +12237,23 @@
         <v>13007</v>
       </c>
       <c r="B150" s="15" t="s">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="C150" s="14">
         <v>3</v>
       </c>
       <c r="E150" s="14" t="s">
-        <v>471</v>
+        <v>455</v>
       </c>
       <c r="F150" s="14"/>
       <c r="G150" s="14"/>
       <c r="H150" s="14" t="s">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="I150" s="14"/>
       <c r="J150" s="14"/>
       <c r="L150" s="16" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="O150" s="14">
         <v>5</v>
@@ -12242,19 +12298,19 @@
         <v>13008</v>
       </c>
       <c r="B151" s="20" t="s">
-        <v>472</v>
+        <v>456</v>
       </c>
       <c r="C151" s="14">
         <v>3</v>
       </c>
       <c r="E151" s="16" t="s">
-        <v>473</v>
+        <v>457</v>
       </c>
       <c r="G151" s="16" t="s">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="H151" s="14" t="s">
-        <v>454</v>
+        <v>438</v>
       </c>
       <c r="I151" s="14"/>
       <c r="J151" s="14"/>
@@ -12268,7 +12324,7 @@
         <v>4</v>
       </c>
       <c r="Q151" s="14" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="R151" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R151" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q151,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q151))),1))</f>
@@ -12304,18 +12360,18 @@
         <v>13009</v>
       </c>
       <c r="B152" s="20" t="s">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="C152" s="14">
         <v>3</v>
       </c>
       <c r="H152" s="14" t="s">
-        <v>452</v>
+        <v>436</v>
       </c>
       <c r="I152" s="14"/>
       <c r="J152" s="14"/>
       <c r="L152" s="16" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="O152" s="14">
         <v>1</v>
@@ -12324,7 +12380,7 @@
         <v>4</v>
       </c>
       <c r="Q152" s="14" t="s">
-        <v>477</v>
+        <v>461</v>
       </c>
       <c r="R152" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R152" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q152,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q152))),1))</f>
@@ -12360,18 +12416,18 @@
         <v>13010</v>
       </c>
       <c r="B153" s="20" t="s">
-        <v>478</v>
+        <v>462</v>
       </c>
       <c r="C153" s="14">
         <v>3</v>
       </c>
       <c r="H153" s="14" t="s">
-        <v>452</v>
+        <v>436</v>
       </c>
       <c r="I153" s="14"/>
       <c r="J153" s="14"/>
       <c r="L153" s="16" t="s">
-        <v>479</v>
+        <v>463</v>
       </c>
       <c r="O153" s="14">
         <v>1</v>
@@ -12380,7 +12436,7 @@
         <v>5</v>
       </c>
       <c r="Q153" s="14" t="s">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="R153" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R153" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q153,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q153))),1))</f>
@@ -12416,19 +12472,19 @@
         <v>13011</v>
       </c>
       <c r="B154" s="15" t="s">
-        <v>481</v>
+        <v>465</v>
       </c>
       <c r="C154" s="14">
         <v>3</v>
       </c>
       <c r="E154" s="16" t="s">
-        <v>1011</v>
+        <v>995</v>
       </c>
       <c r="G154" s="16" t="s">
         <v>149</v>
       </c>
       <c r="H154" s="14" t="s">
-        <v>482</v>
+        <v>466</v>
       </c>
       <c r="I154" s="14"/>
       <c r="J154" s="14"/>
@@ -12439,7 +12495,7 @@
         <v>6</v>
       </c>
       <c r="Q154" s="14" t="s">
-        <v>483</v>
+        <v>467</v>
       </c>
       <c r="R154" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R154" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q154,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q154))),1))</f>
@@ -12475,16 +12531,16 @@
         <v>13012</v>
       </c>
       <c r="B155" s="15" t="s">
-        <v>484</v>
+        <v>468</v>
       </c>
       <c r="C155" s="14">
         <v>3</v>
       </c>
       <c r="H155" s="16" t="s">
-        <v>485</v>
+        <v>469</v>
       </c>
       <c r="L155" s="16" t="s">
-        <v>486</v>
+        <v>470</v>
       </c>
       <c r="O155" s="14">
         <v>1</v>
@@ -12526,18 +12582,18 @@
         <v>13013</v>
       </c>
       <c r="B156" s="20" t="s">
-        <v>487</v>
+        <v>471</v>
       </c>
       <c r="C156" s="14">
         <v>3</v>
       </c>
       <c r="E156" s="14" t="s">
-        <v>488</v>
+        <v>472</v>
       </c>
       <c r="F156" s="14"/>
       <c r="G156" s="14"/>
       <c r="H156" s="16" t="s">
-        <v>489</v>
+        <v>473</v>
       </c>
       <c r="N156" s="16" t="s">
         <v>72</v>
@@ -12549,7 +12605,7 @@
         <v>6</v>
       </c>
       <c r="Q156" s="14" t="s">
-        <v>490</v>
+        <v>474</v>
       </c>
       <c r="R156" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R156" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q156,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q156))),1))</f>
@@ -12585,18 +12641,18 @@
         <v>13014</v>
       </c>
       <c r="B157" s="20" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="C157" s="14">
         <v>3</v>
       </c>
       <c r="E157" s="14" t="s">
-        <v>492</v>
+        <v>476</v>
       </c>
       <c r="F157" s="14"/>
       <c r="G157" s="14"/>
       <c r="H157" s="14" t="s">
-        <v>454</v>
+        <v>438</v>
       </c>
       <c r="I157" s="14"/>
       <c r="J157" s="14"/>
@@ -12637,13 +12693,13 @@
         <v>13015</v>
       </c>
       <c r="B158" s="20" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="C158" s="14">
         <v>3</v>
       </c>
       <c r="H158" s="16" t="s">
-        <v>494</v>
+        <v>478</v>
       </c>
       <c r="P158" s="14">
         <v>14</v>
@@ -12665,7 +12721,7 @@
         <v>20504</v>
       </c>
       <c r="W158" s="14" t="s">
-        <v>495</v>
+        <v>479</v>
       </c>
       <c r="Y158" s="14">
         <v>1</v>
@@ -12682,13 +12738,13 @@
         <v>13016</v>
       </c>
       <c r="B159" s="20" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
       <c r="C159" s="14">
         <v>3</v>
       </c>
       <c r="E159" s="16" t="s">
-        <v>1039</v>
+        <v>1023</v>
       </c>
       <c r="H159" s="16" t="s">
         <v>104</v>
@@ -12700,7 +12756,7 @@
         <v>0</v>
       </c>
       <c r="Q159" s="14" t="s">
-        <v>497</v>
+        <v>481</v>
       </c>
       <c r="R159" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R159" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q159,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q159))),1))</f>
@@ -12730,13 +12786,13 @@
         <v>13017</v>
       </c>
       <c r="B160" s="20" t="s">
-        <v>498</v>
+        <v>482</v>
       </c>
       <c r="C160" s="14">
         <v>3</v>
       </c>
       <c r="H160" s="14" t="s">
-        <v>499</v>
+        <v>483</v>
       </c>
       <c r="I160" s="14"/>
       <c r="J160" s="14"/>
@@ -12771,13 +12827,13 @@
         <v>13018</v>
       </c>
       <c r="B161" s="20" t="s">
-        <v>500</v>
+        <v>484</v>
       </c>
       <c r="C161" s="14">
         <v>3</v>
       </c>
       <c r="H161" s="16" t="s">
-        <v>501</v>
+        <v>485</v>
       </c>
       <c r="L161" s="16" t="s">
         <v>165</v>
@@ -12799,7 +12855,7 @@
         <v>20402</v>
       </c>
       <c r="W161" s="14" t="s">
-        <v>502</v>
+        <v>486</v>
       </c>
       <c r="Y161" s="14">
         <v>1</v>
@@ -12816,13 +12872,13 @@
         <v>13019</v>
       </c>
       <c r="B162" s="15" t="s">
-        <v>503</v>
+        <v>487</v>
       </c>
       <c r="C162" s="14">
         <v>3</v>
       </c>
       <c r="H162" s="16" t="s">
-        <v>504</v>
+        <v>488</v>
       </c>
       <c r="O162" s="14">
         <v>5</v>
@@ -12838,7 +12894,7 @@
         <v>20402</v>
       </c>
       <c r="W162" s="14" t="s">
-        <v>505</v>
+        <v>489</v>
       </c>
       <c r="Y162" s="14">
         <v>1</v>
@@ -12855,16 +12911,16 @@
         <v>13020</v>
       </c>
       <c r="B163" s="15" t="s">
-        <v>506</v>
+        <v>490</v>
       </c>
       <c r="C163" s="14">
         <v>3</v>
       </c>
       <c r="H163" s="16" t="s">
-        <v>501</v>
+        <v>485</v>
       </c>
       <c r="J163" s="16" t="s">
-        <v>507</v>
+        <v>491</v>
       </c>
       <c r="R163" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R163" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q163,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q163))),1))</f>
@@ -12877,7 +12933,7 @@
         <v>20601</v>
       </c>
       <c r="W163" s="14" t="s">
-        <v>508</v>
+        <v>492</v>
       </c>
       <c r="Y163" s="14">
         <v>1</v>
@@ -12894,19 +12950,19 @@
         <v>13021</v>
       </c>
       <c r="B164" s="20" t="s">
-        <v>509</v>
+        <v>493</v>
       </c>
       <c r="C164" s="14">
         <v>3</v>
       </c>
       <c r="G164" s="16" t="s">
-        <v>1026</v>
+        <v>1010</v>
       </c>
       <c r="H164" s="16" t="s">
-        <v>510</v>
+        <v>494</v>
       </c>
       <c r="N164" s="16" t="s">
-        <v>511</v>
+        <v>495</v>
       </c>
       <c r="R164" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R164" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q164,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q164))),1))</f>
@@ -12939,16 +12995,16 @@
         <v>13022</v>
       </c>
       <c r="B165" s="15" t="s">
-        <v>512</v>
+        <v>496</v>
       </c>
       <c r="C165" s="14">
         <v>3</v>
       </c>
       <c r="H165" s="16" t="s">
-        <v>513</v>
+        <v>497</v>
       </c>
       <c r="L165" s="16" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="Q165" s="14" t="s">
         <v>54</v>
@@ -12984,7 +13040,7 @@
         <v>13023</v>
       </c>
       <c r="B166" s="15" t="s">
-        <v>514</v>
+        <v>498</v>
       </c>
       <c r="C166" s="14">
         <v>3</v>
@@ -13011,18 +13067,18 @@
         <v>13024</v>
       </c>
       <c r="B167" s="20" t="s">
-        <v>515</v>
+        <v>499</v>
       </c>
       <c r="C167" s="14">
         <v>3</v>
       </c>
       <c r="H167" s="14" t="s">
-        <v>452</v>
+        <v>436</v>
       </c>
       <c r="I167" s="14"/>
       <c r="J167" s="14"/>
       <c r="L167" s="16" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="O167" s="14">
         <v>1</v>
@@ -13058,20 +13114,20 @@
         <v>13025</v>
       </c>
       <c r="B168" s="15" t="s">
-        <v>516</v>
+        <v>500</v>
       </c>
       <c r="C168" s="14">
         <v>3</v>
       </c>
       <c r="G168" s="14" t="s">
-        <v>1018</v>
+        <v>1002</v>
       </c>
       <c r="H168" s="14" t="s">
-        <v>517</v>
+        <v>501</v>
       </c>
       <c r="I168" s="14"/>
       <c r="L168" s="16" t="s">
-        <v>455</v>
+        <v>439</v>
       </c>
       <c r="R168" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R168" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q168,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q168))),1))</f>
@@ -13087,7 +13143,7 @@
         <v>20506</v>
       </c>
       <c r="W168" s="14" t="s">
-        <v>518</v>
+        <v>502</v>
       </c>
       <c r="Y168" s="14">
         <v>1</v>
@@ -13104,13 +13160,13 @@
         <v>13026</v>
       </c>
       <c r="B169" s="15" t="s">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="C169" s="14">
         <v>3</v>
       </c>
       <c r="E169" s="16" t="s">
-        <v>520</v>
+        <v>504</v>
       </c>
       <c r="R169" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R169" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q169,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q169))),1))</f>
@@ -13123,7 +13179,7 @@
         <v>20506</v>
       </c>
       <c r="W169" s="14" t="s">
-        <v>518</v>
+        <v>502</v>
       </c>
       <c r="Y169" s="14">
         <v>1</v>
@@ -13140,22 +13196,22 @@
         <v>13027</v>
       </c>
       <c r="B170" s="20" t="s">
-        <v>521</v>
+        <v>505</v>
       </c>
       <c r="C170" s="14">
         <v>3</v>
       </c>
       <c r="H170" s="16" t="s">
-        <v>522</v>
+        <v>506</v>
       </c>
       <c r="L170" s="16" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="N170" s="16" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="Q170" s="14" t="s">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="R170" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R170" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q170,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q170))),1))</f>
@@ -13188,22 +13244,22 @@
         <v>13028</v>
       </c>
       <c r="B171" s="15" t="s">
-        <v>525</v>
+        <v>509</v>
       </c>
       <c r="C171" s="14">
         <v>3</v>
       </c>
       <c r="E171" s="16" t="s">
-        <v>492</v>
+        <v>476</v>
       </c>
       <c r="H171" s="16" t="s">
-        <v>526</v>
+        <v>510</v>
       </c>
       <c r="L171" s="16" t="s">
-        <v>527</v>
+        <v>511</v>
       </c>
       <c r="Q171" s="14" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="R171" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R171" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q171,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q171))),1))</f>
@@ -13236,24 +13292,24 @@
         <v>13029</v>
       </c>
       <c r="B172" s="20" t="s">
-        <v>528</v>
+        <v>512</v>
       </c>
       <c r="C172" s="14">
         <v>3</v>
       </c>
       <c r="H172" s="14" t="s">
-        <v>529</v>
+        <v>513</v>
       </c>
       <c r="I172" s="14"/>
       <c r="J172" s="14"/>
       <c r="L172" s="16" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="P172" s="14">
         <v>3</v>
       </c>
       <c r="Q172" s="14" t="s">
-        <v>530</v>
+        <v>514</v>
       </c>
       <c r="R172" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R172" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q172,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q172))),1))</f>
@@ -13286,22 +13342,22 @@
         <v>13030</v>
       </c>
       <c r="B173" s="20" t="s">
-        <v>531</v>
+        <v>515</v>
       </c>
       <c r="C173" s="14">
         <v>3</v>
       </c>
       <c r="H173" s="16" t="s">
-        <v>532</v>
+        <v>516</v>
       </c>
       <c r="L173" s="16" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="P173" s="14">
         <v>3</v>
       </c>
       <c r="Q173" s="14" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="R173" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R173" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q173,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q173))),1))</f>
@@ -13334,25 +13390,25 @@
         <v>13031</v>
       </c>
       <c r="B174" s="20" t="s">
-        <v>533</v>
+        <v>517</v>
       </c>
       <c r="C174" s="14">
         <v>3</v>
       </c>
       <c r="E174" s="16" t="s">
-        <v>534</v>
+        <v>518</v>
       </c>
       <c r="H174" s="16" t="s">
-        <v>457</v>
+        <v>441</v>
       </c>
       <c r="L174" s="16" t="s">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="N174" s="16" t="s">
         <v>72</v>
       </c>
       <c r="Q174" s="14" t="s">
-        <v>536</v>
+        <v>520</v>
       </c>
       <c r="R174" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R174" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q174,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q174))),1))</f>
@@ -13385,16 +13441,16 @@
         <v>13032</v>
       </c>
       <c r="B175" s="20" t="s">
-        <v>537</v>
+        <v>521</v>
       </c>
       <c r="C175" s="14">
         <v>3</v>
       </c>
       <c r="E175" s="16" t="s">
-        <v>492</v>
+        <v>476</v>
       </c>
       <c r="H175" s="14" t="s">
-        <v>538</v>
+        <v>522</v>
       </c>
       <c r="I175" s="14"/>
       <c r="J175" s="14"/>
@@ -13435,19 +13491,19 @@
         <v>13033</v>
       </c>
       <c r="B176" s="20" t="s">
-        <v>539</v>
+        <v>523</v>
       </c>
       <c r="C176" s="14">
         <v>3</v>
       </c>
       <c r="H176" s="16" t="s">
-        <v>540</v>
+        <v>524</v>
       </c>
       <c r="L176" s="16" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="Q176" s="14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="R176" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R176" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q176,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q176))),1))</f>
@@ -13483,10 +13539,10 @@
         <v>3</v>
       </c>
       <c r="H177" s="16" t="s">
-        <v>541</v>
+        <v>525</v>
       </c>
       <c r="L177" s="16" t="s">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="Q177" s="14" t="s">
         <v>251</v>
@@ -13522,13 +13578,13 @@
         <v>3</v>
       </c>
       <c r="E178" s="16" t="s">
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="H178" s="14" t="s">
-        <v>468</v>
+        <v>452</v>
       </c>
       <c r="J178" s="16" t="s">
-        <v>544</v>
+        <v>528</v>
       </c>
       <c r="R178" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R178" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q178,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q178))),1))</f>
@@ -13558,16 +13614,16 @@
         <v>13036</v>
       </c>
       <c r="B179" s="15" t="s">
-        <v>545</v>
+        <v>529</v>
       </c>
       <c r="C179" s="14">
         <v>3</v>
       </c>
       <c r="H179" s="14" t="s">
-        <v>546</v>
+        <v>530</v>
       </c>
       <c r="Q179" s="14" t="s">
-        <v>547</v>
+        <v>531</v>
       </c>
       <c r="R179" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R179" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q179,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q179))),1))</f>
@@ -13603,10 +13659,10 @@
         <v>3</v>
       </c>
       <c r="E180" s="16" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
       <c r="H180" s="14" t="s">
-        <v>549</v>
+        <v>533</v>
       </c>
       <c r="R180" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R180" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q180,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q180))),1))</f>
@@ -13636,22 +13692,22 @@
         <v>13038</v>
       </c>
       <c r="B181" s="15" t="s">
-        <v>550</v>
+        <v>534</v>
       </c>
       <c r="C181" s="14">
         <v>3</v>
       </c>
       <c r="H181" s="14" t="s">
-        <v>551</v>
+        <v>535</v>
       </c>
       <c r="J181" s="16" t="s">
-        <v>552</v>
+        <v>536</v>
       </c>
       <c r="P181" s="14">
         <v>999</v>
       </c>
       <c r="Q181" s="14" t="s">
-        <v>553</v>
+        <v>537</v>
       </c>
       <c r="R181" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R181" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q181,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q181))),1))</f>
@@ -13684,19 +13740,19 @@
         <v>13039</v>
       </c>
       <c r="B182" s="15" t="s">
-        <v>554</v>
+        <v>538</v>
       </c>
       <c r="C182" s="14">
         <v>3</v>
       </c>
       <c r="G182" s="16" t="s">
-        <v>1007</v>
+        <v>991</v>
       </c>
       <c r="H182" s="14" t="s">
-        <v>555</v>
+        <v>539</v>
       </c>
       <c r="N182" s="16" t="s">
-        <v>556</v>
+        <v>540</v>
       </c>
       <c r="R182" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R182" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q182,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q182))),1))</f>
@@ -13729,22 +13785,22 @@
         <v>13040</v>
       </c>
       <c r="B183" s="15" t="s">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="C183" s="14">
         <v>3</v>
       </c>
       <c r="G183" s="16" t="s">
-        <v>1019</v>
+        <v>1003</v>
       </c>
       <c r="H183" s="14" t="s">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="L183" s="16" t="s">
-        <v>558</v>
+        <v>542</v>
       </c>
       <c r="N183" s="16" t="s">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="R183" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R183" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q183,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q183))),1))</f>
@@ -13757,7 +13813,7 @@
         <v>20504</v>
       </c>
       <c r="W183" s="14" t="s">
-        <v>495</v>
+        <v>479</v>
       </c>
       <c r="Y183" s="14">
         <v>1</v>
@@ -13774,25 +13830,25 @@
         <v>13041</v>
       </c>
       <c r="B184" s="15" t="s">
-        <v>560</v>
+        <v>544</v>
       </c>
       <c r="C184" s="14">
         <v>3</v>
       </c>
       <c r="H184" s="14" t="s">
-        <v>561</v>
+        <v>545</v>
       </c>
       <c r="L184" s="16" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="N184" s="16" t="s">
-        <v>562</v>
+        <v>546</v>
       </c>
       <c r="P184" s="14">
         <v>7</v>
       </c>
       <c r="Q184" s="14" t="s">
-        <v>563</v>
+        <v>547</v>
       </c>
       <c r="R184" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R184" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q184,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q184))),1))</f>
@@ -13825,22 +13881,22 @@
         <v>13042</v>
       </c>
       <c r="B185" s="15" t="s">
-        <v>564</v>
+        <v>548</v>
       </c>
       <c r="C185" s="14">
         <v>3</v>
       </c>
       <c r="H185" s="14" t="s">
-        <v>565</v>
+        <v>549</v>
       </c>
       <c r="N185" s="16" t="s">
-        <v>566</v>
+        <v>550</v>
       </c>
       <c r="P185" s="14">
         <v>7</v>
       </c>
       <c r="Q185" s="14" t="s">
-        <v>567</v>
+        <v>551</v>
       </c>
       <c r="R185" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R185" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q185,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q185))),1))</f>
@@ -13873,22 +13929,22 @@
         <v>13043</v>
       </c>
       <c r="B186" s="15" t="s">
-        <v>550</v>
+        <v>534</v>
       </c>
       <c r="C186" s="14">
         <v>3</v>
       </c>
       <c r="H186" s="14" t="s">
-        <v>568</v>
+        <v>552</v>
       </c>
       <c r="J186" s="16" t="s">
-        <v>1020</v>
+        <v>1004</v>
       </c>
       <c r="P186" s="14">
         <v>999</v>
       </c>
       <c r="Q186" s="14" t="s">
-        <v>553</v>
+        <v>537</v>
       </c>
       <c r="R186" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R186" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q186,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q186))),1))</f>
@@ -13921,22 +13977,22 @@
         <v>13044</v>
       </c>
       <c r="B187" s="15" t="s">
-        <v>569</v>
+        <v>553</v>
       </c>
       <c r="C187" s="14">
         <v>3</v>
       </c>
       <c r="H187" s="14" t="s">
-        <v>517</v>
+        <v>501</v>
       </c>
       <c r="J187" s="16" t="s">
-        <v>570</v>
+        <v>554</v>
       </c>
       <c r="P187" s="14">
         <v>999</v>
       </c>
       <c r="Q187" s="14" t="s">
-        <v>571</v>
+        <v>555</v>
       </c>
       <c r="R187" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R187" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q187,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q187))),1))</f>
@@ -13969,22 +14025,22 @@
         <v>13045</v>
       </c>
       <c r="B188" s="15" t="s">
-        <v>569</v>
+        <v>553</v>
       </c>
       <c r="C188" s="14">
         <v>3</v>
       </c>
       <c r="H188" s="14" t="s">
-        <v>510</v>
+        <v>494</v>
       </c>
       <c r="J188" s="16" t="s">
-        <v>570</v>
+        <v>554</v>
       </c>
       <c r="P188" s="14">
         <v>999</v>
       </c>
       <c r="Q188" s="14" t="s">
-        <v>571</v>
+        <v>555</v>
       </c>
       <c r="R188" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R188" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q188,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q188))),1))</f>
@@ -14017,22 +14073,22 @@
         <v>13046</v>
       </c>
       <c r="B189" s="20" t="s">
-        <v>572</v>
+        <v>556</v>
       </c>
       <c r="C189" s="14">
         <v>3</v>
       </c>
       <c r="G189" s="16" t="s">
-        <v>1012</v>
+        <v>996</v>
       </c>
       <c r="H189" s="14" t="s">
-        <v>522</v>
+        <v>506</v>
       </c>
       <c r="L189" s="16" t="s">
-        <v>573</v>
+        <v>557</v>
       </c>
       <c r="N189" s="16" t="s">
-        <v>574</v>
+        <v>558</v>
       </c>
       <c r="O189" s="14">
         <v>2</v>
@@ -14068,19 +14124,19 @@
         <v>13047</v>
       </c>
       <c r="B190" s="15" t="s">
-        <v>575</v>
+        <v>559</v>
       </c>
       <c r="C190" s="14">
         <v>3</v>
       </c>
       <c r="H190" s="14" t="s">
-        <v>549</v>
+        <v>533</v>
       </c>
       <c r="J190" s="16" t="s">
-        <v>576</v>
+        <v>560</v>
       </c>
       <c r="Q190" s="14" t="s">
-        <v>577</v>
+        <v>561</v>
       </c>
       <c r="R190" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R190" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q190,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q190))),1))</f>
@@ -14113,25 +14169,25 @@
         <v>13048</v>
       </c>
       <c r="B191" s="15" t="s">
-        <v>578</v>
+        <v>562</v>
       </c>
       <c r="C191" s="14">
         <v>3</v>
       </c>
       <c r="E191" s="16" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="H191" s="16" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="L191" s="16" t="s">
-        <v>579</v>
+        <v>563</v>
       </c>
       <c r="N191" s="16" t="s">
         <v>72</v>
       </c>
       <c r="Q191" s="14" t="s">
-        <v>580</v>
+        <v>564</v>
       </c>
       <c r="R191" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R191" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q191,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q191))),1))</f>
@@ -14164,16 +14220,16 @@
         <v>13049</v>
       </c>
       <c r="B192" s="15" t="s">
-        <v>581</v>
+        <v>565</v>
       </c>
       <c r="C192" s="14">
         <v>3</v>
       </c>
       <c r="H192" s="16" t="s">
-        <v>522</v>
+        <v>506</v>
       </c>
       <c r="L192" s="16" t="s">
-        <v>582</v>
+        <v>566</v>
       </c>
       <c r="O192" s="14">
         <v>2</v>
@@ -14182,7 +14238,7 @@
         <v>12</v>
       </c>
       <c r="Q192" s="14" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="R192" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R192" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q192,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q192))),1))</f>
@@ -14215,16 +14271,16 @@
         <v>13050</v>
       </c>
       <c r="B193" s="15" t="s">
-        <v>583</v>
+        <v>567</v>
       </c>
       <c r="C193" s="14">
         <v>3</v>
       </c>
       <c r="H193" s="16" t="s">
-        <v>454</v>
+        <v>438</v>
       </c>
       <c r="L193" s="16" t="s">
-        <v>582</v>
+        <v>566</v>
       </c>
       <c r="O193" s="14">
         <v>2</v>
@@ -14233,7 +14289,7 @@
         <v>6</v>
       </c>
       <c r="Q193" s="14" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="R193" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R193" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q193,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q193))),1))</f>
@@ -14266,16 +14322,16 @@
         <v>13051</v>
       </c>
       <c r="B194" s="15" t="s">
-        <v>584</v>
+        <v>568</v>
       </c>
       <c r="C194" s="14">
         <v>3</v>
       </c>
       <c r="H194" s="16" t="s">
-        <v>585</v>
+        <v>569</v>
       </c>
       <c r="L194" s="16" t="s">
-        <v>586</v>
+        <v>570</v>
       </c>
       <c r="R194" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R194" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q194,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q194))),1))</f>
@@ -14305,19 +14361,19 @@
         <v>13052</v>
       </c>
       <c r="B195" s="15" t="s">
-        <v>587</v>
+        <v>571</v>
       </c>
       <c r="C195" s="14">
         <v>3</v>
       </c>
       <c r="E195" s="16" t="s">
-        <v>588</v>
+        <v>572</v>
       </c>
       <c r="H195" s="16" t="s">
-        <v>589</v>
+        <v>573</v>
       </c>
       <c r="L195" s="24" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="Q195" s="1" t="s">
         <v>54</v>
@@ -14356,19 +14412,19 @@
         <v>13053</v>
       </c>
       <c r="B196" s="15" t="s">
-        <v>590</v>
+        <v>574</v>
       </c>
       <c r="C196" s="14">
         <v>3</v>
       </c>
       <c r="H196" s="16" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="L196" s="16" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="Q196" s="14" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="R196" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R196" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q196,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q196))),1))</f>
@@ -14404,19 +14460,19 @@
         <v>13054</v>
       </c>
       <c r="B197" s="15" t="s">
-        <v>593</v>
+        <v>577</v>
       </c>
       <c r="C197" s="14">
         <v>3</v>
       </c>
       <c r="H197" s="16" t="s">
-        <v>522</v>
+        <v>506</v>
       </c>
       <c r="L197" s="16" t="s">
-        <v>594</v>
+        <v>578</v>
       </c>
       <c r="Q197" s="14" t="s">
-        <v>547</v>
+        <v>531</v>
       </c>
       <c r="R197" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R197" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q197,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q197))),1))</f>
@@ -14452,22 +14508,22 @@
         <v>13055</v>
       </c>
       <c r="B198" s="15" t="s">
-        <v>595</v>
+        <v>579</v>
       </c>
       <c r="C198" s="14">
         <v>3</v>
       </c>
       <c r="E198" s="16" t="s">
-        <v>596</v>
+        <v>580</v>
       </c>
       <c r="H198" s="16" t="s">
-        <v>597</v>
+        <v>581</v>
       </c>
       <c r="L198" s="16" t="s">
-        <v>598</v>
+        <v>582</v>
       </c>
       <c r="Q198" s="14" t="s">
-        <v>571</v>
+        <v>555</v>
       </c>
       <c r="R198" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R198" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q198,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q198))),1))</f>
@@ -14503,19 +14559,19 @@
         <v>13056</v>
       </c>
       <c r="B199" s="15" t="s">
-        <v>599</v>
+        <v>583</v>
       </c>
       <c r="C199" s="14">
         <v>3</v>
       </c>
       <c r="G199" s="16" t="s">
-        <v>600</v>
+        <v>584</v>
       </c>
       <c r="H199" s="16" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="Q199" s="14" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="R199" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R199" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q199,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q199))),1))</f>
@@ -14551,16 +14607,16 @@
         <v>13057</v>
       </c>
       <c r="B200" s="15" t="s">
-        <v>603</v>
+        <v>587</v>
       </c>
       <c r="C200" s="14">
         <v>3</v>
       </c>
       <c r="E200" s="16" t="s">
-        <v>604</v>
+        <v>588</v>
       </c>
       <c r="H200" s="16" t="s">
-        <v>605</v>
+        <v>589</v>
       </c>
       <c r="R200" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R200" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q200,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q200))),1))</f>
@@ -14590,16 +14646,16 @@
         <v>13058</v>
       </c>
       <c r="B201" s="15" t="s">
-        <v>606</v>
+        <v>590</v>
       </c>
       <c r="C201" s="14">
         <v>3</v>
       </c>
       <c r="H201" s="16" t="s">
-        <v>607</v>
+        <v>591</v>
       </c>
       <c r="L201" s="16" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="O201" s="16">
         <v>800065</v>
@@ -14608,7 +14664,7 @@
         <v>12</v>
       </c>
       <c r="Q201" s="14" t="s">
-        <v>608</v>
+        <v>592</v>
       </c>
       <c r="R201" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R201" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q201,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q201))),1))</f>
@@ -14644,19 +14700,19 @@
         <v>13059</v>
       </c>
       <c r="B202" s="15" t="s">
-        <v>609</v>
+        <v>593</v>
       </c>
       <c r="C202" s="14">
         <v>3</v>
       </c>
       <c r="E202" s="16" t="s">
-        <v>610</v>
+        <v>594</v>
       </c>
       <c r="H202" s="16" t="s">
-        <v>611</v>
+        <v>595</v>
       </c>
       <c r="J202" s="16" t="s">
-        <v>612</v>
+        <v>596</v>
       </c>
       <c r="N202" s="16" t="s">
         <v>72</v>
@@ -14701,19 +14757,19 @@
         <v>13060</v>
       </c>
       <c r="B203" s="15" t="s">
-        <v>613</v>
+        <v>597</v>
       </c>
       <c r="C203" s="14">
         <v>3</v>
       </c>
       <c r="E203" s="16" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="H203" s="16" t="s">
-        <v>614</v>
+        <v>598</v>
       </c>
       <c r="L203" s="16" t="s">
-        <v>615</v>
+        <v>599</v>
       </c>
       <c r="O203" s="16">
         <v>800067</v>
@@ -14752,22 +14808,22 @@
         <v>13061</v>
       </c>
       <c r="B204" s="15" t="s">
-        <v>616</v>
+        <v>600</v>
       </c>
       <c r="C204" s="14">
         <v>3</v>
       </c>
       <c r="E204" s="16" t="s">
-        <v>617</v>
+        <v>601</v>
       </c>
       <c r="H204" s="16" t="s">
-        <v>1022</v>
+        <v>1006</v>
       </c>
       <c r="N204" s="16" t="s">
         <v>72</v>
       </c>
       <c r="Q204" s="14" t="s">
-        <v>618</v>
+        <v>602</v>
       </c>
       <c r="R204" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R204" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q204,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q204))),1))</f>
@@ -14800,16 +14856,16 @@
         <v>13062</v>
       </c>
       <c r="B205" s="15" t="s">
-        <v>619</v>
+        <v>603</v>
       </c>
       <c r="C205" s="14">
         <v>3</v>
       </c>
       <c r="H205" s="16" t="s">
-        <v>620</v>
+        <v>604</v>
       </c>
       <c r="Q205" s="14" t="s">
-        <v>621</v>
+        <v>605</v>
       </c>
       <c r="R205" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R205" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q205,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q205))),1))</f>
@@ -14842,19 +14898,19 @@
         <v>13063</v>
       </c>
       <c r="B206" s="15" t="s">
-        <v>622</v>
+        <v>606</v>
       </c>
       <c r="C206" s="14">
         <v>3</v>
       </c>
       <c r="H206" s="16" t="s">
-        <v>623</v>
+        <v>607</v>
       </c>
       <c r="P206" s="14">
         <v>9</v>
       </c>
       <c r="Q206" s="14" t="s">
-        <v>624</v>
+        <v>608</v>
       </c>
       <c r="R206" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R206" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q206,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q206))),1))</f>
@@ -14887,22 +14943,22 @@
         <v>13064</v>
       </c>
       <c r="B207" s="15" t="s">
-        <v>625</v>
+        <v>609</v>
       </c>
       <c r="C207" s="14">
         <v>3</v>
       </c>
       <c r="E207" s="16" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="H207" s="16" t="s">
-        <v>522</v>
+        <v>506</v>
       </c>
       <c r="J207" s="16" t="s">
-        <v>626</v>
+        <v>610</v>
       </c>
       <c r="N207" s="16" t="s">
-        <v>1034</v>
+        <v>1018</v>
       </c>
       <c r="Q207" s="14" t="s">
         <v>152</v>
@@ -14938,25 +14994,25 @@
         <v>13065</v>
       </c>
       <c r="B208" s="15" t="s">
-        <v>627</v>
+        <v>611</v>
       </c>
       <c r="C208" s="14">
         <v>3</v>
       </c>
       <c r="H208" s="16" t="s">
-        <v>628</v>
+        <v>612</v>
       </c>
       <c r="J208" s="16" t="s">
-        <v>629</v>
+        <v>613</v>
       </c>
       <c r="N208" s="16" t="s">
-        <v>630</v>
+        <v>614</v>
       </c>
       <c r="O208" s="14">
         <v>1</v>
       </c>
       <c r="Q208" s="14" t="s">
-        <v>631</v>
+        <v>615</v>
       </c>
       <c r="R208" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R208" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q208,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q208))),1))</f>
@@ -14989,22 +15045,22 @@
         <v>13066</v>
       </c>
       <c r="B209" s="23" t="s">
-        <v>632</v>
+        <v>616</v>
       </c>
       <c r="C209" s="14">
         <v>3</v>
       </c>
       <c r="G209" s="16" t="s">
-        <v>633</v>
+        <v>617</v>
       </c>
       <c r="H209" s="16" t="s">
-        <v>517</v>
+        <v>501</v>
       </c>
       <c r="J209" s="16" t="s">
-        <v>634</v>
+        <v>618</v>
       </c>
       <c r="N209" s="16" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="O209" s="14">
         <v>1</v>
@@ -15043,7 +15099,7 @@
         <v>13067</v>
       </c>
       <c r="B210" s="15" t="s">
-        <v>635</v>
+        <v>619</v>
       </c>
       <c r="C210" s="14">
         <v>3</v>
@@ -15052,18 +15108,18 @@
       <c r="F210" s="14"/>
       <c r="G210" s="14"/>
       <c r="H210" s="14" t="s">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="I210" s="14"/>
       <c r="J210" s="14"/>
       <c r="K210" s="14"/>
       <c r="L210" s="14" t="s">
-        <v>636</v>
+        <v>620</v>
       </c>
       <c r="M210" s="14"/>
       <c r="N210" s="14"/>
       <c r="Q210" s="14" t="s">
-        <v>637</v>
+        <v>621</v>
       </c>
       <c r="R210" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R210" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q210,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q210))),1))</f>
@@ -15096,17 +15152,17 @@
         <v>13068</v>
       </c>
       <c r="B211" s="15" t="s">
-        <v>638</v>
+        <v>622</v>
       </c>
       <c r="C211" s="14">
         <v>3</v>
       </c>
       <c r="E211" s="14" t="s">
-        <v>639</v>
+        <v>623</v>
       </c>
       <c r="F211" s="14"/>
       <c r="H211" s="14" t="s">
-        <v>640</v>
+        <v>624</v>
       </c>
       <c r="I211" s="14"/>
       <c r="J211" s="14"/>
@@ -15148,7 +15204,7 @@
         <v>13069</v>
       </c>
       <c r="B212" s="15" t="s">
-        <v>641</v>
+        <v>625</v>
       </c>
       <c r="C212" s="14">
         <v>3</v>
@@ -15157,18 +15213,18 @@
       <c r="F212" s="14"/>
       <c r="G212" s="14"/>
       <c r="H212" s="14" t="s">
-        <v>642</v>
+        <v>626</v>
       </c>
       <c r="I212" s="14"/>
       <c r="J212" s="14" t="s">
-        <v>643</v>
+        <v>627</v>
       </c>
       <c r="K212" s="14"/>
       <c r="L212" s="14"/>
       <c r="M212" s="14"/>
       <c r="N212" s="14"/>
       <c r="Q212" s="14" t="s">
-        <v>644</v>
+        <v>628</v>
       </c>
       <c r="R212" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R212" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q212,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q212))),1))</f>
@@ -15201,7 +15257,7 @@
         <v>13070</v>
       </c>
       <c r="B213" s="15" t="s">
-        <v>645</v>
+        <v>629</v>
       </c>
       <c r="C213" s="14">
         <v>3</v>
@@ -15210,15 +15266,15 @@
       <c r="F213" s="14"/>
       <c r="G213" s="14"/>
       <c r="H213" s="14" t="s">
-        <v>452</v>
+        <v>436</v>
       </c>
       <c r="I213" s="14"/>
       <c r="J213" s="14" t="s">
-        <v>646</v>
+        <v>630</v>
       </c>
       <c r="K213" s="14"/>
       <c r="L213" s="14" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="M213" s="14"/>
       <c r="N213" s="14"/>
@@ -15226,7 +15282,7 @@
         <v>2</v>
       </c>
       <c r="Q213" s="14" t="s">
-        <v>647</v>
+        <v>631</v>
       </c>
       <c r="R213" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R213" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q213,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q213))),1))</f>
@@ -15259,16 +15315,16 @@
         <v>13071</v>
       </c>
       <c r="B214" s="15" t="s">
-        <v>648</v>
+        <v>632</v>
       </c>
       <c r="C214" s="14">
         <v>3</v>
       </c>
       <c r="E214" s="16" t="s">
-        <v>649</v>
+        <v>633</v>
       </c>
       <c r="G214" s="16" t="s">
-        <v>650</v>
+        <v>634</v>
       </c>
       <c r="R214" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R214" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q214,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q214))),1))</f>
@@ -15281,7 +15337,7 @@
         <v>20402</v>
       </c>
       <c r="W214" s="14" t="s">
-        <v>651</v>
+        <v>635</v>
       </c>
       <c r="Y214" s="14">
         <v>1</v>
@@ -15298,16 +15354,16 @@
         <v>13072</v>
       </c>
       <c r="B215" s="15" t="s">
-        <v>652</v>
+        <v>636</v>
       </c>
       <c r="C215" s="14">
         <v>3</v>
       </c>
       <c r="E215" s="16" t="s">
-        <v>653</v>
+        <v>637</v>
       </c>
       <c r="H215" s="16" t="s">
-        <v>654</v>
+        <v>638</v>
       </c>
       <c r="O215" s="14">
         <v>7</v>
@@ -15346,16 +15402,16 @@
         <v>3</v>
       </c>
       <c r="G216" s="16" t="s">
-        <v>655</v>
+        <v>639</v>
       </c>
       <c r="H216" s="16" t="s">
-        <v>457</v>
+        <v>441</v>
       </c>
       <c r="L216" s="16" t="s">
-        <v>455</v>
+        <v>439</v>
       </c>
       <c r="N216" s="16" t="s">
-        <v>656</v>
+        <v>640</v>
       </c>
       <c r="O216" s="14">
         <v>1</v>
@@ -15380,7 +15436,7 @@
         <v>20507</v>
       </c>
       <c r="W216" s="14" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="Y216" s="14">
         <v>1</v>
@@ -15400,13 +15456,13 @@
         <v>3</v>
       </c>
       <c r="E217" s="16" t="s">
-        <v>460</v>
+        <v>444</v>
       </c>
       <c r="H217" s="16" t="s">
-        <v>454</v>
+        <v>438</v>
       </c>
       <c r="L217" s="16" t="s">
-        <v>1028</v>
+        <v>1012</v>
       </c>
       <c r="N217" s="16" t="s">
         <v>72</v>
@@ -15418,7 +15474,7 @@
         <v>6</v>
       </c>
       <c r="Q217" s="14" t="s">
-        <v>657</v>
+        <v>641</v>
       </c>
       <c r="R217" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R217" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q217,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q217))),1))</f>
@@ -15434,7 +15490,7 @@
         <v>20507</v>
       </c>
       <c r="W217" s="14" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="Y217" s="14">
         <v>1</v>
@@ -15451,19 +15507,19 @@
         <v>13075</v>
       </c>
       <c r="B218" s="15" t="s">
-        <v>658</v>
+        <v>642</v>
       </c>
       <c r="C218" s="14">
         <v>3</v>
       </c>
       <c r="G218" s="16" t="s">
-        <v>659</v>
+        <v>643</v>
       </c>
       <c r="H218" s="16" t="s">
-        <v>517</v>
+        <v>501</v>
       </c>
       <c r="L218" s="16" t="s">
-        <v>660</v>
+        <v>644</v>
       </c>
       <c r="O218" s="14">
         <v>1</v>
@@ -15472,7 +15528,7 @@
         <v>3</v>
       </c>
       <c r="Q218" s="14" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="R218" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R218" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q218,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q218))),1))</f>
@@ -15488,7 +15544,7 @@
         <v>20507</v>
       </c>
       <c r="W218" s="14" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="Y218" s="14">
         <v>1</v>
@@ -15508,10 +15564,10 @@
         <v>3</v>
       </c>
       <c r="H219" s="16" t="s">
-        <v>1031</v>
+        <v>1015</v>
       </c>
       <c r="L219" s="16" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="O219" s="14">
         <v>1</v>
@@ -15536,7 +15592,7 @@
         <v>20507</v>
       </c>
       <c r="W219" s="14" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="Y219" s="14">
         <v>1</v>
@@ -15556,7 +15612,7 @@
         <v>3</v>
       </c>
       <c r="H220" s="16" t="s">
-        <v>661</v>
+        <v>645</v>
       </c>
       <c r="O220" s="14">
         <v>4</v>
@@ -15565,7 +15621,7 @@
         <v>999</v>
       </c>
       <c r="Q220" s="14" t="s">
-        <v>662</v>
+        <v>646</v>
       </c>
       <c r="R220" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R220" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q220,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q220))),1))</f>
@@ -15581,7 +15637,7 @@
         <v>20507</v>
       </c>
       <c r="W220" s="14" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="Y220" s="14">
         <v>1</v>
@@ -15601,7 +15657,7 @@
         <v>3</v>
       </c>
       <c r="H221" s="16" t="s">
-        <v>663</v>
+        <v>647</v>
       </c>
       <c r="O221" s="14">
         <v>5</v>
@@ -15610,7 +15666,7 @@
         <v>999</v>
       </c>
       <c r="Q221" s="14" t="s">
-        <v>664</v>
+        <v>648</v>
       </c>
       <c r="R221" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R221" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q221,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q221))),1))</f>
@@ -15626,7 +15682,7 @@
         <v>20507</v>
       </c>
       <c r="W221" s="14" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="Y221" s="14">
         <v>1</v>
@@ -15646,16 +15702,16 @@
         <v>3</v>
       </c>
       <c r="E222" s="16" t="s">
-        <v>665</v>
+        <v>649</v>
       </c>
       <c r="G222" s="16" t="s">
         <v>149</v>
       </c>
       <c r="H222" s="16" t="s">
-        <v>666</v>
+        <v>650</v>
       </c>
       <c r="L222" s="16" t="s">
-        <v>667</v>
+        <v>651</v>
       </c>
       <c r="O222" s="14">
         <v>4</v>
@@ -15680,7 +15736,7 @@
         <v>20507</v>
       </c>
       <c r="W222" s="14" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="Y222" s="14">
         <v>1</v>
@@ -15700,13 +15756,13 @@
         <v>3</v>
       </c>
       <c r="H223" s="16" t="s">
-        <v>668</v>
+        <v>652</v>
       </c>
       <c r="J223" s="16" t="s">
-        <v>669</v>
+        <v>653</v>
       </c>
       <c r="N223" s="16" t="s">
-        <v>670</v>
+        <v>654</v>
       </c>
       <c r="O223" s="14">
         <v>7</v>
@@ -15731,7 +15787,7 @@
         <v>20507</v>
       </c>
       <c r="W223" s="14" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="Y223" s="14">
         <v>1</v>
@@ -15748,16 +15804,16 @@
         <v>13081</v>
       </c>
       <c r="B224" s="15" t="s">
-        <v>671</v>
+        <v>655</v>
       </c>
       <c r="C224" s="14">
         <v>3</v>
       </c>
       <c r="H224" s="16" t="s">
-        <v>672</v>
+        <v>656</v>
       </c>
       <c r="Q224" s="14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="R224" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R224" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q224,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q224))),1))</f>
@@ -15793,10 +15849,10 @@
         <v>3</v>
       </c>
       <c r="H225" s="16" t="s">
-        <v>673</v>
+        <v>657</v>
       </c>
       <c r="N225" s="16" t="s">
-        <v>674</v>
+        <v>658</v>
       </c>
       <c r="O225" s="14">
         <v>5</v>
@@ -15805,7 +15861,7 @@
         <v>6</v>
       </c>
       <c r="Q225" s="14" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="R225" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R225" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q225,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q225))),1))</f>
@@ -15821,7 +15877,7 @@
         <v>20507</v>
       </c>
       <c r="W225" s="14" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="Y225" s="14">
         <v>1</v>
@@ -15838,16 +15894,16 @@
         <v>13083</v>
       </c>
       <c r="B226" s="15" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="C226" s="14">
         <v>3</v>
       </c>
       <c r="H226" s="16" t="s">
-        <v>677</v>
+        <v>661</v>
       </c>
       <c r="J226" s="16" t="s">
-        <v>678</v>
+        <v>662</v>
       </c>
       <c r="P226" s="14">
         <v>999</v>
@@ -15880,13 +15936,13 @@
         <v>13084</v>
       </c>
       <c r="B227" s="15" t="s">
-        <v>679</v>
+        <v>663</v>
       </c>
       <c r="C227" s="14">
         <v>3</v>
       </c>
       <c r="H227" s="16" t="s">
-        <v>1023</v>
+        <v>1007</v>
       </c>
       <c r="P227" s="14">
         <v>999</v>
@@ -15919,7 +15975,7 @@
         <v>13085</v>
       </c>
       <c r="B228" s="15" t="s">
-        <v>680</v>
+        <v>664</v>
       </c>
       <c r="C228" s="14">
         <v>3</v>
@@ -15928,10 +15984,10 @@
         <v>149</v>
       </c>
       <c r="H228" s="16" t="s">
-        <v>681</v>
+        <v>665</v>
       </c>
       <c r="J228" s="16" t="s">
-        <v>682</v>
+        <v>666</v>
       </c>
       <c r="P228" s="14">
         <v>999</v>
@@ -15964,18 +16020,18 @@
         <v>13086</v>
       </c>
       <c r="B229" s="15" t="s">
-        <v>683</v>
+        <v>667</v>
       </c>
       <c r="C229" s="14">
         <v>3</v>
       </c>
       <c r="H229" s="14" t="s">
-        <v>457</v>
+        <v>441</v>
       </c>
       <c r="I229" s="14"/>
       <c r="J229" s="14"/>
       <c r="L229" s="16" t="s">
-        <v>684</v>
+        <v>668</v>
       </c>
       <c r="P229" s="14">
         <v>999</v>
@@ -16008,13 +16064,13 @@
         <v>13087</v>
       </c>
       <c r="B230" s="15" t="s">
-        <v>685</v>
+        <v>669</v>
       </c>
       <c r="C230" s="14">
         <v>3</v>
       </c>
       <c r="H230" s="16" t="s">
-        <v>686</v>
+        <v>670</v>
       </c>
       <c r="P230" s="14">
         <v>999</v>
@@ -16047,16 +16103,16 @@
         <v>13088</v>
       </c>
       <c r="B231" s="15" t="s">
-        <v>687</v>
+        <v>671</v>
       </c>
       <c r="C231" s="14">
         <v>3</v>
       </c>
       <c r="H231" s="16" t="s">
-        <v>688</v>
+        <v>672</v>
       </c>
       <c r="L231" s="16" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P231" s="14">
         <v>999</v>
@@ -16089,13 +16145,13 @@
         <v>13089</v>
       </c>
       <c r="B232" s="15" t="s">
-        <v>689</v>
+        <v>673</v>
       </c>
       <c r="C232" s="14">
         <v>3</v>
       </c>
       <c r="H232" s="16" t="s">
-        <v>690</v>
+        <v>674</v>
       </c>
       <c r="P232" s="14">
         <v>999</v>
@@ -16128,16 +16184,16 @@
         <v>13090</v>
       </c>
       <c r="B233" s="15" t="s">
-        <v>691</v>
+        <v>675</v>
       </c>
       <c r="C233" s="14">
         <v>3</v>
       </c>
       <c r="H233" s="16" t="s">
-        <v>692</v>
+        <v>676</v>
       </c>
       <c r="J233" s="16" t="s">
-        <v>693</v>
+        <v>677</v>
       </c>
       <c r="P233" s="14">
         <v>999</v>
@@ -16170,16 +16226,16 @@
         <v>13091</v>
       </c>
       <c r="B234" s="15" t="s">
-        <v>694</v>
+        <v>678</v>
       </c>
       <c r="C234" s="14">
         <v>3</v>
       </c>
       <c r="E234" s="16" t="s">
-        <v>492</v>
+        <v>476</v>
       </c>
       <c r="H234" s="16" t="s">
-        <v>695</v>
+        <v>679</v>
       </c>
       <c r="N234" s="16" t="s">
         <v>72</v>
@@ -16218,21 +16274,21 @@
         <v>13092</v>
       </c>
       <c r="B235" s="15" t="s">
-        <v>696</v>
+        <v>680</v>
       </c>
       <c r="C235" s="14">
         <v>3</v>
       </c>
       <c r="E235" s="16" t="s">
-        <v>697</v>
+        <v>681</v>
       </c>
       <c r="H235" s="16" t="s">
-        <v>698</v>
+        <v>682</v>
       </c>
       <c r="I235" s="14"/>
       <c r="J235" s="14"/>
       <c r="L235" s="16" t="s">
-        <v>699</v>
+        <v>683</v>
       </c>
       <c r="R235" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R235" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q235,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q235))),1))</f>
@@ -16259,16 +16315,16 @@
         <v>13093</v>
       </c>
       <c r="B236" s="15" t="s">
-        <v>700</v>
+        <v>684</v>
       </c>
       <c r="C236" s="14">
         <v>3</v>
       </c>
       <c r="H236" s="16" t="s">
-        <v>701</v>
+        <v>685</v>
       </c>
       <c r="N236" s="16" t="s">
-        <v>702</v>
+        <v>686</v>
       </c>
       <c r="R236" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R236" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q236,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q236))),1))</f>
@@ -16281,7 +16337,7 @@
         <v>20508</v>
       </c>
       <c r="W236" s="14" t="s">
-        <v>703</v>
+        <v>687</v>
       </c>
       <c r="Y236" s="14">
         <v>1</v>
@@ -16298,13 +16354,13 @@
         <v>13094</v>
       </c>
       <c r="B237" s="15" t="s">
-        <v>704</v>
+        <v>688</v>
       </c>
       <c r="C237" s="14">
         <v>3</v>
       </c>
       <c r="H237" s="16" t="s">
-        <v>705</v>
+        <v>689</v>
       </c>
       <c r="R237" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R237" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q237,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q237))),1))</f>
@@ -16328,22 +16384,22 @@
         <v>13095</v>
       </c>
       <c r="B238" s="15" t="s">
-        <v>550</v>
+        <v>534</v>
       </c>
       <c r="C238" s="14">
         <v>3</v>
       </c>
       <c r="H238" s="14" t="s">
-        <v>551</v>
+        <v>535</v>
       </c>
       <c r="J238" s="16" t="s">
-        <v>1024</v>
+        <v>1008</v>
       </c>
       <c r="P238" s="14">
         <v>999</v>
       </c>
       <c r="Q238" s="14" t="s">
-        <v>553</v>
+        <v>537</v>
       </c>
       <c r="R238" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R238" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q238,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q238))),1))</f>
@@ -16373,22 +16429,22 @@
         <v>13096</v>
       </c>
       <c r="B239" s="15" t="s">
-        <v>550</v>
+        <v>534</v>
       </c>
       <c r="C239" s="14">
         <v>3</v>
       </c>
       <c r="H239" s="14" t="s">
-        <v>568</v>
+        <v>552</v>
       </c>
       <c r="J239" s="16" t="s">
-        <v>706</v>
+        <v>690</v>
       </c>
       <c r="P239" s="14">
         <v>999</v>
       </c>
       <c r="Q239" s="14" t="s">
-        <v>553</v>
+        <v>537</v>
       </c>
       <c r="R239" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R239" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q239,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q239))),1))</f>
@@ -16418,22 +16474,22 @@
         <v>13097</v>
       </c>
       <c r="B240" s="15" t="s">
-        <v>569</v>
+        <v>553</v>
       </c>
       <c r="C240" s="14">
         <v>3</v>
       </c>
       <c r="H240" s="14" t="s">
-        <v>517</v>
+        <v>501</v>
       </c>
       <c r="J240" s="16" t="s">
-        <v>707</v>
+        <v>691</v>
       </c>
       <c r="P240" s="14">
         <v>999</v>
       </c>
       <c r="Q240" s="14" t="s">
-        <v>571</v>
+        <v>555</v>
       </c>
       <c r="R240" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R240" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q240,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q240))),1))</f>
@@ -16463,22 +16519,22 @@
         <v>13098</v>
       </c>
       <c r="B241" s="15" t="s">
-        <v>569</v>
+        <v>553</v>
       </c>
       <c r="C241" s="14">
         <v>3</v>
       </c>
       <c r="H241" s="14" t="s">
-        <v>510</v>
+        <v>494</v>
       </c>
       <c r="J241" s="16" t="s">
-        <v>707</v>
+        <v>691</v>
       </c>
       <c r="P241" s="14">
         <v>999</v>
       </c>
       <c r="Q241" s="14" t="s">
-        <v>571</v>
+        <v>555</v>
       </c>
       <c r="R241" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R241" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q241,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q241))),1))</f>
@@ -16508,16 +16564,16 @@
         <v>13099</v>
       </c>
       <c r="B242" s="15" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="C242" s="14">
         <v>3</v>
       </c>
       <c r="H242" s="16" t="s">
-        <v>708</v>
+        <v>692</v>
       </c>
       <c r="J242" s="16" t="s">
-        <v>678</v>
+        <v>662</v>
       </c>
       <c r="P242" s="14">
         <v>999</v>
@@ -16550,13 +16606,13 @@
         <v>13100</v>
       </c>
       <c r="B243" s="15" t="s">
-        <v>679</v>
+        <v>663</v>
       </c>
       <c r="C243" s="14">
         <v>3</v>
       </c>
       <c r="H243" s="16" t="s">
-        <v>1025</v>
+        <v>1009</v>
       </c>
       <c r="P243" s="14">
         <v>999</v>
@@ -16589,18 +16645,18 @@
         <v>13101</v>
       </c>
       <c r="B244" s="15" t="s">
-        <v>683</v>
+        <v>667</v>
       </c>
       <c r="C244" s="14">
         <v>3</v>
       </c>
       <c r="H244" s="14" t="s">
-        <v>611</v>
+        <v>595</v>
       </c>
       <c r="I244" s="14"/>
       <c r="J244" s="14"/>
       <c r="L244" s="16" t="s">
-        <v>684</v>
+        <v>668</v>
       </c>
       <c r="P244" s="14">
         <v>999</v>
@@ -16633,13 +16689,13 @@
         <v>13102</v>
       </c>
       <c r="B245" s="15" t="s">
-        <v>685</v>
+        <v>669</v>
       </c>
       <c r="C245" s="14">
         <v>3</v>
       </c>
       <c r="H245" s="16" t="s">
-        <v>709</v>
+        <v>693</v>
       </c>
       <c r="P245" s="14">
         <v>999</v>
@@ -16672,16 +16728,16 @@
         <v>13103</v>
       </c>
       <c r="B246" s="15" t="s">
-        <v>687</v>
+        <v>671</v>
       </c>
       <c r="C246" s="14">
         <v>3</v>
       </c>
       <c r="H246" s="16" t="s">
-        <v>710</v>
+        <v>694</v>
       </c>
       <c r="L246" s="16" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P246" s="14">
         <v>999</v>
@@ -16714,16 +16770,16 @@
         <v>13104</v>
       </c>
       <c r="B247" s="15" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="C247" s="14">
         <v>3</v>
       </c>
       <c r="H247" s="16" t="s">
-        <v>711</v>
+        <v>695</v>
       </c>
       <c r="J247" s="16" t="s">
-        <v>678</v>
+        <v>662</v>
       </c>
       <c r="P247" s="14">
         <v>999</v>
@@ -16756,13 +16812,13 @@
         <v>13105</v>
       </c>
       <c r="B248" s="15" t="s">
-        <v>679</v>
+        <v>663</v>
       </c>
       <c r="C248" s="14">
         <v>3</v>
       </c>
       <c r="H248" s="16" t="s">
-        <v>712</v>
+        <v>696</v>
       </c>
       <c r="P248" s="14">
         <v>999</v>
@@ -16795,18 +16851,18 @@
         <v>13106</v>
       </c>
       <c r="B249" s="15" t="s">
-        <v>683</v>
+        <v>667</v>
       </c>
       <c r="C249" s="14">
         <v>3</v>
       </c>
       <c r="H249" s="14" t="s">
-        <v>713</v>
+        <v>697</v>
       </c>
       <c r="I249" s="14"/>
       <c r="J249" s="14"/>
       <c r="L249" s="16" t="s">
-        <v>684</v>
+        <v>668</v>
       </c>
       <c r="P249" s="14">
         <v>999</v>
@@ -16839,13 +16895,13 @@
         <v>13107</v>
       </c>
       <c r="B250" s="15" t="s">
-        <v>685</v>
+        <v>669</v>
       </c>
       <c r="C250" s="14">
         <v>3</v>
       </c>
       <c r="H250" s="16" t="s">
-        <v>714</v>
+        <v>698</v>
       </c>
       <c r="P250" s="14">
         <v>999</v>
@@ -16878,16 +16934,16 @@
         <v>13108</v>
       </c>
       <c r="B251" s="15" t="s">
-        <v>687</v>
+        <v>671</v>
       </c>
       <c r="C251" s="14">
         <v>3</v>
       </c>
       <c r="H251" s="16" t="s">
-        <v>715</v>
+        <v>699</v>
       </c>
       <c r="L251" s="16" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P251" s="14">
         <v>999</v>
@@ -16920,7 +16976,7 @@
         <v>13109</v>
       </c>
       <c r="B252" s="15" t="s">
-        <v>716</v>
+        <v>700</v>
       </c>
       <c r="C252" s="14">
         <v>3</v>
@@ -16936,7 +16992,7 @@
         <v>20407</v>
       </c>
       <c r="W252" s="14" t="s">
-        <v>717</v>
+        <v>701</v>
       </c>
       <c r="Y252" s="14">
         <v>1</v>
@@ -16956,7 +17012,7 @@
         <v>3</v>
       </c>
       <c r="H253" s="16" t="s">
-        <v>718</v>
+        <v>702</v>
       </c>
       <c r="R253" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R253" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q253,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q253))),1))</f>
@@ -16969,7 +17025,7 @@
         <v>20508</v>
       </c>
       <c r="W253" s="14" t="s">
-        <v>703</v>
+        <v>687</v>
       </c>
       <c r="Y253" s="14">
         <v>1</v>
@@ -16989,7 +17045,7 @@
         <v>3</v>
       </c>
       <c r="H254" s="16" t="s">
-        <v>719</v>
+        <v>703</v>
       </c>
       <c r="R254" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R254" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q254,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q254))),1))</f>
@@ -17002,7 +17058,7 @@
         <v>20508</v>
       </c>
       <c r="W254" s="14" t="s">
-        <v>703</v>
+        <v>687</v>
       </c>
       <c r="Y254" s="14">
         <v>1</v>
@@ -17022,7 +17078,7 @@
         <v>3</v>
       </c>
       <c r="H255" s="16" t="s">
-        <v>720</v>
+        <v>704</v>
       </c>
       <c r="R255" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R255" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q255,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q255))),1))</f>
@@ -17055,7 +17111,7 @@
         <v>3</v>
       </c>
       <c r="H256" s="16" t="s">
-        <v>721</v>
+        <v>705</v>
       </c>
       <c r="R256" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R256" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q256,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q256))),1))</f>
@@ -17088,22 +17144,22 @@
         <v>3</v>
       </c>
       <c r="G257" s="16" t="s">
-        <v>722</v>
+        <v>706</v>
       </c>
       <c r="H257" s="16" t="s">
-        <v>723</v>
+        <v>707</v>
       </c>
       <c r="J257" s="16" t="s">
-        <v>724</v>
+        <v>708</v>
       </c>
       <c r="L257" s="16" t="s">
-        <v>725</v>
+        <v>709</v>
       </c>
       <c r="P257" s="14">
         <v>5</v>
       </c>
       <c r="Q257" s="14" t="s">
-        <v>726</v>
+        <v>710</v>
       </c>
       <c r="R257" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R257" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q257,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q257))),1))</f>
@@ -17122,7 +17178,7 @@
         <v>20602</v>
       </c>
       <c r="W257" s="14" t="s">
-        <v>727</v>
+        <v>711</v>
       </c>
       <c r="Y257" s="14">
         <v>1</v>
@@ -17139,16 +17195,16 @@
         <v>13115</v>
       </c>
       <c r="B258" s="15" t="s">
-        <v>728</v>
+        <v>712</v>
       </c>
       <c r="C258" s="14">
         <v>3</v>
       </c>
       <c r="H258" s="16" t="s">
-        <v>729</v>
+        <v>713</v>
       </c>
       <c r="L258" s="16" t="s">
-        <v>730</v>
+        <v>714</v>
       </c>
       <c r="P258" s="14">
         <v>999</v>
@@ -17190,16 +17246,16 @@
         <v>3</v>
       </c>
       <c r="H259" s="16" t="s">
-        <v>731</v>
+        <v>715</v>
       </c>
       <c r="J259" s="16" t="s">
-        <v>732</v>
+        <v>716</v>
       </c>
       <c r="L259" s="16" t="s">
-        <v>733</v>
+        <v>717</v>
       </c>
       <c r="Q259" s="14" t="s">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="S259" s="14">
         <v>1</v>
@@ -17234,16 +17290,16 @@
         <v>3</v>
       </c>
       <c r="E260" s="16" t="s">
-        <v>734</v>
+        <v>718</v>
       </c>
       <c r="H260" s="16" t="s">
-        <v>611</v>
+        <v>595</v>
       </c>
       <c r="J260" s="16" t="s">
-        <v>735</v>
+        <v>719</v>
       </c>
       <c r="L260" s="16" t="s">
-        <v>736</v>
+        <v>720</v>
       </c>
       <c r="N260" s="16" t="s">
         <v>72</v>
@@ -17281,10 +17337,10 @@
         <v>3</v>
       </c>
       <c r="H261" s="16" t="s">
-        <v>737</v>
+        <v>721</v>
       </c>
       <c r="L261" s="16" t="s">
-        <v>738</v>
+        <v>722</v>
       </c>
       <c r="S261" s="14">
         <v>1</v>
@@ -17316,13 +17372,13 @@
         <v>14001</v>
       </c>
       <c r="B264" s="15" t="s">
-        <v>739</v>
+        <v>723</v>
       </c>
       <c r="C264" s="14">
         <v>4</v>
       </c>
       <c r="H264" s="16" t="s">
-        <v>740</v>
+        <v>724</v>
       </c>
       <c r="O264" s="14">
         <v>3</v>
@@ -17331,7 +17387,7 @@
         <v>3</v>
       </c>
       <c r="Q264" s="14" t="s">
-        <v>741</v>
+        <v>725</v>
       </c>
       <c r="R264" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R264" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q264,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q264))),1))</f>
@@ -17350,7 +17406,7 @@
         <v>20304</v>
       </c>
       <c r="W264" s="14" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="Y264" s="14">
         <v>2</v>
@@ -17367,16 +17423,16 @@
         <v>14002</v>
       </c>
       <c r="B265" s="15" t="s">
-        <v>742</v>
+        <v>726</v>
       </c>
       <c r="C265" s="14">
         <v>4</v>
       </c>
       <c r="E265" s="16" t="s">
-        <v>743</v>
+        <v>727</v>
       </c>
       <c r="H265" s="16" t="s">
-        <v>744</v>
+        <v>728</v>
       </c>
       <c r="O265" s="14">
         <v>6</v>
@@ -17385,7 +17441,7 @@
         <v>3</v>
       </c>
       <c r="Q265" s="14" t="s">
-        <v>745</v>
+        <v>729</v>
       </c>
       <c r="R265" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R265" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q265,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q265))),1))</f>
@@ -17404,7 +17460,7 @@
         <v>20304</v>
       </c>
       <c r="W265" s="14" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="Y265" s="14">
         <v>2</v>
@@ -17421,7 +17477,7 @@
         <v>14003</v>
       </c>
       <c r="B266" s="15" t="s">
-        <v>746</v>
+        <v>730</v>
       </c>
       <c r="C266" s="14">
         <v>4</v>
@@ -17433,10 +17489,10 @@
         <v>197</v>
       </c>
       <c r="H266" s="16" t="s">
-        <v>747</v>
+        <v>731</v>
       </c>
       <c r="L266" s="16" t="s">
-        <v>748</v>
+        <v>732</v>
       </c>
       <c r="O266" s="14">
         <v>3</v>
@@ -17445,7 +17501,7 @@
         <v>4</v>
       </c>
       <c r="Q266" s="14" t="s">
-        <v>749</v>
+        <v>733</v>
       </c>
       <c r="R266" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R266" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q266,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q266))),1))</f>
@@ -17464,7 +17520,7 @@
         <v>20302</v>
       </c>
       <c r="W266" s="14" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="Y266" s="14">
         <v>2</v>
@@ -17481,7 +17537,7 @@
         <v>14004</v>
       </c>
       <c r="B267" s="15" t="s">
-        <v>750</v>
+        <v>734</v>
       </c>
       <c r="C267" s="14">
         <v>4</v>
@@ -17490,13 +17546,13 @@
         <v>217</v>
       </c>
       <c r="H267" s="16" t="s">
-        <v>751</v>
+        <v>735</v>
       </c>
       <c r="N267" s="16" t="s">
         <v>72</v>
       </c>
       <c r="Q267" s="14" t="s">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="R267" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R267" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q267,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q267))),1))</f>
@@ -17512,7 +17568,7 @@
         <v>20302</v>
       </c>
       <c r="W267" s="14" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="Y267" s="14">
         <v>2</v>
@@ -17529,7 +17585,7 @@
         <v>14005</v>
       </c>
       <c r="B268" s="15" t="s">
-        <v>752</v>
+        <v>736</v>
       </c>
       <c r="C268" s="14">
         <v>4</v>
@@ -17538,13 +17594,13 @@
         <v>217</v>
       </c>
       <c r="H268" s="16" t="s">
-        <v>753</v>
+        <v>737</v>
       </c>
       <c r="N268" s="16" t="s">
         <v>72</v>
       </c>
       <c r="Q268" s="14" t="s">
-        <v>657</v>
+        <v>641</v>
       </c>
       <c r="R268" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R268" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q268,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q268))),1))</f>
@@ -17560,7 +17616,7 @@
         <v>20302</v>
       </c>
       <c r="W268" s="14" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="Y268" s="14">
         <v>2</v>
@@ -17577,16 +17633,16 @@
         <v>14006</v>
       </c>
       <c r="B269" s="15" t="s">
-        <v>754</v>
+        <v>738</v>
       </c>
       <c r="C269" s="14">
         <v>4</v>
       </c>
       <c r="H269" s="16" t="s">
-        <v>455</v>
+        <v>439</v>
       </c>
       <c r="L269" s="16" t="s">
-        <v>755</v>
+        <v>739</v>
       </c>
       <c r="O269" s="14">
         <v>3</v>
@@ -17605,7 +17661,7 @@
         <v>20302</v>
       </c>
       <c r="W269" s="14" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="Y269" s="14">
         <v>2</v>
@@ -17622,7 +17678,7 @@
         <v>14007</v>
       </c>
       <c r="B270" s="20" t="s">
-        <v>756</v>
+        <v>740</v>
       </c>
       <c r="C270" s="14">
         <v>4</v>
@@ -17631,10 +17687,10 @@
         <v>81</v>
       </c>
       <c r="H270" s="16" t="s">
-        <v>757</v>
+        <v>741</v>
       </c>
       <c r="L270" s="16" t="s">
-        <v>758</v>
+        <v>742</v>
       </c>
       <c r="O270" s="14">
         <v>1</v>
@@ -17643,7 +17699,7 @@
         <v>4</v>
       </c>
       <c r="Q270" s="14" t="s">
-        <v>759</v>
+        <v>743</v>
       </c>
       <c r="R270" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R270" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q270,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q270))),1))</f>
@@ -17676,7 +17732,7 @@
         <v>14008</v>
       </c>
       <c r="B271" s="20" t="s">
-        <v>760</v>
+        <v>744</v>
       </c>
       <c r="C271" s="14">
         <v>4</v>
@@ -17685,10 +17741,10 @@
         <v>81</v>
       </c>
       <c r="H271" s="16" t="s">
-        <v>761</v>
+        <v>745</v>
       </c>
       <c r="L271" s="16" t="s">
-        <v>762</v>
+        <v>746</v>
       </c>
       <c r="O271" s="14">
         <v>1</v>
@@ -17697,7 +17753,7 @@
         <v>4</v>
       </c>
       <c r="Q271" s="14" t="s">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="R271" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R271" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q271,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q271))),1))</f>
@@ -17730,16 +17786,16 @@
         <v>14009</v>
       </c>
       <c r="B272" s="15" t="s">
-        <v>763</v>
+        <v>747</v>
       </c>
       <c r="C272" s="14">
         <v>4</v>
       </c>
       <c r="E272" s="16" t="s">
-        <v>764</v>
+        <v>748</v>
       </c>
       <c r="H272" s="16" t="s">
-        <v>765</v>
+        <v>749</v>
       </c>
       <c r="N272" s="16" t="s">
         <v>170</v>
@@ -17748,7 +17804,7 @@
         <v>2</v>
       </c>
       <c r="Q272" s="14" t="s">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="R272" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R272" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q272,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q272))),1))</f>
@@ -17764,7 +17820,7 @@
         <v>20406</v>
       </c>
       <c r="W272" s="14" t="s">
-        <v>766</v>
+        <v>750</v>
       </c>
       <c r="Y272" s="14">
         <v>2</v>
@@ -17781,13 +17837,13 @@
         <v>14010</v>
       </c>
       <c r="B273" s="15" t="s">
-        <v>767</v>
+        <v>751</v>
       </c>
       <c r="C273" s="14">
         <v>4</v>
       </c>
       <c r="H273" s="16" t="s">
-        <v>768</v>
+        <v>752</v>
       </c>
       <c r="R273" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R273" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q273,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q273))),1))</f>
@@ -17797,7 +17853,7 @@
         <v>20302</v>
       </c>
       <c r="W273" s="14" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="Y273" s="14">
         <v>2</v>
@@ -17814,16 +17870,16 @@
         <v>14011</v>
       </c>
       <c r="B274" s="15" t="s">
-        <v>769</v>
+        <v>753</v>
       </c>
       <c r="C274" s="14">
         <v>4</v>
       </c>
       <c r="E274" s="16" t="s">
-        <v>770</v>
+        <v>754</v>
       </c>
       <c r="H274" s="16" t="s">
-        <v>771</v>
+        <v>755</v>
       </c>
       <c r="R274" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R274" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q274,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q274))),1))</f>
@@ -17833,7 +17889,7 @@
         <v>20302</v>
       </c>
       <c r="W274" s="14" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="Y274" s="14">
         <v>2</v>
@@ -17850,7 +17906,7 @@
         <v>14012</v>
       </c>
       <c r="B275" s="15" t="s">
-        <v>772</v>
+        <v>756</v>
       </c>
       <c r="C275" s="14">
         <v>4</v>
@@ -17874,19 +17930,19 @@
         <v>14013</v>
       </c>
       <c r="B276" s="15" t="s">
-        <v>773</v>
+        <v>757</v>
       </c>
       <c r="C276" s="14">
         <v>4</v>
       </c>
       <c r="E276" s="16" t="s">
-        <v>774</v>
+        <v>758</v>
       </c>
       <c r="H276" s="16" t="s">
-        <v>775</v>
+        <v>759</v>
       </c>
       <c r="Q276" s="14" t="s">
-        <v>776</v>
+        <v>760</v>
       </c>
       <c r="R276" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R276" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q276,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q276))),1))</f>
@@ -17916,19 +17972,19 @@
         <v>14014</v>
       </c>
       <c r="B277" s="20" t="s">
-        <v>777</v>
+        <v>761</v>
       </c>
       <c r="C277" s="14">
         <v>4</v>
       </c>
       <c r="E277" s="16" t="s">
-        <v>1035</v>
+        <v>1019</v>
       </c>
       <c r="H277" s="16" t="s">
-        <v>765</v>
+        <v>749</v>
       </c>
       <c r="Q277" s="14" t="s">
-        <v>657</v>
+        <v>641</v>
       </c>
       <c r="R277" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R277" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q277,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q277))),1))</f>
@@ -17958,19 +18014,19 @@
         <v>14015</v>
       </c>
       <c r="B278" s="15" t="s">
-        <v>778</v>
+        <v>762</v>
       </c>
       <c r="C278" s="14">
         <v>4</v>
       </c>
       <c r="E278" s="16" t="s">
-        <v>779</v>
+        <v>763</v>
       </c>
       <c r="H278" s="16" t="s">
-        <v>765</v>
+        <v>749</v>
       </c>
       <c r="Q278" s="14" t="s">
-        <v>780</v>
+        <v>764</v>
       </c>
       <c r="R278" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R278" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q278,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q278))),1))</f>
@@ -17986,7 +18042,7 @@
         <v>20304</v>
       </c>
       <c r="W278" s="14" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="Y278" s="14">
         <v>2</v>
@@ -18003,7 +18059,7 @@
         <v>14016</v>
       </c>
       <c r="B279" s="15" t="s">
-        <v>781</v>
+        <v>765</v>
       </c>
       <c r="C279" s="14">
         <v>4</v>
@@ -18015,7 +18071,7 @@
         <v>197</v>
       </c>
       <c r="H279" s="16" t="s">
-        <v>782</v>
+        <v>766</v>
       </c>
       <c r="O279" s="14">
         <v>3</v>
@@ -18031,7 +18087,7 @@
         <v>20602</v>
       </c>
       <c r="W279" s="14" t="s">
-        <v>727</v>
+        <v>711</v>
       </c>
       <c r="Y279" s="14">
         <v>2</v>
@@ -18048,19 +18104,19 @@
         <v>14017</v>
       </c>
       <c r="B280" s="15" t="s">
-        <v>783</v>
+        <v>767</v>
       </c>
       <c r="C280" s="14">
         <v>4</v>
       </c>
       <c r="E280" s="16" t="s">
-        <v>784</v>
+        <v>768</v>
       </c>
       <c r="H280" s="16" t="s">
-        <v>785</v>
+        <v>769</v>
       </c>
       <c r="L280" s="16" t="s">
-        <v>786</v>
+        <v>770</v>
       </c>
       <c r="O280" s="14">
         <v>7</v>
@@ -18079,7 +18135,7 @@
         <v>20602</v>
       </c>
       <c r="W280" s="14" t="s">
-        <v>727</v>
+        <v>711</v>
       </c>
       <c r="Y280" s="14">
         <v>2</v>
@@ -18096,7 +18152,7 @@
         <v>14018</v>
       </c>
       <c r="B281" s="15" t="s">
-        <v>787</v>
+        <v>771</v>
       </c>
       <c r="C281" s="14">
         <v>4</v>
@@ -18144,16 +18200,16 @@
         <v>14019</v>
       </c>
       <c r="B282" s="15" t="s">
-        <v>788</v>
+        <v>772</v>
       </c>
       <c r="C282" s="14">
         <v>4</v>
       </c>
       <c r="E282" s="16" t="s">
-        <v>789</v>
+        <v>773</v>
       </c>
       <c r="H282" s="16" t="s">
-        <v>790</v>
+        <v>774</v>
       </c>
       <c r="R282" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R282" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q282,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q282))),1))</f>
@@ -18183,19 +18239,19 @@
         <v>14020</v>
       </c>
       <c r="B283" s="20" t="s">
-        <v>791</v>
+        <v>775</v>
       </c>
       <c r="C283" s="14">
         <v>4</v>
       </c>
       <c r="E283" s="16" t="s">
-        <v>792</v>
+        <v>776</v>
       </c>
       <c r="H283" s="16" t="s">
-        <v>793</v>
+        <v>777</v>
       </c>
       <c r="Q283" s="14" t="s">
-        <v>794</v>
+        <v>778</v>
       </c>
       <c r="R283" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R283" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q283,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q283))),1))</f>
@@ -18225,25 +18281,25 @@
         <v>14021</v>
       </c>
       <c r="B284" s="15" t="s">
-        <v>795</v>
+        <v>779</v>
       </c>
       <c r="C284" s="14">
         <v>4</v>
       </c>
       <c r="G284" s="16" t="s">
-        <v>796</v>
+        <v>780</v>
       </c>
       <c r="H284" s="16" t="s">
-        <v>797</v>
+        <v>781</v>
       </c>
       <c r="L284" s="16" t="s">
-        <v>798</v>
+        <v>782</v>
       </c>
       <c r="P284" s="14">
         <v>999</v>
       </c>
       <c r="Q284" s="14" t="s">
-        <v>794</v>
+        <v>778</v>
       </c>
       <c r="R284" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R284" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q284,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q284))),1))</f>
@@ -18273,25 +18329,25 @@
         <v>14022</v>
       </c>
       <c r="B285" s="15" t="s">
-        <v>795</v>
+        <v>779</v>
       </c>
       <c r="C285" s="14">
         <v>4</v>
       </c>
       <c r="G285" s="16" t="s">
-        <v>796</v>
+        <v>780</v>
       </c>
       <c r="H285" s="16" t="s">
-        <v>799</v>
+        <v>783</v>
       </c>
       <c r="L285" s="16" t="s">
-        <v>798</v>
+        <v>782</v>
       </c>
       <c r="P285" s="14">
         <v>999</v>
       </c>
       <c r="Q285" s="14" t="s">
-        <v>794</v>
+        <v>778</v>
       </c>
       <c r="R285" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R285" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q285,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q285))),1))</f>
@@ -18321,22 +18377,22 @@
         <v>14023</v>
       </c>
       <c r="B286" s="15" t="s">
-        <v>800</v>
+        <v>784</v>
       </c>
       <c r="C286" s="14">
         <v>4</v>
       </c>
       <c r="H286" s="16" t="s">
-        <v>801</v>
+        <v>785</v>
       </c>
       <c r="J286" s="16" t="s">
-        <v>802</v>
+        <v>786</v>
       </c>
       <c r="P286" s="14">
         <v>999</v>
       </c>
       <c r="Q286" s="14" t="s">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="R286" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R286" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q286,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q286))),1))</f>
@@ -18366,22 +18422,22 @@
         <v>14024</v>
       </c>
       <c r="B287" s="15" t="s">
-        <v>800</v>
+        <v>784</v>
       </c>
       <c r="C287" s="14">
         <v>4</v>
       </c>
       <c r="H287" s="16" t="s">
-        <v>803</v>
+        <v>787</v>
       </c>
       <c r="J287" s="16" t="s">
-        <v>802</v>
+        <v>786</v>
       </c>
       <c r="P287" s="14">
         <v>999</v>
       </c>
       <c r="Q287" s="14" t="s">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="R287" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R287" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q287,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q287))),1))</f>
@@ -18411,22 +18467,22 @@
         <v>14025</v>
       </c>
       <c r="B288" s="15" t="s">
-        <v>804</v>
+        <v>788</v>
       </c>
       <c r="C288" s="14">
         <v>4</v>
       </c>
       <c r="G288" s="16" t="s">
-        <v>805</v>
+        <v>789</v>
       </c>
       <c r="H288" s="16" t="s">
         <v>53</v>
       </c>
       <c r="J288" s="16" t="s">
-        <v>806</v>
+        <v>790</v>
       </c>
       <c r="Q288" s="14" t="s">
-        <v>807</v>
+        <v>791</v>
       </c>
       <c r="R288" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R288" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q288,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q288))),1))</f>
@@ -18456,22 +18512,22 @@
         <v>14026</v>
       </c>
       <c r="B289" s="15" t="s">
-        <v>804</v>
+        <v>788</v>
       </c>
       <c r="C289" s="14">
         <v>4</v>
       </c>
       <c r="G289" s="16" t="s">
-        <v>805</v>
+        <v>789</v>
       </c>
       <c r="H289" s="16" t="s">
         <v>53</v>
       </c>
       <c r="J289" s="16" t="s">
-        <v>806</v>
+        <v>790</v>
       </c>
       <c r="Q289" s="14" t="s">
-        <v>808</v>
+        <v>792</v>
       </c>
       <c r="R289" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R289" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q289,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q289))),1))</f>
@@ -18501,16 +18557,16 @@
         <v>14027</v>
       </c>
       <c r="B290" s="15" t="s">
-        <v>809</v>
+        <v>793</v>
       </c>
       <c r="C290" s="14">
         <v>4</v>
       </c>
       <c r="H290" s="16" t="s">
-        <v>810</v>
+        <v>794</v>
       </c>
       <c r="N290" s="16" t="s">
-        <v>811</v>
+        <v>795</v>
       </c>
       <c r="O290" s="14">
         <v>3</v>
@@ -18546,22 +18602,22 @@
         <v>14028</v>
       </c>
       <c r="B291" s="15" t="s">
-        <v>812</v>
+        <v>796</v>
       </c>
       <c r="C291" s="14">
         <v>4</v>
       </c>
       <c r="E291" s="16" t="s">
-        <v>813</v>
+        <v>797</v>
       </c>
       <c r="G291" s="16" t="s">
         <v>149</v>
       </c>
       <c r="H291" s="16" t="s">
-        <v>814</v>
+        <v>798</v>
       </c>
       <c r="N291" s="16" t="s">
-        <v>815</v>
+        <v>799</v>
       </c>
       <c r="R291" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R291" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q291,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q291))),1))</f>
@@ -18588,7 +18644,7 @@
         <v>14029</v>
       </c>
       <c r="B292" s="15" t="s">
-        <v>816</v>
+        <v>800</v>
       </c>
       <c r="C292" s="14">
         <v>4</v>
@@ -18621,19 +18677,19 @@
         <v>14030</v>
       </c>
       <c r="B293" s="15" t="s">
-        <v>817</v>
+        <v>801</v>
       </c>
       <c r="C293" s="14">
         <v>4</v>
       </c>
       <c r="E293" s="16" t="s">
-        <v>818</v>
+        <v>802</v>
       </c>
       <c r="H293" s="16" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="J293" s="16" t="s">
-        <v>819</v>
+        <v>803</v>
       </c>
       <c r="L293" s="16" t="s">
         <v>165</v>
@@ -18666,16 +18722,16 @@
         <v>14031</v>
       </c>
       <c r="B294" s="15" t="s">
-        <v>820</v>
+        <v>804</v>
       </c>
       <c r="C294" s="14">
         <v>4</v>
       </c>
       <c r="H294" s="16" t="s">
-        <v>821</v>
+        <v>805</v>
       </c>
       <c r="N294" s="16" t="s">
-        <v>822</v>
+        <v>806</v>
       </c>
       <c r="P294" s="14">
         <v>1</v>
@@ -18714,7 +18770,7 @@
         <v>14032</v>
       </c>
       <c r="B295" s="15" t="s">
-        <v>823</v>
+        <v>807</v>
       </c>
       <c r="C295" s="14">
         <v>4</v>
@@ -18726,16 +18782,16 @@
         <v>197</v>
       </c>
       <c r="H295" s="16" t="s">
-        <v>824</v>
+        <v>808</v>
       </c>
       <c r="L295" s="16" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="P295" s="14">
         <v>5</v>
       </c>
       <c r="Q295" s="14" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="R295" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R295" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q295,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q295))),1))</f>
@@ -18748,7 +18804,7 @@
         <v>20402</v>
       </c>
       <c r="W295" s="14" t="s">
-        <v>502</v>
+        <v>486</v>
       </c>
       <c r="Y295" s="14">
         <v>2</v>
@@ -18765,13 +18821,13 @@
         <v>14033</v>
       </c>
       <c r="B296" s="15" t="s">
-        <v>825</v>
+        <v>809</v>
       </c>
       <c r="C296" s="14">
         <v>4</v>
       </c>
       <c r="H296" s="16" t="s">
-        <v>826</v>
+        <v>810</v>
       </c>
       <c r="P296" s="14">
         <v>12</v>
@@ -18784,7 +18840,7 @@
         <v>20407</v>
       </c>
       <c r="W296" s="14" t="s">
-        <v>717</v>
+        <v>701</v>
       </c>
       <c r="Y296" s="14">
         <v>2</v>
@@ -18801,13 +18857,13 @@
         <v>14034</v>
       </c>
       <c r="B297" s="15" t="s">
-        <v>827</v>
+        <v>811</v>
       </c>
       <c r="C297" s="14">
         <v>4</v>
       </c>
       <c r="H297" s="16" t="s">
-        <v>828</v>
+        <v>812</v>
       </c>
       <c r="P297" s="14">
         <v>7</v>
@@ -18823,7 +18879,7 @@
         <v>20603</v>
       </c>
       <c r="W297" s="14" t="s">
-        <v>829</v>
+        <v>813</v>
       </c>
       <c r="Y297" s="14">
         <v>2</v>
@@ -18840,16 +18896,16 @@
         <v>14035</v>
       </c>
       <c r="B298" s="15" t="s">
-        <v>830</v>
+        <v>814</v>
       </c>
       <c r="C298" s="14">
         <v>4</v>
       </c>
       <c r="E298" s="16" t="s">
-        <v>831</v>
+        <v>815</v>
       </c>
       <c r="H298" s="16" t="s">
-        <v>832</v>
+        <v>816</v>
       </c>
       <c r="P298" s="14">
         <v>2</v>
@@ -18862,7 +18918,7 @@
         <v>20603</v>
       </c>
       <c r="W298" s="14" t="s">
-        <v>829</v>
+        <v>813</v>
       </c>
       <c r="Y298" s="14">
         <v>2</v>
@@ -18879,19 +18935,19 @@
         <v>14036</v>
       </c>
       <c r="B299" s="15" t="s">
-        <v>833</v>
+        <v>817</v>
       </c>
       <c r="C299" s="14">
         <v>4</v>
       </c>
       <c r="E299" s="16" t="s">
-        <v>834</v>
+        <v>818</v>
       </c>
       <c r="H299" s="16" t="s">
-        <v>835</v>
+        <v>819</v>
       </c>
       <c r="J299" s="16" t="s">
-        <v>836</v>
+        <v>820</v>
       </c>
       <c r="P299" s="14">
         <v>999</v>
@@ -18924,19 +18980,19 @@
         <v>14037</v>
       </c>
       <c r="B300" s="15" t="s">
-        <v>837</v>
+        <v>821</v>
       </c>
       <c r="C300" s="14">
         <v>4</v>
       </c>
       <c r="E300" s="16" t="s">
-        <v>834</v>
+        <v>818</v>
       </c>
       <c r="H300" s="16" t="s">
-        <v>838</v>
+        <v>822</v>
       </c>
       <c r="J300" s="16" t="s">
-        <v>839</v>
+        <v>823</v>
       </c>
       <c r="P300" s="14">
         <v>999</v>
@@ -18969,16 +19025,16 @@
         <v>14038</v>
       </c>
       <c r="B301" s="15" t="s">
-        <v>840</v>
+        <v>824</v>
       </c>
       <c r="C301" s="14">
         <v>4</v>
       </c>
       <c r="H301" s="16" t="s">
-        <v>841</v>
+        <v>825</v>
       </c>
       <c r="J301" s="16" t="s">
-        <v>842</v>
+        <v>826</v>
       </c>
       <c r="P301" s="14">
         <v>10</v>
@@ -18991,7 +19047,7 @@
         <v>20302</v>
       </c>
       <c r="W301" s="14" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="Y301" s="14">
         <v>2</v>
@@ -19008,7 +19064,7 @@
         <v>14039</v>
       </c>
       <c r="B302" s="23" t="s">
-        <v>843</v>
+        <v>827</v>
       </c>
       <c r="C302" s="14">
         <v>4</v>
@@ -19017,13 +19073,13 @@
         <v>153</v>
       </c>
       <c r="H302" s="16" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="L302" s="16" t="s">
-        <v>346</v>
+        <v>330</v>
       </c>
       <c r="N302" s="16" t="s">
-        <v>844</v>
+        <v>828</v>
       </c>
       <c r="P302" s="14">
         <v>6</v>
@@ -19056,7 +19112,7 @@
         <v>14040</v>
       </c>
       <c r="B303" s="15" t="s">
-        <v>845</v>
+        <v>829</v>
       </c>
       <c r="C303" s="14">
         <v>4</v>
@@ -19065,7 +19121,7 @@
         <v>157</v>
       </c>
       <c r="H303" s="16" t="s">
-        <v>846</v>
+        <v>830</v>
       </c>
       <c r="P303" s="14">
         <v>5</v>
@@ -19101,22 +19157,22 @@
         <v>14041</v>
       </c>
       <c r="B304" s="15" t="s">
-        <v>847</v>
+        <v>831</v>
       </c>
       <c r="C304" s="14">
         <v>4</v>
       </c>
       <c r="E304" s="16" t="s">
-        <v>848</v>
+        <v>832</v>
       </c>
       <c r="H304" s="16" t="s">
-        <v>849</v>
+        <v>833</v>
       </c>
       <c r="P304" s="14">
         <v>7</v>
       </c>
       <c r="Q304" s="14" t="s">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="R304" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R304" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q304,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q304))),1))</f>
@@ -19129,7 +19185,7 @@
         <v>20402</v>
       </c>
       <c r="W304" s="14" t="s">
-        <v>505</v>
+        <v>489</v>
       </c>
       <c r="Y304" s="14">
         <v>2</v>
@@ -19146,19 +19202,19 @@
         <v>14042</v>
       </c>
       <c r="B305" s="15" t="s">
-        <v>850</v>
+        <v>834</v>
       </c>
       <c r="C305" s="14">
         <v>4</v>
       </c>
       <c r="H305" s="16" t="s">
-        <v>851</v>
+        <v>835</v>
       </c>
       <c r="L305" s="16" t="s">
-        <v>852</v>
+        <v>836</v>
       </c>
       <c r="Q305" s="14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="R305" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R305" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q305,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q305))),1))</f>
@@ -19191,10 +19247,10 @@
         <v>4</v>
       </c>
       <c r="H306" s="16" t="s">
-        <v>853</v>
+        <v>837</v>
       </c>
       <c r="J306" s="16" t="s">
-        <v>854</v>
+        <v>838</v>
       </c>
       <c r="Q306" s="14" t="s">
         <v>132</v>
@@ -19227,16 +19283,16 @@
         <v>14044</v>
       </c>
       <c r="B307" s="15" t="s">
-        <v>855</v>
+        <v>839</v>
       </c>
       <c r="C307" s="14">
         <v>4</v>
       </c>
       <c r="H307" s="16" t="s">
-        <v>856</v>
+        <v>840</v>
       </c>
       <c r="J307" s="16" t="s">
-        <v>857</v>
+        <v>841</v>
       </c>
       <c r="R307" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R307" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q307,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q307))),1))</f>
@@ -19263,7 +19319,7 @@
         <v>14045</v>
       </c>
       <c r="B308" s="15" t="s">
-        <v>858</v>
+        <v>842</v>
       </c>
       <c r="C308" s="14">
         <v>4</v>
@@ -19278,13 +19334,13 @@
         <v>14046</v>
       </c>
       <c r="B309" s="15" t="s">
-        <v>859</v>
+        <v>843</v>
       </c>
       <c r="C309" s="14">
         <v>4</v>
       </c>
       <c r="H309" s="16" t="s">
-        <v>860</v>
+        <v>844</v>
       </c>
       <c r="O309" s="14">
         <v>6</v>
@@ -19300,7 +19356,7 @@
         <v>20402</v>
       </c>
       <c r="W309" s="14" t="s">
-        <v>651</v>
+        <v>635</v>
       </c>
       <c r="Y309" s="14">
         <v>2</v>
@@ -19317,16 +19373,16 @@
         <v>14047</v>
       </c>
       <c r="B310" s="15" t="s">
-        <v>861</v>
+        <v>845</v>
       </c>
       <c r="C310" s="14">
         <v>4</v>
       </c>
       <c r="E310" s="16" t="s">
-        <v>862</v>
+        <v>846</v>
       </c>
       <c r="H310" s="16" t="s">
-        <v>863</v>
+        <v>847</v>
       </c>
       <c r="O310" s="14">
         <v>1</v>
@@ -19348,7 +19404,7 @@
         <v>20407</v>
       </c>
       <c r="W310" s="14" t="s">
-        <v>717</v>
+        <v>701</v>
       </c>
       <c r="Y310" s="14">
         <v>2</v>
@@ -19389,10 +19445,10 @@
         <v>4</v>
       </c>
       <c r="E312" s="16" t="s">
-        <v>588</v>
+        <v>572</v>
       </c>
       <c r="H312" s="16" t="s">
-        <v>864</v>
+        <v>848</v>
       </c>
       <c r="O312" s="14">
         <v>6</v>
@@ -19408,7 +19464,7 @@
         <v>20307</v>
       </c>
       <c r="W312" s="14" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="Y312" s="14">
         <v>2</v>
@@ -19428,16 +19484,16 @@
         <v>4</v>
       </c>
       <c r="E313" s="16" t="s">
-        <v>588</v>
+        <v>572</v>
       </c>
       <c r="H313" s="16" t="s">
-        <v>865</v>
+        <v>849</v>
       </c>
       <c r="O313" s="14">
         <v>6</v>
       </c>
       <c r="Q313" s="14" t="s">
-        <v>547</v>
+        <v>531</v>
       </c>
       <c r="R313" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R313" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q313,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q313))),1))</f>
@@ -19447,7 +19503,7 @@
         <v>20307</v>
       </c>
       <c r="W313" s="14" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="Y313" s="14">
         <v>2</v>
@@ -19467,10 +19523,10 @@
         <v>4</v>
       </c>
       <c r="E314" s="16" t="s">
-        <v>588</v>
+        <v>572</v>
       </c>
       <c r="H314" s="16" t="s">
-        <v>866</v>
+        <v>850</v>
       </c>
       <c r="O314" s="14">
         <v>6</v>
@@ -19486,7 +19542,7 @@
         <v>20307</v>
       </c>
       <c r="W314" s="14" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="Y314" s="14">
         <v>2</v>
@@ -19503,19 +19559,19 @@
         <v>14052</v>
       </c>
       <c r="B315" s="15" t="s">
-        <v>867</v>
+        <v>851</v>
       </c>
       <c r="C315" s="14">
         <v>4</v>
       </c>
       <c r="E315" s="16" t="s">
-        <v>669</v>
+        <v>653</v>
       </c>
       <c r="H315" s="16" t="s">
-        <v>868</v>
+        <v>852</v>
       </c>
       <c r="N315" s="16" t="s">
-        <v>511</v>
+        <v>495</v>
       </c>
       <c r="O315" s="14">
         <v>4</v>
@@ -19524,7 +19580,7 @@
         <v>1</v>
       </c>
       <c r="Q315" s="14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="R315" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R315" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q315,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q315))),1))</f>
@@ -19540,7 +19596,7 @@
         <v>20507</v>
       </c>
       <c r="W315" s="14" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="Y315" s="14">
         <v>2</v>
@@ -19557,19 +19613,19 @@
         <v>14053</v>
       </c>
       <c r="B316" s="15" t="s">
-        <v>869</v>
+        <v>853</v>
       </c>
       <c r="C316" s="14">
         <v>4</v>
       </c>
       <c r="E316" s="16" t="s">
-        <v>870</v>
+        <v>854</v>
       </c>
       <c r="H316" s="16" t="s">
-        <v>871</v>
+        <v>855</v>
       </c>
       <c r="N316" s="16" t="s">
-        <v>872</v>
+        <v>856</v>
       </c>
       <c r="O316" s="14">
         <v>5</v>
@@ -19578,7 +19634,7 @@
         <v>1</v>
       </c>
       <c r="Q316" s="14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="R316" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R316" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q316,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q316))),1))</f>
@@ -19594,7 +19650,7 @@
         <v>20507</v>
       </c>
       <c r="W316" s="14" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="Y316" s="14">
         <v>2</v>
@@ -19611,19 +19667,19 @@
         <v>14054</v>
       </c>
       <c r="B317" s="15" t="s">
-        <v>873</v>
+        <v>857</v>
       </c>
       <c r="C317" s="14">
         <v>4</v>
       </c>
       <c r="E317" s="16" t="s">
-        <v>874</v>
+        <v>858</v>
       </c>
       <c r="H317" s="16" t="s">
-        <v>875</v>
+        <v>859</v>
       </c>
       <c r="N317" s="16" t="s">
-        <v>876</v>
+        <v>860</v>
       </c>
       <c r="O317" s="14">
         <v>6</v>
@@ -19632,7 +19688,7 @@
         <v>1</v>
       </c>
       <c r="Q317" s="14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="R317" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R317" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q317,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q317))),1))</f>
@@ -19648,7 +19704,7 @@
         <v>20507</v>
       </c>
       <c r="W317" s="14" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="Y317" s="14">
         <v>2</v>
@@ -19668,10 +19724,10 @@
         <v>4</v>
       </c>
       <c r="H318" s="16" t="s">
-        <v>877</v>
+        <v>861</v>
       </c>
       <c r="L318" s="16" t="s">
-        <v>878</v>
+        <v>862</v>
       </c>
       <c r="O318" s="14">
         <v>6</v>
@@ -19680,7 +19736,7 @@
         <v>99</v>
       </c>
       <c r="Q318" s="14" t="s">
-        <v>759</v>
+        <v>743</v>
       </c>
       <c r="R318" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R318" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q318,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q318))),1))</f>
@@ -19696,7 +19752,7 @@
         <v>20507</v>
       </c>
       <c r="W318" s="14" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="Y318" s="14">
         <v>2</v>
@@ -19713,13 +19769,13 @@
         <v>14056</v>
       </c>
       <c r="B319" s="15" t="s">
-        <v>879</v>
+        <v>863</v>
       </c>
       <c r="C319" s="14">
         <v>4</v>
       </c>
       <c r="H319" s="16" t="s">
-        <v>880</v>
+        <v>864</v>
       </c>
       <c r="O319" s="14">
         <v>1</v>
@@ -19728,7 +19784,7 @@
         <v>8</v>
       </c>
       <c r="Q319" s="14" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="R319" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R319" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q319,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q319))),1))</f>
@@ -19744,7 +19800,7 @@
         <v>20507</v>
       </c>
       <c r="W319" s="14" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="Y319" s="14">
         <v>2</v>
@@ -19761,16 +19817,16 @@
         <v>14057</v>
       </c>
       <c r="B320" s="15" t="s">
-        <v>881</v>
+        <v>865</v>
       </c>
       <c r="C320" s="14">
         <v>4</v>
       </c>
       <c r="E320" s="16" t="s">
-        <v>882</v>
+        <v>866</v>
       </c>
       <c r="H320" s="16" t="s">
-        <v>883</v>
+        <v>867</v>
       </c>
       <c r="O320" s="14">
         <v>6</v>
@@ -19779,7 +19835,7 @@
         <v>8</v>
       </c>
       <c r="Q320" s="14" t="s">
-        <v>884</v>
+        <v>868</v>
       </c>
       <c r="R320" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R320" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q320,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q320))),1))</f>
@@ -19795,7 +19851,7 @@
         <v>20507</v>
       </c>
       <c r="W320" s="14" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="Y320" s="14">
         <v>2</v>
@@ -19812,16 +19868,16 @@
         <v>14058</v>
       </c>
       <c r="B321" s="15" t="s">
-        <v>885</v>
+        <v>869</v>
       </c>
       <c r="C321" s="14">
         <v>4</v>
       </c>
       <c r="H321" s="16" t="s">
-        <v>886</v>
+        <v>870</v>
       </c>
       <c r="N321" s="16" t="s">
-        <v>887</v>
+        <v>871</v>
       </c>
       <c r="O321" s="14">
         <v>5</v>
@@ -19830,7 +19886,7 @@
         <v>999</v>
       </c>
       <c r="Q321" s="14" t="s">
-        <v>749</v>
+        <v>733</v>
       </c>
       <c r="R321" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R321" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q321,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q321))),1))</f>
@@ -19846,7 +19902,7 @@
         <v>20507</v>
       </c>
       <c r="W321" s="14" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="Y321" s="14">
         <v>2</v>
@@ -19863,16 +19919,16 @@
         <v>14059</v>
       </c>
       <c r="B322" s="15" t="s">
-        <v>888</v>
+        <v>872</v>
       </c>
       <c r="C322" s="14">
         <v>4</v>
       </c>
       <c r="H322" s="16" t="s">
-        <v>889</v>
+        <v>873</v>
       </c>
       <c r="L322" s="16" t="s">
-        <v>890</v>
+        <v>874</v>
       </c>
       <c r="R322" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R322" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q322,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q322))),1))</f>
@@ -19882,7 +19938,7 @@
         <v>20406</v>
       </c>
       <c r="W322" s="14" t="s">
-        <v>766</v>
+        <v>750</v>
       </c>
       <c r="Y322" s="14">
         <v>2</v>
@@ -19902,7 +19958,7 @@
         <v>4</v>
       </c>
       <c r="H323" s="16" t="s">
-        <v>891</v>
+        <v>875</v>
       </c>
       <c r="R323" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R323" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q323,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q323))),1))</f>
@@ -19932,7 +19988,7 @@
         <v>4</v>
       </c>
       <c r="H324" s="16" t="s">
-        <v>892</v>
+        <v>876</v>
       </c>
       <c r="R324" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R324" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q324,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q324))),1))</f>
@@ -19945,7 +20001,7 @@
         <v>20405</v>
       </c>
       <c r="W324" s="14" t="s">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="Y324" s="14">
         <v>2</v>
@@ -19962,13 +20018,13 @@
         <v>14062</v>
       </c>
       <c r="B325" s="15" t="s">
-        <v>893</v>
+        <v>877</v>
       </c>
       <c r="C325" s="14">
         <v>4</v>
       </c>
       <c r="H325" s="16" t="s">
-        <v>894</v>
+        <v>878</v>
       </c>
       <c r="L325" s="16" t="s">
         <v>165</v>
@@ -20001,16 +20057,16 @@
         <v>14063</v>
       </c>
       <c r="B326" s="15" t="s">
-        <v>895</v>
+        <v>879</v>
       </c>
       <c r="C326" s="14">
         <v>4</v>
       </c>
       <c r="H326" s="16" t="s">
-        <v>896</v>
+        <v>880</v>
       </c>
       <c r="J326" s="16" t="s">
-        <v>897</v>
+        <v>881</v>
       </c>
       <c r="R326" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R326" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q326,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q326))),1))</f>
@@ -20037,7 +20093,7 @@
         <v>14064</v>
       </c>
       <c r="B327" s="15" t="s">
-        <v>898</v>
+        <v>882</v>
       </c>
       <c r="C327" s="14">
         <v>4</v>
@@ -20046,10 +20102,10 @@
         <v>90</v>
       </c>
       <c r="H327" s="16" t="s">
-        <v>899</v>
+        <v>883</v>
       </c>
       <c r="N327" s="16" t="s">
-        <v>1036</v>
+        <v>1020</v>
       </c>
       <c r="P327" s="14">
         <v>999</v>
@@ -20079,16 +20135,16 @@
         <v>14065</v>
       </c>
       <c r="B328" s="15" t="s">
-        <v>900</v>
+        <v>884</v>
       </c>
       <c r="C328" s="14">
         <v>4</v>
       </c>
       <c r="H328" s="16" t="s">
-        <v>1029</v>
+        <v>1013</v>
       </c>
       <c r="N328" s="16" t="s">
-        <v>901</v>
+        <v>885</v>
       </c>
       <c r="O328" s="16"/>
       <c r="R328" s="14" t="e" cm="1">
@@ -20099,7 +20155,7 @@
         <v>20409</v>
       </c>
       <c r="W328" s="14" t="s">
-        <v>432</v>
+        <v>416</v>
       </c>
       <c r="Y328" s="14">
         <v>2</v>
@@ -20116,25 +20172,25 @@
         <v>14066</v>
       </c>
       <c r="B329" s="15" t="s">
-        <v>795</v>
+        <v>779</v>
       </c>
       <c r="C329" s="14">
         <v>4</v>
       </c>
       <c r="G329" s="16" t="s">
-        <v>1005</v>
+        <v>989</v>
       </c>
       <c r="H329" s="16" t="s">
-        <v>797</v>
+        <v>781</v>
       </c>
       <c r="L329" s="16" t="s">
-        <v>903</v>
+        <v>887</v>
       </c>
       <c r="P329" s="14">
         <v>999</v>
       </c>
       <c r="Q329" s="14" t="s">
-        <v>794</v>
+        <v>778</v>
       </c>
       <c r="R329" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R329" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q329,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q329))),1))</f>
@@ -20164,25 +20220,25 @@
         <v>14067</v>
       </c>
       <c r="B330" s="15" t="s">
-        <v>795</v>
+        <v>779</v>
       </c>
       <c r="C330" s="14">
         <v>4</v>
       </c>
       <c r="G330" s="16" t="s">
-        <v>902</v>
+        <v>886</v>
       </c>
       <c r="H330" s="16" t="s">
-        <v>799</v>
+        <v>783</v>
       </c>
       <c r="L330" s="16" t="s">
-        <v>903</v>
+        <v>887</v>
       </c>
       <c r="P330" s="14">
         <v>999</v>
       </c>
       <c r="Q330" s="14" t="s">
-        <v>794</v>
+        <v>778</v>
       </c>
       <c r="R330" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R330" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q330,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q330))),1))</f>
@@ -20212,22 +20268,22 @@
         <v>14068</v>
       </c>
       <c r="B331" s="15" t="s">
-        <v>800</v>
+        <v>784</v>
       </c>
       <c r="C331" s="14">
         <v>4</v>
       </c>
       <c r="H331" s="16" t="s">
-        <v>801</v>
+        <v>785</v>
       </c>
       <c r="J331" s="16" t="s">
-        <v>904</v>
+        <v>888</v>
       </c>
       <c r="P331" s="14">
         <v>999</v>
       </c>
       <c r="Q331" s="14" t="s">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="R331" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R331" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q331,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q331))),1))</f>
@@ -20248,22 +20304,22 @@
         <v>14069</v>
       </c>
       <c r="B332" s="15" t="s">
-        <v>800</v>
+        <v>784</v>
       </c>
       <c r="C332" s="14">
         <v>4</v>
       </c>
       <c r="H332" s="16" t="s">
-        <v>905</v>
+        <v>889</v>
       </c>
       <c r="J332" s="16" t="s">
-        <v>904</v>
+        <v>888</v>
       </c>
       <c r="P332" s="14">
         <v>999</v>
       </c>
       <c r="Q332" s="14" t="s">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="R332" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R332" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q332,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q332))),1))</f>
@@ -20284,13 +20340,13 @@
         <v>14070</v>
       </c>
       <c r="B333" s="15" t="s">
-        <v>893</v>
+        <v>877</v>
       </c>
       <c r="C333" s="14">
         <v>4</v>
       </c>
       <c r="H333" s="16" t="s">
-        <v>906</v>
+        <v>890</v>
       </c>
       <c r="L333" s="16" t="s">
         <v>165</v>
@@ -20323,13 +20379,13 @@
         <v>14071</v>
       </c>
       <c r="B334" s="15" t="s">
-        <v>893</v>
+        <v>877</v>
       </c>
       <c r="C334" s="14">
         <v>4</v>
       </c>
       <c r="H334" s="16" t="s">
-        <v>907</v>
+        <v>891</v>
       </c>
       <c r="L334" s="16" t="s">
         <v>165</v>
@@ -20362,16 +20418,16 @@
         <v>14072</v>
       </c>
       <c r="B335" s="15" t="s">
-        <v>908</v>
+        <v>892</v>
       </c>
       <c r="C335" s="14">
         <v>4</v>
       </c>
       <c r="H335" s="16" t="s">
-        <v>909</v>
+        <v>893</v>
       </c>
       <c r="L335" s="16" t="s">
-        <v>910</v>
+        <v>894</v>
       </c>
       <c r="R335" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R335" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q335,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q335))),1))</f>
@@ -20381,7 +20437,7 @@
         <v>20503</v>
       </c>
       <c r="W335" s="14" t="s">
-        <v>420</v>
+        <v>404</v>
       </c>
       <c r="Y335" s="14">
         <v>2</v>
@@ -20398,16 +20454,16 @@
         <v>14073</v>
       </c>
       <c r="B336" s="15" t="s">
-        <v>911</v>
+        <v>895</v>
       </c>
       <c r="C336" s="14">
         <v>4</v>
       </c>
       <c r="H336" s="16" t="s">
-        <v>912</v>
+        <v>896</v>
       </c>
       <c r="Q336" s="14" t="s">
-        <v>913</v>
+        <v>897</v>
       </c>
       <c r="R336" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R336" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q336,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q336))),1))</f>
@@ -20417,7 +20473,7 @@
         <v>20406</v>
       </c>
       <c r="W336" s="14" t="s">
-        <v>766</v>
+        <v>750</v>
       </c>
       <c r="Y336" s="14">
         <v>2</v>
@@ -20437,13 +20493,13 @@
         <v>4</v>
       </c>
       <c r="G337" s="16" t="s">
-        <v>914</v>
+        <v>898</v>
       </c>
       <c r="H337" s="16" t="s">
-        <v>915</v>
+        <v>899</v>
       </c>
       <c r="Q337" s="14" t="s">
-        <v>808</v>
+        <v>792</v>
       </c>
       <c r="R337" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R337" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q337,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q337))),1))</f>
@@ -20453,7 +20509,7 @@
         <v>20503</v>
       </c>
       <c r="W337" s="14" t="s">
-        <v>420</v>
+        <v>404</v>
       </c>
       <c r="Y337" s="14">
         <v>2</v>
@@ -20470,13 +20526,13 @@
         <v>14075</v>
       </c>
       <c r="B338" s="15" t="s">
-        <v>916</v>
+        <v>900</v>
       </c>
       <c r="C338" s="14">
         <v>4</v>
       </c>
       <c r="H338" s="16" t="s">
-        <v>917</v>
+        <v>901</v>
       </c>
       <c r="R338" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R338" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q338,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q338))),1))</f>
@@ -20497,19 +20553,19 @@
         <v>14076</v>
       </c>
       <c r="B339" s="23" t="s">
-        <v>918</v>
+        <v>902</v>
       </c>
       <c r="C339" s="14">
         <v>4</v>
       </c>
       <c r="E339" s="16" t="s">
-        <v>789</v>
+        <v>773</v>
       </c>
       <c r="H339" s="16" t="s">
-        <v>919</v>
+        <v>903</v>
       </c>
       <c r="J339" s="16" t="s">
-        <v>920</v>
+        <v>904</v>
       </c>
       <c r="R339" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R339" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q339,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q339))),1))</f>
@@ -20539,7 +20595,7 @@
         <v>4</v>
       </c>
       <c r="H340" s="16" t="s">
-        <v>921</v>
+        <v>905</v>
       </c>
       <c r="R340" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R340" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q340,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q340))),1))</f>
@@ -20563,7 +20619,7 @@
         <v>4</v>
       </c>
       <c r="H341" s="16" t="s">
-        <v>922</v>
+        <v>906</v>
       </c>
       <c r="L341" s="16" t="s">
         <v>95</v>
@@ -20587,16 +20643,16 @@
         <v>14079</v>
       </c>
       <c r="B342" s="15" t="s">
-        <v>923</v>
+        <v>907</v>
       </c>
       <c r="C342" s="14">
         <v>4</v>
       </c>
       <c r="H342" s="16" t="s">
-        <v>924</v>
+        <v>908</v>
       </c>
       <c r="L342" s="16" t="s">
-        <v>925</v>
+        <v>909</v>
       </c>
       <c r="R342" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R342" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q342,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q342))),1))</f>
@@ -20623,7 +20679,7 @@
         <v>4</v>
       </c>
       <c r="H343" s="16" t="s">
-        <v>926</v>
+        <v>910</v>
       </c>
       <c r="R343" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R343" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q343,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q343))),1))</f>
@@ -20633,7 +20689,7 @@
         <v>20705</v>
       </c>
       <c r="W343" s="14" t="s">
-        <v>927</v>
+        <v>911</v>
       </c>
       <c r="Y343" s="14">
         <v>1</v>
@@ -20653,10 +20709,10 @@
         <v>4</v>
       </c>
       <c r="H344" s="16" t="s">
-        <v>928</v>
+        <v>912</v>
       </c>
       <c r="N344" s="16" t="s">
-        <v>929</v>
+        <v>913</v>
       </c>
       <c r="R344" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R344" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q344,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q344))),1))</f>
@@ -20666,7 +20722,7 @@
         <v>20705</v>
       </c>
       <c r="W344" s="14" t="s">
-        <v>927</v>
+        <v>911</v>
       </c>
       <c r="Y344" s="14">
         <v>1</v>
@@ -20686,10 +20742,10 @@
         <v>4</v>
       </c>
       <c r="H345" s="16" t="s">
-        <v>930</v>
+        <v>914</v>
       </c>
       <c r="N345" s="16" t="s">
-        <v>931</v>
+        <v>915</v>
       </c>
       <c r="R345" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R345" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q345,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q345))),1))</f>
@@ -20699,7 +20755,7 @@
         <v>20705</v>
       </c>
       <c r="W345" s="14" t="s">
-        <v>927</v>
+        <v>911</v>
       </c>
       <c r="Y345" s="14">
         <v>1</v>
@@ -20719,16 +20775,16 @@
         <v>4</v>
       </c>
       <c r="E346" s="16" t="s">
-        <v>932</v>
+        <v>916</v>
       </c>
       <c r="G346" s="16" t="s">
         <v>197</v>
       </c>
       <c r="H346" s="16" t="s">
-        <v>933</v>
+        <v>917</v>
       </c>
       <c r="L346" s="16" t="s">
-        <v>934</v>
+        <v>918</v>
       </c>
       <c r="Q346" s="14" t="s">
         <v>275</v>
@@ -20755,13 +20811,13 @@
         <v>14084</v>
       </c>
       <c r="B347" s="15" t="s">
-        <v>935</v>
+        <v>919</v>
       </c>
       <c r="C347" s="14">
         <v>4</v>
       </c>
       <c r="E347" s="16" t="s">
-        <v>936</v>
+        <v>920</v>
       </c>
       <c r="R347" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R347" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q347,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q347))),1))</f>
@@ -20776,19 +20832,19 @@
         <v>14085</v>
       </c>
       <c r="B348" s="15" t="s">
-        <v>937</v>
+        <v>921</v>
       </c>
       <c r="C348" s="14">
         <v>4</v>
       </c>
       <c r="E348" s="16" t="s">
-        <v>938</v>
+        <v>922</v>
       </c>
       <c r="H348" s="16" t="s">
-        <v>939</v>
+        <v>923</v>
       </c>
       <c r="L348" s="16" t="s">
-        <v>940</v>
+        <v>924</v>
       </c>
       <c r="Q348" s="14" t="s">
         <v>88</v>
@@ -20818,19 +20874,19 @@
         <v>14086</v>
       </c>
       <c r="B349" s="15" t="s">
-        <v>941</v>
+        <v>925</v>
       </c>
       <c r="C349" s="14">
         <v>4</v>
       </c>
       <c r="E349" s="16" t="s">
-        <v>942</v>
+        <v>926</v>
       </c>
       <c r="H349" s="16" t="s">
-        <v>939</v>
+        <v>923</v>
       </c>
       <c r="L349" s="16" t="s">
-        <v>943</v>
+        <v>927</v>
       </c>
       <c r="Q349" s="14" t="s">
         <v>88</v>
@@ -20863,19 +20919,19 @@
         <v>4</v>
       </c>
       <c r="E350" s="16" t="s">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="G350" s="16" t="s">
-        <v>944</v>
+        <v>928</v>
       </c>
       <c r="H350" s="16" t="s">
-        <v>945</v>
+        <v>929</v>
       </c>
       <c r="L350" s="16" t="s">
-        <v>946</v>
+        <v>930</v>
       </c>
       <c r="N350" s="16" t="s">
-        <v>947</v>
+        <v>931</v>
       </c>
       <c r="O350" s="14">
         <v>3</v>
@@ -20884,7 +20940,7 @@
         <v>12</v>
       </c>
       <c r="Q350" s="14" t="s">
-        <v>884</v>
+        <v>868</v>
       </c>
       <c r="R350" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R350" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q350,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q350))),1))</f>
@@ -20914,7 +20970,7 @@
         <v>14088</v>
       </c>
       <c r="H351" s="16" t="s">
-        <v>948</v>
+        <v>932</v>
       </c>
       <c r="T351" s="14" t="s">
         <v>50</v>
@@ -20957,15 +21013,15 @@
         <v>72</v>
       </c>
       <c r="C1" t="s">
-        <v>949</v>
+        <v>933</v>
       </c>
       <c r="E1" t="s">
-        <v>950</v>
+        <v>934</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>951</v>
+        <v>935</v>
       </c>
       <c r="C2" t="s">
         <v>236</v>
@@ -20975,28 +21031,28 @@
         <v>8</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>952</v>
+        <v>936</v>
       </c>
       <c r="F2">
         <f>COUNTIF(Skill!V:V,20702)</f>
         <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>953</v>
+        <v>937</v>
       </c>
       <c r="H2">
         <f>COUNTIF(Skill!V:V,20402)</f>
         <v>6</v>
       </c>
       <c r="I2" t="s">
-        <v>954</v>
+        <v>938</v>
       </c>
       <c r="J2">
         <f>COUNTIF(Skill!V:V,20307)</f>
         <v>4</v>
       </c>
       <c r="K2" t="s">
-        <v>927</v>
+        <v>911</v>
       </c>
       <c r="L2">
         <f>COUNTIF(Skill!V:V,20705)</f>
@@ -21007,24 +21063,24 @@
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
-        <v>955</v>
+        <v>939</v>
       </c>
       <c r="C3" t="s">
-        <v>508</v>
+        <v>492</v>
       </c>
       <c r="D3">
         <f>COUNTIF(Skill!V:V,20601)</f>
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>727</v>
+        <v>711</v>
       </c>
       <c r="F3">
         <f>COUNTIF(Skill!V:V,20602)</f>
         <v>3</v>
       </c>
       <c r="G3" t="s">
-        <v>829</v>
+        <v>813</v>
       </c>
       <c r="H3">
         <f>COUNTIF(Skill!V:V,20603)</f>
@@ -21042,10 +21098,10 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>956</v>
+        <v>940</v>
       </c>
       <c r="C4" t="s">
-        <v>409</v>
+        <v>393</v>
       </c>
       <c r="D4">
         <f>COUNTIF(Skill!V:V,20501)</f>
@@ -21059,14 +21115,14 @@
         <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>420</v>
+        <v>404</v>
       </c>
       <c r="H4">
         <f>COUNTIF(Skill!V:V,20503)</f>
         <v>5</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>957</v>
+        <v>941</v>
       </c>
       <c r="J4">
         <f>COUNTIF(Skill!V:V,20504)</f>
@@ -21080,21 +21136,21 @@
         <v>6</v>
       </c>
       <c r="M4" t="s">
-        <v>518</v>
+        <v>502</v>
       </c>
       <c r="N4">
         <f>COUNTIF(Skill!V:V,20506)</f>
         <v>2</v>
       </c>
       <c r="O4" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="P4">
         <f>COUNTIF(Skill!V:V,20507)</f>
         <v>21</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>958</v>
+        <v>942</v>
       </c>
       <c r="R4">
         <f>COUNTIF(Skill!V:V,20508)</f>
@@ -21104,7 +21160,7 @@
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>959</v>
+        <v>943</v>
       </c>
       <c r="C5" t="s">
         <v>180</v>
@@ -21130,35 +21186,35 @@
         <v>6</v>
       </c>
       <c r="K5" t="s">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="L5">
         <f>COUNTIF(Skill!V:V,20405)</f>
         <v>2</v>
       </c>
       <c r="M5" t="s">
-        <v>766</v>
+        <v>750</v>
       </c>
       <c r="N5">
         <f>COUNTIF(Skill!V:V,20406)</f>
         <v>3</v>
       </c>
       <c r="O5" t="s">
-        <v>717</v>
+        <v>701</v>
       </c>
       <c r="P5">
         <f>COUNTIF(Skill!V:V,20407)</f>
         <v>3</v>
       </c>
       <c r="Q5" t="s">
-        <v>960</v>
+        <v>944</v>
       </c>
       <c r="R5">
         <f>COUNTIF(Skill!V:V,20408)</f>
         <v>0</v>
       </c>
       <c r="S5" t="s">
-        <v>432</v>
+        <v>416</v>
       </c>
       <c r="T5">
         <f>COUNTIF(Skill!V:V,20409)</f>
@@ -21167,7 +21223,7 @@
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
-        <v>961</v>
+        <v>945</v>
       </c>
       <c r="C6" t="s">
         <v>55</v>
@@ -21177,7 +21233,7 @@
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="F6">
         <f>COUNTIF(Skill!V:V,20302)</f>
@@ -21191,7 +21247,7 @@
         <v>8</v>
       </c>
       <c r="I6" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="J6">
         <f>COUNTIF(Skill!V:V,20304)</f>
@@ -21205,7 +21261,7 @@
         <v>7</v>
       </c>
       <c r="M6" t="s">
-        <v>962</v>
+        <v>946</v>
       </c>
       <c r="N6">
         <f>COUNTIF(Skill!V:V,20306)</f>
@@ -21218,7 +21274,7 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
-        <v>963</v>
+        <v>947</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>58</v>
@@ -21235,7 +21291,7 @@
         <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>964</v>
+        <v>948</v>
       </c>
       <c r="H7">
         <f>COUNTIF(Skill!V:V,20203)</f>
@@ -21249,7 +21305,7 @@
         <v>5</v>
       </c>
       <c r="K7" t="s">
-        <v>965</v>
+        <v>949</v>
       </c>
       <c r="L7">
         <f>COUNTIF(Skill!V:V,20205)</f>
@@ -21260,7 +21316,7 @@
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>966</v>
+        <v>950</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>67</v>
@@ -21283,30 +21339,30 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.15">
       <c r="G13" t="s">
-        <v>967</v>
+        <v>951</v>
       </c>
       <c r="H13" s="25" t="s">
-        <v>968</v>
+        <v>952</v>
       </c>
       <c r="I13" s="25"/>
       <c r="J13" s="25" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K13" s="25"/>
       <c r="L13" s="25" t="s">
-        <v>969</v>
+        <v>953</v>
       </c>
       <c r="M13" s="25"/>
       <c r="Q13" t="s">
-        <v>970</v>
+        <v>954</v>
       </c>
       <c r="R13" t="s">
-        <v>971</v>
+        <v>955</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.15">
       <c r="G14" t="s">
-        <v>955</v>
+        <v>939</v>
       </c>
       <c r="H14" s="25">
         <v>125</v>
@@ -21321,7 +21377,7 @@
       </c>
       <c r="M14" s="25"/>
       <c r="Q14" t="s">
-        <v>972</v>
+        <v>956</v>
       </c>
       <c r="R14" t="s">
         <v>183</v>
@@ -21329,7 +21385,7 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.15">
       <c r="G15" t="s">
-        <v>956</v>
+        <v>940</v>
       </c>
       <c r="H15" s="25">
         <v>120</v>
@@ -21344,15 +21400,15 @@
       </c>
       <c r="M15" s="25"/>
       <c r="Q15" t="s">
-        <v>973</v>
+        <v>957</v>
       </c>
       <c r="R15" t="s">
-        <v>497</v>
+        <v>481</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.15">
       <c r="G16" t="s">
-        <v>959</v>
+        <v>943</v>
       </c>
       <c r="H16" s="25">
         <v>115</v>
@@ -21367,15 +21423,15 @@
       </c>
       <c r="M16" s="25"/>
       <c r="Q16" t="s">
-        <v>974</v>
+        <v>958</v>
       </c>
       <c r="R16" t="s">
-        <v>427</v>
+        <v>411</v>
       </c>
     </row>
     <row r="17" spans="7:15" x14ac:dyDescent="0.15">
       <c r="G17" t="s">
-        <v>961</v>
+        <v>945</v>
       </c>
       <c r="H17" s="25">
         <v>110</v>
@@ -21392,7 +21448,7 @@
     </row>
     <row r="18" spans="7:15" x14ac:dyDescent="0.15">
       <c r="G18" t="s">
-        <v>963</v>
+        <v>947</v>
       </c>
       <c r="H18" s="25">
         <v>105</v>
@@ -21409,7 +21465,7 @@
     </row>
     <row r="19" spans="7:15" x14ac:dyDescent="0.15">
       <c r="G19" t="s">
-        <v>966</v>
+        <v>950</v>
       </c>
       <c r="H19" s="25">
         <v>100</v>
@@ -21430,18 +21486,18 @@
     </row>
     <row r="21" spans="7:15" x14ac:dyDescent="0.15">
       <c r="G21" t="s">
-        <v>975</v>
+        <v>959</v>
       </c>
       <c r="H21" s="25" t="s">
-        <v>976</v>
+        <v>960</v>
       </c>
       <c r="I21" s="25"/>
       <c r="J21" s="25" t="s">
-        <v>977</v>
+        <v>961</v>
       </c>
       <c r="K21" s="25"/>
       <c r="L21" s="25" t="s">
-        <v>978</v>
+        <v>962</v>
       </c>
       <c r="M21" s="26"/>
       <c r="O21" s="10"/>
@@ -21503,31 +21559,31 @@
   <sheetData>
     <row r="3" spans="1:16" x14ac:dyDescent="0.15">
       <c r="B3" t="s">
-        <v>979</v>
+        <v>963</v>
       </c>
       <c r="C3" t="s">
-        <v>980</v>
+        <v>964</v>
       </c>
       <c r="D3" t="s">
-        <v>981</v>
+        <v>965</v>
       </c>
       <c r="H3" t="s">
-        <v>963</v>
+        <v>947</v>
       </c>
       <c r="I3" t="s">
-        <v>961</v>
+        <v>945</v>
       </c>
       <c r="J3" t="s">
-        <v>959</v>
+        <v>943</v>
       </c>
       <c r="K3" t="s">
-        <v>956</v>
+        <v>940</v>
       </c>
       <c r="L3" t="s">
-        <v>955</v>
+        <v>939</v>
       </c>
       <c r="M3" t="s">
-        <v>951</v>
+        <v>935</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.15">
@@ -21535,13 +21591,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>982</v>
+        <v>966</v>
       </c>
       <c r="C4" t="s">
-        <v>983</v>
+        <v>967</v>
       </c>
       <c r="D4" t="s">
-        <v>984</v>
+        <v>968</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.15">
@@ -21549,13 +21605,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>985</v>
+        <v>969</v>
       </c>
       <c r="C5" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D5" t="s">
-        <v>986</v>
+        <v>970</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.15">
@@ -21563,13 +21619,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>987</v>
+        <v>971</v>
       </c>
       <c r="C6" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D6" t="s">
-        <v>988</v>
+        <v>972</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.15">
@@ -21577,13 +21633,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>989</v>
+        <v>973</v>
       </c>
       <c r="C7" t="s">
-        <v>983</v>
+        <v>967</v>
       </c>
       <c r="D7" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.15">
@@ -21591,13 +21647,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>991</v>
+        <v>975</v>
       </c>
       <c r="C8" t="s">
-        <v>983</v>
+        <v>967</v>
       </c>
       <c r="D8" t="s">
-        <v>992</v>
+        <v>976</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.15">
@@ -21605,13 +21661,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>993</v>
+        <v>977</v>
       </c>
       <c r="C9" t="s">
-        <v>983</v>
+        <v>967</v>
       </c>
       <c r="D9" t="s">
-        <v>994</v>
+        <v>978</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.15">
@@ -21619,13 +21675,13 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>995</v>
+        <v>979</v>
       </c>
       <c r="C10" t="s">
-        <v>983</v>
+        <v>967</v>
       </c>
       <c r="D10" t="s">
-        <v>996</v>
+        <v>980</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.15">
@@ -21646,7 +21702,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.15">
       <c r="F16" t="s">
-        <v>997</v>
+        <v>981</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
@@ -21658,7 +21714,7 @@
     <row r="17" spans="5:16" x14ac:dyDescent="0.15">
       <c r="E17" s="6"/>
       <c r="F17" t="s">
-        <v>998</v>
+        <v>982</v>
       </c>
       <c r="G17" s="6"/>
       <c r="J17" s="6"/>
@@ -21669,7 +21725,7 @@
     <row r="18" spans="5:16" x14ac:dyDescent="0.15">
       <c r="E18" s="6"/>
       <c r="F18" t="s">
-        <v>999</v>
+        <v>983</v>
       </c>
       <c r="G18" s="6"/>
       <c r="J18" s="6"/>
@@ -21823,7 +21879,7 @@
         <v>14</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>1000</v>
+        <v>984</v>
       </c>
       <c r="Y1" s="3" t="s">
         <v>16</v>
@@ -21848,25 +21904,25 @@
         <v>22</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>1001</v>
+        <v>985</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>1002</v>
+        <v>986</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>1003</v>
+        <v>987</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>29</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>1004</v>
+        <v>988</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>31</v>
@@ -21970,7 +22026,7 @@
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B27" s="1" t="s">
-        <v>497</v>
+        <v>481</v>
       </c>
       <c r="C27" s="1" cm="1">
         <f t="array" ref="C27">SUMPRODUCT(LEN(P:P)-LEN(SUBSTITUTE(P:P,"↑","")))</f>
@@ -21997,7 +22053,7 @@
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B30" s="1" t="s">
-        <v>427</v>
+        <v>411</v>
       </c>
       <c r="C30" s="1" cm="1">
         <f t="array" ref="C30">SUMPRODUCT(LEN(P:P)-LEN(SUBSTITUTE(P:P,"→","")))</f>

--- a/Luban/Excel/Skill.xlsx
+++ b/Luban/Excel/Skill.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03FC4958-5772-4AEB-A756-6E5ADD0C8244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13C18145-15EF-4E8A-B6F2-A87FA32F662A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -642,7 +642,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2047" uniqueCount="1126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2047" uniqueCount="1125">
   <si>
     <t>id</t>
   </si>
@@ -1511,15 +1511,9 @@
     <t>施力压迫</t>
   </si>
   <si>
-    <t>对目标造成125%技的伤害，施加3层刚屏合3层玄屏</t>
-  </si>
-  <si>
     <t>←←→↑</t>
   </si>
   <si>
-    <t>对目标造成135%技的伤害，施加3层刚屏合3层玄屏</t>
-  </si>
-  <si>
     <t>迭浪倾川</t>
   </si>
   <si>
@@ -1544,12 +1538,6 @@
     <t>随机获得3个键</t>
   </si>
   <si>
-    <t>对目标造成125%技的伤害，窃取目标1个增益状态</t>
-  </si>
-  <si>
-    <t>若键的数量大于敌手则威力增加10的百分比，且时窃取目标1个增益状态的效果改为交锋时触发</t>
-  </si>
-  <si>
     <t>←→</t>
   </si>
   <si>
@@ -1697,36 +1685,18 @@
     <t>霜连天</t>
   </si>
   <si>
-    <t>施加3层玄屏状态</t>
-  </si>
-  <si>
     <t>残月分江</t>
   </si>
   <si>
-    <t>招式的玄炁消耗转为当前90%，至多90</t>
-  </si>
-  <si>
-    <t>对目标造成125%技的伤害，至少造成80%技的伤害时返还消耗的键</t>
-  </si>
-  <si>
     <t>←↓↓→</t>
   </si>
   <si>
     <t>追魂破</t>
   </si>
   <si>
-    <t>重新在敌手中随机选择行动目标，行动加快1息或延迟1息，招式的玄炁消耗转为当前70%，至多70</t>
-  </si>
-  <si>
-    <t>对目标造成140%技的伤害，施加1层过劲状态</t>
-  </si>
-  <si>
     <t>送长离</t>
   </si>
   <si>
-    <t>对目标造成130%技的伤害，消耗目标剩余行动次数等量的键（至多2）</t>
-  </si>
-  <si>
     <t>↓→→</t>
   </si>
   <si>
@@ -1742,24 +1712,9 @@
     <t>走旱势</t>
   </si>
   <si>
-    <t>对目标造成125%技的伤害，施加3层赤沸状态</t>
-  </si>
-  <si>
-    <t>消耗目标25玄炁</t>
-  </si>
-  <si>
-    <t>对目标造成165%技的伤害，若目标体大于自身则恢复伤害量一半的体，若目标体小于自身则再造成伤害量一半的伤害</t>
-  </si>
-  <si>
-    <t>刚炁+70</t>
-  </si>
-  <si>
     <t>←←→→</t>
   </si>
   <si>
-    <t>对目标造成120%技的伤害，恢复本回合受到伤害30%的体</t>
-  </si>
-  <si>
     <t>玄炁+10</t>
   </si>
   <si>
@@ -1769,54 +1724,27 @@
     <t>吮吸生机</t>
   </si>
   <si>
-    <t>对目标造成160%技的伤害，扣除其15%全部属性并增加等量的属性，消耗其20刚炁20玄炁并增加等量的炁</t>
-  </si>
-  <si>
     <t>仅能对存在10层毒瘴状态的敌手使用</t>
   </si>
   <si>
     <t>死气纠缠</t>
   </si>
   <si>
-    <t>若目标毒瘴状态层数低于自身则威力增加20的百分比</t>
-  </si>
-  <si>
     <t>凋零</t>
   </si>
   <si>
-    <t>对目标造成120%技的伤害，施加随机按键的1层封穴状态和1层过劲状态</t>
-  </si>
-  <si>
-    <t>若敌手的毒瘴状态层数不低于自身则不会被敌手破招</t>
-  </si>
-  <si>
     <t>夜盖胧刀</t>
   </si>
   <si>
-    <t>对目标造成140%技的伤害，施加3层破绽状态</t>
-  </si>
-  <si>
     <t>若时段为夜则玄炁消耗减少5</t>
   </si>
   <si>
     <t>←←→</t>
   </si>
   <si>
-    <t>若互为目标且目标招式未带有↓键则本次行动不会被破招</t>
-  </si>
-  <si>
-    <t>本次行动不会被招式未带有↓键的敌手破招</t>
-  </si>
-  <si>
     <t>天汉落子</t>
   </si>
   <si>
-    <t>对目标造成150%技的伤害，随机封锁目标两个键直到回合结束</t>
-  </si>
-  <si>
-    <t>获得3层心眼状态和3层巧增状态</t>
-  </si>
-  <si>
     <t>若时段为昼则炁的消耗改为刚炁</t>
   </si>
   <si>
@@ -1829,9 +1757,6 @@
     <t>碎琉璃</t>
   </si>
   <si>
-    <t>施加等同目标行动招式包含的键数量的伤口状态</t>
-  </si>
-  <si>
     <t>↓↑→→</t>
   </si>
   <si>
@@ -1841,18 +1766,9 @@
     <t>道合清一</t>
   </si>
   <si>
-    <t>招式的玄炁消耗转为当前100%，至多100</t>
-  </si>
-  <si>
-    <t>获得5层巧增</t>
-  </si>
-  <si>
     <t>对目标造成160%技的伤害，造成的伤害不会被削减</t>
   </si>
   <si>
-    <t>刚炁+当前100%（至少30）</t>
-  </si>
-  <si>
     <t>玄炁与刚炁相同时可使用</t>
   </si>
   <si>
@@ -1862,15 +1778,9 @@
     <t>三丹炎</t>
   </si>
   <si>
-    <t>对目标造成150%技的伤害，施加3层破绽状态和3层失衡状态</t>
-  </si>
-  <si>
     <t>拒之千里</t>
   </si>
   <si>
-    <t>清除自身1层异常状态</t>
-  </si>
-  <si>
     <t>获得1层避殃状态</t>
   </si>
   <si>
@@ -1883,22 +1793,13 @@
     <t>律令风行</t>
   </si>
   <si>
-    <t>获得1层迅速</t>
-  </si>
-  <si>
     <t>造成120%技的伤害</t>
   </si>
   <si>
-    <t>每次使用该招式威力增加10的百分比且获得的迅速状态增加1层、玄消耗增加20；每消耗1个键减少5玄炁消耗但不会低于{[int]}（10+使用次数*5）直到下次使用</t>
-  </si>
-  <si>
     <t>天公道</t>
   </si>
   <si>
     <t>阴流杀</t>
-  </si>
-  <si>
-    <t>对目标造成110%技的伤害，单方面攻击施加3层赤沸状态，若目标本回合还未行动过则额外施加2层赤沸状态</t>
   </si>
   <si>
     <t>比</t>
@@ -4156,6 +4057,134 @@
   </si>
   <si>
     <t>对目标造成135%技的伤害，施加3层寒沁状态</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>施加3层玄屏状态</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>招式的玄炁消耗转为当前90%，至多90</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>对目标造成125%技的伤害，至少造成80%技的伤害时返还消耗的键</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>重新在敌手中随机选择行动目标，行动加快1息或延迟1息，招式的玄炁消耗转为当前70%，至多70</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>对目标造成140%技的伤害，施加1层过劲状态</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>对目标造成130%技的伤害，消耗目标剩余行动次数等量的键（至多2）</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗目标25玄炁</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>对目标造成125%技的伤害，施加3层赤沸状态</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>对目标造成165%技的伤害，若目标体大于自身则恢复伤害量一半的体，若目标体小于自身则再造成伤害量一半的伤害</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁+70</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>对目标造成120%技的伤害，恢复本回合受到伤害30%的体</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄炁+10</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>对目标造成160%技的伤害，扣除其15%全部属性并增加等量的属性，消耗其20刚炁20玄炁并增加等量的炁</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>若目标毒瘴状态层数低于自身则威力增加20的百分比</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>对目标造成120%技的伤害，施加随机按键的1层封穴状态和1层过劲状态</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>若敌手的毒瘴状态层数不低于自身则不会被敌手破招</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>对目标造成140%技的伤害，施加3层破绽状态</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>若互为目标且目标招式未带有↓键则本次行动不会被破招</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>本次行动不会被招式未带有↓键的敌手破招</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>对目标造成150%技的伤害，随机封锁目标两个键直到回合结束</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得3层心眼状态和3层巧增状态</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>招式的玄炁消耗转为当前70%，至多70</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>施加等同目标行动招式包含的键数量的伤口状态</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>招式的玄炁消耗转为当前100%，至多100</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁+当前100%（至少30）</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得5层巧增</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>对目标造成150%技的伤害，施加3层破绽状态和3层失衡状态</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>清除自身1层异常状态</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得1层避殃状态</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得1层迅速</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次使用该招式威力增加10的百分比且获得的迅速状态增加1层、玄消耗增加20；每消耗1个键减少5玄炁消耗但不会低于{[int]}（10+使用次数*5）直到下次使用</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>对目标造成110%技的伤害，单方面攻击施加3层赤沸状态，若目标本回合还未行动过则额外施加2层赤沸状态</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -4935,16 +4964,16 @@
         <v>1</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>1053</v>
+        <v>1020</v>
       </c>
       <c r="G4" s="16" t="s">
         <v>46</v>
       </c>
       <c r="J4" s="16" t="s">
-        <v>1027</v>
+        <v>994</v>
       </c>
       <c r="L4" s="16" t="s">
-        <v>1047</v>
+        <v>1014</v>
       </c>
       <c r="O4" s="14">
         <v>1</v>
@@ -4995,13 +5024,13 @@
         <v>1</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>1045</v>
+        <v>1012</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>1052</v>
+        <v>1019</v>
       </c>
       <c r="L5" s="16" t="s">
-        <v>1047</v>
+        <v>1014</v>
       </c>
       <c r="O5" s="14">
         <v>1</v>
@@ -5055,7 +5084,7 @@
         <v>46</v>
       </c>
       <c r="J6" s="16" t="s">
-        <v>1054</v>
+        <v>1021</v>
       </c>
       <c r="O6" s="14">
         <v>1</v>
@@ -5106,7 +5135,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="J7" s="16" t="s">
         <v>60</v>
@@ -5609,13 +5638,13 @@
         <v>11013</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>1024</v>
+        <v>991</v>
       </c>
       <c r="C16" s="14">
         <v>1</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>1023</v>
+        <v>990</v>
       </c>
       <c r="H16" s="16" t="s">
         <v>104</v>
@@ -5672,7 +5701,7 @@
         <v>107</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>990</v>
+        <v>957</v>
       </c>
       <c r="I17" s="14"/>
       <c r="J17" s="14"/>
@@ -5905,12 +5934,12 @@
         <v>125</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>1033</v>
+        <v>1000</v>
       </c>
       <c r="I21" s="14"/>
       <c r="J21" s="14"/>
       <c r="L21" s="16" t="s">
-        <v>1034</v>
+        <v>1001</v>
       </c>
       <c r="O21" s="14" t="s">
         <v>126</v>
@@ -5964,12 +5993,12 @@
         <v>125</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>1036</v>
+        <v>1003</v>
       </c>
       <c r="I22" s="14"/>
       <c r="J22" s="14"/>
       <c r="L22" s="16" t="s">
-        <v>1035</v>
+        <v>1002</v>
       </c>
       <c r="O22" s="14" t="s">
         <v>126</v>
@@ -6023,7 +6052,7 @@
         <v>130</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>1040</v>
+        <v>1007</v>
       </c>
       <c r="I23" s="14"/>
       <c r="J23" s="14"/>
@@ -6031,7 +6060,7 @@
         <v>131</v>
       </c>
       <c r="N23" s="16" t="s">
-        <v>1055</v>
+        <v>1022</v>
       </c>
       <c r="O23" s="14" t="s">
         <v>126</v>
@@ -6082,10 +6111,10 @@
         <v>1</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>1058</v>
+        <v>1025</v>
       </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
@@ -6138,15 +6167,15 @@
         <v>1</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>1040</v>
+        <v>1007</v>
       </c>
       <c r="I25" s="14"/>
       <c r="J25" s="14"/>
       <c r="L25" s="16" t="s">
-        <v>1060</v>
+        <v>1027</v>
       </c>
       <c r="O25" s="14" t="s">
         <v>126</v>
@@ -6197,15 +6226,15 @@
         <v>1</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>1022</v>
+        <v>989</v>
       </c>
       <c r="H26" s="14"/>
       <c r="I26" s="14"/>
       <c r="J26" s="14" t="s">
-        <v>1061</v>
+        <v>1028</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>1047</v>
+        <v>1014</v>
       </c>
       <c r="O26" s="14">
         <v>1</v>
@@ -6256,15 +6285,15 @@
         <v>1</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>1062</v>
+        <v>1029</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>1063</v>
+        <v>1030</v>
       </c>
       <c r="I27" s="14"/>
       <c r="J27" s="14"/>
       <c r="L27" s="16" t="s">
-        <v>1064</v>
+        <v>1031</v>
       </c>
       <c r="O27" s="14">
         <v>2</v>
@@ -6315,15 +6344,15 @@
         <v>1</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>1025</v>
+        <v>992</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>1065</v>
+        <v>1032</v>
       </c>
       <c r="I28" s="14"/>
       <c r="J28" s="14"/>
       <c r="L28" s="16" t="s">
-        <v>1066</v>
+        <v>1033</v>
       </c>
       <c r="O28" s="14">
         <v>2</v>
@@ -6374,10 +6403,10 @@
         <v>1</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>1052</v>
+        <v>1019</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>1067</v>
+        <v>1034</v>
       </c>
       <c r="I29" s="14"/>
       <c r="J29" s="14"/>
@@ -6435,7 +6464,7 @@
       <c r="H30" s="14"/>
       <c r="I30" s="14"/>
       <c r="J30" s="14" t="s">
-        <v>1068</v>
+        <v>1035</v>
       </c>
       <c r="O30" s="14">
         <v>1</v>
@@ -6494,7 +6523,7 @@
       <c r="I31" s="14"/>
       <c r="J31" s="14"/>
       <c r="N31" s="16" t="s">
-        <v>1069</v>
+        <v>1036</v>
       </c>
       <c r="O31" s="14">
         <v>1</v>
@@ -6545,12 +6574,12 @@
         <v>1</v>
       </c>
       <c r="H32" s="14" t="s">
-        <v>1070</v>
+        <v>1037</v>
       </c>
       <c r="I32" s="14"/>
       <c r="J32" s="14"/>
       <c r="L32" s="16" t="s">
-        <v>1071</v>
+        <v>1038</v>
       </c>
       <c r="O32" s="14">
         <v>5</v>
@@ -6595,22 +6624,22 @@
         <v>11030</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>1026</v>
+        <v>993</v>
       </c>
       <c r="C33" s="14">
         <v>1</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>1072</v>
+        <v>1039</v>
       </c>
       <c r="H33" s="14"/>
       <c r="I33" s="14"/>
       <c r="J33" s="14"/>
       <c r="L33" s="16" t="s">
-        <v>1073</v>
+        <v>1040</v>
       </c>
       <c r="N33" s="16" t="s">
-        <v>1074</v>
+        <v>1041</v>
       </c>
       <c r="O33" s="14">
         <v>1</v>
@@ -6661,10 +6690,10 @@
         <v>1</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>1075</v>
+        <v>1042</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>1076</v>
+        <v>1043</v>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="14"/>
@@ -6717,13 +6746,13 @@
         <v>1</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>993</v>
+        <v>960</v>
       </c>
       <c r="H35" s="14"/>
       <c r="I35" s="14"/>
       <c r="J35" s="14"/>
       <c r="L35" s="16" t="s">
-        <v>1047</v>
+        <v>1014</v>
       </c>
       <c r="O35" s="14" t="s">
         <v>160</v>
@@ -6774,14 +6803,14 @@
         <v>1</v>
       </c>
       <c r="H36" s="16" t="s">
-        <v>1077</v>
+        <v>1044</v>
       </c>
       <c r="I36" s="14"/>
       <c r="L36" s="16" t="s">
-        <v>1078</v>
+        <v>1045</v>
       </c>
       <c r="N36" s="16" t="s">
-        <v>1018</v>
+        <v>985</v>
       </c>
       <c r="O36" s="14">
         <v>1</v>
@@ -6832,10 +6861,10 @@
         <v>1</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>1079</v>
+        <v>1046</v>
       </c>
       <c r="H37" s="16" t="s">
-        <v>1080</v>
+        <v>1047</v>
       </c>
       <c r="I37" s="14"/>
       <c r="J37" s="14"/>
@@ -6882,7 +6911,7 @@
         <v>1</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>1081</v>
+        <v>1048</v>
       </c>
       <c r="H38" s="14" t="s">
         <v>168</v>
@@ -6935,7 +6964,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="16" t="s">
-        <v>1041</v>
+        <v>1008</v>
       </c>
       <c r="O39" s="14" t="s">
         <v>171</v>
@@ -6977,11 +7006,11 @@
         <v>1</v>
       </c>
       <c r="H40" s="14" t="s">
-        <v>1037</v>
+        <v>1004</v>
       </c>
       <c r="I40" s="14"/>
       <c r="J40" s="16" t="s">
-        <v>1082</v>
+        <v>1049</v>
       </c>
       <c r="O40" s="14" t="s">
         <v>171</v>
@@ -7026,11 +7055,11 @@
         <v>137</v>
       </c>
       <c r="H41" s="14" t="s">
-        <v>1028</v>
+        <v>995</v>
       </c>
       <c r="I41" s="14"/>
       <c r="J41" s="16" t="s">
-        <v>1027</v>
+        <v>994</v>
       </c>
       <c r="O41" s="14" t="s">
         <v>175</v>
@@ -7066,17 +7095,17 @@
         <v>11039</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>1017</v>
+        <v>984</v>
       </c>
       <c r="C42" s="14">
         <v>1</v>
       </c>
       <c r="F42" s="14"/>
       <c r="G42" s="16" t="s">
-        <v>1030</v>
+        <v>997</v>
       </c>
       <c r="H42" s="14" t="s">
-        <v>1029</v>
+        <v>996</v>
       </c>
       <c r="N42" s="16" t="s">
         <v>176</v>
@@ -7121,7 +7150,7 @@
         <v>1</v>
       </c>
       <c r="H43" s="16" t="s">
-        <v>1042</v>
+        <v>1009</v>
       </c>
       <c r="O43" s="14" t="s">
         <v>171</v>
@@ -7166,12 +7195,12 @@
         <v>125</v>
       </c>
       <c r="H44" s="14" t="s">
-        <v>1031</v>
+        <v>998</v>
       </c>
       <c r="I44" s="14"/>
       <c r="J44" s="14"/>
       <c r="L44" s="16" t="s">
-        <v>1032</v>
+        <v>999</v>
       </c>
       <c r="O44" s="14" t="s">
         <v>126</v>
@@ -7219,12 +7248,12 @@
         <v>125</v>
       </c>
       <c r="H45" s="14" t="s">
-        <v>1038</v>
+        <v>1005</v>
       </c>
       <c r="I45" s="14"/>
       <c r="J45" s="14"/>
       <c r="L45" s="16" t="s">
-        <v>1039</v>
+        <v>1006</v>
       </c>
       <c r="O45" s="14" t="s">
         <v>126</v>
@@ -7269,15 +7298,15 @@
         <v>1</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="H46" s="14" t="s">
-        <v>1040</v>
+        <v>1007</v>
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14"/>
       <c r="L46" s="16" t="s">
-        <v>1032</v>
+        <v>999</v>
       </c>
       <c r="O46" s="14" t="s">
         <v>126</v>
@@ -7322,15 +7351,15 @@
         <v>1</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>1059</v>
+        <v>1026</v>
       </c>
       <c r="H47" s="14" t="s">
-        <v>1040</v>
+        <v>1007</v>
       </c>
       <c r="I47" s="14"/>
       <c r="J47" s="14"/>
       <c r="L47" s="16" t="s">
-        <v>1039</v>
+        <v>1006</v>
       </c>
       <c r="O47" s="14" t="s">
         <v>126</v>
@@ -7428,7 +7457,7 @@
         <v>1</v>
       </c>
       <c r="H49" s="16" t="s">
-        <v>1042</v>
+        <v>1009</v>
       </c>
       <c r="O49" s="14" t="s">
         <v>171</v>
@@ -7470,11 +7499,11 @@
         <v>1</v>
       </c>
       <c r="H50" s="14" t="s">
-        <v>1037</v>
+        <v>1004</v>
       </c>
       <c r="I50" s="14"/>
       <c r="J50" s="16" t="s">
-        <v>1083</v>
+        <v>1050</v>
       </c>
       <c r="O50" s="14" t="s">
         <v>171</v>
@@ -7513,7 +7542,7 @@
         <v>1</v>
       </c>
       <c r="H51" s="16" t="s">
-        <v>1043</v>
+        <v>1010</v>
       </c>
       <c r="I51" s="14"/>
       <c r="J51" s="14"/>
@@ -7539,7 +7568,7 @@
         <v>1</v>
       </c>
       <c r="H52" s="14" t="s">
-        <v>1044</v>
+        <v>1011</v>
       </c>
       <c r="I52" s="14"/>
       <c r="J52" s="14"/>
@@ -7568,18 +7597,18 @@
         <v>1</v>
       </c>
       <c r="E53" s="16" t="s">
-        <v>1046</v>
+        <v>1013</v>
       </c>
       <c r="G53" s="16" t="s">
-        <v>1084</v>
+        <v>1051</v>
       </c>
       <c r="H53" s="14"/>
       <c r="I53" s="14"/>
       <c r="J53" s="16" t="s">
-        <v>1027</v>
+        <v>994</v>
       </c>
       <c r="L53" s="16" t="s">
-        <v>1045</v>
+        <v>1012</v>
       </c>
       <c r="Q53" s="14" t="s">
         <v>179</v>
@@ -7627,7 +7656,7 @@
         <v>182</v>
       </c>
       <c r="L54" s="16" t="s">
-        <v>1047</v>
+        <v>1014</v>
       </c>
       <c r="O54" s="14">
         <v>1</v>
@@ -7669,12 +7698,12 @@
         <v>185</v>
       </c>
       <c r="H55" s="16" t="s">
-        <v>1049</v>
+        <v>1016</v>
       </c>
       <c r="I55" s="14"/>
       <c r="J55" s="14"/>
       <c r="L55" s="16" t="s">
-        <v>1048</v>
+        <v>1015</v>
       </c>
       <c r="Q55" s="14" t="s">
         <v>186</v>
@@ -7716,13 +7745,13 @@
       <c r="F56" s="14"/>
       <c r="G56" s="14"/>
       <c r="H56" s="14" t="s">
-        <v>1050</v>
+        <v>1017</v>
       </c>
       <c r="I56" s="14"/>
       <c r="J56" s="14"/>
       <c r="K56" s="14"/>
       <c r="L56" s="14" t="s">
-        <v>1051</v>
+        <v>1018</v>
       </c>
       <c r="M56" s="14"/>
       <c r="N56" s="14" t="s">
@@ -8029,7 +8058,7 @@
       <c r="I64" s="14"/>
       <c r="J64" s="14"/>
       <c r="L64" s="16" t="s">
-        <v>1085</v>
+        <v>1052</v>
       </c>
       <c r="O64" s="14">
         <v>1</v>
@@ -8192,7 +8221,7 @@
         <v>2</v>
       </c>
       <c r="E67" s="16" t="s">
-        <v>1086</v>
+        <v>1053</v>
       </c>
       <c r="H67" s="14" t="s">
         <v>202</v>
@@ -8200,7 +8229,7 @@
       <c r="I67" s="14"/>
       <c r="J67" s="14"/>
       <c r="L67" s="16" t="s">
-        <v>1087</v>
+        <v>1054</v>
       </c>
       <c r="O67" s="14">
         <v>1</v>
@@ -8369,12 +8398,12 @@
         <v>2</v>
       </c>
       <c r="H70" s="14" t="s">
-        <v>1088</v>
+        <v>1055</v>
       </c>
       <c r="I70" s="14"/>
       <c r="J70" s="14"/>
       <c r="L70" s="16" t="s">
-        <v>1085</v>
+        <v>1052</v>
       </c>
       <c r="O70" s="14">
         <v>3</v>
@@ -8425,16 +8454,16 @@
         <v>2</v>
       </c>
       <c r="E71" s="16" t="s">
-        <v>1091</v>
+        <v>1058</v>
       </c>
       <c r="H71" s="16" t="s">
         <v>223</v>
       </c>
       <c r="J71" s="16" t="s">
-        <v>1090</v>
+        <v>1057</v>
       </c>
       <c r="L71" s="16" t="s">
-        <v>1089</v>
+        <v>1056</v>
       </c>
       <c r="O71" s="14">
         <v>6</v>
@@ -8485,13 +8514,13 @@
         <v>2</v>
       </c>
       <c r="G72" s="16" t="s">
-        <v>997</v>
+        <v>964</v>
       </c>
       <c r="H72" s="16" t="s">
         <v>231</v>
       </c>
       <c r="L72" s="16" t="s">
-        <v>1092</v>
+        <v>1059</v>
       </c>
       <c r="O72" s="14">
         <v>1</v>
@@ -9099,10 +9128,10 @@
         <v>2</v>
       </c>
       <c r="G84" s="16" t="s">
-        <v>1093</v>
+        <v>1060</v>
       </c>
       <c r="H84" s="16" t="s">
-        <v>1094</v>
+        <v>1061</v>
       </c>
       <c r="P84" s="14">
         <v>7</v>
@@ -9230,13 +9259,13 @@
         <v>2</v>
       </c>
       <c r="H87" s="16" t="s">
-        <v>1095</v>
+        <v>1062</v>
       </c>
       <c r="J87" s="16" t="s">
-        <v>992</v>
+        <v>959</v>
       </c>
       <c r="Q87" s="14" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="R87" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R87" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q87,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q87))),1))</f>
@@ -9278,14 +9307,14 @@
         <v>2</v>
       </c>
       <c r="G88" s="16" t="s">
-        <v>1097</v>
+        <v>1064</v>
       </c>
       <c r="H88" s="16" t="s">
-        <v>1096</v>
+        <v>1063</v>
       </c>
       <c r="I88" s="14"/>
       <c r="Q88" s="14" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="R88" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R88" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q88,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q88))),1))</f>
@@ -9321,23 +9350,23 @@
         <v>12026</v>
       </c>
       <c r="B89" s="15" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C89" s="14">
         <v>2</v>
       </c>
       <c r="H89" s="16" t="s">
-        <v>1098</v>
+        <v>1065</v>
       </c>
       <c r="I89" s="14"/>
       <c r="J89" s="14" t="s">
-        <v>1099</v>
+        <v>1066</v>
       </c>
       <c r="L89" s="16" t="s">
-        <v>1100</v>
+        <v>1067</v>
       </c>
       <c r="Q89" s="14" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="R89" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R89" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q89,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q89))),1))</f>
@@ -9361,24 +9390,24 @@
         <v>12027</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C90" s="14">
         <v>2</v>
       </c>
       <c r="E90" s="16" t="s">
-        <v>1057</v>
+        <v>1024</v>
       </c>
       <c r="H90" s="16" t="s">
-        <v>1101</v>
+        <v>1068</v>
       </c>
       <c r="I90" s="14"/>
       <c r="J90" s="14"/>
       <c r="L90" s="16" t="s">
-        <v>1102</v>
+        <v>1069</v>
       </c>
       <c r="Q90" s="14" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="R90" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R90" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q90,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q90))),1))</f>
@@ -9414,23 +9443,23 @@
         <v>12028</v>
       </c>
       <c r="B91" s="15" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C91" s="14">
         <v>2</v>
       </c>
       <c r="E91" s="16" t="s">
-        <v>1103</v>
+        <v>1070</v>
       </c>
       <c r="H91" s="16" t="s">
-        <v>1104</v>
+        <v>1071</v>
       </c>
       <c r="I91" s="14"/>
       <c r="J91" s="16" t="s">
-        <v>1105</v>
+        <v>1072</v>
       </c>
       <c r="Q91" s="14" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="R91" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R91" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q91,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q91))),1))</f>
@@ -9466,7 +9495,7 @@
         <v>12029</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C92" s="14">
         <v>2</v>
@@ -9475,15 +9504,15 @@
         <v>134</v>
       </c>
       <c r="H92" s="16" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="I92" s="14"/>
       <c r="J92" s="14"/>
       <c r="L92" s="16" t="s">
-        <v>1106</v>
+        <v>1073</v>
       </c>
       <c r="Q92" s="14" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="R92" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R92" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q92,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q92))),1))</f>
@@ -9519,23 +9548,23 @@
         <v>12030</v>
       </c>
       <c r="B93" s="15" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C93" s="14">
         <v>2</v>
       </c>
       <c r="E93" s="16" t="s">
-        <v>1103</v>
+        <v>1070</v>
       </c>
       <c r="H93" s="16" t="s">
-        <v>1107</v>
+        <v>1074</v>
       </c>
       <c r="I93" s="14"/>
       <c r="J93" s="16" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="Q93" s="14" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="R93" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R93" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q93,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q93))),1))</f>
@@ -9571,18 +9600,18 @@
         <v>12031</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C94" s="14">
         <v>2</v>
       </c>
       <c r="H94" s="14" t="s">
-        <v>1108</v>
+        <v>1075</v>
       </c>
       <c r="I94" s="14"/>
       <c r="J94" s="14"/>
       <c r="Q94" s="14" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="R94" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R94" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q94,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q94))),1))</f>
@@ -9618,22 +9647,22 @@
         <v>12032</v>
       </c>
       <c r="B95" s="15" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C95" s="14">
         <v>2</v>
       </c>
       <c r="G95" s="16" t="s">
-        <v>998</v>
+        <v>965</v>
       </c>
       <c r="H95" s="22" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="J95" s="16" t="s">
-        <v>1117</v>
+        <v>1084</v>
       </c>
       <c r="N95" s="16" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="R95" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R95" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q95,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q95))),1))</f>
@@ -9663,19 +9692,19 @@
         <v>12033</v>
       </c>
       <c r="B96" s="15" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C96" s="14">
         <v>2</v>
       </c>
       <c r="G96" s="16" t="s">
-        <v>999</v>
+        <v>966</v>
       </c>
       <c r="H96" s="16" t="s">
-        <v>1109</v>
+        <v>1076</v>
       </c>
       <c r="N96" s="16" t="s">
-        <v>1001</v>
+        <v>968</v>
       </c>
       <c r="R96" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R96" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q96,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q96))),1))</f>
@@ -9705,16 +9734,16 @@
         <v>12034</v>
       </c>
       <c r="B97" s="15" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C97" s="14">
         <v>2</v>
       </c>
       <c r="G97" s="16" t="s">
-        <v>1000</v>
+        <v>967</v>
       </c>
       <c r="H97" s="22" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="R97" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R97" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q97,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q97))),1))</f>
@@ -9744,16 +9773,16 @@
         <v>12035</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C98" s="14">
         <v>2</v>
       </c>
       <c r="H98" s="16" t="s">
-        <v>1110</v>
+        <v>1077</v>
       </c>
       <c r="L98" s="16" t="s">
-        <v>1111</v>
+        <v>1078</v>
       </c>
       <c r="R98" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R98" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q98,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q98))),1))</f>
@@ -9772,7 +9801,7 @@
         <v>20302</v>
       </c>
       <c r="W98" s="14" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Y98" s="14">
         <v>2</v>
@@ -9789,19 +9818,19 @@
         <v>12036</v>
       </c>
       <c r="B99" s="15" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C99" s="14">
         <v>2</v>
       </c>
       <c r="E99" s="16" t="s">
-        <v>1112</v>
+        <v>1079</v>
       </c>
       <c r="H99" s="16" t="s">
-        <v>1113</v>
+        <v>1080</v>
       </c>
       <c r="L99" s="16" t="s">
-        <v>1085</v>
+        <v>1052</v>
       </c>
       <c r="R99" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R99" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q99,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q99))),1))</f>
@@ -9837,13 +9866,13 @@
         <v>12037</v>
       </c>
       <c r="B100" s="15" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C100" s="14">
         <v>2</v>
       </c>
       <c r="H100" s="16" t="s">
-        <v>1114</v>
+        <v>1081</v>
       </c>
       <c r="R100" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R100" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q100,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q100))),1))</f>
@@ -9862,7 +9891,7 @@
         <v>20304</v>
       </c>
       <c r="W100" s="14" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="Y100" s="14">
         <v>1</v>
@@ -9879,22 +9908,22 @@
         <v>12038</v>
       </c>
       <c r="B101" s="15" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C101" s="14">
         <v>2</v>
       </c>
       <c r="E101" s="16" t="s">
-        <v>1115</v>
+        <v>1082</v>
       </c>
       <c r="G101" s="16" t="s">
-        <v>1116</v>
+        <v>1083</v>
       </c>
       <c r="H101" s="16" t="s">
-        <v>1118</v>
+        <v>1085</v>
       </c>
       <c r="J101" s="16" t="s">
-        <v>1119</v>
+        <v>1086</v>
       </c>
       <c r="N101" s="16" t="s">
         <v>72</v>
@@ -9933,22 +9962,22 @@
         <v>12039</v>
       </c>
       <c r="B102" s="15" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C102" s="14">
         <v>2</v>
       </c>
       <c r="E102" s="16" t="s">
-        <v>1120</v>
+        <v>1087</v>
       </c>
       <c r="H102" s="16" t="s">
-        <v>1121</v>
+        <v>1088</v>
       </c>
       <c r="L102" s="16" t="s">
-        <v>1122</v>
+        <v>1089</v>
       </c>
       <c r="Q102" s="14" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="R102" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R102" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q102,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q102))),1))</f>
@@ -9984,19 +10013,19 @@
         <v>12040</v>
       </c>
       <c r="B103" s="15" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C103" s="14">
         <v>2</v>
       </c>
       <c r="H103" s="16" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="L103" s="16" t="s">
-        <v>1123</v>
+        <v>1090</v>
       </c>
       <c r="Q103" s="14" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="R103" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R103" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q103,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q103))),1))</f>
@@ -10032,19 +10061,19 @@
         <v>12041</v>
       </c>
       <c r="B104" s="15" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C104" s="14">
         <v>2</v>
       </c>
       <c r="E104" s="16" t="s">
-        <v>1124</v>
+        <v>1091</v>
       </c>
       <c r="H104" s="16" t="s">
-        <v>1125</v>
+        <v>1092</v>
       </c>
       <c r="L104" s="16" t="s">
-        <v>1087</v>
+        <v>1054</v>
       </c>
       <c r="R104" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R104" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q104,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q104))),1))</f>
@@ -10080,16 +10109,16 @@
         <v>12042</v>
       </c>
       <c r="B105" s="15" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C105" s="14">
         <v>2</v>
       </c>
       <c r="H105" s="16" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="L105" s="16" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="R105" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R105" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q105,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q105))),1))</f>
@@ -10125,19 +10154,19 @@
         <v>12043</v>
       </c>
       <c r="B106" s="15" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C106" s="14">
         <v>2</v>
       </c>
       <c r="E106" s="16" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="H106" s="16" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="J106" s="16" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="L106" s="16" t="s">
         <v>214</v>
@@ -10176,16 +10205,16 @@
         <v>12044</v>
       </c>
       <c r="B107" s="15" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C107" s="14">
         <v>2</v>
       </c>
       <c r="H107" s="16" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="Q107" s="14" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="R107" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R107" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q107,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q107))),1))</f>
@@ -10221,7 +10250,7 @@
         <v>12045</v>
       </c>
       <c r="B108" s="15" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C108" s="14">
         <v>2</v>
@@ -10230,13 +10259,13 @@
         <v>218</v>
       </c>
       <c r="J108" s="16" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="L108" s="16" t="s">
         <v>154</v>
       </c>
       <c r="Q108" s="14" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="R108" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R108" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q108,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q108))),1))</f>
@@ -10272,25 +10301,25 @@
         <v>12046</v>
       </c>
       <c r="B109" s="15" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C109" s="14">
         <v>2</v>
       </c>
       <c r="E109" s="16" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="H109" s="16" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="J109" s="16" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="N109" s="16" t="s">
         <v>72</v>
       </c>
       <c r="Q109" s="14" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="R109" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R109" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q109,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q109))),1))</f>
@@ -10326,13 +10355,13 @@
         <v>12047</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C110" s="14">
         <v>2</v>
       </c>
       <c r="H110" s="16" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="Q110" s="14" t="s">
         <v>246</v>
@@ -10374,7 +10403,7 @@
         <v>2</v>
       </c>
       <c r="E111" s="16" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="H111" s="16" t="s">
         <v>206</v>
@@ -10383,7 +10412,7 @@
         <v>203</v>
       </c>
       <c r="Q111" s="14" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="R111" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R111" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q111,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q111))),1))</f>
@@ -10419,7 +10448,7 @@
         <v>12049</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C112" s="14">
         <v>2</v>
@@ -10428,10 +10457,10 @@
         <v>210</v>
       </c>
       <c r="J112" s="16" t="s">
-        <v>351</v>
+        <v>1093</v>
       </c>
       <c r="Q112" s="14" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="R112" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R112" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q112,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q112))),1))</f>
@@ -10467,22 +10496,22 @@
         <v>12050</v>
       </c>
       <c r="B113" s="15" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="C113" s="14">
         <v>2</v>
       </c>
       <c r="E113" s="16" t="s">
-        <v>353</v>
+        <v>1094</v>
       </c>
       <c r="H113" s="16" t="s">
-        <v>354</v>
+        <v>1095</v>
       </c>
       <c r="N113" s="16" t="s">
         <v>72</v>
       </c>
       <c r="Q113" s="14" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="R113" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R113" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q113,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q113))),1))</f>
@@ -10518,16 +10547,16 @@
         <v>12051</v>
       </c>
       <c r="B114" s="15" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="C114" s="14">
         <v>2</v>
       </c>
       <c r="E114" s="16" t="s">
-        <v>357</v>
+        <v>1096</v>
       </c>
       <c r="H114" s="16" t="s">
-        <v>358</v>
+        <v>1097</v>
       </c>
       <c r="I114" s="14"/>
       <c r="J114" s="14"/>
@@ -10571,13 +10600,13 @@
         <v>12052</v>
       </c>
       <c r="B115" s="15" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="C115" s="14">
         <v>2</v>
       </c>
       <c r="H115" s="16" t="s">
-        <v>360</v>
+        <v>1098</v>
       </c>
       <c r="N115" s="16" t="s">
         <v>170</v>
@@ -10589,7 +10618,7 @@
         <v>4</v>
       </c>
       <c r="Q115" s="14" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="R115" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R115" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q115,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q115))),1))</f>
@@ -10608,7 +10637,7 @@
         <v>20307</v>
       </c>
       <c r="W115" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="Y115" s="14">
         <v>2</v>
@@ -10625,7 +10654,7 @@
         <v>12053</v>
       </c>
       <c r="B116" s="15" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="C116" s="14">
         <v>2</v>
@@ -10636,10 +10665,10 @@
       <c r="I116" s="14"/>
       <c r="J116" s="14"/>
       <c r="L116" s="16" t="s">
-        <v>1014</v>
+        <v>981</v>
       </c>
       <c r="N116" s="16" t="s">
-        <v>1021</v>
+        <v>988</v>
       </c>
       <c r="O116" s="14">
         <v>1</v>
@@ -10664,7 +10693,7 @@
         <v>20507</v>
       </c>
       <c r="W116" s="14" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="Y116" s="14">
         <v>1</v>
@@ -10681,18 +10710,18 @@
         <v>12054</v>
       </c>
       <c r="B117" s="15" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="C117" s="14">
         <v>2</v>
       </c>
       <c r="H117" s="16" t="s">
-        <v>366</v>
+        <v>1100</v>
       </c>
       <c r="I117" s="14"/>
       <c r="J117" s="14"/>
       <c r="L117" s="16" t="s">
-        <v>367</v>
+        <v>1099</v>
       </c>
       <c r="O117" s="14">
         <v>1</v>
@@ -10717,7 +10746,7 @@
         <v>20507</v>
       </c>
       <c r="W117" s="14" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="Y117" s="14">
         <v>2</v>
@@ -10737,12 +10766,12 @@
         <v>2</v>
       </c>
       <c r="H118" s="16" t="s">
-        <v>368</v>
+        <v>1101</v>
       </c>
       <c r="I118" s="14"/>
       <c r="J118" s="14"/>
       <c r="L118" s="16" t="s">
-        <v>369</v>
+        <v>1102</v>
       </c>
       <c r="O118" s="14">
         <v>6</v>
@@ -10751,7 +10780,7 @@
         <v>999</v>
       </c>
       <c r="Q118" s="14" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="R118" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R118" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q118,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q118))),1))</f>
@@ -10767,7 +10796,7 @@
         <v>20507</v>
       </c>
       <c r="W118" s="14" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="Y118" s="14">
         <v>1</v>
@@ -10787,10 +10816,10 @@
         <v>2</v>
       </c>
       <c r="H119" s="16" t="s">
-        <v>371</v>
+        <v>1103</v>
       </c>
       <c r="L119" s="16" t="s">
-        <v>372</v>
+        <v>1104</v>
       </c>
       <c r="N119" s="16" t="s">
         <v>170</v>
@@ -10802,7 +10831,7 @@
         <v>8</v>
       </c>
       <c r="Q119" s="14" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="R119" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R119" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q119,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q119))),1))</f>
@@ -10818,7 +10847,7 @@
         <v>20507</v>
       </c>
       <c r="W119" s="14" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="Y119" s="14">
         <v>1</v>
@@ -10835,21 +10864,21 @@
         <v>12057</v>
       </c>
       <c r="B120" s="15" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="C120" s="14">
         <v>2</v>
       </c>
       <c r="H120" s="14" t="s">
-        <v>375</v>
+        <v>1105</v>
       </c>
       <c r="I120" s="14"/>
       <c r="J120" s="14"/>
       <c r="L120" s="16" t="s">
-        <v>1011</v>
+        <v>978</v>
       </c>
       <c r="N120" s="16" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="P120" s="14">
         <v>999</v>
@@ -10882,16 +10911,16 @@
         <v>12058</v>
       </c>
       <c r="B121" s="15" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="C121" s="14">
         <v>2</v>
       </c>
       <c r="G121" s="16" t="s">
-        <v>378</v>
+        <v>1106</v>
       </c>
       <c r="H121" s="16" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="P121" s="14">
         <v>999</v>
@@ -10924,17 +10953,17 @@
         <v>12059</v>
       </c>
       <c r="B122" s="15" t="s">
-        <v>379</v>
+        <v>362</v>
       </c>
       <c r="C122" s="14">
         <v>2</v>
       </c>
       <c r="H122" s="16" t="s">
-        <v>380</v>
+        <v>1107</v>
       </c>
       <c r="I122" s="14"/>
       <c r="J122" s="14" t="s">
-        <v>381</v>
+        <v>1108</v>
       </c>
       <c r="P122" s="14">
         <v>999</v>
@@ -10967,21 +10996,21 @@
         <v>12060</v>
       </c>
       <c r="B123" s="15" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="C123" s="14">
         <v>2</v>
       </c>
       <c r="H123" s="16" t="s">
-        <v>383</v>
+        <v>1109</v>
       </c>
       <c r="I123" s="14"/>
       <c r="J123" s="14"/>
       <c r="N123" s="16" t="s">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="Q123" s="14" t="s">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="R123" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R123" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q123,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q123))),1))</f>
@@ -11023,13 +11052,13 @@
         <v>2</v>
       </c>
       <c r="H124" s="16" t="s">
+        <v>1062</v>
+      </c>
+      <c r="J124" s="16" t="s">
+        <v>1110</v>
+      </c>
+      <c r="Q124" s="14" t="s">
         <v>289</v>
-      </c>
-      <c r="J124" s="16" t="s">
-        <v>386</v>
-      </c>
-      <c r="Q124" s="14" t="s">
-        <v>290</v>
       </c>
       <c r="R124" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R124" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q124,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q124))),1))</f>
@@ -11065,14 +11094,14 @@
         <v>2</v>
       </c>
       <c r="G125" s="16" t="s">
-        <v>387</v>
+        <v>1111</v>
       </c>
       <c r="H125" s="16" t="s">
-        <v>291</v>
+        <v>1063</v>
       </c>
       <c r="I125" s="14"/>
       <c r="Q125" s="14" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="R125" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R125" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q125,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q125))),1))</f>
@@ -11102,23 +11131,23 @@
         <v>12063</v>
       </c>
       <c r="B126" s="15" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C126" s="14">
         <v>2</v>
       </c>
       <c r="G126" s="16" t="s">
-        <v>299</v>
+        <v>1070</v>
       </c>
       <c r="H126" s="16" t="s">
-        <v>300</v>
+        <v>1071</v>
       </c>
       <c r="I126" s="14"/>
       <c r="J126" s="16" t="s">
-        <v>301</v>
+        <v>1072</v>
       </c>
       <c r="Q126" s="14" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="R126" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R126" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q126,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q126))),1))</f>
@@ -11148,23 +11177,23 @@
         <v>12064</v>
       </c>
       <c r="B127" s="15" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C127" s="14">
         <v>2</v>
       </c>
       <c r="G127" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="H127" s="16" t="s">
         <v>299</v>
-      </c>
-      <c r="H127" s="16" t="s">
-        <v>303</v>
       </c>
       <c r="I127" s="14"/>
       <c r="J127" s="16" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="Q127" s="14" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="R127" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R127" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q127,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q127))),1))</f>
@@ -11194,27 +11223,27 @@
         <v>12065</v>
       </c>
       <c r="B128" s="15" t="s">
-        <v>388</v>
+        <v>366</v>
       </c>
       <c r="C128" s="14">
         <v>2</v>
       </c>
       <c r="H128" s="16" t="s">
-        <v>389</v>
+        <v>1112</v>
       </c>
       <c r="I128" s="14"/>
       <c r="J128" s="14"/>
       <c r="L128" s="16" t="s">
-        <v>390</v>
+        <v>1113</v>
       </c>
       <c r="N128" s="16" t="s">
-        <v>391</v>
+        <v>367</v>
       </c>
       <c r="O128" s="14">
         <v>3</v>
       </c>
       <c r="Q128" s="14" t="s">
-        <v>392</v>
+        <v>368</v>
       </c>
       <c r="R128" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R128" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q128,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q128))),1))</f>
@@ -11233,7 +11262,7 @@
         <v>20501</v>
       </c>
       <c r="W128" s="14" t="s">
-        <v>393</v>
+        <v>369</v>
       </c>
       <c r="Y128" s="14">
         <v>2</v>
@@ -11250,26 +11279,26 @@
         <v>12066</v>
       </c>
       <c r="B129" s="15" t="s">
-        <v>394</v>
+        <v>370</v>
       </c>
       <c r="C129" s="14">
         <v>2</v>
       </c>
       <c r="E129" s="16" t="s">
-        <v>222</v>
+        <v>1114</v>
       </c>
       <c r="H129" s="16" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="I129" s="14"/>
       <c r="J129" s="14" t="s">
-        <v>395</v>
+        <v>1115</v>
       </c>
       <c r="N129" s="16" t="s">
         <v>72</v>
       </c>
       <c r="Q129" s="14" t="s">
-        <v>396</v>
+        <v>371</v>
       </c>
       <c r="R129" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R129" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q129,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q129))),1))</f>
@@ -11288,7 +11317,7 @@
         <v>20405</v>
       </c>
       <c r="W129" s="14" t="s">
-        <v>397</v>
+        <v>372</v>
       </c>
       <c r="Y129" s="14">
         <v>1</v>
@@ -11305,27 +11334,27 @@
         <v>12067</v>
       </c>
       <c r="B130" s="15" t="s">
-        <v>398</v>
+        <v>373</v>
       </c>
       <c r="C130" s="14">
         <v>2</v>
       </c>
       <c r="E130" s="16" t="s">
-        <v>399</v>
+        <v>1116</v>
       </c>
       <c r="G130" s="16" t="s">
-        <v>400</v>
+        <v>1118</v>
       </c>
       <c r="H130" s="16" t="s">
-        <v>401</v>
+        <v>374</v>
       </c>
       <c r="I130" s="14"/>
       <c r="J130" s="14"/>
       <c r="L130" s="16" t="s">
-        <v>402</v>
+        <v>1117</v>
       </c>
       <c r="N130" s="16" t="s">
-        <v>403</v>
+        <v>375</v>
       </c>
       <c r="R130" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R130" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q130,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q130))),1))</f>
@@ -11344,7 +11373,7 @@
         <v>20503</v>
       </c>
       <c r="W130" s="14" t="s">
-        <v>404</v>
+        <v>376</v>
       </c>
       <c r="Y130" s="14">
         <v>1</v>
@@ -11361,16 +11390,16 @@
         <v>12068</v>
       </c>
       <c r="B131" s="15" t="s">
-        <v>405</v>
+        <v>377</v>
       </c>
       <c r="C131" s="14">
         <v>2</v>
       </c>
       <c r="G131" s="16" t="s">
-        <v>994</v>
+        <v>961</v>
       </c>
       <c r="H131" s="16" t="s">
-        <v>406</v>
+        <v>1119</v>
       </c>
       <c r="I131" s="14"/>
       <c r="J131" s="14"/>
@@ -11391,7 +11420,7 @@
         <v>20503</v>
       </c>
       <c r="W131" s="14" t="s">
-        <v>404</v>
+        <v>376</v>
       </c>
       <c r="Y131" s="14">
         <v>2</v>
@@ -11408,20 +11437,20 @@
         <v>12069</v>
       </c>
       <c r="B132" s="15" t="s">
-        <v>407</v>
+        <v>378</v>
       </c>
       <c r="C132" s="14">
         <v>2</v>
       </c>
       <c r="E132" s="16" t="s">
-        <v>408</v>
+        <v>1120</v>
       </c>
       <c r="H132" s="16" t="s">
         <v>210</v>
       </c>
       <c r="I132" s="14"/>
       <c r="J132" s="14" t="s">
-        <v>409</v>
+        <v>1121</v>
       </c>
       <c r="Q132" s="14" t="s">
         <v>266</v>
@@ -11443,7 +11472,7 @@
         <v>20503</v>
       </c>
       <c r="W132" s="14" t="s">
-        <v>404</v>
+        <v>376</v>
       </c>
       <c r="Y132" s="14">
         <v>2</v>
@@ -11460,13 +11489,13 @@
         <v>12070</v>
       </c>
       <c r="B133" s="20" t="s">
-        <v>410</v>
+        <v>380</v>
       </c>
       <c r="C133" s="14">
         <v>2</v>
       </c>
       <c r="E133" s="16" t="s">
-        <v>1023</v>
+        <v>990</v>
       </c>
       <c r="H133" s="16" t="s">
         <v>104</v>
@@ -11478,7 +11507,7 @@
         <v>0</v>
       </c>
       <c r="Q133" s="14" t="s">
-        <v>411</v>
+        <v>381</v>
       </c>
       <c r="R133" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R133" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q133,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q133))),1))</f>
@@ -11508,19 +11537,19 @@
         <v>12071</v>
       </c>
       <c r="B134" s="15" t="s">
-        <v>412</v>
+        <v>382</v>
       </c>
       <c r="C134" s="14">
         <v>2</v>
       </c>
       <c r="E134" s="16" t="s">
-        <v>413</v>
+        <v>1122</v>
       </c>
       <c r="H134" s="16" t="s">
-        <v>414</v>
+        <v>383</v>
       </c>
       <c r="N134" s="16" t="s">
-        <v>415</v>
+        <v>1123</v>
       </c>
       <c r="R134" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R134" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q134,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q134))),1))</f>
@@ -11539,7 +11568,7 @@
         <v>20409</v>
       </c>
       <c r="W134" s="14" t="s">
-        <v>416</v>
+        <v>384</v>
       </c>
       <c r="Y134" s="14">
         <v>1</v>
@@ -11556,13 +11585,13 @@
         <v>12072</v>
       </c>
       <c r="B135" s="15" t="s">
-        <v>417</v>
+        <v>385</v>
       </c>
       <c r="C135" s="14">
         <v>2</v>
       </c>
       <c r="H135" s="16" t="s">
-        <v>1016</v>
+        <v>983</v>
       </c>
       <c r="I135" s="14"/>
       <c r="J135" s="14"/>
@@ -11591,7 +11620,7 @@
         <v>2</v>
       </c>
       <c r="H136" s="14" t="s">
-        <v>418</v>
+        <v>1124</v>
       </c>
       <c r="I136" s="14"/>
       <c r="J136" s="14"/>
@@ -11617,20 +11646,20 @@
         <v>12074</v>
       </c>
       <c r="B137" s="15" t="s">
-        <v>419</v>
+        <v>386</v>
       </c>
       <c r="C137" s="14">
         <v>2</v>
       </c>
       <c r="H137" s="16" t="s">
-        <v>420</v>
+        <v>387</v>
       </c>
       <c r="I137" s="14"/>
       <c r="J137" s="14" t="s">
-        <v>421</v>
+        <v>388</v>
       </c>
       <c r="N137" s="16" t="s">
-        <v>422</v>
+        <v>389</v>
       </c>
       <c r="R137" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R137" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q137,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q137))),1))</f>
@@ -11654,20 +11683,20 @@
         <v>12075</v>
       </c>
       <c r="B138" s="15" t="s">
-        <v>423</v>
+        <v>390</v>
       </c>
       <c r="C138" s="14">
         <v>2</v>
       </c>
       <c r="H138" s="16" t="s">
-        <v>420</v>
+        <v>387</v>
       </c>
       <c r="I138" s="14"/>
       <c r="J138" s="14" t="s">
-        <v>424</v>
+        <v>391</v>
       </c>
       <c r="N138" s="16" t="s">
-        <v>422</v>
+        <v>389</v>
       </c>
       <c r="R138" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R138" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q138,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q138))),1))</f>
@@ -11694,15 +11723,15 @@
         <v>2</v>
       </c>
       <c r="H139" s="16" t="s">
-        <v>425</v>
+        <v>392</v>
       </c>
       <c r="I139" s="14"/>
       <c r="J139" s="14"/>
       <c r="L139" s="14" t="s">
-        <v>426</v>
+        <v>393</v>
       </c>
       <c r="Q139" s="14" t="s">
-        <v>427</v>
+        <v>394</v>
       </c>
       <c r="R139" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R139" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q139,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q139))),1))</f>
@@ -11741,18 +11770,18 @@
         <v>2</v>
       </c>
       <c r="E140" s="16" t="s">
-        <v>428</v>
+        <v>395</v>
       </c>
       <c r="H140" s="16" t="s">
-        <v>429</v>
+        <v>396</v>
       </c>
       <c r="I140" s="14"/>
       <c r="J140" s="14"/>
       <c r="L140" s="16" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="N140" s="16" t="s">
-        <v>430</v>
+        <v>397</v>
       </c>
       <c r="P140" s="14">
         <v>3</v>
@@ -11797,10 +11826,10 @@
         <v>2</v>
       </c>
       <c r="E141" s="16" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="H141" s="14" t="s">
-        <v>431</v>
+        <v>398</v>
       </c>
       <c r="I141" s="14"/>
       <c r="J141" s="14"/>
@@ -11811,7 +11840,7 @@
         <v>1</v>
       </c>
       <c r="Q141" s="14" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="R141" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R141" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q141,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q141))),1))</f>
@@ -11844,15 +11873,15 @@
     </row>
     <row r="142" spans="1:27" ht="33" x14ac:dyDescent="0.15">
       <c r="H142" s="16" t="s">
-        <v>432</v>
+        <v>399</v>
       </c>
       <c r="I142" s="14"/>
       <c r="J142" s="14"/>
       <c r="L142" s="16" t="s">
-        <v>433</v>
+        <v>400</v>
       </c>
       <c r="N142" s="16" t="s">
-        <v>434</v>
+        <v>401</v>
       </c>
       <c r="O142" s="14">
         <v>7</v>
@@ -11870,7 +11899,7 @@
         <v>20507</v>
       </c>
       <c r="W142" s="14" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="Y142" s="14">
         <v>7</v>
@@ -11892,18 +11921,18 @@
         <v>13001</v>
       </c>
       <c r="B144" s="20" t="s">
-        <v>435</v>
+        <v>402</v>
       </c>
       <c r="C144" s="14">
         <v>3</v>
       </c>
       <c r="H144" s="14" t="s">
-        <v>436</v>
+        <v>403</v>
       </c>
       <c r="I144" s="14"/>
       <c r="J144" s="14"/>
       <c r="L144" s="16" t="s">
-        <v>372</v>
+        <v>1104</v>
       </c>
       <c r="O144" s="14">
         <v>1</v>
@@ -11948,18 +11977,18 @@
         <v>13002</v>
       </c>
       <c r="B145" s="20" t="s">
-        <v>437</v>
+        <v>404</v>
       </c>
       <c r="C145" s="14">
         <v>3</v>
       </c>
       <c r="H145" s="14" t="s">
-        <v>438</v>
+        <v>405</v>
       </c>
       <c r="I145" s="14"/>
       <c r="J145" s="14"/>
       <c r="L145" s="16" t="s">
-        <v>439</v>
+        <v>406</v>
       </c>
       <c r="O145" s="14">
         <v>1</v>
@@ -12004,18 +12033,18 @@
         <v>13003</v>
       </c>
       <c r="B146" s="20" t="s">
-        <v>440</v>
+        <v>407</v>
       </c>
       <c r="C146" s="14">
         <v>3</v>
       </c>
       <c r="H146" s="14" t="s">
-        <v>441</v>
+        <v>408</v>
       </c>
       <c r="I146" s="14"/>
       <c r="J146" s="14"/>
       <c r="L146" s="16" t="s">
-        <v>442</v>
+        <v>409</v>
       </c>
       <c r="O146" s="14">
         <v>1</v>
@@ -12060,21 +12089,21 @@
         <v>13004</v>
       </c>
       <c r="B147" s="20" t="s">
-        <v>443</v>
+        <v>410</v>
       </c>
       <c r="C147" s="14">
         <v>3</v>
       </c>
       <c r="E147" s="16" t="s">
-        <v>444</v>
+        <v>411</v>
       </c>
       <c r="H147" s="14" t="s">
-        <v>436</v>
+        <v>403</v>
       </c>
       <c r="I147" s="14"/>
       <c r="J147" s="14"/>
       <c r="L147" s="16" t="s">
-        <v>445</v>
+        <v>412</v>
       </c>
       <c r="O147" s="14">
         <v>1</v>
@@ -12119,21 +12148,21 @@
         <v>13005</v>
       </c>
       <c r="B148" s="20" t="s">
-        <v>446</v>
+        <v>413</v>
       </c>
       <c r="C148" s="14">
         <v>3</v>
       </c>
       <c r="E148" s="16" t="s">
-        <v>447</v>
+        <v>414</v>
       </c>
       <c r="H148" s="14" t="s">
-        <v>448</v>
+        <v>415</v>
       </c>
       <c r="I148" s="14"/>
       <c r="J148" s="14"/>
       <c r="L148" s="16" t="s">
-        <v>449</v>
+        <v>416</v>
       </c>
       <c r="O148" s="14">
         <v>1</v>
@@ -12178,21 +12207,21 @@
         <v>13006</v>
       </c>
       <c r="B149" s="20" t="s">
-        <v>450</v>
+        <v>417</v>
       </c>
       <c r="C149" s="14">
         <v>3</v>
       </c>
       <c r="E149" s="16" t="s">
-        <v>451</v>
+        <v>418</v>
       </c>
       <c r="H149" s="14" t="s">
-        <v>452</v>
+        <v>419</v>
       </c>
       <c r="I149" s="14"/>
       <c r="J149" s="14"/>
       <c r="L149" s="16" t="s">
-        <v>453</v>
+        <v>420</v>
       </c>
       <c r="O149" s="14">
         <v>1</v>
@@ -12237,23 +12266,23 @@
         <v>13007</v>
       </c>
       <c r="B150" s="15" t="s">
-        <v>454</v>
+        <v>421</v>
       </c>
       <c r="C150" s="14">
         <v>3</v>
       </c>
       <c r="E150" s="14" t="s">
-        <v>455</v>
+        <v>422</v>
       </c>
       <c r="F150" s="14"/>
       <c r="G150" s="14"/>
       <c r="H150" s="14" t="s">
-        <v>448</v>
+        <v>415</v>
       </c>
       <c r="I150" s="14"/>
       <c r="J150" s="14"/>
       <c r="L150" s="16" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="O150" s="14">
         <v>5</v>
@@ -12298,19 +12327,19 @@
         <v>13008</v>
       </c>
       <c r="B151" s="20" t="s">
-        <v>456</v>
+        <v>423</v>
       </c>
       <c r="C151" s="14">
         <v>3</v>
       </c>
       <c r="E151" s="16" t="s">
-        <v>457</v>
+        <v>424</v>
       </c>
       <c r="G151" s="16" t="s">
-        <v>458</v>
+        <v>425</v>
       </c>
       <c r="H151" s="14" t="s">
-        <v>438</v>
+        <v>405</v>
       </c>
       <c r="I151" s="14"/>
       <c r="J151" s="14"/>
@@ -12324,7 +12353,7 @@
         <v>4</v>
       </c>
       <c r="Q151" s="14" t="s">
-        <v>459</v>
+        <v>426</v>
       </c>
       <c r="R151" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R151" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q151,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q151))),1))</f>
@@ -12360,18 +12389,18 @@
         <v>13009</v>
       </c>
       <c r="B152" s="20" t="s">
-        <v>460</v>
+        <v>427</v>
       </c>
       <c r="C152" s="14">
         <v>3</v>
       </c>
       <c r="H152" s="14" t="s">
-        <v>436</v>
+        <v>403</v>
       </c>
       <c r="I152" s="14"/>
       <c r="J152" s="14"/>
       <c r="L152" s="16" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="O152" s="14">
         <v>1</v>
@@ -12380,7 +12409,7 @@
         <v>4</v>
       </c>
       <c r="Q152" s="14" t="s">
-        <v>461</v>
+        <v>428</v>
       </c>
       <c r="R152" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R152" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q152,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q152))),1))</f>
@@ -12416,18 +12445,18 @@
         <v>13010</v>
       </c>
       <c r="B153" s="20" t="s">
-        <v>462</v>
+        <v>429</v>
       </c>
       <c r="C153" s="14">
         <v>3</v>
       </c>
       <c r="H153" s="14" t="s">
-        <v>436</v>
+        <v>403</v>
       </c>
       <c r="I153" s="14"/>
       <c r="J153" s="14"/>
       <c r="L153" s="16" t="s">
-        <v>463</v>
+        <v>430</v>
       </c>
       <c r="O153" s="14">
         <v>1</v>
@@ -12436,7 +12465,7 @@
         <v>5</v>
       </c>
       <c r="Q153" s="14" t="s">
-        <v>464</v>
+        <v>431</v>
       </c>
       <c r="R153" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R153" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q153,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q153))),1))</f>
@@ -12472,19 +12501,19 @@
         <v>13011</v>
       </c>
       <c r="B154" s="15" t="s">
-        <v>465</v>
+        <v>432</v>
       </c>
       <c r="C154" s="14">
         <v>3</v>
       </c>
       <c r="E154" s="16" t="s">
-        <v>995</v>
+        <v>962</v>
       </c>
       <c r="G154" s="16" t="s">
         <v>149</v>
       </c>
       <c r="H154" s="14" t="s">
-        <v>466</v>
+        <v>433</v>
       </c>
       <c r="I154" s="14"/>
       <c r="J154" s="14"/>
@@ -12495,7 +12524,7 @@
         <v>6</v>
       </c>
       <c r="Q154" s="14" t="s">
-        <v>467</v>
+        <v>434</v>
       </c>
       <c r="R154" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R154" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q154,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q154))),1))</f>
@@ -12531,16 +12560,16 @@
         <v>13012</v>
       </c>
       <c r="B155" s="15" t="s">
-        <v>468</v>
+        <v>435</v>
       </c>
       <c r="C155" s="14">
         <v>3</v>
       </c>
       <c r="H155" s="16" t="s">
-        <v>469</v>
+        <v>436</v>
       </c>
       <c r="L155" s="16" t="s">
-        <v>470</v>
+        <v>437</v>
       </c>
       <c r="O155" s="14">
         <v>1</v>
@@ -12582,18 +12611,18 @@
         <v>13013</v>
       </c>
       <c r="B156" s="20" t="s">
-        <v>471</v>
+        <v>438</v>
       </c>
       <c r="C156" s="14">
         <v>3</v>
       </c>
       <c r="E156" s="14" t="s">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="F156" s="14"/>
       <c r="G156" s="14"/>
       <c r="H156" s="16" t="s">
-        <v>473</v>
+        <v>440</v>
       </c>
       <c r="N156" s="16" t="s">
         <v>72</v>
@@ -12605,7 +12634,7 @@
         <v>6</v>
       </c>
       <c r="Q156" s="14" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="R156" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R156" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q156,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q156))),1))</f>
@@ -12641,18 +12670,18 @@
         <v>13014</v>
       </c>
       <c r="B157" s="20" t="s">
-        <v>475</v>
+        <v>442</v>
       </c>
       <c r="C157" s="14">
         <v>3</v>
       </c>
       <c r="E157" s="14" t="s">
-        <v>476</v>
+        <v>443</v>
       </c>
       <c r="F157" s="14"/>
       <c r="G157" s="14"/>
       <c r="H157" s="14" t="s">
-        <v>438</v>
+        <v>405</v>
       </c>
       <c r="I157" s="14"/>
       <c r="J157" s="14"/>
@@ -12693,13 +12722,13 @@
         <v>13015</v>
       </c>
       <c r="B158" s="20" t="s">
-        <v>477</v>
+        <v>444</v>
       </c>
       <c r="C158" s="14">
         <v>3</v>
       </c>
       <c r="H158" s="16" t="s">
-        <v>478</v>
+        <v>445</v>
       </c>
       <c r="P158" s="14">
         <v>14</v>
@@ -12721,7 +12750,7 @@
         <v>20504</v>
       </c>
       <c r="W158" s="14" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="Y158" s="14">
         <v>1</v>
@@ -12738,13 +12767,13 @@
         <v>13016</v>
       </c>
       <c r="B159" s="20" t="s">
-        <v>480</v>
+        <v>447</v>
       </c>
       <c r="C159" s="14">
         <v>3</v>
       </c>
       <c r="E159" s="16" t="s">
-        <v>1023</v>
+        <v>990</v>
       </c>
       <c r="H159" s="16" t="s">
         <v>104</v>
@@ -12756,7 +12785,7 @@
         <v>0</v>
       </c>
       <c r="Q159" s="14" t="s">
-        <v>481</v>
+        <v>448</v>
       </c>
       <c r="R159" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R159" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q159,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q159))),1))</f>
@@ -12786,13 +12815,13 @@
         <v>13017</v>
       </c>
       <c r="B160" s="20" t="s">
-        <v>482</v>
+        <v>449</v>
       </c>
       <c r="C160" s="14">
         <v>3</v>
       </c>
       <c r="H160" s="14" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="I160" s="14"/>
       <c r="J160" s="14"/>
@@ -12827,13 +12856,13 @@
         <v>13018</v>
       </c>
       <c r="B161" s="20" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="C161" s="14">
         <v>3</v>
       </c>
       <c r="H161" s="16" t="s">
-        <v>485</v>
+        <v>452</v>
       </c>
       <c r="L161" s="16" t="s">
         <v>165</v>
@@ -12855,7 +12884,7 @@
         <v>20402</v>
       </c>
       <c r="W161" s="14" t="s">
-        <v>486</v>
+        <v>453</v>
       </c>
       <c r="Y161" s="14">
         <v>1</v>
@@ -12872,13 +12901,13 @@
         <v>13019</v>
       </c>
       <c r="B162" s="15" t="s">
-        <v>487</v>
+        <v>454</v>
       </c>
       <c r="C162" s="14">
         <v>3</v>
       </c>
       <c r="H162" s="16" t="s">
-        <v>488</v>
+        <v>455</v>
       </c>
       <c r="O162" s="14">
         <v>5</v>
@@ -12894,7 +12923,7 @@
         <v>20402</v>
       </c>
       <c r="W162" s="14" t="s">
-        <v>489</v>
+        <v>456</v>
       </c>
       <c r="Y162" s="14">
         <v>1</v>
@@ -12911,16 +12940,16 @@
         <v>13020</v>
       </c>
       <c r="B163" s="15" t="s">
-        <v>490</v>
+        <v>457</v>
       </c>
       <c r="C163" s="14">
         <v>3</v>
       </c>
       <c r="H163" s="16" t="s">
-        <v>485</v>
+        <v>452</v>
       </c>
       <c r="J163" s="16" t="s">
-        <v>491</v>
+        <v>458</v>
       </c>
       <c r="R163" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R163" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q163,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q163))),1))</f>
@@ -12933,7 +12962,7 @@
         <v>20601</v>
       </c>
       <c r="W163" s="14" t="s">
-        <v>492</v>
+        <v>459</v>
       </c>
       <c r="Y163" s="14">
         <v>1</v>
@@ -12950,19 +12979,19 @@
         <v>13021</v>
       </c>
       <c r="B164" s="20" t="s">
-        <v>493</v>
+        <v>460</v>
       </c>
       <c r="C164" s="14">
         <v>3</v>
       </c>
       <c r="G164" s="16" t="s">
-        <v>1010</v>
+        <v>977</v>
       </c>
       <c r="H164" s="16" t="s">
-        <v>494</v>
+        <v>461</v>
       </c>
       <c r="N164" s="16" t="s">
-        <v>495</v>
+        <v>462</v>
       </c>
       <c r="R164" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R164" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q164,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q164))),1))</f>
@@ -12995,16 +13024,16 @@
         <v>13022</v>
       </c>
       <c r="B165" s="15" t="s">
-        <v>496</v>
+        <v>463</v>
       </c>
       <c r="C165" s="14">
         <v>3</v>
       </c>
       <c r="H165" s="16" t="s">
-        <v>497</v>
+        <v>464</v>
       </c>
       <c r="L165" s="16" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="Q165" s="14" t="s">
         <v>54</v>
@@ -13040,7 +13069,7 @@
         <v>13023</v>
       </c>
       <c r="B166" s="15" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="C166" s="14">
         <v>3</v>
@@ -13067,18 +13096,18 @@
         <v>13024</v>
       </c>
       <c r="B167" s="20" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="C167" s="14">
         <v>3</v>
       </c>
       <c r="H167" s="14" t="s">
-        <v>436</v>
+        <v>403</v>
       </c>
       <c r="I167" s="14"/>
       <c r="J167" s="14"/>
       <c r="L167" s="16" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="O167" s="14">
         <v>1</v>
@@ -13114,20 +13143,20 @@
         <v>13025</v>
       </c>
       <c r="B168" s="15" t="s">
-        <v>500</v>
+        <v>467</v>
       </c>
       <c r="C168" s="14">
         <v>3</v>
       </c>
       <c r="G168" s="14" t="s">
-        <v>1002</v>
+        <v>969</v>
       </c>
       <c r="H168" s="14" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="I168" s="14"/>
       <c r="L168" s="16" t="s">
-        <v>439</v>
+        <v>406</v>
       </c>
       <c r="R168" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R168" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q168,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q168))),1))</f>
@@ -13143,7 +13172,7 @@
         <v>20506</v>
       </c>
       <c r="W168" s="14" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="Y168" s="14">
         <v>1</v>
@@ -13160,13 +13189,13 @@
         <v>13026</v>
       </c>
       <c r="B169" s="15" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="C169" s="14">
         <v>3</v>
       </c>
       <c r="E169" s="16" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="R169" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R169" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q169,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q169))),1))</f>
@@ -13179,7 +13208,7 @@
         <v>20506</v>
       </c>
       <c r="W169" s="14" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="Y169" s="14">
         <v>1</v>
@@ -13196,22 +13225,22 @@
         <v>13027</v>
       </c>
       <c r="B170" s="20" t="s">
-        <v>505</v>
+        <v>472</v>
       </c>
       <c r="C170" s="14">
         <v>3</v>
       </c>
       <c r="H170" s="16" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="L170" s="16" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="N170" s="16" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="Q170" s="14" t="s">
-        <v>508</v>
+        <v>475</v>
       </c>
       <c r="R170" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R170" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q170,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q170))),1))</f>
@@ -13244,22 +13273,22 @@
         <v>13028</v>
       </c>
       <c r="B171" s="15" t="s">
-        <v>509</v>
+        <v>476</v>
       </c>
       <c r="C171" s="14">
         <v>3</v>
       </c>
       <c r="E171" s="16" t="s">
-        <v>476</v>
+        <v>443</v>
       </c>
       <c r="H171" s="16" t="s">
-        <v>510</v>
+        <v>477</v>
       </c>
       <c r="L171" s="16" t="s">
-        <v>511</v>
+        <v>478</v>
       </c>
       <c r="Q171" s="14" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="R171" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R171" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q171,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q171))),1))</f>
@@ -13292,24 +13321,24 @@
         <v>13029</v>
       </c>
       <c r="B172" s="20" t="s">
-        <v>512</v>
+        <v>479</v>
       </c>
       <c r="C172" s="14">
         <v>3</v>
       </c>
       <c r="H172" s="14" t="s">
-        <v>513</v>
+        <v>480</v>
       </c>
       <c r="I172" s="14"/>
       <c r="J172" s="14"/>
       <c r="L172" s="16" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="P172" s="14">
         <v>3</v>
       </c>
       <c r="Q172" s="14" t="s">
-        <v>514</v>
+        <v>481</v>
       </c>
       <c r="R172" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R172" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q172,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q172))),1))</f>
@@ -13342,22 +13371,22 @@
         <v>13030</v>
       </c>
       <c r="B173" s="20" t="s">
-        <v>515</v>
+        <v>482</v>
       </c>
       <c r="C173" s="14">
         <v>3</v>
       </c>
       <c r="H173" s="16" t="s">
-        <v>516</v>
+        <v>483</v>
       </c>
       <c r="L173" s="16" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="P173" s="14">
         <v>3</v>
       </c>
       <c r="Q173" s="14" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="R173" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R173" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q173,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q173))),1))</f>
@@ -13390,25 +13419,25 @@
         <v>13031</v>
       </c>
       <c r="B174" s="20" t="s">
-        <v>517</v>
+        <v>484</v>
       </c>
       <c r="C174" s="14">
         <v>3</v>
       </c>
       <c r="E174" s="16" t="s">
-        <v>518</v>
+        <v>485</v>
       </c>
       <c r="H174" s="16" t="s">
-        <v>441</v>
+        <v>408</v>
       </c>
       <c r="L174" s="16" t="s">
-        <v>519</v>
+        <v>486</v>
       </c>
       <c r="N174" s="16" t="s">
         <v>72</v>
       </c>
       <c r="Q174" s="14" t="s">
-        <v>520</v>
+        <v>487</v>
       </c>
       <c r="R174" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R174" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q174,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q174))),1))</f>
@@ -13441,16 +13470,16 @@
         <v>13032</v>
       </c>
       <c r="B175" s="20" t="s">
-        <v>521</v>
+        <v>488</v>
       </c>
       <c r="C175" s="14">
         <v>3</v>
       </c>
       <c r="E175" s="16" t="s">
-        <v>476</v>
+        <v>443</v>
       </c>
       <c r="H175" s="14" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="I175" s="14"/>
       <c r="J175" s="14"/>
@@ -13491,19 +13520,19 @@
         <v>13033</v>
       </c>
       <c r="B176" s="20" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="C176" s="14">
         <v>3</v>
       </c>
       <c r="H176" s="16" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="L176" s="16" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="Q176" s="14" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="R176" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R176" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q176,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q176))),1))</f>
@@ -13539,10 +13568,10 @@
         <v>3</v>
       </c>
       <c r="H177" s="16" t="s">
-        <v>525</v>
+        <v>492</v>
       </c>
       <c r="L177" s="16" t="s">
-        <v>526</v>
+        <v>493</v>
       </c>
       <c r="Q177" s="14" t="s">
         <v>251</v>
@@ -13578,13 +13607,13 @@
         <v>3</v>
       </c>
       <c r="E178" s="16" t="s">
-        <v>527</v>
+        <v>494</v>
       </c>
       <c r="H178" s="14" t="s">
-        <v>452</v>
+        <v>419</v>
       </c>
       <c r="J178" s="16" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
       <c r="R178" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R178" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q178,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q178))),1))</f>
@@ -13614,16 +13643,16 @@
         <v>13036</v>
       </c>
       <c r="B179" s="15" t="s">
-        <v>529</v>
+        <v>496</v>
       </c>
       <c r="C179" s="14">
         <v>3</v>
       </c>
       <c r="H179" s="14" t="s">
-        <v>530</v>
+        <v>497</v>
       </c>
       <c r="Q179" s="14" t="s">
-        <v>531</v>
+        <v>498</v>
       </c>
       <c r="R179" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R179" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q179,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q179))),1))</f>
@@ -13659,10 +13688,10 @@
         <v>3</v>
       </c>
       <c r="E180" s="16" t="s">
-        <v>532</v>
+        <v>499</v>
       </c>
       <c r="H180" s="14" t="s">
-        <v>533</v>
+        <v>500</v>
       </c>
       <c r="R180" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R180" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q180,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q180))),1))</f>
@@ -13692,22 +13721,22 @@
         <v>13038</v>
       </c>
       <c r="B181" s="15" t="s">
-        <v>534</v>
+        <v>501</v>
       </c>
       <c r="C181" s="14">
         <v>3</v>
       </c>
       <c r="H181" s="14" t="s">
-        <v>535</v>
+        <v>502</v>
       </c>
       <c r="J181" s="16" t="s">
-        <v>536</v>
+        <v>503</v>
       </c>
       <c r="P181" s="14">
         <v>999</v>
       </c>
       <c r="Q181" s="14" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="R181" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R181" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q181,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q181))),1))</f>
@@ -13740,19 +13769,19 @@
         <v>13039</v>
       </c>
       <c r="B182" s="15" t="s">
-        <v>538</v>
+        <v>505</v>
       </c>
       <c r="C182" s="14">
         <v>3</v>
       </c>
       <c r="G182" s="16" t="s">
-        <v>991</v>
+        <v>958</v>
       </c>
       <c r="H182" s="14" t="s">
-        <v>539</v>
+        <v>506</v>
       </c>
       <c r="N182" s="16" t="s">
-        <v>540</v>
+        <v>507</v>
       </c>
       <c r="R182" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R182" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q182,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q182))),1))</f>
@@ -13785,22 +13814,22 @@
         <v>13040</v>
       </c>
       <c r="B183" s="15" t="s">
-        <v>541</v>
+        <v>508</v>
       </c>
       <c r="C183" s="14">
         <v>3</v>
       </c>
       <c r="G183" s="16" t="s">
-        <v>1003</v>
+        <v>970</v>
       </c>
       <c r="H183" s="14" t="s">
-        <v>448</v>
+        <v>415</v>
       </c>
       <c r="L183" s="16" t="s">
-        <v>542</v>
+        <v>509</v>
       </c>
       <c r="N183" s="16" t="s">
-        <v>543</v>
+        <v>510</v>
       </c>
       <c r="R183" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R183" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q183,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q183))),1))</f>
@@ -13813,7 +13842,7 @@
         <v>20504</v>
       </c>
       <c r="W183" s="14" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="Y183" s="14">
         <v>1</v>
@@ -13830,25 +13859,25 @@
         <v>13041</v>
       </c>
       <c r="B184" s="15" t="s">
-        <v>544</v>
+        <v>511</v>
       </c>
       <c r="C184" s="14">
         <v>3</v>
       </c>
       <c r="H184" s="14" t="s">
-        <v>545</v>
+        <v>512</v>
       </c>
       <c r="L184" s="16" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="N184" s="16" t="s">
-        <v>546</v>
+        <v>513</v>
       </c>
       <c r="P184" s="14">
         <v>7</v>
       </c>
       <c r="Q184" s="14" t="s">
-        <v>547</v>
+        <v>514</v>
       </c>
       <c r="R184" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R184" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q184,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q184))),1))</f>
@@ -13881,22 +13910,22 @@
         <v>13042</v>
       </c>
       <c r="B185" s="15" t="s">
-        <v>548</v>
+        <v>515</v>
       </c>
       <c r="C185" s="14">
         <v>3</v>
       </c>
       <c r="H185" s="14" t="s">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="N185" s="16" t="s">
-        <v>550</v>
+        <v>517</v>
       </c>
       <c r="P185" s="14">
         <v>7</v>
       </c>
       <c r="Q185" s="14" t="s">
-        <v>551</v>
+        <v>518</v>
       </c>
       <c r="R185" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R185" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q185,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q185))),1))</f>
@@ -13929,22 +13958,22 @@
         <v>13043</v>
       </c>
       <c r="B186" s="15" t="s">
-        <v>534</v>
+        <v>501</v>
       </c>
       <c r="C186" s="14">
         <v>3</v>
       </c>
       <c r="H186" s="14" t="s">
-        <v>552</v>
+        <v>519</v>
       </c>
       <c r="J186" s="16" t="s">
-        <v>1004</v>
+        <v>971</v>
       </c>
       <c r="P186" s="14">
         <v>999</v>
       </c>
       <c r="Q186" s="14" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="R186" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R186" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q186,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q186))),1))</f>
@@ -13977,22 +14006,22 @@
         <v>13044</v>
       </c>
       <c r="B187" s="15" t="s">
-        <v>553</v>
+        <v>520</v>
       </c>
       <c r="C187" s="14">
         <v>3</v>
       </c>
       <c r="H187" s="14" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="J187" s="16" t="s">
-        <v>554</v>
+        <v>521</v>
       </c>
       <c r="P187" s="14">
         <v>999</v>
       </c>
       <c r="Q187" s="14" t="s">
-        <v>555</v>
+        <v>522</v>
       </c>
       <c r="R187" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R187" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q187,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q187))),1))</f>
@@ -14025,22 +14054,22 @@
         <v>13045</v>
       </c>
       <c r="B188" s="15" t="s">
-        <v>553</v>
+        <v>520</v>
       </c>
       <c r="C188" s="14">
         <v>3</v>
       </c>
       <c r="H188" s="14" t="s">
-        <v>494</v>
+        <v>461</v>
       </c>
       <c r="J188" s="16" t="s">
-        <v>554</v>
+        <v>521</v>
       </c>
       <c r="P188" s="14">
         <v>999</v>
       </c>
       <c r="Q188" s="14" t="s">
-        <v>555</v>
+        <v>522</v>
       </c>
       <c r="R188" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R188" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q188,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q188))),1))</f>
@@ -14073,22 +14102,22 @@
         <v>13046</v>
       </c>
       <c r="B189" s="20" t="s">
-        <v>556</v>
+        <v>523</v>
       </c>
       <c r="C189" s="14">
         <v>3</v>
       </c>
       <c r="G189" s="16" t="s">
-        <v>996</v>
+        <v>963</v>
       </c>
       <c r="H189" s="14" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="L189" s="16" t="s">
-        <v>557</v>
+        <v>524</v>
       </c>
       <c r="N189" s="16" t="s">
-        <v>558</v>
+        <v>525</v>
       </c>
       <c r="O189" s="14">
         <v>2</v>
@@ -14124,19 +14153,19 @@
         <v>13047</v>
       </c>
       <c r="B190" s="15" t="s">
-        <v>559</v>
+        <v>526</v>
       </c>
       <c r="C190" s="14">
         <v>3</v>
       </c>
       <c r="H190" s="14" t="s">
-        <v>533</v>
+        <v>500</v>
       </c>
       <c r="J190" s="16" t="s">
-        <v>560</v>
+        <v>527</v>
       </c>
       <c r="Q190" s="14" t="s">
-        <v>561</v>
+        <v>528</v>
       </c>
       <c r="R190" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R190" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q190,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q190))),1))</f>
@@ -14169,25 +14198,25 @@
         <v>13048</v>
       </c>
       <c r="B191" s="15" t="s">
-        <v>562</v>
+        <v>529</v>
       </c>
       <c r="C191" s="14">
         <v>3</v>
       </c>
       <c r="E191" s="16" t="s">
-        <v>451</v>
+        <v>418</v>
       </c>
       <c r="H191" s="16" t="s">
-        <v>1005</v>
+        <v>972</v>
       </c>
       <c r="L191" s="16" t="s">
-        <v>563</v>
+        <v>530</v>
       </c>
       <c r="N191" s="16" t="s">
         <v>72</v>
       </c>
       <c r="Q191" s="14" t="s">
-        <v>564</v>
+        <v>531</v>
       </c>
       <c r="R191" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R191" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q191,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q191))),1))</f>
@@ -14220,16 +14249,16 @@
         <v>13049</v>
       </c>
       <c r="B192" s="15" t="s">
-        <v>565</v>
+        <v>532</v>
       </c>
       <c r="C192" s="14">
         <v>3</v>
       </c>
       <c r="H192" s="16" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="L192" s="16" t="s">
-        <v>566</v>
+        <v>533</v>
       </c>
       <c r="O192" s="14">
         <v>2</v>
@@ -14238,7 +14267,7 @@
         <v>12</v>
       </c>
       <c r="Q192" s="14" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="R192" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R192" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q192,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q192))),1))</f>
@@ -14271,16 +14300,16 @@
         <v>13050</v>
       </c>
       <c r="B193" s="15" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="C193" s="14">
         <v>3</v>
       </c>
       <c r="H193" s="16" t="s">
-        <v>438</v>
+        <v>405</v>
       </c>
       <c r="L193" s="16" t="s">
-        <v>566</v>
+        <v>533</v>
       </c>
       <c r="O193" s="14">
         <v>2</v>
@@ -14289,7 +14318,7 @@
         <v>6</v>
       </c>
       <c r="Q193" s="14" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="R193" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R193" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q193,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q193))),1))</f>
@@ -14322,16 +14351,16 @@
         <v>13051</v>
       </c>
       <c r="B194" s="15" t="s">
-        <v>568</v>
+        <v>535</v>
       </c>
       <c r="C194" s="14">
         <v>3</v>
       </c>
       <c r="H194" s="16" t="s">
-        <v>569</v>
+        <v>536</v>
       </c>
       <c r="L194" s="16" t="s">
-        <v>570</v>
+        <v>537</v>
       </c>
       <c r="R194" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R194" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q194,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q194))),1))</f>
@@ -14361,19 +14390,19 @@
         <v>13052</v>
       </c>
       <c r="B195" s="15" t="s">
-        <v>571</v>
+        <v>538</v>
       </c>
       <c r="C195" s="14">
         <v>3</v>
       </c>
       <c r="E195" s="16" t="s">
-        <v>572</v>
+        <v>539</v>
       </c>
       <c r="H195" s="16" t="s">
-        <v>573</v>
+        <v>540</v>
       </c>
       <c r="L195" s="24" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="Q195" s="1" t="s">
         <v>54</v>
@@ -14412,19 +14441,19 @@
         <v>13053</v>
       </c>
       <c r="B196" s="15" t="s">
-        <v>574</v>
+        <v>541</v>
       </c>
       <c r="C196" s="14">
         <v>3</v>
       </c>
       <c r="H196" s="16" t="s">
-        <v>575</v>
+        <v>542</v>
       </c>
       <c r="L196" s="16" t="s">
-        <v>576</v>
+        <v>543</v>
       </c>
       <c r="Q196" s="14" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="R196" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R196" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q196,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q196))),1))</f>
@@ -14460,19 +14489,19 @@
         <v>13054</v>
       </c>
       <c r="B197" s="15" t="s">
-        <v>577</v>
+        <v>544</v>
       </c>
       <c r="C197" s="14">
         <v>3</v>
       </c>
       <c r="H197" s="16" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="L197" s="16" t="s">
-        <v>578</v>
+        <v>545</v>
       </c>
       <c r="Q197" s="14" t="s">
-        <v>531</v>
+        <v>498</v>
       </c>
       <c r="R197" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R197" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q197,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q197))),1))</f>
@@ -14508,22 +14537,22 @@
         <v>13055</v>
       </c>
       <c r="B198" s="15" t="s">
-        <v>579</v>
+        <v>546</v>
       </c>
       <c r="C198" s="14">
         <v>3</v>
       </c>
       <c r="E198" s="16" t="s">
-        <v>580</v>
+        <v>547</v>
       </c>
       <c r="H198" s="16" t="s">
-        <v>581</v>
+        <v>548</v>
       </c>
       <c r="L198" s="16" t="s">
-        <v>582</v>
+        <v>549</v>
       </c>
       <c r="Q198" s="14" t="s">
-        <v>555</v>
+        <v>522</v>
       </c>
       <c r="R198" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R198" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q198,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q198))),1))</f>
@@ -14559,19 +14588,19 @@
         <v>13056</v>
       </c>
       <c r="B199" s="15" t="s">
-        <v>583</v>
+        <v>550</v>
       </c>
       <c r="C199" s="14">
         <v>3</v>
       </c>
       <c r="G199" s="16" t="s">
-        <v>584</v>
+        <v>551</v>
       </c>
       <c r="H199" s="16" t="s">
-        <v>585</v>
+        <v>552</v>
       </c>
       <c r="Q199" s="14" t="s">
-        <v>586</v>
+        <v>553</v>
       </c>
       <c r="R199" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R199" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q199,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q199))),1))</f>
@@ -14607,16 +14636,16 @@
         <v>13057</v>
       </c>
       <c r="B200" s="15" t="s">
-        <v>587</v>
+        <v>554</v>
       </c>
       <c r="C200" s="14">
         <v>3</v>
       </c>
       <c r="E200" s="16" t="s">
-        <v>588</v>
+        <v>555</v>
       </c>
       <c r="H200" s="16" t="s">
-        <v>589</v>
+        <v>556</v>
       </c>
       <c r="R200" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R200" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q200,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q200))),1))</f>
@@ -14646,16 +14675,16 @@
         <v>13058</v>
       </c>
       <c r="B201" s="15" t="s">
-        <v>590</v>
+        <v>557</v>
       </c>
       <c r="C201" s="14">
         <v>3</v>
       </c>
       <c r="H201" s="16" t="s">
-        <v>591</v>
+        <v>558</v>
       </c>
       <c r="L201" s="16" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="O201" s="16">
         <v>800065</v>
@@ -14664,7 +14693,7 @@
         <v>12</v>
       </c>
       <c r="Q201" s="14" t="s">
-        <v>592</v>
+        <v>559</v>
       </c>
       <c r="R201" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R201" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q201,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q201))),1))</f>
@@ -14700,19 +14729,19 @@
         <v>13059</v>
       </c>
       <c r="B202" s="15" t="s">
-        <v>593</v>
+        <v>560</v>
       </c>
       <c r="C202" s="14">
         <v>3</v>
       </c>
       <c r="E202" s="16" t="s">
-        <v>594</v>
+        <v>561</v>
       </c>
       <c r="H202" s="16" t="s">
-        <v>595</v>
+        <v>562</v>
       </c>
       <c r="J202" s="16" t="s">
-        <v>596</v>
+        <v>563</v>
       </c>
       <c r="N202" s="16" t="s">
         <v>72</v>
@@ -14757,19 +14786,19 @@
         <v>13060</v>
       </c>
       <c r="B203" s="15" t="s">
-        <v>597</v>
+        <v>564</v>
       </c>
       <c r="C203" s="14">
         <v>3</v>
       </c>
       <c r="E203" s="16" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="H203" s="16" t="s">
-        <v>598</v>
+        <v>565</v>
       </c>
       <c r="L203" s="16" t="s">
-        <v>599</v>
+        <v>566</v>
       </c>
       <c r="O203" s="16">
         <v>800067</v>
@@ -14808,22 +14837,22 @@
         <v>13061</v>
       </c>
       <c r="B204" s="15" t="s">
-        <v>600</v>
+        <v>567</v>
       </c>
       <c r="C204" s="14">
         <v>3</v>
       </c>
       <c r="E204" s="16" t="s">
-        <v>601</v>
+        <v>568</v>
       </c>
       <c r="H204" s="16" t="s">
-        <v>1006</v>
+        <v>973</v>
       </c>
       <c r="N204" s="16" t="s">
         <v>72</v>
       </c>
       <c r="Q204" s="14" t="s">
-        <v>602</v>
+        <v>569</v>
       </c>
       <c r="R204" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R204" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q204,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q204))),1))</f>
@@ -14856,16 +14885,16 @@
         <v>13062</v>
       </c>
       <c r="B205" s="15" t="s">
-        <v>603</v>
+        <v>570</v>
       </c>
       <c r="C205" s="14">
         <v>3</v>
       </c>
       <c r="H205" s="16" t="s">
-        <v>604</v>
+        <v>571</v>
       </c>
       <c r="Q205" s="14" t="s">
-        <v>605</v>
+        <v>572</v>
       </c>
       <c r="R205" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R205" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q205,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q205))),1))</f>
@@ -14898,19 +14927,19 @@
         <v>13063</v>
       </c>
       <c r="B206" s="15" t="s">
-        <v>606</v>
+        <v>573</v>
       </c>
       <c r="C206" s="14">
         <v>3</v>
       </c>
       <c r="H206" s="16" t="s">
-        <v>607</v>
+        <v>574</v>
       </c>
       <c r="P206" s="14">
         <v>9</v>
       </c>
       <c r="Q206" s="14" t="s">
-        <v>608</v>
+        <v>575</v>
       </c>
       <c r="R206" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R206" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q206,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q206))),1))</f>
@@ -14943,22 +14972,22 @@
         <v>13064</v>
       </c>
       <c r="B207" s="15" t="s">
-        <v>609</v>
+        <v>576</v>
       </c>
       <c r="C207" s="14">
         <v>3</v>
       </c>
       <c r="E207" s="16" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="H207" s="16" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="J207" s="16" t="s">
-        <v>610</v>
+        <v>577</v>
       </c>
       <c r="N207" s="16" t="s">
-        <v>1018</v>
+        <v>985</v>
       </c>
       <c r="Q207" s="14" t="s">
         <v>152</v>
@@ -14994,25 +15023,25 @@
         <v>13065</v>
       </c>
       <c r="B208" s="15" t="s">
-        <v>611</v>
+        <v>578</v>
       </c>
       <c r="C208" s="14">
         <v>3</v>
       </c>
       <c r="H208" s="16" t="s">
-        <v>612</v>
+        <v>579</v>
       </c>
       <c r="J208" s="16" t="s">
-        <v>613</v>
+        <v>580</v>
       </c>
       <c r="N208" s="16" t="s">
-        <v>614</v>
+        <v>581</v>
       </c>
       <c r="O208" s="14">
         <v>1</v>
       </c>
       <c r="Q208" s="14" t="s">
-        <v>615</v>
+        <v>582</v>
       </c>
       <c r="R208" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R208" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q208,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q208))),1))</f>
@@ -15045,22 +15074,22 @@
         <v>13066</v>
       </c>
       <c r="B209" s="23" t="s">
-        <v>616</v>
+        <v>583</v>
       </c>
       <c r="C209" s="14">
         <v>3</v>
       </c>
       <c r="G209" s="16" t="s">
-        <v>617</v>
+        <v>584</v>
       </c>
       <c r="H209" s="16" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="J209" s="16" t="s">
-        <v>618</v>
+        <v>585</v>
       </c>
       <c r="N209" s="16" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="O209" s="14">
         <v>1</v>
@@ -15099,7 +15128,7 @@
         <v>13067</v>
       </c>
       <c r="B210" s="15" t="s">
-        <v>619</v>
+        <v>586</v>
       </c>
       <c r="C210" s="14">
         <v>3</v>
@@ -15108,18 +15137,18 @@
       <c r="F210" s="14"/>
       <c r="G210" s="14"/>
       <c r="H210" s="14" t="s">
-        <v>448</v>
+        <v>415</v>
       </c>
       <c r="I210" s="14"/>
       <c r="J210" s="14"/>
       <c r="K210" s="14"/>
       <c r="L210" s="14" t="s">
-        <v>620</v>
+        <v>587</v>
       </c>
       <c r="M210" s="14"/>
       <c r="N210" s="14"/>
       <c r="Q210" s="14" t="s">
-        <v>621</v>
+        <v>588</v>
       </c>
       <c r="R210" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R210" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q210,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q210))),1))</f>
@@ -15152,17 +15181,17 @@
         <v>13068</v>
       </c>
       <c r="B211" s="15" t="s">
-        <v>622</v>
+        <v>589</v>
       </c>
       <c r="C211" s="14">
         <v>3</v>
       </c>
       <c r="E211" s="14" t="s">
-        <v>623</v>
+        <v>590</v>
       </c>
       <c r="F211" s="14"/>
       <c r="H211" s="14" t="s">
-        <v>624</v>
+        <v>591</v>
       </c>
       <c r="I211" s="14"/>
       <c r="J211" s="14"/>
@@ -15204,7 +15233,7 @@
         <v>13069</v>
       </c>
       <c r="B212" s="15" t="s">
-        <v>625</v>
+        <v>592</v>
       </c>
       <c r="C212" s="14">
         <v>3</v>
@@ -15213,18 +15242,18 @@
       <c r="F212" s="14"/>
       <c r="G212" s="14"/>
       <c r="H212" s="14" t="s">
-        <v>626</v>
+        <v>593</v>
       </c>
       <c r="I212" s="14"/>
       <c r="J212" s="14" t="s">
-        <v>627</v>
+        <v>594</v>
       </c>
       <c r="K212" s="14"/>
       <c r="L212" s="14"/>
       <c r="M212" s="14"/>
       <c r="N212" s="14"/>
       <c r="Q212" s="14" t="s">
-        <v>628</v>
+        <v>595</v>
       </c>
       <c r="R212" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R212" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q212,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q212))),1))</f>
@@ -15257,7 +15286,7 @@
         <v>13070</v>
       </c>
       <c r="B213" s="15" t="s">
-        <v>629</v>
+        <v>596</v>
       </c>
       <c r="C213" s="14">
         <v>3</v>
@@ -15266,15 +15295,15 @@
       <c r="F213" s="14"/>
       <c r="G213" s="14"/>
       <c r="H213" s="14" t="s">
-        <v>436</v>
+        <v>403</v>
       </c>
       <c r="I213" s="14"/>
       <c r="J213" s="14" t="s">
-        <v>630</v>
+        <v>597</v>
       </c>
       <c r="K213" s="14"/>
       <c r="L213" s="14" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="M213" s="14"/>
       <c r="N213" s="14"/>
@@ -15282,7 +15311,7 @@
         <v>2</v>
       </c>
       <c r="Q213" s="14" t="s">
-        <v>631</v>
+        <v>598</v>
       </c>
       <c r="R213" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R213" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q213,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q213))),1))</f>
@@ -15315,16 +15344,16 @@
         <v>13071</v>
       </c>
       <c r="B214" s="15" t="s">
-        <v>632</v>
+        <v>599</v>
       </c>
       <c r="C214" s="14">
         <v>3</v>
       </c>
       <c r="E214" s="16" t="s">
-        <v>633</v>
+        <v>600</v>
       </c>
       <c r="G214" s="16" t="s">
-        <v>634</v>
+        <v>601</v>
       </c>
       <c r="R214" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R214" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q214,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q214))),1))</f>
@@ -15337,7 +15366,7 @@
         <v>20402</v>
       </c>
       <c r="W214" s="14" t="s">
-        <v>635</v>
+        <v>602</v>
       </c>
       <c r="Y214" s="14">
         <v>1</v>
@@ -15354,16 +15383,16 @@
         <v>13072</v>
       </c>
       <c r="B215" s="15" t="s">
-        <v>636</v>
+        <v>603</v>
       </c>
       <c r="C215" s="14">
         <v>3</v>
       </c>
       <c r="E215" s="16" t="s">
-        <v>637</v>
+        <v>604</v>
       </c>
       <c r="H215" s="16" t="s">
-        <v>638</v>
+        <v>605</v>
       </c>
       <c r="O215" s="14">
         <v>7</v>
@@ -15402,16 +15431,16 @@
         <v>3</v>
       </c>
       <c r="G216" s="16" t="s">
-        <v>639</v>
+        <v>606</v>
       </c>
       <c r="H216" s="16" t="s">
-        <v>441</v>
+        <v>408</v>
       </c>
       <c r="L216" s="16" t="s">
-        <v>439</v>
+        <v>406</v>
       </c>
       <c r="N216" s="16" t="s">
-        <v>640</v>
+        <v>607</v>
       </c>
       <c r="O216" s="14">
         <v>1</v>
@@ -15436,7 +15465,7 @@
         <v>20507</v>
       </c>
       <c r="W216" s="14" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="Y216" s="14">
         <v>1</v>
@@ -15456,13 +15485,13 @@
         <v>3</v>
       </c>
       <c r="E217" s="16" t="s">
-        <v>444</v>
+        <v>411</v>
       </c>
       <c r="H217" s="16" t="s">
-        <v>438</v>
+        <v>405</v>
       </c>
       <c r="L217" s="16" t="s">
-        <v>1012</v>
+        <v>979</v>
       </c>
       <c r="N217" s="16" t="s">
         <v>72</v>
@@ -15474,7 +15503,7 @@
         <v>6</v>
       </c>
       <c r="Q217" s="14" t="s">
-        <v>641</v>
+        <v>608</v>
       </c>
       <c r="R217" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R217" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q217,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q217))),1))</f>
@@ -15490,7 +15519,7 @@
         <v>20507</v>
       </c>
       <c r="W217" s="14" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="Y217" s="14">
         <v>1</v>
@@ -15507,19 +15536,19 @@
         <v>13075</v>
       </c>
       <c r="B218" s="15" t="s">
-        <v>642</v>
+        <v>609</v>
       </c>
       <c r="C218" s="14">
         <v>3</v>
       </c>
       <c r="G218" s="16" t="s">
-        <v>643</v>
+        <v>610</v>
       </c>
       <c r="H218" s="16" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="L218" s="16" t="s">
-        <v>644</v>
+        <v>611</v>
       </c>
       <c r="O218" s="14">
         <v>1</v>
@@ -15528,7 +15557,7 @@
         <v>3</v>
       </c>
       <c r="Q218" s="14" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="R218" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R218" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q218,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q218))),1))</f>
@@ -15544,7 +15573,7 @@
         <v>20507</v>
       </c>
       <c r="W218" s="14" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="Y218" s="14">
         <v>1</v>
@@ -15564,10 +15593,10 @@
         <v>3</v>
       </c>
       <c r="H219" s="16" t="s">
-        <v>1015</v>
+        <v>982</v>
       </c>
       <c r="L219" s="16" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="O219" s="14">
         <v>1</v>
@@ -15592,7 +15621,7 @@
         <v>20507</v>
       </c>
       <c r="W219" s="14" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="Y219" s="14">
         <v>1</v>
@@ -15612,7 +15641,7 @@
         <v>3</v>
       </c>
       <c r="H220" s="16" t="s">
-        <v>645</v>
+        <v>612</v>
       </c>
       <c r="O220" s="14">
         <v>4</v>
@@ -15621,7 +15650,7 @@
         <v>999</v>
       </c>
       <c r="Q220" s="14" t="s">
-        <v>646</v>
+        <v>613</v>
       </c>
       <c r="R220" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R220" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q220,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q220))),1))</f>
@@ -15637,7 +15666,7 @@
         <v>20507</v>
       </c>
       <c r="W220" s="14" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="Y220" s="14">
         <v>1</v>
@@ -15657,7 +15686,7 @@
         <v>3</v>
       </c>
       <c r="H221" s="16" t="s">
-        <v>647</v>
+        <v>614</v>
       </c>
       <c r="O221" s="14">
         <v>5</v>
@@ -15666,7 +15695,7 @@
         <v>999</v>
       </c>
       <c r="Q221" s="14" t="s">
-        <v>648</v>
+        <v>615</v>
       </c>
       <c r="R221" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R221" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q221,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q221))),1))</f>
@@ -15682,7 +15711,7 @@
         <v>20507</v>
       </c>
       <c r="W221" s="14" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="Y221" s="14">
         <v>1</v>
@@ -15702,16 +15731,16 @@
         <v>3</v>
       </c>
       <c r="E222" s="16" t="s">
-        <v>649</v>
+        <v>616</v>
       </c>
       <c r="G222" s="16" t="s">
         <v>149</v>
       </c>
       <c r="H222" s="16" t="s">
-        <v>650</v>
+        <v>617</v>
       </c>
       <c r="L222" s="16" t="s">
-        <v>651</v>
+        <v>618</v>
       </c>
       <c r="O222" s="14">
         <v>4</v>
@@ -15736,7 +15765,7 @@
         <v>20507</v>
       </c>
       <c r="W222" s="14" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="Y222" s="14">
         <v>1</v>
@@ -15756,13 +15785,13 @@
         <v>3</v>
       </c>
       <c r="H223" s="16" t="s">
-        <v>652</v>
+        <v>619</v>
       </c>
       <c r="J223" s="16" t="s">
-        <v>653</v>
+        <v>620</v>
       </c>
       <c r="N223" s="16" t="s">
-        <v>654</v>
+        <v>621</v>
       </c>
       <c r="O223" s="14">
         <v>7</v>
@@ -15787,7 +15816,7 @@
         <v>20507</v>
       </c>
       <c r="W223" s="14" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="Y223" s="14">
         <v>1</v>
@@ -15804,16 +15833,16 @@
         <v>13081</v>
       </c>
       <c r="B224" s="15" t="s">
-        <v>655</v>
+        <v>622</v>
       </c>
       <c r="C224" s="14">
         <v>3</v>
       </c>
       <c r="H224" s="16" t="s">
-        <v>656</v>
+        <v>623</v>
       </c>
       <c r="Q224" s="14" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="R224" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R224" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q224,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q224))),1))</f>
@@ -15849,10 +15878,10 @@
         <v>3</v>
       </c>
       <c r="H225" s="16" t="s">
-        <v>657</v>
+        <v>624</v>
       </c>
       <c r="N225" s="16" t="s">
-        <v>658</v>
+        <v>625</v>
       </c>
       <c r="O225" s="14">
         <v>5</v>
@@ -15861,7 +15890,7 @@
         <v>6</v>
       </c>
       <c r="Q225" s="14" t="s">
-        <v>659</v>
+        <v>626</v>
       </c>
       <c r="R225" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R225" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q225,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q225))),1))</f>
@@ -15877,7 +15906,7 @@
         <v>20507</v>
       </c>
       <c r="W225" s="14" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="Y225" s="14">
         <v>1</v>
@@ -15894,16 +15923,16 @@
         <v>13083</v>
       </c>
       <c r="B226" s="15" t="s">
-        <v>660</v>
+        <v>627</v>
       </c>
       <c r="C226" s="14">
         <v>3</v>
       </c>
       <c r="H226" s="16" t="s">
-        <v>661</v>
+        <v>628</v>
       </c>
       <c r="J226" s="16" t="s">
-        <v>662</v>
+        <v>629</v>
       </c>
       <c r="P226" s="14">
         <v>999</v>
@@ -15936,13 +15965,13 @@
         <v>13084</v>
       </c>
       <c r="B227" s="15" t="s">
-        <v>663</v>
+        <v>630</v>
       </c>
       <c r="C227" s="14">
         <v>3</v>
       </c>
       <c r="H227" s="16" t="s">
-        <v>1007</v>
+        <v>974</v>
       </c>
       <c r="P227" s="14">
         <v>999</v>
@@ -15975,7 +16004,7 @@
         <v>13085</v>
       </c>
       <c r="B228" s="15" t="s">
-        <v>664</v>
+        <v>631</v>
       </c>
       <c r="C228" s="14">
         <v>3</v>
@@ -15984,10 +16013,10 @@
         <v>149</v>
       </c>
       <c r="H228" s="16" t="s">
-        <v>665</v>
+        <v>632</v>
       </c>
       <c r="J228" s="16" t="s">
-        <v>666</v>
+        <v>633</v>
       </c>
       <c r="P228" s="14">
         <v>999</v>
@@ -16020,18 +16049,18 @@
         <v>13086</v>
       </c>
       <c r="B229" s="15" t="s">
-        <v>667</v>
+        <v>634</v>
       </c>
       <c r="C229" s="14">
         <v>3</v>
       </c>
       <c r="H229" s="14" t="s">
-        <v>441</v>
+        <v>408</v>
       </c>
       <c r="I229" s="14"/>
       <c r="J229" s="14"/>
       <c r="L229" s="16" t="s">
-        <v>668</v>
+        <v>635</v>
       </c>
       <c r="P229" s="14">
         <v>999</v>
@@ -16064,13 +16093,13 @@
         <v>13087</v>
       </c>
       <c r="B230" s="15" t="s">
-        <v>669</v>
+        <v>636</v>
       </c>
       <c r="C230" s="14">
         <v>3</v>
       </c>
       <c r="H230" s="16" t="s">
-        <v>670</v>
+        <v>637</v>
       </c>
       <c r="P230" s="14">
         <v>999</v>
@@ -16103,16 +16132,16 @@
         <v>13088</v>
       </c>
       <c r="B231" s="15" t="s">
-        <v>671</v>
+        <v>638</v>
       </c>
       <c r="C231" s="14">
         <v>3</v>
       </c>
       <c r="H231" s="16" t="s">
-        <v>672</v>
+        <v>639</v>
       </c>
       <c r="L231" s="16" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="P231" s="14">
         <v>999</v>
@@ -16145,13 +16174,13 @@
         <v>13089</v>
       </c>
       <c r="B232" s="15" t="s">
-        <v>673</v>
+        <v>640</v>
       </c>
       <c r="C232" s="14">
         <v>3</v>
       </c>
       <c r="H232" s="16" t="s">
-        <v>674</v>
+        <v>641</v>
       </c>
       <c r="P232" s="14">
         <v>999</v>
@@ -16184,16 +16213,16 @@
         <v>13090</v>
       </c>
       <c r="B233" s="15" t="s">
-        <v>675</v>
+        <v>642</v>
       </c>
       <c r="C233" s="14">
         <v>3</v>
       </c>
       <c r="H233" s="16" t="s">
-        <v>676</v>
+        <v>643</v>
       </c>
       <c r="J233" s="16" t="s">
-        <v>677</v>
+        <v>644</v>
       </c>
       <c r="P233" s="14">
         <v>999</v>
@@ -16226,16 +16255,16 @@
         <v>13091</v>
       </c>
       <c r="B234" s="15" t="s">
-        <v>678</v>
+        <v>645</v>
       </c>
       <c r="C234" s="14">
         <v>3</v>
       </c>
       <c r="E234" s="16" t="s">
-        <v>476</v>
+        <v>443</v>
       </c>
       <c r="H234" s="16" t="s">
-        <v>679</v>
+        <v>646</v>
       </c>
       <c r="N234" s="16" t="s">
         <v>72</v>
@@ -16274,21 +16303,21 @@
         <v>13092</v>
       </c>
       <c r="B235" s="15" t="s">
-        <v>680</v>
+        <v>647</v>
       </c>
       <c r="C235" s="14">
         <v>3</v>
       </c>
       <c r="E235" s="16" t="s">
-        <v>681</v>
+        <v>648</v>
       </c>
       <c r="H235" s="16" t="s">
-        <v>682</v>
+        <v>649</v>
       </c>
       <c r="I235" s="14"/>
       <c r="J235" s="14"/>
       <c r="L235" s="16" t="s">
-        <v>683</v>
+        <v>650</v>
       </c>
       <c r="R235" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R235" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q235,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q235))),1))</f>
@@ -16315,16 +16344,16 @@
         <v>13093</v>
       </c>
       <c r="B236" s="15" t="s">
-        <v>684</v>
+        <v>651</v>
       </c>
       <c r="C236" s="14">
         <v>3</v>
       </c>
       <c r="H236" s="16" t="s">
-        <v>685</v>
+        <v>652</v>
       </c>
       <c r="N236" s="16" t="s">
-        <v>686</v>
+        <v>653</v>
       </c>
       <c r="R236" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R236" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q236,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q236))),1))</f>
@@ -16337,7 +16366,7 @@
         <v>20508</v>
       </c>
       <c r="W236" s="14" t="s">
-        <v>687</v>
+        <v>654</v>
       </c>
       <c r="Y236" s="14">
         <v>1</v>
@@ -16354,13 +16383,13 @@
         <v>13094</v>
       </c>
       <c r="B237" s="15" t="s">
-        <v>688</v>
+        <v>655</v>
       </c>
       <c r="C237" s="14">
         <v>3</v>
       </c>
       <c r="H237" s="16" t="s">
-        <v>689</v>
+        <v>656</v>
       </c>
       <c r="R237" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R237" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q237,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q237))),1))</f>
@@ -16384,22 +16413,22 @@
         <v>13095</v>
       </c>
       <c r="B238" s="15" t="s">
-        <v>534</v>
+        <v>501</v>
       </c>
       <c r="C238" s="14">
         <v>3</v>
       </c>
       <c r="H238" s="14" t="s">
-        <v>535</v>
+        <v>502</v>
       </c>
       <c r="J238" s="16" t="s">
-        <v>1008</v>
+        <v>975</v>
       </c>
       <c r="P238" s="14">
         <v>999</v>
       </c>
       <c r="Q238" s="14" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="R238" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R238" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q238,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q238))),1))</f>
@@ -16429,22 +16458,22 @@
         <v>13096</v>
       </c>
       <c r="B239" s="15" t="s">
-        <v>534</v>
+        <v>501</v>
       </c>
       <c r="C239" s="14">
         <v>3</v>
       </c>
       <c r="H239" s="14" t="s">
-        <v>552</v>
+        <v>519</v>
       </c>
       <c r="J239" s="16" t="s">
-        <v>690</v>
+        <v>657</v>
       </c>
       <c r="P239" s="14">
         <v>999</v>
       </c>
       <c r="Q239" s="14" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="R239" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R239" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q239,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q239))),1))</f>
@@ -16474,22 +16503,22 @@
         <v>13097</v>
       </c>
       <c r="B240" s="15" t="s">
-        <v>553</v>
+        <v>520</v>
       </c>
       <c r="C240" s="14">
         <v>3</v>
       </c>
       <c r="H240" s="14" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="J240" s="16" t="s">
-        <v>691</v>
+        <v>658</v>
       </c>
       <c r="P240" s="14">
         <v>999</v>
       </c>
       <c r="Q240" s="14" t="s">
-        <v>555</v>
+        <v>522</v>
       </c>
       <c r="R240" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R240" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q240,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q240))),1))</f>
@@ -16519,22 +16548,22 @@
         <v>13098</v>
       </c>
       <c r="B241" s="15" t="s">
-        <v>553</v>
+        <v>520</v>
       </c>
       <c r="C241" s="14">
         <v>3</v>
       </c>
       <c r="H241" s="14" t="s">
-        <v>494</v>
+        <v>461</v>
       </c>
       <c r="J241" s="16" t="s">
-        <v>691</v>
+        <v>658</v>
       </c>
       <c r="P241" s="14">
         <v>999</v>
       </c>
       <c r="Q241" s="14" t="s">
-        <v>555</v>
+        <v>522</v>
       </c>
       <c r="R241" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R241" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q241,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q241))),1))</f>
@@ -16564,16 +16593,16 @@
         <v>13099</v>
       </c>
       <c r="B242" s="15" t="s">
-        <v>660</v>
+        <v>627</v>
       </c>
       <c r="C242" s="14">
         <v>3</v>
       </c>
       <c r="H242" s="16" t="s">
-        <v>692</v>
+        <v>659</v>
       </c>
       <c r="J242" s="16" t="s">
-        <v>662</v>
+        <v>629</v>
       </c>
       <c r="P242" s="14">
         <v>999</v>
@@ -16606,13 +16635,13 @@
         <v>13100</v>
       </c>
       <c r="B243" s="15" t="s">
-        <v>663</v>
+        <v>630</v>
       </c>
       <c r="C243" s="14">
         <v>3</v>
       </c>
       <c r="H243" s="16" t="s">
-        <v>1009</v>
+        <v>976</v>
       </c>
       <c r="P243" s="14">
         <v>999</v>
@@ -16645,18 +16674,18 @@
         <v>13101</v>
       </c>
       <c r="B244" s="15" t="s">
-        <v>667</v>
+        <v>634</v>
       </c>
       <c r="C244" s="14">
         <v>3</v>
       </c>
       <c r="H244" s="14" t="s">
-        <v>595</v>
+        <v>562</v>
       </c>
       <c r="I244" s="14"/>
       <c r="J244" s="14"/>
       <c r="L244" s="16" t="s">
-        <v>668</v>
+        <v>635</v>
       </c>
       <c r="P244" s="14">
         <v>999</v>
@@ -16689,13 +16718,13 @@
         <v>13102</v>
       </c>
       <c r="B245" s="15" t="s">
-        <v>669</v>
+        <v>636</v>
       </c>
       <c r="C245" s="14">
         <v>3</v>
       </c>
       <c r="H245" s="16" t="s">
-        <v>693</v>
+        <v>660</v>
       </c>
       <c r="P245" s="14">
         <v>999</v>
@@ -16728,16 +16757,16 @@
         <v>13103</v>
       </c>
       <c r="B246" s="15" t="s">
-        <v>671</v>
+        <v>638</v>
       </c>
       <c r="C246" s="14">
         <v>3</v>
       </c>
       <c r="H246" s="16" t="s">
-        <v>694</v>
+        <v>661</v>
       </c>
       <c r="L246" s="16" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="P246" s="14">
         <v>999</v>
@@ -16770,16 +16799,16 @@
         <v>13104</v>
       </c>
       <c r="B247" s="15" t="s">
-        <v>660</v>
+        <v>627</v>
       </c>
       <c r="C247" s="14">
         <v>3</v>
       </c>
       <c r="H247" s="16" t="s">
-        <v>695</v>
+        <v>662</v>
       </c>
       <c r="J247" s="16" t="s">
-        <v>662</v>
+        <v>629</v>
       </c>
       <c r="P247" s="14">
         <v>999</v>
@@ -16812,13 +16841,13 @@
         <v>13105</v>
       </c>
       <c r="B248" s="15" t="s">
-        <v>663</v>
+        <v>630</v>
       </c>
       <c r="C248" s="14">
         <v>3</v>
       </c>
       <c r="H248" s="16" t="s">
-        <v>696</v>
+        <v>663</v>
       </c>
       <c r="P248" s="14">
         <v>999</v>
@@ -16851,18 +16880,18 @@
         <v>13106</v>
       </c>
       <c r="B249" s="15" t="s">
-        <v>667</v>
+        <v>634</v>
       </c>
       <c r="C249" s="14">
         <v>3</v>
       </c>
       <c r="H249" s="14" t="s">
-        <v>697</v>
+        <v>664</v>
       </c>
       <c r="I249" s="14"/>
       <c r="J249" s="14"/>
       <c r="L249" s="16" t="s">
-        <v>668</v>
+        <v>635</v>
       </c>
       <c r="P249" s="14">
         <v>999</v>
@@ -16895,13 +16924,13 @@
         <v>13107</v>
       </c>
       <c r="B250" s="15" t="s">
-        <v>669</v>
+        <v>636</v>
       </c>
       <c r="C250" s="14">
         <v>3</v>
       </c>
       <c r="H250" s="16" t="s">
-        <v>698</v>
+        <v>665</v>
       </c>
       <c r="P250" s="14">
         <v>999</v>
@@ -16934,16 +16963,16 @@
         <v>13108</v>
       </c>
       <c r="B251" s="15" t="s">
-        <v>671</v>
+        <v>638</v>
       </c>
       <c r="C251" s="14">
         <v>3</v>
       </c>
       <c r="H251" s="16" t="s">
-        <v>699</v>
+        <v>666</v>
       </c>
       <c r="L251" s="16" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="P251" s="14">
         <v>999</v>
@@ -16976,7 +17005,7 @@
         <v>13109</v>
       </c>
       <c r="B252" s="15" t="s">
-        <v>700</v>
+        <v>667</v>
       </c>
       <c r="C252" s="14">
         <v>3</v>
@@ -16992,7 +17021,7 @@
         <v>20407</v>
       </c>
       <c r="W252" s="14" t="s">
-        <v>701</v>
+        <v>668</v>
       </c>
       <c r="Y252" s="14">
         <v>1</v>
@@ -17012,7 +17041,7 @@
         <v>3</v>
       </c>
       <c r="H253" s="16" t="s">
-        <v>702</v>
+        <v>669</v>
       </c>
       <c r="R253" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R253" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q253,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q253))),1))</f>
@@ -17025,7 +17054,7 @@
         <v>20508</v>
       </c>
       <c r="W253" s="14" t="s">
-        <v>687</v>
+        <v>654</v>
       </c>
       <c r="Y253" s="14">
         <v>1</v>
@@ -17045,7 +17074,7 @@
         <v>3</v>
       </c>
       <c r="H254" s="16" t="s">
-        <v>703</v>
+        <v>670</v>
       </c>
       <c r="R254" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R254" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q254,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q254))),1))</f>
@@ -17058,7 +17087,7 @@
         <v>20508</v>
       </c>
       <c r="W254" s="14" t="s">
-        <v>687</v>
+        <v>654</v>
       </c>
       <c r="Y254" s="14">
         <v>1</v>
@@ -17078,7 +17107,7 @@
         <v>3</v>
       </c>
       <c r="H255" s="16" t="s">
-        <v>704</v>
+        <v>671</v>
       </c>
       <c r="R255" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R255" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q255,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q255))),1))</f>
@@ -17111,7 +17140,7 @@
         <v>3</v>
       </c>
       <c r="H256" s="16" t="s">
-        <v>705</v>
+        <v>672</v>
       </c>
       <c r="R256" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R256" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q256,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q256))),1))</f>
@@ -17144,22 +17173,22 @@
         <v>3</v>
       </c>
       <c r="G257" s="16" t="s">
-        <v>706</v>
+        <v>673</v>
       </c>
       <c r="H257" s="16" t="s">
-        <v>707</v>
+        <v>674</v>
       </c>
       <c r="J257" s="16" t="s">
-        <v>708</v>
+        <v>675</v>
       </c>
       <c r="L257" s="16" t="s">
-        <v>709</v>
+        <v>676</v>
       </c>
       <c r="P257" s="14">
         <v>5</v>
       </c>
       <c r="Q257" s="14" t="s">
-        <v>710</v>
+        <v>677</v>
       </c>
       <c r="R257" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R257" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q257,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q257))),1))</f>
@@ -17178,7 +17207,7 @@
         <v>20602</v>
       </c>
       <c r="W257" s="14" t="s">
-        <v>711</v>
+        <v>678</v>
       </c>
       <c r="Y257" s="14">
         <v>1</v>
@@ -17195,16 +17224,16 @@
         <v>13115</v>
       </c>
       <c r="B258" s="15" t="s">
-        <v>712</v>
+        <v>679</v>
       </c>
       <c r="C258" s="14">
         <v>3</v>
       </c>
       <c r="H258" s="16" t="s">
-        <v>713</v>
+        <v>680</v>
       </c>
       <c r="L258" s="16" t="s">
-        <v>714</v>
+        <v>681</v>
       </c>
       <c r="P258" s="14">
         <v>999</v>
@@ -17246,16 +17275,16 @@
         <v>3</v>
       </c>
       <c r="H259" s="16" t="s">
-        <v>715</v>
+        <v>682</v>
       </c>
       <c r="J259" s="16" t="s">
-        <v>716</v>
+        <v>683</v>
       </c>
       <c r="L259" s="16" t="s">
-        <v>717</v>
+        <v>684</v>
       </c>
       <c r="Q259" s="14" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="S259" s="14">
         <v>1</v>
@@ -17290,16 +17319,16 @@
         <v>3</v>
       </c>
       <c r="E260" s="16" t="s">
-        <v>718</v>
+        <v>685</v>
       </c>
       <c r="H260" s="16" t="s">
-        <v>595</v>
+        <v>562</v>
       </c>
       <c r="J260" s="16" t="s">
-        <v>719</v>
+        <v>686</v>
       </c>
       <c r="L260" s="16" t="s">
-        <v>720</v>
+        <v>687</v>
       </c>
       <c r="N260" s="16" t="s">
         <v>72</v>
@@ -17337,10 +17366,10 @@
         <v>3</v>
       </c>
       <c r="H261" s="16" t="s">
-        <v>721</v>
+        <v>688</v>
       </c>
       <c r="L261" s="16" t="s">
-        <v>722</v>
+        <v>689</v>
       </c>
       <c r="S261" s="14">
         <v>1</v>
@@ -17372,13 +17401,13 @@
         <v>14001</v>
       </c>
       <c r="B264" s="15" t="s">
-        <v>723</v>
+        <v>690</v>
       </c>
       <c r="C264" s="14">
         <v>4</v>
       </c>
       <c r="H264" s="16" t="s">
-        <v>724</v>
+        <v>691</v>
       </c>
       <c r="O264" s="14">
         <v>3</v>
@@ -17387,7 +17416,7 @@
         <v>3</v>
       </c>
       <c r="Q264" s="14" t="s">
-        <v>725</v>
+        <v>692</v>
       </c>
       <c r="R264" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R264" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q264,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q264))),1))</f>
@@ -17406,7 +17435,7 @@
         <v>20304</v>
       </c>
       <c r="W264" s="14" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="Y264" s="14">
         <v>2</v>
@@ -17423,16 +17452,16 @@
         <v>14002</v>
       </c>
       <c r="B265" s="15" t="s">
-        <v>726</v>
+        <v>693</v>
       </c>
       <c r="C265" s="14">
         <v>4</v>
       </c>
       <c r="E265" s="16" t="s">
-        <v>727</v>
+        <v>694</v>
       </c>
       <c r="H265" s="16" t="s">
-        <v>728</v>
+        <v>695</v>
       </c>
       <c r="O265" s="14">
         <v>6</v>
@@ -17441,7 +17470,7 @@
         <v>3</v>
       </c>
       <c r="Q265" s="14" t="s">
-        <v>729</v>
+        <v>696</v>
       </c>
       <c r="R265" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R265" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q265,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q265))),1))</f>
@@ -17460,7 +17489,7 @@
         <v>20304</v>
       </c>
       <c r="W265" s="14" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="Y265" s="14">
         <v>2</v>
@@ -17477,7 +17506,7 @@
         <v>14003</v>
       </c>
       <c r="B266" s="15" t="s">
-        <v>730</v>
+        <v>697</v>
       </c>
       <c r="C266" s="14">
         <v>4</v>
@@ -17489,10 +17518,10 @@
         <v>197</v>
       </c>
       <c r="H266" s="16" t="s">
-        <v>731</v>
+        <v>698</v>
       </c>
       <c r="L266" s="16" t="s">
-        <v>732</v>
+        <v>699</v>
       </c>
       <c r="O266" s="14">
         <v>3</v>
@@ -17501,7 +17530,7 @@
         <v>4</v>
       </c>
       <c r="Q266" s="14" t="s">
-        <v>733</v>
+        <v>700</v>
       </c>
       <c r="R266" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R266" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q266,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q266))),1))</f>
@@ -17520,7 +17549,7 @@
         <v>20302</v>
       </c>
       <c r="W266" s="14" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Y266" s="14">
         <v>2</v>
@@ -17537,7 +17566,7 @@
         <v>14004</v>
       </c>
       <c r="B267" s="15" t="s">
-        <v>734</v>
+        <v>701</v>
       </c>
       <c r="C267" s="14">
         <v>4</v>
@@ -17546,13 +17575,13 @@
         <v>217</v>
       </c>
       <c r="H267" s="16" t="s">
-        <v>735</v>
+        <v>702</v>
       </c>
       <c r="N267" s="16" t="s">
         <v>72</v>
       </c>
       <c r="Q267" s="14" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="R267" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R267" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q267,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q267))),1))</f>
@@ -17568,7 +17597,7 @@
         <v>20302</v>
       </c>
       <c r="W267" s="14" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Y267" s="14">
         <v>2</v>
@@ -17585,7 +17614,7 @@
         <v>14005</v>
       </c>
       <c r="B268" s="15" t="s">
-        <v>736</v>
+        <v>703</v>
       </c>
       <c r="C268" s="14">
         <v>4</v>
@@ -17594,13 +17623,13 @@
         <v>217</v>
       </c>
       <c r="H268" s="16" t="s">
-        <v>737</v>
+        <v>704</v>
       </c>
       <c r="N268" s="16" t="s">
         <v>72</v>
       </c>
       <c r="Q268" s="14" t="s">
-        <v>641</v>
+        <v>608</v>
       </c>
       <c r="R268" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R268" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q268,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q268))),1))</f>
@@ -17616,7 +17645,7 @@
         <v>20302</v>
       </c>
       <c r="W268" s="14" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Y268" s="14">
         <v>2</v>
@@ -17633,16 +17662,16 @@
         <v>14006</v>
       </c>
       <c r="B269" s="15" t="s">
-        <v>738</v>
+        <v>705</v>
       </c>
       <c r="C269" s="14">
         <v>4</v>
       </c>
       <c r="H269" s="16" t="s">
-        <v>439</v>
+        <v>406</v>
       </c>
       <c r="L269" s="16" t="s">
-        <v>739</v>
+        <v>706</v>
       </c>
       <c r="O269" s="14">
         <v>3</v>
@@ -17661,7 +17690,7 @@
         <v>20302</v>
       </c>
       <c r="W269" s="14" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Y269" s="14">
         <v>2</v>
@@ -17678,7 +17707,7 @@
         <v>14007</v>
       </c>
       <c r="B270" s="20" t="s">
-        <v>740</v>
+        <v>707</v>
       </c>
       <c r="C270" s="14">
         <v>4</v>
@@ -17687,10 +17716,10 @@
         <v>81</v>
       </c>
       <c r="H270" s="16" t="s">
-        <v>741</v>
+        <v>708</v>
       </c>
       <c r="L270" s="16" t="s">
-        <v>742</v>
+        <v>709</v>
       </c>
       <c r="O270" s="14">
         <v>1</v>
@@ -17699,7 +17728,7 @@
         <v>4</v>
       </c>
       <c r="Q270" s="14" t="s">
-        <v>743</v>
+        <v>710</v>
       </c>
       <c r="R270" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R270" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q270,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q270))),1))</f>
@@ -17732,7 +17761,7 @@
         <v>14008</v>
       </c>
       <c r="B271" s="20" t="s">
-        <v>744</v>
+        <v>711</v>
       </c>
       <c r="C271" s="14">
         <v>4</v>
@@ -17741,10 +17770,10 @@
         <v>81</v>
       </c>
       <c r="H271" s="16" t="s">
-        <v>745</v>
+        <v>712</v>
       </c>
       <c r="L271" s="16" t="s">
-        <v>746</v>
+        <v>713</v>
       </c>
       <c r="O271" s="14">
         <v>1</v>
@@ -17753,7 +17782,7 @@
         <v>4</v>
       </c>
       <c r="Q271" s="14" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="R271" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R271" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q271,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q271))),1))</f>
@@ -17786,16 +17815,16 @@
         <v>14009</v>
       </c>
       <c r="B272" s="15" t="s">
-        <v>747</v>
+        <v>714</v>
       </c>
       <c r="C272" s="14">
         <v>4</v>
       </c>
       <c r="E272" s="16" t="s">
-        <v>748</v>
+        <v>715</v>
       </c>
       <c r="H272" s="16" t="s">
-        <v>749</v>
+        <v>716</v>
       </c>
       <c r="N272" s="16" t="s">
         <v>170</v>
@@ -17804,7 +17833,7 @@
         <v>2</v>
       </c>
       <c r="Q272" s="14" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="R272" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R272" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q272,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q272))),1))</f>
@@ -17820,7 +17849,7 @@
         <v>20406</v>
       </c>
       <c r="W272" s="14" t="s">
-        <v>750</v>
+        <v>717</v>
       </c>
       <c r="Y272" s="14">
         <v>2</v>
@@ -17837,13 +17866,13 @@
         <v>14010</v>
       </c>
       <c r="B273" s="15" t="s">
-        <v>751</v>
+        <v>718</v>
       </c>
       <c r="C273" s="14">
         <v>4</v>
       </c>
       <c r="H273" s="16" t="s">
-        <v>752</v>
+        <v>719</v>
       </c>
       <c r="R273" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R273" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q273,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q273))),1))</f>
@@ -17853,7 +17882,7 @@
         <v>20302</v>
       </c>
       <c r="W273" s="14" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Y273" s="14">
         <v>2</v>
@@ -17870,16 +17899,16 @@
         <v>14011</v>
       </c>
       <c r="B274" s="15" t="s">
-        <v>753</v>
+        <v>720</v>
       </c>
       <c r="C274" s="14">
         <v>4</v>
       </c>
       <c r="E274" s="16" t="s">
-        <v>754</v>
+        <v>721</v>
       </c>
       <c r="H274" s="16" t="s">
-        <v>755</v>
+        <v>722</v>
       </c>
       <c r="R274" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R274" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q274,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q274))),1))</f>
@@ -17889,7 +17918,7 @@
         <v>20302</v>
       </c>
       <c r="W274" s="14" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Y274" s="14">
         <v>2</v>
@@ -17906,7 +17935,7 @@
         <v>14012</v>
       </c>
       <c r="B275" s="15" t="s">
-        <v>756</v>
+        <v>723</v>
       </c>
       <c r="C275" s="14">
         <v>4</v>
@@ -17930,19 +17959,19 @@
         <v>14013</v>
       </c>
       <c r="B276" s="15" t="s">
-        <v>757</v>
+        <v>724</v>
       </c>
       <c r="C276" s="14">
         <v>4</v>
       </c>
       <c r="E276" s="16" t="s">
-        <v>758</v>
+        <v>725</v>
       </c>
       <c r="H276" s="16" t="s">
-        <v>759</v>
+        <v>726</v>
       </c>
       <c r="Q276" s="14" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="R276" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R276" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q276,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q276))),1))</f>
@@ -17972,19 +18001,19 @@
         <v>14014</v>
       </c>
       <c r="B277" s="20" t="s">
-        <v>761</v>
+        <v>728</v>
       </c>
       <c r="C277" s="14">
         <v>4</v>
       </c>
       <c r="E277" s="16" t="s">
-        <v>1019</v>
+        <v>986</v>
       </c>
       <c r="H277" s="16" t="s">
-        <v>749</v>
+        <v>716</v>
       </c>
       <c r="Q277" s="14" t="s">
-        <v>641</v>
+        <v>608</v>
       </c>
       <c r="R277" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R277" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q277,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q277))),1))</f>
@@ -18014,19 +18043,19 @@
         <v>14015</v>
       </c>
       <c r="B278" s="15" t="s">
-        <v>762</v>
+        <v>729</v>
       </c>
       <c r="C278" s="14">
         <v>4</v>
       </c>
       <c r="E278" s="16" t="s">
-        <v>763</v>
+        <v>730</v>
       </c>
       <c r="H278" s="16" t="s">
-        <v>749</v>
+        <v>716</v>
       </c>
       <c r="Q278" s="14" t="s">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="R278" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R278" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q278,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q278))),1))</f>
@@ -18042,7 +18071,7 @@
         <v>20304</v>
       </c>
       <c r="W278" s="14" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="Y278" s="14">
         <v>2</v>
@@ -18059,7 +18088,7 @@
         <v>14016</v>
       </c>
       <c r="B279" s="15" t="s">
-        <v>765</v>
+        <v>732</v>
       </c>
       <c r="C279" s="14">
         <v>4</v>
@@ -18071,7 +18100,7 @@
         <v>197</v>
       </c>
       <c r="H279" s="16" t="s">
-        <v>766</v>
+        <v>733</v>
       </c>
       <c r="O279" s="14">
         <v>3</v>
@@ -18087,7 +18116,7 @@
         <v>20602</v>
       </c>
       <c r="W279" s="14" t="s">
-        <v>711</v>
+        <v>678</v>
       </c>
       <c r="Y279" s="14">
         <v>2</v>
@@ -18104,19 +18133,19 @@
         <v>14017</v>
       </c>
       <c r="B280" s="15" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="C280" s="14">
         <v>4</v>
       </c>
       <c r="E280" s="16" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="H280" s="16" t="s">
-        <v>769</v>
+        <v>736</v>
       </c>
       <c r="L280" s="16" t="s">
-        <v>770</v>
+        <v>737</v>
       </c>
       <c r="O280" s="14">
         <v>7</v>
@@ -18135,7 +18164,7 @@
         <v>20602</v>
       </c>
       <c r="W280" s="14" t="s">
-        <v>711</v>
+        <v>678</v>
       </c>
       <c r="Y280" s="14">
         <v>2</v>
@@ -18152,7 +18181,7 @@
         <v>14018</v>
       </c>
       <c r="B281" s="15" t="s">
-        <v>771</v>
+        <v>738</v>
       </c>
       <c r="C281" s="14">
         <v>4</v>
@@ -18200,16 +18229,16 @@
         <v>14019</v>
       </c>
       <c r="B282" s="15" t="s">
-        <v>772</v>
+        <v>739</v>
       </c>
       <c r="C282" s="14">
         <v>4</v>
       </c>
       <c r="E282" s="16" t="s">
-        <v>773</v>
+        <v>740</v>
       </c>
       <c r="H282" s="16" t="s">
-        <v>774</v>
+        <v>741</v>
       </c>
       <c r="R282" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R282" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q282,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q282))),1))</f>
@@ -18239,19 +18268,19 @@
         <v>14020</v>
       </c>
       <c r="B283" s="20" t="s">
-        <v>775</v>
+        <v>742</v>
       </c>
       <c r="C283" s="14">
         <v>4</v>
       </c>
       <c r="E283" s="16" t="s">
-        <v>776</v>
+        <v>743</v>
       </c>
       <c r="H283" s="16" t="s">
-        <v>777</v>
+        <v>744</v>
       </c>
       <c r="Q283" s="14" t="s">
-        <v>778</v>
+        <v>745</v>
       </c>
       <c r="R283" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R283" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q283,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q283))),1))</f>
@@ -18281,25 +18310,25 @@
         <v>14021</v>
       </c>
       <c r="B284" s="15" t="s">
-        <v>779</v>
+        <v>746</v>
       </c>
       <c r="C284" s="14">
         <v>4</v>
       </c>
       <c r="G284" s="16" t="s">
-        <v>780</v>
+        <v>747</v>
       </c>
       <c r="H284" s="16" t="s">
-        <v>781</v>
+        <v>748</v>
       </c>
       <c r="L284" s="16" t="s">
-        <v>782</v>
+        <v>749</v>
       </c>
       <c r="P284" s="14">
         <v>999</v>
       </c>
       <c r="Q284" s="14" t="s">
-        <v>778</v>
+        <v>745</v>
       </c>
       <c r="R284" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R284" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q284,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q284))),1))</f>
@@ -18329,25 +18358,25 @@
         <v>14022</v>
       </c>
       <c r="B285" s="15" t="s">
-        <v>779</v>
+        <v>746</v>
       </c>
       <c r="C285" s="14">
         <v>4</v>
       </c>
       <c r="G285" s="16" t="s">
-        <v>780</v>
+        <v>747</v>
       </c>
       <c r="H285" s="16" t="s">
-        <v>783</v>
+        <v>750</v>
       </c>
       <c r="L285" s="16" t="s">
-        <v>782</v>
+        <v>749</v>
       </c>
       <c r="P285" s="14">
         <v>999</v>
       </c>
       <c r="Q285" s="14" t="s">
-        <v>778</v>
+        <v>745</v>
       </c>
       <c r="R285" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R285" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q285,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q285))),1))</f>
@@ -18377,22 +18406,22 @@
         <v>14023</v>
       </c>
       <c r="B286" s="15" t="s">
-        <v>784</v>
+        <v>751</v>
       </c>
       <c r="C286" s="14">
         <v>4</v>
       </c>
       <c r="H286" s="16" t="s">
-        <v>785</v>
+        <v>752</v>
       </c>
       <c r="J286" s="16" t="s">
-        <v>786</v>
+        <v>753</v>
       </c>
       <c r="P286" s="14">
         <v>999</v>
       </c>
       <c r="Q286" s="14" t="s">
-        <v>464</v>
+        <v>431</v>
       </c>
       <c r="R286" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R286" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q286,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q286))),1))</f>
@@ -18422,22 +18451,22 @@
         <v>14024</v>
       </c>
       <c r="B287" s="15" t="s">
-        <v>784</v>
+        <v>751</v>
       </c>
       <c r="C287" s="14">
         <v>4</v>
       </c>
       <c r="H287" s="16" t="s">
-        <v>787</v>
+        <v>754</v>
       </c>
       <c r="J287" s="16" t="s">
-        <v>786</v>
+        <v>753</v>
       </c>
       <c r="P287" s="14">
         <v>999</v>
       </c>
       <c r="Q287" s="14" t="s">
-        <v>464</v>
+        <v>431</v>
       </c>
       <c r="R287" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R287" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q287,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q287))),1))</f>
@@ -18467,22 +18496,22 @@
         <v>14025</v>
       </c>
       <c r="B288" s="15" t="s">
-        <v>788</v>
+        <v>755</v>
       </c>
       <c r="C288" s="14">
         <v>4</v>
       </c>
       <c r="G288" s="16" t="s">
-        <v>789</v>
+        <v>756</v>
       </c>
       <c r="H288" s="16" t="s">
         <v>53</v>
       </c>
       <c r="J288" s="16" t="s">
-        <v>790</v>
+        <v>757</v>
       </c>
       <c r="Q288" s="14" t="s">
-        <v>791</v>
+        <v>758</v>
       </c>
       <c r="R288" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R288" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q288,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q288))),1))</f>
@@ -18512,22 +18541,22 @@
         <v>14026</v>
       </c>
       <c r="B289" s="15" t="s">
-        <v>788</v>
+        <v>755</v>
       </c>
       <c r="C289" s="14">
         <v>4</v>
       </c>
       <c r="G289" s="16" t="s">
-        <v>789</v>
+        <v>756</v>
       </c>
       <c r="H289" s="16" t="s">
         <v>53</v>
       </c>
       <c r="J289" s="16" t="s">
-        <v>790</v>
+        <v>757</v>
       </c>
       <c r="Q289" s="14" t="s">
-        <v>792</v>
+        <v>759</v>
       </c>
       <c r="R289" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R289" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q289,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q289))),1))</f>
@@ -18557,16 +18586,16 @@
         <v>14027</v>
       </c>
       <c r="B290" s="15" t="s">
-        <v>793</v>
+        <v>760</v>
       </c>
       <c r="C290" s="14">
         <v>4</v>
       </c>
       <c r="H290" s="16" t="s">
-        <v>794</v>
+        <v>761</v>
       </c>
       <c r="N290" s="16" t="s">
-        <v>795</v>
+        <v>762</v>
       </c>
       <c r="O290" s="14">
         <v>3</v>
@@ -18602,22 +18631,22 @@
         <v>14028</v>
       </c>
       <c r="B291" s="15" t="s">
-        <v>796</v>
+        <v>763</v>
       </c>
       <c r="C291" s="14">
         <v>4</v>
       </c>
       <c r="E291" s="16" t="s">
-        <v>797</v>
+        <v>764</v>
       </c>
       <c r="G291" s="16" t="s">
         <v>149</v>
       </c>
       <c r="H291" s="16" t="s">
-        <v>798</v>
+        <v>765</v>
       </c>
       <c r="N291" s="16" t="s">
-        <v>799</v>
+        <v>766</v>
       </c>
       <c r="R291" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R291" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q291,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q291))),1))</f>
@@ -18644,7 +18673,7 @@
         <v>14029</v>
       </c>
       <c r="B292" s="15" t="s">
-        <v>800</v>
+        <v>767</v>
       </c>
       <c r="C292" s="14">
         <v>4</v>
@@ -18677,19 +18706,19 @@
         <v>14030</v>
       </c>
       <c r="B293" s="15" t="s">
-        <v>801</v>
+        <v>768</v>
       </c>
       <c r="C293" s="14">
         <v>4</v>
       </c>
       <c r="E293" s="16" t="s">
-        <v>802</v>
+        <v>769</v>
       </c>
       <c r="H293" s="16" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="J293" s="16" t="s">
-        <v>803</v>
+        <v>770</v>
       </c>
       <c r="L293" s="16" t="s">
         <v>165</v>
@@ -18722,16 +18751,16 @@
         <v>14031</v>
       </c>
       <c r="B294" s="15" t="s">
-        <v>804</v>
+        <v>771</v>
       </c>
       <c r="C294" s="14">
         <v>4</v>
       </c>
       <c r="H294" s="16" t="s">
-        <v>805</v>
+        <v>772</v>
       </c>
       <c r="N294" s="16" t="s">
-        <v>806</v>
+        <v>773</v>
       </c>
       <c r="P294" s="14">
         <v>1</v>
@@ -18770,7 +18799,7 @@
         <v>14032</v>
       </c>
       <c r="B295" s="15" t="s">
-        <v>807</v>
+        <v>774</v>
       </c>
       <c r="C295" s="14">
         <v>4</v>
@@ -18782,16 +18811,16 @@
         <v>197</v>
       </c>
       <c r="H295" s="16" t="s">
-        <v>808</v>
+        <v>775</v>
       </c>
       <c r="L295" s="16" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="P295" s="14">
         <v>5</v>
       </c>
       <c r="Q295" s="14" t="s">
-        <v>659</v>
+        <v>626</v>
       </c>
       <c r="R295" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R295" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q295,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q295))),1))</f>
@@ -18804,7 +18833,7 @@
         <v>20402</v>
       </c>
       <c r="W295" s="14" t="s">
-        <v>486</v>
+        <v>453</v>
       </c>
       <c r="Y295" s="14">
         <v>2</v>
@@ -18821,13 +18850,13 @@
         <v>14033</v>
       </c>
       <c r="B296" s="15" t="s">
-        <v>809</v>
+        <v>776</v>
       </c>
       <c r="C296" s="14">
         <v>4</v>
       </c>
       <c r="H296" s="16" t="s">
-        <v>810</v>
+        <v>777</v>
       </c>
       <c r="P296" s="14">
         <v>12</v>
@@ -18840,7 +18869,7 @@
         <v>20407</v>
       </c>
       <c r="W296" s="14" t="s">
-        <v>701</v>
+        <v>668</v>
       </c>
       <c r="Y296" s="14">
         <v>2</v>
@@ -18857,13 +18886,13 @@
         <v>14034</v>
       </c>
       <c r="B297" s="15" t="s">
-        <v>811</v>
+        <v>778</v>
       </c>
       <c r="C297" s="14">
         <v>4</v>
       </c>
       <c r="H297" s="16" t="s">
-        <v>812</v>
+        <v>779</v>
       </c>
       <c r="P297" s="14">
         <v>7</v>
@@ -18879,7 +18908,7 @@
         <v>20603</v>
       </c>
       <c r="W297" s="14" t="s">
-        <v>813</v>
+        <v>780</v>
       </c>
       <c r="Y297" s="14">
         <v>2</v>
@@ -18896,16 +18925,16 @@
         <v>14035</v>
       </c>
       <c r="B298" s="15" t="s">
-        <v>814</v>
+        <v>781</v>
       </c>
       <c r="C298" s="14">
         <v>4</v>
       </c>
       <c r="E298" s="16" t="s">
-        <v>815</v>
+        <v>782</v>
       </c>
       <c r="H298" s="16" t="s">
-        <v>816</v>
+        <v>783</v>
       </c>
       <c r="P298" s="14">
         <v>2</v>
@@ -18918,7 +18947,7 @@
         <v>20603</v>
       </c>
       <c r="W298" s="14" t="s">
-        <v>813</v>
+        <v>780</v>
       </c>
       <c r="Y298" s="14">
         <v>2</v>
@@ -18935,19 +18964,19 @@
         <v>14036</v>
       </c>
       <c r="B299" s="15" t="s">
-        <v>817</v>
+        <v>784</v>
       </c>
       <c r="C299" s="14">
         <v>4</v>
       </c>
       <c r="E299" s="16" t="s">
-        <v>818</v>
+        <v>785</v>
       </c>
       <c r="H299" s="16" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="J299" s="16" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="P299" s="14">
         <v>999</v>
@@ -18980,19 +19009,19 @@
         <v>14037</v>
       </c>
       <c r="B300" s="15" t="s">
-        <v>821</v>
+        <v>788</v>
       </c>
       <c r="C300" s="14">
         <v>4</v>
       </c>
       <c r="E300" s="16" t="s">
-        <v>818</v>
+        <v>785</v>
       </c>
       <c r="H300" s="16" t="s">
-        <v>822</v>
+        <v>789</v>
       </c>
       <c r="J300" s="16" t="s">
-        <v>823</v>
+        <v>790</v>
       </c>
       <c r="P300" s="14">
         <v>999</v>
@@ -19025,16 +19054,16 @@
         <v>14038</v>
       </c>
       <c r="B301" s="15" t="s">
-        <v>824</v>
+        <v>791</v>
       </c>
       <c r="C301" s="14">
         <v>4</v>
       </c>
       <c r="H301" s="16" t="s">
-        <v>825</v>
+        <v>792</v>
       </c>
       <c r="J301" s="16" t="s">
-        <v>826</v>
+        <v>793</v>
       </c>
       <c r="P301" s="14">
         <v>10</v>
@@ -19047,7 +19076,7 @@
         <v>20302</v>
       </c>
       <c r="W301" s="14" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Y301" s="14">
         <v>2</v>
@@ -19064,7 +19093,7 @@
         <v>14039</v>
       </c>
       <c r="B302" s="23" t="s">
-        <v>827</v>
+        <v>794</v>
       </c>
       <c r="C302" s="14">
         <v>4</v>
@@ -19073,13 +19102,13 @@
         <v>153</v>
       </c>
       <c r="H302" s="16" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="L302" s="16" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="N302" s="16" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="P302" s="14">
         <v>6</v>
@@ -19112,7 +19141,7 @@
         <v>14040</v>
       </c>
       <c r="B303" s="15" t="s">
-        <v>829</v>
+        <v>796</v>
       </c>
       <c r="C303" s="14">
         <v>4</v>
@@ -19121,7 +19150,7 @@
         <v>157</v>
       </c>
       <c r="H303" s="16" t="s">
-        <v>830</v>
+        <v>797</v>
       </c>
       <c r="P303" s="14">
         <v>5</v>
@@ -19157,22 +19186,22 @@
         <v>14041</v>
       </c>
       <c r="B304" s="15" t="s">
-        <v>831</v>
+        <v>798</v>
       </c>
       <c r="C304" s="14">
         <v>4</v>
       </c>
       <c r="E304" s="16" t="s">
-        <v>832</v>
+        <v>799</v>
       </c>
       <c r="H304" s="16" t="s">
-        <v>833</v>
+        <v>800</v>
       </c>
       <c r="P304" s="14">
         <v>7</v>
       </c>
       <c r="Q304" s="14" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="R304" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R304" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q304,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q304))),1))</f>
@@ -19185,7 +19214,7 @@
         <v>20402</v>
       </c>
       <c r="W304" s="14" t="s">
-        <v>489</v>
+        <v>456</v>
       </c>
       <c r="Y304" s="14">
         <v>2</v>
@@ -19202,19 +19231,19 @@
         <v>14042</v>
       </c>
       <c r="B305" s="15" t="s">
-        <v>834</v>
+        <v>801</v>
       </c>
       <c r="C305" s="14">
         <v>4</v>
       </c>
       <c r="H305" s="16" t="s">
-        <v>835</v>
+        <v>802</v>
       </c>
       <c r="L305" s="16" t="s">
-        <v>836</v>
+        <v>803</v>
       </c>
       <c r="Q305" s="14" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="R305" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R305" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q305,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q305))),1))</f>
@@ -19247,10 +19276,10 @@
         <v>4</v>
       </c>
       <c r="H306" s="16" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="J306" s="16" t="s">
-        <v>838</v>
+        <v>805</v>
       </c>
       <c r="Q306" s="14" t="s">
         <v>132</v>
@@ -19283,16 +19312,16 @@
         <v>14044</v>
       </c>
       <c r="B307" s="15" t="s">
-        <v>839</v>
+        <v>806</v>
       </c>
       <c r="C307" s="14">
         <v>4</v>
       </c>
       <c r="H307" s="16" t="s">
-        <v>840</v>
+        <v>807</v>
       </c>
       <c r="J307" s="16" t="s">
-        <v>841</v>
+        <v>808</v>
       </c>
       <c r="R307" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R307" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q307,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q307))),1))</f>
@@ -19319,7 +19348,7 @@
         <v>14045</v>
       </c>
       <c r="B308" s="15" t="s">
-        <v>842</v>
+        <v>809</v>
       </c>
       <c r="C308" s="14">
         <v>4</v>
@@ -19334,13 +19363,13 @@
         <v>14046</v>
       </c>
       <c r="B309" s="15" t="s">
-        <v>843</v>
+        <v>810</v>
       </c>
       <c r="C309" s="14">
         <v>4</v>
       </c>
       <c r="H309" s="16" t="s">
-        <v>844</v>
+        <v>811</v>
       </c>
       <c r="O309" s="14">
         <v>6</v>
@@ -19356,7 +19385,7 @@
         <v>20402</v>
       </c>
       <c r="W309" s="14" t="s">
-        <v>635</v>
+        <v>602</v>
       </c>
       <c r="Y309" s="14">
         <v>2</v>
@@ -19373,16 +19402,16 @@
         <v>14047</v>
       </c>
       <c r="B310" s="15" t="s">
-        <v>845</v>
+        <v>812</v>
       </c>
       <c r="C310" s="14">
         <v>4</v>
       </c>
       <c r="E310" s="16" t="s">
-        <v>846</v>
+        <v>813</v>
       </c>
       <c r="H310" s="16" t="s">
-        <v>847</v>
+        <v>814</v>
       </c>
       <c r="O310" s="14">
         <v>1</v>
@@ -19404,7 +19433,7 @@
         <v>20407</v>
       </c>
       <c r="W310" s="14" t="s">
-        <v>701</v>
+        <v>668</v>
       </c>
       <c r="Y310" s="14">
         <v>2</v>
@@ -19445,10 +19474,10 @@
         <v>4</v>
       </c>
       <c r="E312" s="16" t="s">
-        <v>572</v>
+        <v>539</v>
       </c>
       <c r="H312" s="16" t="s">
-        <v>848</v>
+        <v>815</v>
       </c>
       <c r="O312" s="14">
         <v>6</v>
@@ -19464,7 +19493,7 @@
         <v>20307</v>
       </c>
       <c r="W312" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="Y312" s="14">
         <v>2</v>
@@ -19484,16 +19513,16 @@
         <v>4</v>
       </c>
       <c r="E313" s="16" t="s">
-        <v>572</v>
+        <v>539</v>
       </c>
       <c r="H313" s="16" t="s">
-        <v>849</v>
+        <v>816</v>
       </c>
       <c r="O313" s="14">
         <v>6</v>
       </c>
       <c r="Q313" s="14" t="s">
-        <v>531</v>
+        <v>498</v>
       </c>
       <c r="R313" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R313" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q313,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q313))),1))</f>
@@ -19503,7 +19532,7 @@
         <v>20307</v>
       </c>
       <c r="W313" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="Y313" s="14">
         <v>2</v>
@@ -19523,10 +19552,10 @@
         <v>4</v>
       </c>
       <c r="E314" s="16" t="s">
-        <v>572</v>
+        <v>539</v>
       </c>
       <c r="H314" s="16" t="s">
-        <v>850</v>
+        <v>817</v>
       </c>
       <c r="O314" s="14">
         <v>6</v>
@@ -19542,7 +19571,7 @@
         <v>20307</v>
       </c>
       <c r="W314" s="14" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="Y314" s="14">
         <v>2</v>
@@ -19559,19 +19588,19 @@
         <v>14052</v>
       </c>
       <c r="B315" s="15" t="s">
-        <v>851</v>
+        <v>818</v>
       </c>
       <c r="C315" s="14">
         <v>4</v>
       </c>
       <c r="E315" s="16" t="s">
-        <v>653</v>
+        <v>620</v>
       </c>
       <c r="H315" s="16" t="s">
-        <v>852</v>
+        <v>819</v>
       </c>
       <c r="N315" s="16" t="s">
-        <v>495</v>
+        <v>462</v>
       </c>
       <c r="O315" s="14">
         <v>4</v>
@@ -19580,7 +19609,7 @@
         <v>1</v>
       </c>
       <c r="Q315" s="14" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="R315" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R315" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q315,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q315))),1))</f>
@@ -19596,7 +19625,7 @@
         <v>20507</v>
       </c>
       <c r="W315" s="14" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="Y315" s="14">
         <v>2</v>
@@ -19613,19 +19642,19 @@
         <v>14053</v>
       </c>
       <c r="B316" s="15" t="s">
-        <v>853</v>
+        <v>820</v>
       </c>
       <c r="C316" s="14">
         <v>4</v>
       </c>
       <c r="E316" s="16" t="s">
-        <v>854</v>
+        <v>821</v>
       </c>
       <c r="H316" s="16" t="s">
-        <v>855</v>
+        <v>822</v>
       </c>
       <c r="N316" s="16" t="s">
-        <v>856</v>
+        <v>823</v>
       </c>
       <c r="O316" s="14">
         <v>5</v>
@@ -19634,7 +19663,7 @@
         <v>1</v>
       </c>
       <c r="Q316" s="14" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="R316" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R316" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q316,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q316))),1))</f>
@@ -19650,7 +19679,7 @@
         <v>20507</v>
       </c>
       <c r="W316" s="14" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="Y316" s="14">
         <v>2</v>
@@ -19667,19 +19696,19 @@
         <v>14054</v>
       </c>
       <c r="B317" s="15" t="s">
-        <v>857</v>
+        <v>824</v>
       </c>
       <c r="C317" s="14">
         <v>4</v>
       </c>
       <c r="E317" s="16" t="s">
-        <v>858</v>
+        <v>825</v>
       </c>
       <c r="H317" s="16" t="s">
-        <v>859</v>
+        <v>826</v>
       </c>
       <c r="N317" s="16" t="s">
-        <v>860</v>
+        <v>827</v>
       </c>
       <c r="O317" s="14">
         <v>6</v>
@@ -19688,7 +19717,7 @@
         <v>1</v>
       </c>
       <c r="Q317" s="14" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="R317" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R317" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q317,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q317))),1))</f>
@@ -19704,7 +19733,7 @@
         <v>20507</v>
       </c>
       <c r="W317" s="14" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="Y317" s="14">
         <v>2</v>
@@ -19724,10 +19753,10 @@
         <v>4</v>
       </c>
       <c r="H318" s="16" t="s">
-        <v>861</v>
+        <v>828</v>
       </c>
       <c r="L318" s="16" t="s">
-        <v>862</v>
+        <v>829</v>
       </c>
       <c r="O318" s="14">
         <v>6</v>
@@ -19736,7 +19765,7 @@
         <v>99</v>
       </c>
       <c r="Q318" s="14" t="s">
-        <v>743</v>
+        <v>710</v>
       </c>
       <c r="R318" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R318" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q318,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q318))),1))</f>
@@ -19752,7 +19781,7 @@
         <v>20507</v>
       </c>
       <c r="W318" s="14" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="Y318" s="14">
         <v>2</v>
@@ -19769,13 +19798,13 @@
         <v>14056</v>
       </c>
       <c r="B319" s="15" t="s">
-        <v>863</v>
+        <v>830</v>
       </c>
       <c r="C319" s="14">
         <v>4</v>
       </c>
       <c r="H319" s="16" t="s">
-        <v>864</v>
+        <v>831</v>
       </c>
       <c r="O319" s="14">
         <v>1</v>
@@ -19784,7 +19813,7 @@
         <v>8</v>
       </c>
       <c r="Q319" s="14" t="s">
-        <v>659</v>
+        <v>626</v>
       </c>
       <c r="R319" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R319" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q319,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q319))),1))</f>
@@ -19800,7 +19829,7 @@
         <v>20507</v>
       </c>
       <c r="W319" s="14" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="Y319" s="14">
         <v>2</v>
@@ -19817,16 +19846,16 @@
         <v>14057</v>
       </c>
       <c r="B320" s="15" t="s">
-        <v>865</v>
+        <v>832</v>
       </c>
       <c r="C320" s="14">
         <v>4</v>
       </c>
       <c r="E320" s="16" t="s">
-        <v>866</v>
+        <v>833</v>
       </c>
       <c r="H320" s="16" t="s">
-        <v>867</v>
+        <v>834</v>
       </c>
       <c r="O320" s="14">
         <v>6</v>
@@ -19835,7 +19864,7 @@
         <v>8</v>
       </c>
       <c r="Q320" s="14" t="s">
-        <v>868</v>
+        <v>835</v>
       </c>
       <c r="R320" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R320" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q320,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q320))),1))</f>
@@ -19851,7 +19880,7 @@
         <v>20507</v>
       </c>
       <c r="W320" s="14" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="Y320" s="14">
         <v>2</v>
@@ -19868,16 +19897,16 @@
         <v>14058</v>
       </c>
       <c r="B321" s="15" t="s">
-        <v>869</v>
+        <v>836</v>
       </c>
       <c r="C321" s="14">
         <v>4</v>
       </c>
       <c r="H321" s="16" t="s">
-        <v>870</v>
+        <v>837</v>
       </c>
       <c r="N321" s="16" t="s">
-        <v>871</v>
+        <v>838</v>
       </c>
       <c r="O321" s="14">
         <v>5</v>
@@ -19886,7 +19915,7 @@
         <v>999</v>
       </c>
       <c r="Q321" s="14" t="s">
-        <v>733</v>
+        <v>700</v>
       </c>
       <c r="R321" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R321" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q321,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q321))),1))</f>
@@ -19902,7 +19931,7 @@
         <v>20507</v>
       </c>
       <c r="W321" s="14" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="Y321" s="14">
         <v>2</v>
@@ -19919,16 +19948,16 @@
         <v>14059</v>
       </c>
       <c r="B322" s="15" t="s">
-        <v>872</v>
+        <v>839</v>
       </c>
       <c r="C322" s="14">
         <v>4</v>
       </c>
       <c r="H322" s="16" t="s">
-        <v>873</v>
+        <v>840</v>
       </c>
       <c r="L322" s="16" t="s">
-        <v>874</v>
+        <v>841</v>
       </c>
       <c r="R322" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R322" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q322,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q322))),1))</f>
@@ -19938,7 +19967,7 @@
         <v>20406</v>
       </c>
       <c r="W322" s="14" t="s">
-        <v>750</v>
+        <v>717</v>
       </c>
       <c r="Y322" s="14">
         <v>2</v>
@@ -19958,7 +19987,7 @@
         <v>4</v>
       </c>
       <c r="H323" s="16" t="s">
-        <v>875</v>
+        <v>842</v>
       </c>
       <c r="R323" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R323" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q323,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q323))),1))</f>
@@ -19988,7 +20017,7 @@
         <v>4</v>
       </c>
       <c r="H324" s="16" t="s">
-        <v>876</v>
+        <v>843</v>
       </c>
       <c r="R324" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R324" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q324,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q324))),1))</f>
@@ -20001,7 +20030,7 @@
         <v>20405</v>
       </c>
       <c r="W324" s="14" t="s">
-        <v>397</v>
+        <v>372</v>
       </c>
       <c r="Y324" s="14">
         <v>2</v>
@@ -20018,13 +20047,13 @@
         <v>14062</v>
       </c>
       <c r="B325" s="15" t="s">
-        <v>877</v>
+        <v>844</v>
       </c>
       <c r="C325" s="14">
         <v>4</v>
       </c>
       <c r="H325" s="16" t="s">
-        <v>878</v>
+        <v>845</v>
       </c>
       <c r="L325" s="16" t="s">
         <v>165</v>
@@ -20057,16 +20086,16 @@
         <v>14063</v>
       </c>
       <c r="B326" s="15" t="s">
-        <v>879</v>
+        <v>846</v>
       </c>
       <c r="C326" s="14">
         <v>4</v>
       </c>
       <c r="H326" s="16" t="s">
-        <v>880</v>
+        <v>847</v>
       </c>
       <c r="J326" s="16" t="s">
-        <v>881</v>
+        <v>848</v>
       </c>
       <c r="R326" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R326" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q326,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q326))),1))</f>
@@ -20093,7 +20122,7 @@
         <v>14064</v>
       </c>
       <c r="B327" s="15" t="s">
-        <v>882</v>
+        <v>849</v>
       </c>
       <c r="C327" s="14">
         <v>4</v>
@@ -20102,10 +20131,10 @@
         <v>90</v>
       </c>
       <c r="H327" s="16" t="s">
-        <v>883</v>
+        <v>850</v>
       </c>
       <c r="N327" s="16" t="s">
-        <v>1020</v>
+        <v>987</v>
       </c>
       <c r="P327" s="14">
         <v>999</v>
@@ -20135,16 +20164,16 @@
         <v>14065</v>
       </c>
       <c r="B328" s="15" t="s">
-        <v>884</v>
+        <v>851</v>
       </c>
       <c r="C328" s="14">
         <v>4</v>
       </c>
       <c r="H328" s="16" t="s">
-        <v>1013</v>
+        <v>980</v>
       </c>
       <c r="N328" s="16" t="s">
-        <v>885</v>
+        <v>852</v>
       </c>
       <c r="O328" s="16"/>
       <c r="R328" s="14" t="e" cm="1">
@@ -20155,7 +20184,7 @@
         <v>20409</v>
       </c>
       <c r="W328" s="14" t="s">
-        <v>416</v>
+        <v>384</v>
       </c>
       <c r="Y328" s="14">
         <v>2</v>
@@ -20172,25 +20201,25 @@
         <v>14066</v>
       </c>
       <c r="B329" s="15" t="s">
-        <v>779</v>
+        <v>746</v>
       </c>
       <c r="C329" s="14">
         <v>4</v>
       </c>
       <c r="G329" s="16" t="s">
-        <v>989</v>
+        <v>956</v>
       </c>
       <c r="H329" s="16" t="s">
-        <v>781</v>
+        <v>748</v>
       </c>
       <c r="L329" s="16" t="s">
-        <v>887</v>
+        <v>854</v>
       </c>
       <c r="P329" s="14">
         <v>999</v>
       </c>
       <c r="Q329" s="14" t="s">
-        <v>778</v>
+        <v>745</v>
       </c>
       <c r="R329" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R329" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q329,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q329))),1))</f>
@@ -20220,25 +20249,25 @@
         <v>14067</v>
       </c>
       <c r="B330" s="15" t="s">
-        <v>779</v>
+        <v>746</v>
       </c>
       <c r="C330" s="14">
         <v>4</v>
       </c>
       <c r="G330" s="16" t="s">
-        <v>886</v>
+        <v>853</v>
       </c>
       <c r="H330" s="16" t="s">
-        <v>783</v>
+        <v>750</v>
       </c>
       <c r="L330" s="16" t="s">
-        <v>887</v>
+        <v>854</v>
       </c>
       <c r="P330" s="14">
         <v>999</v>
       </c>
       <c r="Q330" s="14" t="s">
-        <v>778</v>
+        <v>745</v>
       </c>
       <c r="R330" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R330" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q330,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q330))),1))</f>
@@ -20268,22 +20297,22 @@
         <v>14068</v>
       </c>
       <c r="B331" s="15" t="s">
-        <v>784</v>
+        <v>751</v>
       </c>
       <c r="C331" s="14">
         <v>4</v>
       </c>
       <c r="H331" s="16" t="s">
-        <v>785</v>
+        <v>752</v>
       </c>
       <c r="J331" s="16" t="s">
-        <v>888</v>
+        <v>855</v>
       </c>
       <c r="P331" s="14">
         <v>999</v>
       </c>
       <c r="Q331" s="14" t="s">
-        <v>464</v>
+        <v>431</v>
       </c>
       <c r="R331" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R331" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q331,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q331))),1))</f>
@@ -20304,22 +20333,22 @@
         <v>14069</v>
       </c>
       <c r="B332" s="15" t="s">
-        <v>784</v>
+        <v>751</v>
       </c>
       <c r="C332" s="14">
         <v>4</v>
       </c>
       <c r="H332" s="16" t="s">
-        <v>889</v>
+        <v>856</v>
       </c>
       <c r="J332" s="16" t="s">
-        <v>888</v>
+        <v>855</v>
       </c>
       <c r="P332" s="14">
         <v>999</v>
       </c>
       <c r="Q332" s="14" t="s">
-        <v>464</v>
+        <v>431</v>
       </c>
       <c r="R332" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R332" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q332,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q332))),1))</f>
@@ -20340,13 +20369,13 @@
         <v>14070</v>
       </c>
       <c r="B333" s="15" t="s">
-        <v>877</v>
+        <v>844</v>
       </c>
       <c r="C333" s="14">
         <v>4</v>
       </c>
       <c r="H333" s="16" t="s">
-        <v>890</v>
+        <v>857</v>
       </c>
       <c r="L333" s="16" t="s">
         <v>165</v>
@@ -20379,13 +20408,13 @@
         <v>14071</v>
       </c>
       <c r="B334" s="15" t="s">
-        <v>877</v>
+        <v>844</v>
       </c>
       <c r="C334" s="14">
         <v>4</v>
       </c>
       <c r="H334" s="16" t="s">
-        <v>891</v>
+        <v>858</v>
       </c>
       <c r="L334" s="16" t="s">
         <v>165</v>
@@ -20418,16 +20447,16 @@
         <v>14072</v>
       </c>
       <c r="B335" s="15" t="s">
-        <v>892</v>
+        <v>859</v>
       </c>
       <c r="C335" s="14">
         <v>4</v>
       </c>
       <c r="H335" s="16" t="s">
-        <v>893</v>
+        <v>860</v>
       </c>
       <c r="L335" s="16" t="s">
-        <v>894</v>
+        <v>861</v>
       </c>
       <c r="R335" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R335" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q335,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q335))),1))</f>
@@ -20437,7 +20466,7 @@
         <v>20503</v>
       </c>
       <c r="W335" s="14" t="s">
-        <v>404</v>
+        <v>376</v>
       </c>
       <c r="Y335" s="14">
         <v>2</v>
@@ -20454,16 +20483,16 @@
         <v>14073</v>
       </c>
       <c r="B336" s="15" t="s">
-        <v>895</v>
+        <v>862</v>
       </c>
       <c r="C336" s="14">
         <v>4</v>
       </c>
       <c r="H336" s="16" t="s">
-        <v>896</v>
+        <v>863</v>
       </c>
       <c r="Q336" s="14" t="s">
-        <v>897</v>
+        <v>864</v>
       </c>
       <c r="R336" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R336" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q336,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q336))),1))</f>
@@ -20473,7 +20502,7 @@
         <v>20406</v>
       </c>
       <c r="W336" s="14" t="s">
-        <v>750</v>
+        <v>717</v>
       </c>
       <c r="Y336" s="14">
         <v>2</v>
@@ -20493,13 +20522,13 @@
         <v>4</v>
       </c>
       <c r="G337" s="16" t="s">
-        <v>898</v>
+        <v>865</v>
       </c>
       <c r="H337" s="16" t="s">
-        <v>899</v>
+        <v>866</v>
       </c>
       <c r="Q337" s="14" t="s">
-        <v>792</v>
+        <v>759</v>
       </c>
       <c r="R337" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R337" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q337,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q337))),1))</f>
@@ -20509,7 +20538,7 @@
         <v>20503</v>
       </c>
       <c r="W337" s="14" t="s">
-        <v>404</v>
+        <v>376</v>
       </c>
       <c r="Y337" s="14">
         <v>2</v>
@@ -20526,13 +20555,13 @@
         <v>14075</v>
       </c>
       <c r="B338" s="15" t="s">
-        <v>900</v>
+        <v>867</v>
       </c>
       <c r="C338" s="14">
         <v>4</v>
       </c>
       <c r="H338" s="16" t="s">
-        <v>901</v>
+        <v>868</v>
       </c>
       <c r="R338" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R338" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q338,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q338))),1))</f>
@@ -20553,19 +20582,19 @@
         <v>14076</v>
       </c>
       <c r="B339" s="23" t="s">
-        <v>902</v>
+        <v>869</v>
       </c>
       <c r="C339" s="14">
         <v>4</v>
       </c>
       <c r="E339" s="16" t="s">
-        <v>773</v>
+        <v>740</v>
       </c>
       <c r="H339" s="16" t="s">
-        <v>903</v>
+        <v>870</v>
       </c>
       <c r="J339" s="16" t="s">
-        <v>904</v>
+        <v>871</v>
       </c>
       <c r="R339" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R339" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q339,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q339))),1))</f>
@@ -20595,7 +20624,7 @@
         <v>4</v>
       </c>
       <c r="H340" s="16" t="s">
-        <v>905</v>
+        <v>872</v>
       </c>
       <c r="R340" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R340" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q340,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q340))),1))</f>
@@ -20619,7 +20648,7 @@
         <v>4</v>
       </c>
       <c r="H341" s="16" t="s">
-        <v>906</v>
+        <v>873</v>
       </c>
       <c r="L341" s="16" t="s">
         <v>95</v>
@@ -20643,16 +20672,16 @@
         <v>14079</v>
       </c>
       <c r="B342" s="15" t="s">
-        <v>907</v>
+        <v>874</v>
       </c>
       <c r="C342" s="14">
         <v>4</v>
       </c>
       <c r="H342" s="16" t="s">
-        <v>908</v>
+        <v>875</v>
       </c>
       <c r="L342" s="16" t="s">
-        <v>909</v>
+        <v>876</v>
       </c>
       <c r="R342" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R342" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q342,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q342))),1))</f>
@@ -20679,7 +20708,7 @@
         <v>4</v>
       </c>
       <c r="H343" s="16" t="s">
-        <v>910</v>
+        <v>877</v>
       </c>
       <c r="R343" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R343" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q343,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q343))),1))</f>
@@ -20689,7 +20718,7 @@
         <v>20705</v>
       </c>
       <c r="W343" s="14" t="s">
-        <v>911</v>
+        <v>878</v>
       </c>
       <c r="Y343" s="14">
         <v>1</v>
@@ -20709,10 +20738,10 @@
         <v>4</v>
       </c>
       <c r="H344" s="16" t="s">
-        <v>912</v>
+        <v>879</v>
       </c>
       <c r="N344" s="16" t="s">
-        <v>913</v>
+        <v>880</v>
       </c>
       <c r="R344" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R344" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q344,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q344))),1))</f>
@@ -20722,7 +20751,7 @@
         <v>20705</v>
       </c>
       <c r="W344" s="14" t="s">
-        <v>911</v>
+        <v>878</v>
       </c>
       <c r="Y344" s="14">
         <v>1</v>
@@ -20742,10 +20771,10 @@
         <v>4</v>
       </c>
       <c r="H345" s="16" t="s">
-        <v>914</v>
+        <v>881</v>
       </c>
       <c r="N345" s="16" t="s">
-        <v>915</v>
+        <v>882</v>
       </c>
       <c r="R345" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R345" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q345,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q345))),1))</f>
@@ -20755,7 +20784,7 @@
         <v>20705</v>
       </c>
       <c r="W345" s="14" t="s">
-        <v>911</v>
+        <v>878</v>
       </c>
       <c r="Y345" s="14">
         <v>1</v>
@@ -20775,16 +20804,16 @@
         <v>4</v>
       </c>
       <c r="E346" s="16" t="s">
-        <v>916</v>
+        <v>883</v>
       </c>
       <c r="G346" s="16" t="s">
         <v>197</v>
       </c>
       <c r="H346" s="16" t="s">
-        <v>917</v>
+        <v>884</v>
       </c>
       <c r="L346" s="16" t="s">
-        <v>918</v>
+        <v>885</v>
       </c>
       <c r="Q346" s="14" t="s">
         <v>275</v>
@@ -20811,13 +20840,13 @@
         <v>14084</v>
       </c>
       <c r="B347" s="15" t="s">
-        <v>919</v>
+        <v>886</v>
       </c>
       <c r="C347" s="14">
         <v>4</v>
       </c>
       <c r="E347" s="16" t="s">
-        <v>920</v>
+        <v>887</v>
       </c>
       <c r="R347" s="14" t="e" cm="1">
         <f t="array" aca="1" ref="R347" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q347,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q347))),1))</f>
@@ -20832,19 +20861,19 @@
         <v>14085</v>
       </c>
       <c r="B348" s="15" t="s">
-        <v>921</v>
+        <v>888</v>
       </c>
       <c r="C348" s="14">
         <v>4</v>
       </c>
       <c r="E348" s="16" t="s">
-        <v>922</v>
+        <v>889</v>
       </c>
       <c r="H348" s="16" t="s">
-        <v>923</v>
+        <v>890</v>
       </c>
       <c r="L348" s="16" t="s">
-        <v>924</v>
+        <v>891</v>
       </c>
       <c r="Q348" s="14" t="s">
         <v>88</v>
@@ -20874,19 +20903,19 @@
         <v>14086</v>
       </c>
       <c r="B349" s="15" t="s">
-        <v>925</v>
+        <v>892</v>
       </c>
       <c r="C349" s="14">
         <v>4</v>
       </c>
       <c r="E349" s="16" t="s">
-        <v>926</v>
+        <v>893</v>
       </c>
       <c r="H349" s="16" t="s">
-        <v>923</v>
+        <v>890</v>
       </c>
       <c r="L349" s="16" t="s">
-        <v>927</v>
+        <v>894</v>
       </c>
       <c r="Q349" s="14" t="s">
         <v>88</v>
@@ -20919,19 +20948,19 @@
         <v>4</v>
       </c>
       <c r="E350" s="16" t="s">
-        <v>409</v>
+        <v>379</v>
       </c>
       <c r="G350" s="16" t="s">
-        <v>928</v>
+        <v>895</v>
       </c>
       <c r="H350" s="16" t="s">
-        <v>929</v>
+        <v>896</v>
       </c>
       <c r="L350" s="16" t="s">
-        <v>930</v>
+        <v>897</v>
       </c>
       <c r="N350" s="16" t="s">
-        <v>931</v>
+        <v>898</v>
       </c>
       <c r="O350" s="14">
         <v>3</v>
@@ -20940,7 +20969,7 @@
         <v>12</v>
       </c>
       <c r="Q350" s="14" t="s">
-        <v>868</v>
+        <v>835</v>
       </c>
       <c r="R350" s="14" t="str" cm="1">
         <f t="array" aca="1" ref="R350" ca="1">_xlfn.TEXTJOIN(",",TRUE,MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($Q350,"↑","1"),"↓","2"),"←","3"),"→","4"),ROW(INDIRECT("1:"&amp;LEN($Q350))),1))</f>
@@ -20970,7 +20999,7 @@
         <v>14088</v>
       </c>
       <c r="H351" s="16" t="s">
-        <v>932</v>
+        <v>899</v>
       </c>
       <c r="T351" s="14" t="s">
         <v>50</v>
@@ -21013,15 +21042,15 @@
         <v>72</v>
       </c>
       <c r="C1" t="s">
-        <v>933</v>
+        <v>900</v>
       </c>
       <c r="E1" t="s">
-        <v>934</v>
+        <v>901</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>935</v>
+        <v>902</v>
       </c>
       <c r="C2" t="s">
         <v>236</v>
@@ -21031,28 +21060,28 @@
         <v>8</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>936</v>
+        <v>903</v>
       </c>
       <c r="F2">
         <f>COUNTIF(Skill!V:V,20702)</f>
         <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>937</v>
+        <v>904</v>
       </c>
       <c r="H2">
         <f>COUNTIF(Skill!V:V,20402)</f>
         <v>6</v>
       </c>
       <c r="I2" t="s">
-        <v>938</v>
+        <v>905</v>
       </c>
       <c r="J2">
         <f>COUNTIF(Skill!V:V,20307)</f>
         <v>4</v>
       </c>
       <c r="K2" t="s">
-        <v>911</v>
+        <v>878</v>
       </c>
       <c r="L2">
         <f>COUNTIF(Skill!V:V,20705)</f>
@@ -21063,24 +21092,24 @@
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
-        <v>939</v>
+        <v>906</v>
       </c>
       <c r="C3" t="s">
-        <v>492</v>
+        <v>459</v>
       </c>
       <c r="D3">
         <f>COUNTIF(Skill!V:V,20601)</f>
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>711</v>
+        <v>678</v>
       </c>
       <c r="F3">
         <f>COUNTIF(Skill!V:V,20602)</f>
         <v>3</v>
       </c>
       <c r="G3" t="s">
-        <v>813</v>
+        <v>780</v>
       </c>
       <c r="H3">
         <f>COUNTIF(Skill!V:V,20603)</f>
@@ -21098,10 +21127,10 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>940</v>
+        <v>907</v>
       </c>
       <c r="C4" t="s">
-        <v>393</v>
+        <v>369</v>
       </c>
       <c r="D4">
         <f>COUNTIF(Skill!V:V,20501)</f>
@@ -21115,14 +21144,14 @@
         <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>404</v>
+        <v>376</v>
       </c>
       <c r="H4">
         <f>COUNTIF(Skill!V:V,20503)</f>
         <v>5</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>941</v>
+        <v>908</v>
       </c>
       <c r="J4">
         <f>COUNTIF(Skill!V:V,20504)</f>
@@ -21136,21 +21165,21 @@
         <v>6</v>
       </c>
       <c r="M4" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="N4">
         <f>COUNTIF(Skill!V:V,20506)</f>
         <v>2</v>
       </c>
       <c r="O4" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="P4">
         <f>COUNTIF(Skill!V:V,20507)</f>
         <v>21</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>942</v>
+        <v>909</v>
       </c>
       <c r="R4">
         <f>COUNTIF(Skill!V:V,20508)</f>
@@ -21160,7 +21189,7 @@
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>943</v>
+        <v>910</v>
       </c>
       <c r="C5" t="s">
         <v>180</v>
@@ -21186,35 +21215,35 @@
         <v>6</v>
       </c>
       <c r="K5" t="s">
-        <v>397</v>
+        <v>372</v>
       </c>
       <c r="L5">
         <f>COUNTIF(Skill!V:V,20405)</f>
         <v>2</v>
       </c>
       <c r="M5" t="s">
-        <v>750</v>
+        <v>717</v>
       </c>
       <c r="N5">
         <f>COUNTIF(Skill!V:V,20406)</f>
         <v>3</v>
       </c>
       <c r="O5" t="s">
-        <v>701</v>
+        <v>668</v>
       </c>
       <c r="P5">
         <f>COUNTIF(Skill!V:V,20407)</f>
         <v>3</v>
       </c>
       <c r="Q5" t="s">
-        <v>944</v>
+        <v>911</v>
       </c>
       <c r="R5">
         <f>COUNTIF(Skill!V:V,20408)</f>
         <v>0</v>
       </c>
       <c r="S5" t="s">
-        <v>416</v>
+        <v>384</v>
       </c>
       <c r="T5">
         <f>COUNTIF(Skill!V:V,20409)</f>
@@ -21223,7 +21252,7 @@
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
-        <v>945</v>
+        <v>912</v>
       </c>
       <c r="C6" t="s">
         <v>55</v>
@@ -21233,7 +21262,7 @@
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="F6">
         <f>COUNTIF(Skill!V:V,20302)</f>
@@ -21247,7 +21276,7 @@
         <v>8</v>
       </c>
       <c r="I6" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="J6">
         <f>COUNTIF(Skill!V:V,20304)</f>
@@ -21261,7 +21290,7 @@
         <v>7</v>
       </c>
       <c r="M6" t="s">
-        <v>946</v>
+        <v>913</v>
       </c>
       <c r="N6">
         <f>COUNTIF(Skill!V:V,20306)</f>
@@ -21274,7 +21303,7 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
-        <v>947</v>
+        <v>914</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>58</v>
@@ -21291,7 +21320,7 @@
         <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>948</v>
+        <v>915</v>
       </c>
       <c r="H7">
         <f>COUNTIF(Skill!V:V,20203)</f>
@@ -21305,7 +21334,7 @@
         <v>5</v>
       </c>
       <c r="K7" t="s">
-        <v>949</v>
+        <v>916</v>
       </c>
       <c r="L7">
         <f>COUNTIF(Skill!V:V,20205)</f>
@@ -21316,7 +21345,7 @@
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>950</v>
+        <v>917</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>67</v>
@@ -21339,30 +21368,30 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.15">
       <c r="G13" t="s">
-        <v>951</v>
+        <v>918</v>
       </c>
       <c r="H13" s="25" t="s">
-        <v>952</v>
+        <v>919</v>
       </c>
       <c r="I13" s="25"/>
       <c r="J13" s="25" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="K13" s="25"/>
       <c r="L13" s="25" t="s">
-        <v>953</v>
+        <v>920</v>
       </c>
       <c r="M13" s="25"/>
       <c r="Q13" t="s">
-        <v>954</v>
+        <v>921</v>
       </c>
       <c r="R13" t="s">
-        <v>955</v>
+        <v>922</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.15">
       <c r="G14" t="s">
-        <v>939</v>
+        <v>906</v>
       </c>
       <c r="H14" s="25">
         <v>125</v>
@@ -21377,7 +21406,7 @@
       </c>
       <c r="M14" s="25"/>
       <c r="Q14" t="s">
-        <v>956</v>
+        <v>923</v>
       </c>
       <c r="R14" t="s">
         <v>183</v>
@@ -21385,7 +21414,7 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.15">
       <c r="G15" t="s">
-        <v>940</v>
+        <v>907</v>
       </c>
       <c r="H15" s="25">
         <v>120</v>
@@ -21400,15 +21429,15 @@
       </c>
       <c r="M15" s="25"/>
       <c r="Q15" t="s">
-        <v>957</v>
+        <v>924</v>
       </c>
       <c r="R15" t="s">
-        <v>481</v>
+        <v>448</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.15">
       <c r="G16" t="s">
-        <v>943</v>
+        <v>910</v>
       </c>
       <c r="H16" s="25">
         <v>115</v>
@@ -21423,15 +21452,15 @@
       </c>
       <c r="M16" s="25"/>
       <c r="Q16" t="s">
-        <v>958</v>
+        <v>925</v>
       </c>
       <c r="R16" t="s">
-        <v>411</v>
+        <v>381</v>
       </c>
     </row>
     <row r="17" spans="7:15" x14ac:dyDescent="0.15">
       <c r="G17" t="s">
-        <v>945</v>
+        <v>912</v>
       </c>
       <c r="H17" s="25">
         <v>110</v>
@@ -21448,7 +21477,7 @@
     </row>
     <row r="18" spans="7:15" x14ac:dyDescent="0.15">
       <c r="G18" t="s">
-        <v>947</v>
+        <v>914</v>
       </c>
       <c r="H18" s="25">
         <v>105</v>
@@ -21465,7 +21494,7 @@
     </row>
     <row r="19" spans="7:15" x14ac:dyDescent="0.15">
       <c r="G19" t="s">
-        <v>950</v>
+        <v>917</v>
       </c>
       <c r="H19" s="25">
         <v>100</v>
@@ -21486,18 +21515,18 @@
     </row>
     <row r="21" spans="7:15" x14ac:dyDescent="0.15">
       <c r="G21" t="s">
-        <v>959</v>
+        <v>926</v>
       </c>
       <c r="H21" s="25" t="s">
-        <v>960</v>
+        <v>927</v>
       </c>
       <c r="I21" s="25"/>
       <c r="J21" s="25" t="s">
-        <v>961</v>
+        <v>928</v>
       </c>
       <c r="K21" s="25"/>
       <c r="L21" s="25" t="s">
-        <v>962</v>
+        <v>929</v>
       </c>
       <c r="M21" s="26"/>
       <c r="O21" s="10"/>
@@ -21559,31 +21588,31 @@
   <sheetData>
     <row r="3" spans="1:16" x14ac:dyDescent="0.15">
       <c r="B3" t="s">
-        <v>963</v>
+        <v>930</v>
       </c>
       <c r="C3" t="s">
-        <v>964</v>
+        <v>931</v>
       </c>
       <c r="D3" t="s">
-        <v>965</v>
+        <v>932</v>
       </c>
       <c r="H3" t="s">
-        <v>947</v>
+        <v>914</v>
       </c>
       <c r="I3" t="s">
-        <v>945</v>
+        <v>912</v>
       </c>
       <c r="J3" t="s">
-        <v>943</v>
+        <v>910</v>
       </c>
       <c r="K3" t="s">
-        <v>940</v>
+        <v>907</v>
       </c>
       <c r="L3" t="s">
-        <v>939</v>
+        <v>906</v>
       </c>
       <c r="M3" t="s">
-        <v>935</v>
+        <v>902</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.15">
@@ -21591,13 +21620,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>966</v>
+        <v>933</v>
       </c>
       <c r="C4" t="s">
-        <v>967</v>
+        <v>934</v>
       </c>
       <c r="D4" t="s">
-        <v>968</v>
+        <v>935</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.15">
@@ -21605,13 +21634,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>969</v>
+        <v>936</v>
       </c>
       <c r="C5" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D5" t="s">
-        <v>970</v>
+        <v>937</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.15">
@@ -21619,13 +21648,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>971</v>
+        <v>938</v>
       </c>
       <c r="C6" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D6" t="s">
-        <v>972</v>
+        <v>939</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.15">
@@ -21633,13 +21662,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>973</v>
+        <v>940</v>
       </c>
       <c r="C7" t="s">
-        <v>967</v>
+        <v>934</v>
       </c>
       <c r="D7" t="s">
-        <v>974</v>
+        <v>941</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.15">
@@ -21647,13 +21676,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>975</v>
+        <v>942</v>
       </c>
       <c r="C8" t="s">
-        <v>967</v>
+        <v>934</v>
       </c>
       <c r="D8" t="s">
-        <v>976</v>
+        <v>943</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.15">
@@ -21661,13 +21690,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>977</v>
+        <v>944</v>
       </c>
       <c r="C9" t="s">
-        <v>967</v>
+        <v>934</v>
       </c>
       <c r="D9" t="s">
-        <v>978</v>
+        <v>945</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.15">
@@ -21675,13 +21704,13 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>979</v>
+        <v>946</v>
       </c>
       <c r="C10" t="s">
-        <v>967</v>
+        <v>934</v>
       </c>
       <c r="D10" t="s">
-        <v>980</v>
+        <v>947</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.15">
@@ -21702,7 +21731,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.15">
       <c r="F16" t="s">
-        <v>981</v>
+        <v>948</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
@@ -21714,7 +21743,7 @@
     <row r="17" spans="5:16" x14ac:dyDescent="0.15">
       <c r="E17" s="6"/>
       <c r="F17" t="s">
-        <v>982</v>
+        <v>949</v>
       </c>
       <c r="G17" s="6"/>
       <c r="J17" s="6"/>
@@ -21725,7 +21754,7 @@
     <row r="18" spans="5:16" x14ac:dyDescent="0.15">
       <c r="E18" s="6"/>
       <c r="F18" t="s">
-        <v>983</v>
+        <v>950</v>
       </c>
       <c r="G18" s="6"/>
       <c r="J18" s="6"/>
@@ -21879,7 +21908,7 @@
         <v>14</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>984</v>
+        <v>951</v>
       </c>
       <c r="Y1" s="3" t="s">
         <v>16</v>
@@ -21904,25 +21933,25 @@
         <v>22</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>985</v>
+        <v>952</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>986</v>
+        <v>953</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>987</v>
+        <v>954</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>29</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>988</v>
+        <v>955</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>31</v>
@@ -22026,7 +22055,7 @@
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B27" s="1" t="s">
-        <v>481</v>
+        <v>448</v>
       </c>
       <c r="C27" s="1" cm="1">
         <f t="array" ref="C27">SUMPRODUCT(LEN(P:P)-LEN(SUBSTITUTE(P:P,"↑","")))</f>
@@ -22053,7 +22082,7 @@
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B30" s="1" t="s">
-        <v>411</v>
+        <v>381</v>
       </c>
       <c r="C30" s="1" cm="1">
         <f t="array" ref="C30">SUMPRODUCT(LEN(P:P)-LEN(SUBSTITUTE(P:P,"→","")))</f>
